--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -236,7 +236,11 @@
           <t>Alisa</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>中和區新生街9號</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>0900095907</t>
@@ -18685,7 +18689,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026/03/25  13:00:18</t>
+          <t>2026/03/26  13:00:16</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -1994,7 +1994,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0966517226</t>
+          <t>0916330397</t>
         </is>
       </c>
       <c r="E63" s="4"/>
@@ -14019,18 +14019,22 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
-        </is>
-      </c>
-      <c r="C473" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C473" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E473" s="4"/>
@@ -14048,18 +14052,18 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
+          <t>賴珊珊</t>
         </is>
       </c>
       <c r="C474" s="4"/>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E474" s="4"/>
@@ -14077,22 +14081,18 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C475" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C475" s="4"/>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E475" s="4"/>
@@ -14110,22 +14110,22 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E476" s="4"/>
@@ -14143,22 +14143,22 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>趙云璟</t>
         </is>
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E477" s="4"/>
@@ -14176,18 +14176,22 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C478" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C478" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E478" s="4"/>
@@ -14205,18 +14209,18 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C479" s="4"/>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E479" s="4"/>
@@ -14234,18 +14238,18 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C480" s="4"/>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0986258793</t>
         </is>
       </c>
       <c r="E480" s="4"/>
@@ -14263,20 +14267,24 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C481" s="4"/>
-      <c r="D481" s="4"/>
+      <c r="D481" s="4" t="inlineStr">
+        <is>
+          <t>0982484963</t>
+        </is>
+      </c>
       <c r="E481" s="4"/>
       <c r="F481" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G481" s="5" t="inlineStr">
@@ -14288,24 +14296,20 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C482" s="4"/>
-      <c r="D482" s="4" t="inlineStr">
-        <is>
-          <t>0981898339</t>
-        </is>
-      </c>
+      <c r="D482" s="4"/>
       <c r="E482" s="4"/>
       <c r="F482" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G482" s="5" t="inlineStr">
@@ -14317,18 +14321,18 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C483" s="4"/>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>0903921531</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E483" s="4"/>
@@ -14346,18 +14350,18 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C484" s="4"/>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E484" s="4"/>
@@ -14375,18 +14379,18 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C485" s="4"/>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E485" s="4"/>
@@ -14404,18 +14408,18 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C486" s="4"/>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E486" s="4"/>
@@ -14433,18 +14437,18 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱振為</t>
         </is>
       </c>
       <c r="C487" s="4"/>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E487" s="4"/>
@@ -14462,22 +14466,18 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C488" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱政傑</t>
+        </is>
+      </c>
+      <c r="C488" s="4"/>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E488" s="4"/>
@@ -14495,18 +14495,22 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
-        </is>
-      </c>
-      <c r="C489" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C489" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E489" s="4"/>
@@ -14524,18 +14528,18 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C490" s="4"/>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E490" s="4"/>
@@ -14553,18 +14557,18 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C491" s="4"/>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E491" s="4"/>
@@ -14582,7 +14586,7 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
@@ -14611,18 +14615,18 @@
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C493" s="4"/>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E493" s="4"/>
@@ -14640,16 +14644,20 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B494" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C494" s="4"/>
-      <c r="D494" s="4"/>
+      <c r="D494" s="4" t="inlineStr">
+        <is>
+          <t>0935329653</t>
+        </is>
+      </c>
       <c r="E494" s="4"/>
       <c r="F494" s="4" t="inlineStr">
         <is>
@@ -14665,20 +14673,16 @@
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C495" s="4"/>
-      <c r="D495" s="4" t="inlineStr">
-        <is>
-          <t>0976588171</t>
-        </is>
-      </c>
+      <c r="D495" s="4"/>
       <c r="E495" s="4"/>
       <c r="F495" s="4" t="inlineStr">
         <is>
@@ -14694,18 +14698,18 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C496" s="4"/>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>0972128080</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E496" s="4"/>
@@ -14723,18 +14727,18 @@
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C497" s="4"/>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E497" s="4"/>
@@ -14752,18 +14756,18 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C498" s="4"/>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E498" s="4"/>
@@ -14781,18 +14785,18 @@
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C499" s="4"/>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E499" s="4"/>
@@ -14810,18 +14814,18 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C500" s="4"/>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E500" s="4"/>
@@ -14839,18 +14843,18 @@
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C501" s="4"/>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E501" s="4"/>
@@ -14868,18 +14872,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14897,18 +14901,18 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭鼎昇</t>
         </is>
       </c>
       <c r="C503" s="4"/>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E503" s="4"/>
@@ -14926,22 +14930,18 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C504" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>鄒育燁</t>
+        </is>
+      </c>
+      <c r="C504" s="4"/>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -14959,18 +14959,22 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
-        </is>
-      </c>
-      <c r="C505" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C505" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E505" s="4"/>
@@ -14988,18 +14992,18 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C506" s="4"/>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15017,18 +15021,18 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C507" s="4"/>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15046,18 +15050,18 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C508" s="4"/>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E508" s="4"/>
@@ -15075,18 +15079,18 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C509" s="4"/>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E509" s="4"/>
@@ -15104,18 +15108,18 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C510" s="4"/>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E510" s="4"/>
@@ -15133,18 +15137,18 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭秉霖</t>
         </is>
       </c>
       <c r="C511" s="4"/>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E511" s="4"/>
@@ -15162,22 +15166,18 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C512" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C512" s="4"/>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E512" s="4"/>
@@ -15195,26 +15195,30 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>鄭雁宇</t>
+          <t>鄭鉅耀</t>
         </is>
       </c>
       <c r="C513" s="4" t="inlineStr">
         <is>
-          <t>桃園區國聖二街145號5樓之1</t>
+          <t>新北市五股區成泰路二段208號</t>
         </is>
       </c>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E513" s="4"/>
-      <c r="F513" s="4"/>
+      <c r="F513" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G513" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15224,26 +15228,26 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C514" s="4"/>
+          <t>鄭雁宇</t>
+        </is>
+      </c>
+      <c r="C514" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E514" s="4"/>
-      <c r="F514" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F514" s="4"/>
       <c r="G514" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15253,18 +15257,18 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C515" s="4"/>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E515" s="4"/>
@@ -15282,18 +15286,18 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C516" s="4"/>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E516" s="4"/>
@@ -15311,18 +15315,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15340,18 +15344,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾銘峰</t>
         </is>
       </c>
       <c r="C518" s="4"/>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E518" s="4"/>
@@ -15369,22 +15373,18 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C519" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鐘國禎</t>
+        </is>
+      </c>
+      <c r="C519" s="4"/>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E519" s="4"/>
@@ -15402,18 +15402,22 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
-        </is>
-      </c>
-      <c r="C520" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C520" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E520" s="4"/>
@@ -15431,28 +15435,24 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C521" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>鐘駿霆</t>
+        </is>
+      </c>
+      <c r="C521" s="4"/>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E521" s="4"/>
       <c r="F521" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G521" s="5" t="inlineStr">
@@ -15464,18 +15464,18 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
+          <t>阮海德</t>
         </is>
       </c>
       <c r="C522" s="4"/>
       <c r="D522" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E522" s="4"/>
@@ -15493,18 +15493,22 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
-        </is>
-      </c>
-      <c r="C523" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C523" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E523" s="4"/>
@@ -15522,22 +15526,18 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C524" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿源</t>
+        </is>
+      </c>
+      <c r="C524" s="4"/>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E524" s="4"/>
@@ -15555,18 +15555,18 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
+          <t>阿良</t>
         </is>
       </c>
       <c r="C525" s="4"/>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E525" s="4"/>
@@ -15584,22 +15584,22 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
+          <t>陳仲盟</t>
         </is>
       </c>
       <c r="C526" s="4" t="inlineStr">
         <is>
-          <t>新北市土城區日和街7號22樓</t>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
         </is>
       </c>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15617,22 +15617,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
-        </is>
-      </c>
-      <c r="C527" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路1段28巷118-1號</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C527" s="4"/>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15650,18 +15646,22 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C528" s="4"/>
+          <t>陳俊安</t>
+        </is>
+      </c>
+      <c r="C528" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區日和街7號22樓</t>
+        </is>
+      </c>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15679,18 +15679,22 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
-        </is>
-      </c>
-      <c r="C529" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C529" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15708,18 +15712,18 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C530" s="4"/>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15737,18 +15741,18 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C531" s="4"/>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15766,18 +15770,18 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C532" s="4"/>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15795,18 +15799,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C533" s="4"/>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15824,22 +15828,26 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E534" s="4"/>
-      <c r="F534" s="4"/>
+      <c r="F534" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G534" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15849,18 +15857,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C535" s="4"/>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15878,26 +15886,22 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C536" s="4"/>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E536" s="4"/>
-      <c r="F536" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F536" s="4"/>
       <c r="G536" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15907,18 +15911,18 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C537" s="4"/>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E537" s="4"/>
@@ -15936,22 +15940,18 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C538" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕融</t>
+        </is>
+      </c>
+      <c r="C538" s="4"/>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E538" s="4"/>
@@ -15969,18 +15969,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
+          <t>陳奕閔</t>
         </is>
       </c>
       <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E539" s="4"/>
@@ -15998,18 +15998,22 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
-        </is>
-      </c>
-      <c r="C540" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C540" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16027,18 +16031,18 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C541" s="4"/>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16056,18 +16060,18 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C542" s="4"/>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E542" s="4"/>
@@ -16085,18 +16089,18 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C543" s="4"/>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16114,22 +16118,18 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C544" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳子杰</t>
+        </is>
+      </c>
+      <c r="C544" s="4"/>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E544" s="4"/>
@@ -16147,18 +16147,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
+          <t>陳宏文</t>
         </is>
       </c>
       <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16176,18 +16176,18 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
+          <t>陳宏達</t>
         </is>
       </c>
       <c r="C546" s="4"/>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16205,22 +16205,22 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
+          <t>陳家偉</t>
         </is>
       </c>
       <c r="C547" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
+          <t>宜蘭市神農路一段72號</t>
         </is>
       </c>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E547" s="4"/>
@@ -16238,22 +16238,18 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
-        </is>
-      </c>
-      <c r="C548" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁美街125號</t>
-        </is>
-      </c>
+          <t>陳小雨</t>
+        </is>
+      </c>
+      <c r="C548" s="4"/>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E548" s="4"/>
@@ -16271,18 +16267,18 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
+          <t>陳建宏</t>
         </is>
       </c>
       <c r="C549" s="4"/>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E549" s="4"/>
@@ -16300,18 +16296,22 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
-        </is>
-      </c>
-      <c r="C550" s="4"/>
+          <t>陳建宏(花蓮)</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉佳林31之19號</t>
+        </is>
+      </c>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E550" s="4"/>
@@ -16329,18 +16329,22 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
-        </is>
-      </c>
-      <c r="C551" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E551" s="4"/>
@@ -16358,18 +16362,18 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C552" s="4"/>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16387,18 +16391,18 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C553" s="4"/>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16416,18 +16420,18 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C554" s="4"/>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16445,22 +16449,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C555" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳怡如(彥鈞)</t>
+        </is>
+      </c>
+      <c r="C555" s="4"/>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16478,18 +16478,18 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
+          <t>陳慶壎</t>
         </is>
       </c>
       <c r="C556" s="4"/>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16507,22 +16507,18 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
-        </is>
-      </c>
-      <c r="C557" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區星雲街30號</t>
-        </is>
-      </c>
+          <t>陳敬惟</t>
+        </is>
+      </c>
+      <c r="C557" s="4"/>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16540,22 +16536,22 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
+          <t>陳智盛</t>
         </is>
       </c>
       <c r="C558" s="4" t="inlineStr">
         <is>
-          <t>桃園市南豐街258號</t>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
         </is>
       </c>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16573,18 +16569,18 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
+          <t>陳朋堅</t>
         </is>
       </c>
       <c r="C559" s="4"/>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16602,18 +16598,22 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
-        </is>
-      </c>
-      <c r="C560" s="4"/>
+          <t>陳松廉</t>
+        </is>
+      </c>
+      <c r="C560" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區星雲街30號</t>
+        </is>
+      </c>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16631,18 +16631,22 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
-        </is>
-      </c>
-      <c r="C561" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C561" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16660,18 +16664,18 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C562" s="4"/>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16689,22 +16693,18 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C563" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳柏豪</t>
+        </is>
+      </c>
+      <c r="C563" s="4"/>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16722,18 +16722,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16751,18 +16751,18 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
+          <t>陳正傑</t>
         </is>
       </c>
       <c r="C565" s="4"/>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16780,18 +16780,22 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
-        </is>
-      </c>
-      <c r="C566" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C566" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16809,18 +16813,18 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C567" s="4"/>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16838,22 +16842,18 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C568" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳琇珊</t>
+        </is>
+      </c>
+      <c r="C568" s="4"/>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16871,18 +16871,18 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
+          <t>陳琬瑜</t>
         </is>
       </c>
       <c r="C569" s="4"/>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16900,22 +16900,18 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
-        </is>
-      </c>
-      <c r="C570" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
-        </is>
-      </c>
+          <t>陳璽文</t>
+        </is>
+      </c>
+      <c r="C570" s="4"/>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16933,18 +16929,22 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
-        </is>
-      </c>
-      <c r="C571" s="4"/>
+          <t>陳益銓</t>
+        </is>
+      </c>
+      <c r="C571" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區民生街15巷10號3樓</t>
+        </is>
+      </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -16962,18 +16962,18 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
+          <t>陳秋蓉</t>
         </is>
       </c>
       <c r="C572" s="4"/>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -16991,18 +16991,22 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
-        </is>
-      </c>
-      <c r="C573" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17020,22 +17024,18 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C574" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳貴源</t>
+        </is>
+      </c>
+      <c r="C574" s="4"/>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17053,22 +17053,18 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
-        </is>
-      </c>
-      <c r="C575" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
-        </is>
-      </c>
+          <t>陳達鋒</t>
+        </is>
+      </c>
+      <c r="C575" s="4"/>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17086,22 +17082,18 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
-        </is>
-      </c>
-      <c r="C576" s="4" t="inlineStr">
-        <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C576" s="4"/>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17119,18 +17111,22 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C577" s="4"/>
+          <t>陳長志</t>
+        </is>
+      </c>
+      <c r="C577" s="4" t="inlineStr">
+        <is>
+          <t>新北市新店區安康路</t>
+        </is>
+      </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17148,18 +17144,22 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
-        </is>
-      </c>
-      <c r="C578" s="4"/>
+          <t>陳雯瑄</t>
+        </is>
+      </c>
+      <c r="C578" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+        </is>
+      </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17177,18 +17177,22 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
-        </is>
-      </c>
-      <c r="C579" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17206,18 +17210,18 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C580" s="4"/>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17235,18 +17239,18 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C581" s="4"/>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17264,18 +17268,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17293,18 +17297,18 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C583" s="4"/>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17322,18 +17326,18 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C584" s="4"/>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17351,18 +17355,18 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C585" s="4"/>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17380,18 +17384,18 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C586" s="4"/>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17409,18 +17413,18 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C587" s="4"/>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17438,18 +17442,18 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C588" s="4"/>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17467,22 +17471,18 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C589" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>顏坤川</t>
+        </is>
+      </c>
+      <c r="C589" s="4"/>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17500,18 +17500,18 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
+          <t>顏宏坤</t>
         </is>
       </c>
       <c r="C590" s="4"/>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17529,18 +17529,18 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
+          <t>馬迪</t>
         </is>
       </c>
       <c r="C591" s="4"/>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17558,18 +17558,22 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
-        </is>
-      </c>
-      <c r="C592" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C592" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17587,18 +17591,18 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C593" s="4"/>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17616,18 +17620,18 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C594" s="4"/>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17645,18 +17649,18 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C595" s="4"/>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17674,18 +17678,18 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C596" s="4"/>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17703,22 +17707,18 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C597" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高文宏</t>
+        </is>
+      </c>
+      <c r="C597" s="4"/>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17736,18 +17736,18 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
+          <t>高聖景</t>
         </is>
       </c>
       <c r="C598" s="4"/>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17765,18 +17765,18 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
+          <t>高莉婷</t>
         </is>
       </c>
       <c r="C599" s="4"/>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17794,16 +17794,24 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
-        </is>
-      </c>
-      <c r="C600" s="4"/>
-      <c r="D600" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C600" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
+      <c r="D600" s="4" t="inlineStr">
+        <is>
+          <t>0977121772</t>
+        </is>
+      </c>
       <c r="E600" s="4"/>
       <c r="F600" s="4" t="inlineStr">
         <is>
@@ -17819,18 +17827,18 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C601" s="4"/>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0958180882</t>
+          <t>0937742352</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17848,22 +17856,18 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C602" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
+          <t>魏金漢</t>
+        </is>
+      </c>
+      <c r="C602" s="4"/>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0903975921</t>
+          <t>0989116588</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17881,12 +17885,12 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
+          <t>鴻</t>
         </is>
       </c>
       <c r="C603" s="4"/>
@@ -17906,18 +17910,18 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
+          <t>黃俊翰</t>
         </is>
       </c>
       <c r="C604" s="4"/>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>0938722217</t>
+          <t>0958180882</t>
         </is>
       </c>
       <c r="E604" s="4"/>
@@ -17935,18 +17939,22 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
-        </is>
-      </c>
-      <c r="C605" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C605" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>0989628136</t>
+          <t>0903975921</t>
         </is>
       </c>
       <c r="E605" s="4"/>
@@ -17964,20 +17972,16 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C606" s="4"/>
-      <c r="D606" s="4" t="inlineStr">
-        <is>
-          <t>0981218639</t>
-        </is>
-      </c>
+      <c r="D606" s="4"/>
       <c r="E606" s="4"/>
       <c r="F606" s="4" t="inlineStr">
         <is>
@@ -17993,18 +17997,18 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C607" s="4"/>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E607" s="4"/>
@@ -18022,18 +18026,18 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C608" s="4"/>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E608" s="4"/>
@@ -18051,18 +18055,18 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C609" s="4"/>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18080,18 +18084,18 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C610" s="4"/>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18109,18 +18113,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18138,22 +18142,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C612" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃宥惟</t>
+        </is>
+      </c>
+      <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18171,18 +18171,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18200,18 +18200,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃庠豪</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18229,18 +18229,22 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
-        </is>
-      </c>
-      <c r="C615" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C615" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18258,18 +18262,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18287,18 +18291,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18316,18 +18320,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18345,18 +18349,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18374,18 +18378,18 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C620" s="4"/>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18403,18 +18407,18 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C621" s="4"/>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18432,18 +18436,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18461,22 +18465,26 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C623" s="4"/>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E623" s="4"/>
-      <c r="F623" s="4"/>
+      <c r="F623" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G623" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -18486,18 +18494,18 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C624" s="4"/>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E624" s="4"/>
@@ -18515,18 +18523,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18544,26 +18552,22 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E626" s="4"/>
-      <c r="F626" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F626" s="4"/>
       <c r="G626" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -18573,18 +18577,18 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E627" s="4"/>
@@ -18602,18 +18606,18 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C628" s="4"/>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18631,18 +18635,18 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C629" s="4"/>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E629" s="4"/>
@@ -18660,18 +18664,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18687,9 +18691,96 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>2026/03/26  13:00:16</t>
+      <c r="A631" s="4" t="inlineStr">
+        <is>
+          <t>M2510020007</t>
+        </is>
+      </c>
+      <c r="B631" s="4" t="inlineStr">
+        <is>
+          <t>黃鴻麒</t>
+        </is>
+      </c>
+      <c r="C631" s="4"/>
+      <c r="D631" s="4" t="inlineStr">
+        <is>
+          <t>0930571975</t>
+        </is>
+      </c>
+      <c r="E631" s="4"/>
+      <c r="F631" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G631" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="4" t="inlineStr">
+        <is>
+          <t>M2602270002</t>
+        </is>
+      </c>
+      <c r="B632" s="4" t="inlineStr">
+        <is>
+          <t>黎信宏</t>
+        </is>
+      </c>
+      <c r="C632" s="4"/>
+      <c r="D632" s="4" t="inlineStr">
+        <is>
+          <t>0911024337</t>
+        </is>
+      </c>
+      <c r="E632" s="4"/>
+      <c r="F632" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G632" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B633" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C633" s="4"/>
+      <c r="D633" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E633" s="4"/>
+      <c r="F633" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G633" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026/03/28  13:00:09</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -7657,18 +7657,22 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>M2509260053</t>
+          <t>M2603280002</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>林美雲</t>
-        </is>
-      </c>
-      <c r="C256" s="4"/>
+          <t>林秀英</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區中山北路七段81巷16弄11-2號1樓</t>
+        </is>
+      </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>0920436214</t>
+          <t>0922316858</t>
         </is>
       </c>
       <c r="E256" s="4"/>
@@ -7686,18 +7690,18 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>M2510280002</t>
+          <t>M2509260053</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>林耀武</t>
+          <t>林美雲</t>
         </is>
       </c>
       <c r="C257" s="4"/>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>0911552967</t>
+          <t>0920436214</t>
         </is>
       </c>
       <c r="E257" s="4"/>
@@ -7715,18 +7719,18 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>M2509300005</t>
+          <t>M2510280002</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>林通海</t>
+          <t>林耀武</t>
         </is>
       </c>
       <c r="C258" s="4"/>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>0958589472</t>
+          <t>0911552967</t>
         </is>
       </c>
       <c r="E258" s="4"/>
@@ -7744,18 +7748,18 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>M2511220001</t>
+          <t>M2509300005</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>林鈺倫</t>
+          <t>林通海</t>
         </is>
       </c>
       <c r="C259" s="4"/>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>0988210410</t>
+          <t>0958589472</t>
         </is>
       </c>
       <c r="E259" s="4"/>
@@ -7773,18 +7777,18 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>M2510190005</t>
+          <t>M2511220001</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>林鈺瑩</t>
+          <t>林鈺倫</t>
         </is>
       </c>
       <c r="C260" s="4"/>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>0973789355</t>
+          <t>0988210410</t>
         </is>
       </c>
       <c r="E260" s="4"/>
@@ -7802,18 +7806,18 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>M2511250001</t>
+          <t>M2510190005</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>林雅琦</t>
+          <t>林鈺瑩</t>
         </is>
       </c>
       <c r="C261" s="4"/>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>0917361103</t>
+          <t>0973789355</t>
         </is>
       </c>
       <c r="E261" s="4"/>
@@ -7831,18 +7835,18 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>M2510100002</t>
+          <t>M2511250001</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>林鴻丞</t>
+          <t>林雅琦</t>
         </is>
       </c>
       <c r="C262" s="4"/>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>0989764757</t>
+          <t>0917361103</t>
         </is>
       </c>
       <c r="E262" s="4"/>
@@ -7860,18 +7864,18 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>M2601030004</t>
+          <t>M2510100002</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>柯偉強</t>
+          <t>林鴻丞</t>
         </is>
       </c>
       <c r="C263" s="4"/>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>0976720368</t>
+          <t>0989764757</t>
         </is>
       </c>
       <c r="E263" s="4"/>
@@ -7889,18 +7893,18 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>M2510050009</t>
+          <t>M2601030004</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>梁涵鈞</t>
+          <t>柯偉強</t>
         </is>
       </c>
       <c r="C264" s="4"/>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>0961007059</t>
+          <t>0976720368</t>
         </is>
       </c>
       <c r="E264" s="4"/>
@@ -7918,18 +7922,18 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>M2512210002</t>
+          <t>M2510050009</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>楊啓煌</t>
+          <t>梁涵鈞</t>
         </is>
       </c>
       <c r="C265" s="4"/>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>0970290888</t>
+          <t>0961007059</t>
         </is>
       </c>
       <c r="E265" s="4"/>
@@ -7947,7 +7951,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>M2603240002</t>
+          <t>M2512210002</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -7955,18 +7959,18 @@
           <t>楊啓煌</t>
         </is>
       </c>
-      <c r="C266" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區新生北路三段84巷33號2樓</t>
-        </is>
-      </c>
+      <c r="C266" s="4"/>
       <c r="D266" s="4" t="inlineStr">
         <is>
           <t>0970290888</t>
         </is>
       </c>
       <c r="E266" s="4"/>
-      <c r="F266" s="4"/>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -7976,26 +7980,26 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>M2509260042</t>
+          <t>M2603240002</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>楊士毅</t>
-        </is>
-      </c>
-      <c r="C267" s="4"/>
+          <t>楊啓煌</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>台北市中山區新生北路三段84巷33號2樓</t>
+        </is>
+      </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>0917523878</t>
+          <t>0970290888</t>
         </is>
       </c>
       <c r="E267" s="4"/>
-      <c r="F267" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F267" s="4"/>
       <c r="G267" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -8005,18 +8009,18 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>M2510100008</t>
+          <t>M2509260042</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>楊孝斌</t>
+          <t>楊士毅</t>
         </is>
       </c>
       <c r="C268" s="4"/>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>0916001788</t>
+          <t>0917523878</t>
         </is>
       </c>
       <c r="E268" s="4"/>
@@ -8034,22 +8038,18 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>M2509270002</t>
+          <t>M2510100008</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>楊岱惊</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>桃園市長安街26巷3號</t>
-        </is>
-      </c>
+          <t>楊孝斌</t>
+        </is>
+      </c>
+      <c r="C269" s="4"/>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>0989612191</t>
+          <t>0916001788</t>
         </is>
       </c>
       <c r="E269" s="4"/>
@@ -8067,22 +8067,22 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>M2509270011</t>
+          <t>M2509270002</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>楊庭瑋</t>
+          <t>楊岱惊</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>基隆市中山區復興路151號</t>
+          <t>桃園市長安街26巷3號</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>0963922276</t>
+          <t>0989612191</t>
         </is>
       </c>
       <c r="E270" s="4"/>
@@ -8100,18 +8100,22 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>M2511060001</t>
+          <t>M2509270011</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>楊明晁(四哥)</t>
-        </is>
-      </c>
-      <c r="C271" s="4"/>
+          <t>楊庭瑋</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區復興路151號</t>
+        </is>
+      </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>0968732839</t>
+          <t>0963922276</t>
         </is>
       </c>
       <c r="E271" s="4"/>
@@ -8129,18 +8133,18 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>M2601250001</t>
+          <t>M2511060001</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>楊智傑</t>
+          <t>楊明晁(四哥)</t>
         </is>
       </c>
       <c r="C272" s="4"/>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>0931131821</t>
+          <t>0968732839</t>
         </is>
       </c>
       <c r="E272" s="4"/>
@@ -8158,18 +8162,18 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>M2510030003</t>
+          <t>M2601250001</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>楊智翔</t>
+          <t>楊智傑</t>
         </is>
       </c>
       <c r="C273" s="4"/>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>0975128278</t>
+          <t>0931131821</t>
         </is>
       </c>
       <c r="E273" s="4"/>
@@ -8187,18 +8191,18 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>M2510060004</t>
+          <t>M2510030003</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>楊重九</t>
+          <t>楊智翔</t>
         </is>
       </c>
       <c r="C274" s="4"/>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>0920626999</t>
+          <t>0975128278</t>
         </is>
       </c>
       <c r="E274" s="4"/>
@@ -8216,18 +8220,18 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>M2510080001</t>
+          <t>M2510060004</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>楊錦加</t>
+          <t>楊重九</t>
         </is>
       </c>
       <c r="C275" s="4"/>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>0918872988</t>
+          <t>0920626999</t>
         </is>
       </c>
       <c r="E275" s="4"/>
@@ -8245,16 +8249,20 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>V0020</t>
+          <t>M2510080001</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>榮豪</t>
+          <t>楊錦加</t>
         </is>
       </c>
       <c r="C276" s="4"/>
-      <c r="D276" s="4"/>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>0918872988</t>
+        </is>
+      </c>
       <c r="E276" s="4"/>
       <c r="F276" s="4" t="inlineStr">
         <is>
@@ -8270,20 +8278,16 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>M2602130002</t>
+          <t>V0020</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>榮豪-許</t>
+          <t>榮豪</t>
         </is>
       </c>
       <c r="C277" s="4"/>
-      <c r="D277" s="4" t="inlineStr">
-        <is>
-          <t>0931100879</t>
-        </is>
-      </c>
+      <c r="D277" s="4"/>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="inlineStr">
         <is>
@@ -8299,18 +8303,18 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>M2602080007</t>
+          <t>M2602130002</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>樓俊瑋</t>
+          <t>榮豪-許</t>
         </is>
       </c>
       <c r="C278" s="4"/>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>0910900256</t>
+          <t>0931100879</t>
         </is>
       </c>
       <c r="E278" s="4"/>
@@ -8328,22 +8332,18 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>M2511010001</t>
+          <t>M2602080007</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>武林</t>
-        </is>
-      </c>
-      <c r="C279" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區集美街222號5樓</t>
-        </is>
-      </c>
+          <t>樓俊瑋</t>
+        </is>
+      </c>
+      <c r="C279" s="4"/>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>0913211688</t>
+          <t>0910900256</t>
         </is>
       </c>
       <c r="E279" s="4"/>
@@ -8361,18 +8361,22 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>M2511080005</t>
+          <t>M2511010001</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>毛毛</t>
-        </is>
-      </c>
-      <c r="C280" s="4"/>
+          <t>武林</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區集美街222號5樓</t>
+        </is>
+      </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>0919286386</t>
+          <t>0913211688</t>
         </is>
       </c>
       <c r="E280" s="4"/>
@@ -8390,24 +8394,24 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>Z0001</t>
+          <t>M2511080005</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>民享店</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
-        </is>
-      </c>
-      <c r="D281" s="4"/>
+          <t>毛毛</t>
+        </is>
+      </c>
+      <c r="C281" s="4"/>
+      <c r="D281" s="4" t="inlineStr">
+        <is>
+          <t>0919286386</t>
+        </is>
+      </c>
       <c r="E281" s="4"/>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -8419,15 +8423,19 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>V0014</t>
+          <t>Z0001</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>民享房東</t>
-        </is>
-      </c>
-      <c r="C282" s="4"/>
+          <t>民享店</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
+        </is>
+      </c>
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
       <c r="F282" s="4" t="inlineStr">
@@ -8444,12 +8452,12 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>V0019</t>
+          <t>V0014</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>永豐餘</t>
+          <t>民享房東</t>
         </is>
       </c>
       <c r="C283" s="4"/>
@@ -8457,7 +8465,7 @@
       <c r="E283" s="4"/>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -8469,24 +8477,20 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>M2509260041</t>
+          <t>V0019</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>江世隆(新莊區)</t>
+          <t>永豐餘</t>
         </is>
       </c>
       <c r="C284" s="4"/>
-      <c r="D284" s="4" t="inlineStr">
-        <is>
-          <t>0981243133</t>
-        </is>
-      </c>
+      <c r="D284" s="4"/>
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -8498,18 +8502,18 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>M2510050010</t>
+          <t>M2509260041</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>江仁堂</t>
+          <t>江世隆(新莊區)</t>
         </is>
       </c>
       <c r="C285" s="4"/>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>0986696777</t>
+          <t>0981243133</t>
         </is>
       </c>
       <c r="E285" s="4"/>
@@ -8527,18 +8531,18 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>M2511220002</t>
+          <t>M2510050010</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>江凱逸</t>
+          <t>江仁堂</t>
         </is>
       </c>
       <c r="C286" s="4"/>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>0912312896</t>
+          <t>0986696777</t>
         </is>
       </c>
       <c r="E286" s="4"/>
@@ -8556,16 +8560,20 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>M2509120001</t>
+          <t>M2511220002</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>江哥</t>
+          <t>江凱逸</t>
         </is>
       </c>
       <c r="C287" s="4"/>
-      <c r="D287" s="4"/>
+      <c r="D287" s="4" t="inlineStr">
+        <is>
+          <t>0912312896</t>
+        </is>
+      </c>
       <c r="E287" s="4"/>
       <c r="F287" s="4" t="inlineStr">
         <is>
@@ -8581,20 +8589,16 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>M2509280006</t>
+          <t>M2509120001</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>江宏恩</t>
+          <t>江哥</t>
         </is>
       </c>
       <c r="C288" s="4"/>
-      <c r="D288" s="4" t="inlineStr">
-        <is>
-          <t>0988677410</t>
-        </is>
-      </c>
+      <c r="D288" s="4"/>
       <c r="E288" s="4"/>
       <c r="F288" s="4" t="inlineStr">
         <is>
@@ -8610,18 +8614,18 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>M2510160009</t>
+          <t>M2509280006</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>江育哲</t>
+          <t>江宏恩</t>
         </is>
       </c>
       <c r="C289" s="4"/>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>0916586618</t>
+          <t>0988677410</t>
         </is>
       </c>
       <c r="E289" s="4"/>
@@ -8639,18 +8643,18 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>M2511060005</t>
+          <t>M2510160009</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>池沛潔</t>
+          <t>江育哲</t>
         </is>
       </c>
       <c r="C290" s="4"/>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>0963900636</t>
+          <t>0916586618</t>
         </is>
       </c>
       <c r="E290" s="4"/>
@@ -8668,18 +8672,18 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>M2510240003</t>
+          <t>M2511060005</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>汪鈺修</t>
+          <t>池沛潔</t>
         </is>
       </c>
       <c r="C291" s="4"/>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>0971792952</t>
+          <t>0963900636</t>
         </is>
       </c>
       <c r="E291" s="4"/>
@@ -8697,18 +8701,18 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>M2601030003</t>
+          <t>M2510240003</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>沈大哥</t>
+          <t>汪鈺修</t>
         </is>
       </c>
       <c r="C292" s="4"/>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>0978562818</t>
+          <t>0971792952</t>
         </is>
       </c>
       <c r="E292" s="4"/>
@@ -8726,18 +8730,18 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>M2509300002</t>
+          <t>M2601030003</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>沈明鋒</t>
+          <t>沈大哥</t>
         </is>
       </c>
       <c r="C293" s="4"/>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>0908356227</t>
+          <t>0978562818</t>
         </is>
       </c>
       <c r="E293" s="4"/>
@@ -8755,20 +8759,24 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>V0005</t>
+          <t>M2509300002</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>波蜜企業</t>
+          <t>沈明鋒</t>
         </is>
       </c>
       <c r="C294" s="4"/>
-      <c r="D294" s="4"/>
+      <c r="D294" s="4" t="inlineStr">
+        <is>
+          <t>0908356227</t>
+        </is>
+      </c>
       <c r="E294" s="4"/>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -8780,24 +8788,20 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>M2512200004</t>
+          <t>V0005</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>洪丞鍇</t>
+          <t>波蜜企業</t>
         </is>
       </c>
       <c r="C295" s="4"/>
-      <c r="D295" s="4" t="inlineStr">
-        <is>
-          <t>0952119213</t>
-        </is>
-      </c>
+      <c r="D295" s="4"/>
       <c r="E295" s="4"/>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -8809,18 +8813,18 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>M2602270003</t>
+          <t>M2512200004</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>洪儒明</t>
+          <t>洪丞鍇</t>
         </is>
       </c>
       <c r="C296" s="4"/>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>0960097097</t>
+          <t>0952119213</t>
         </is>
       </c>
       <c r="E296" s="4"/>
@@ -8838,18 +8842,18 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>M2509280012</t>
+          <t>M2602270003</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>洪勝忠</t>
+          <t>洪儒明</t>
         </is>
       </c>
       <c r="C297" s="4"/>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>0917962020</t>
+          <t>0960097097</t>
         </is>
       </c>
       <c r="E297" s="4"/>
@@ -8867,18 +8871,18 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>M2510060001</t>
+          <t>M2509280012</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>洪文輝</t>
+          <t>洪勝忠</t>
         </is>
       </c>
       <c r="C298" s="4"/>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>0909183013</t>
+          <t>0917962020</t>
         </is>
       </c>
       <c r="E298" s="4"/>
@@ -8896,18 +8900,18 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>M2510300003</t>
+          <t>M2510060001</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>洪毅平</t>
+          <t>洪文輝</t>
         </is>
       </c>
       <c r="C299" s="4"/>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>0958266132</t>
+          <t>0909183013</t>
         </is>
       </c>
       <c r="E299" s="4"/>
@@ -8925,18 +8929,18 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>M2510240005</t>
+          <t>M2510300003</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>洪浩鈞</t>
+          <t>洪毅平</t>
         </is>
       </c>
       <c r="C300" s="4"/>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>0939553096</t>
+          <t>0958266132</t>
         </is>
       </c>
       <c r="E300" s="4"/>
@@ -8954,18 +8958,18 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>M2509260019</t>
+          <t>M2510240005</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>洪秋麗</t>
+          <t>洪浩鈞</t>
         </is>
       </c>
       <c r="C301" s="4"/>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>0922210223</t>
+          <t>0939553096</t>
         </is>
       </c>
       <c r="E301" s="4"/>
@@ -8983,18 +8987,18 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>M2512140001</t>
+          <t>M2509260019</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>洪翊珊</t>
+          <t>洪秋麗</t>
         </is>
       </c>
       <c r="C302" s="4"/>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>0968884119</t>
+          <t>0922210223</t>
         </is>
       </c>
       <c r="E302" s="4"/>
@@ -9012,22 +9016,18 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>M2510060006</t>
+          <t>M2512140001</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>洪金賢</t>
-        </is>
-      </c>
-      <c r="C303" s="4" t="inlineStr">
-        <is>
-          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
-        </is>
-      </c>
+          <t>洪翊珊</t>
+        </is>
+      </c>
+      <c r="C303" s="4"/>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>0933702515</t>
+          <t>0968884119</t>
         </is>
       </c>
       <c r="E303" s="4"/>
@@ -9045,22 +9045,22 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>M2602040001</t>
+          <t>M2510060006</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>涂宏忠</t>
+          <t>洪金賢</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>高雄市開發路15-3號</t>
+          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>0963222826</t>
+          <t>0933702515</t>
         </is>
       </c>
       <c r="E304" s="4"/>
@@ -9078,18 +9078,22 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>M2510090009</t>
+          <t>M2602040001</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>游仲強</t>
-        </is>
-      </c>
-      <c r="C305" s="4"/>
+          <t>涂宏忠</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>高雄市開發路15-3號</t>
+        </is>
+      </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>0910671480</t>
+          <t>0963222826</t>
         </is>
       </c>
       <c r="E305" s="4"/>
@@ -9107,18 +9111,18 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>M2602030002</t>
+          <t>M2510090009</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>游凱翔</t>
+          <t>游仲強</t>
         </is>
       </c>
       <c r="C306" s="4"/>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>0978317186</t>
+          <t>0910671480</t>
         </is>
       </c>
       <c r="E306" s="4"/>
@@ -9136,18 +9140,18 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>M2601290001</t>
+          <t>M2602030002</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>游家誠</t>
+          <t>游凱翔</t>
         </is>
       </c>
       <c r="C307" s="4"/>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>0920727320</t>
+          <t>0978317186</t>
         </is>
       </c>
       <c r="E307" s="4"/>
@@ -9165,18 +9169,18 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>M2510090002</t>
+          <t>M2601290001</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>游煥清</t>
+          <t>游家誠</t>
         </is>
       </c>
       <c r="C308" s="4"/>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>0932139705</t>
+          <t>0920727320</t>
         </is>
       </c>
       <c r="E308" s="4"/>
@@ -9194,18 +9198,18 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>M2510100004</t>
+          <t>M2510090002</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>潘文展</t>
+          <t>游煥清</t>
         </is>
       </c>
       <c r="C309" s="4"/>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>0930842995</t>
+          <t>0932139705</t>
         </is>
       </c>
       <c r="E309" s="4"/>
@@ -9223,22 +9227,18 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>M2511230004</t>
+          <t>M2510100004</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>潘正霖(瘋爪子)</t>
-        </is>
-      </c>
-      <c r="C310" s="4" t="inlineStr">
-        <is>
-          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
-        </is>
-      </c>
+          <t>潘文展</t>
+        </is>
+      </c>
+      <c r="C310" s="4"/>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>0983777818</t>
+          <t>0930842995</t>
         </is>
       </c>
       <c r="E310" s="4"/>
@@ -9256,18 +9256,22 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>M2509280010</t>
+          <t>M2511230004</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>潘秀茹</t>
-        </is>
-      </c>
-      <c r="C311" s="4"/>
+          <t>潘正霖(瘋爪子)</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
+        </is>
+      </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>0911900520</t>
+          <t>0983777818</t>
         </is>
       </c>
       <c r="E311" s="4"/>
@@ -9285,18 +9289,18 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>M2601200002</t>
+          <t>M2509280010</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>潘糖糖</t>
+          <t>潘秀茹</t>
         </is>
       </c>
       <c r="C312" s="4"/>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>0976297272</t>
+          <t>0911900520</t>
         </is>
       </c>
       <c r="E312" s="4"/>
@@ -9314,18 +9318,18 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>M2509300016</t>
+          <t>M2601200002</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>潘鳯斌</t>
+          <t>潘糖糖</t>
         </is>
       </c>
       <c r="C313" s="4"/>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>0935502290</t>
+          <t>0976297272</t>
         </is>
       </c>
       <c r="E313" s="4"/>
@@ -9343,16 +9347,20 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>M2509290010</t>
+          <t>M2509300016</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>火牛-批發</t>
+          <t>潘鳯斌</t>
         </is>
       </c>
       <c r="C314" s="4"/>
-      <c r="D314" s="4"/>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>0935502290</t>
+        </is>
+      </c>
       <c r="E314" s="4"/>
       <c r="F314" s="4" t="inlineStr">
         <is>
@@ -9368,12 +9376,12 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>M2512180002</t>
+          <t>M2509290010</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>火牛-老秦</t>
+          <t>火牛-批發</t>
         </is>
       </c>
       <c r="C315" s="4"/>
@@ -9393,12 +9401,12 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>M2512180001</t>
+          <t>M2512180002</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>火牛-阿昌</t>
+          <t>火牛-老秦</t>
         </is>
       </c>
       <c r="C316" s="4"/>
@@ -9418,20 +9426,16 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>M2602140002</t>
+          <t>M2512180001</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>灰灰</t>
+          <t>火牛-阿昌</t>
         </is>
       </c>
       <c r="C317" s="4"/>
-      <c r="D317" s="4" t="inlineStr">
-        <is>
-          <t>0987829134</t>
-        </is>
-      </c>
+      <c r="D317" s="4"/>
       <c r="E317" s="4"/>
       <c r="F317" s="4" t="inlineStr">
         <is>
@@ -9447,18 +9451,18 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>M2509300011</t>
+          <t>M2602140002</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>熊駿天(大熊)</t>
+          <t>灰灰</t>
         </is>
       </c>
       <c r="C318" s="4"/>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>0933131800</t>
+          <t>0987829134</t>
         </is>
       </c>
       <c r="E318" s="4"/>
@@ -9476,18 +9480,18 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>M2602070001</t>
+          <t>M2509300011</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>王RICK</t>
+          <t>熊駿天(大熊)</t>
         </is>
       </c>
       <c r="C319" s="4"/>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>0930106976</t>
+          <t>0933131800</t>
         </is>
       </c>
       <c r="E319" s="4"/>
@@ -9505,22 +9509,18 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>M2510240006</t>
+          <t>M2602070001</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>王中南</t>
-        </is>
-      </c>
-      <c r="C320" s="4" t="inlineStr">
-        <is>
-          <t>桃園市平鎮區快速路166號3樓</t>
-        </is>
-      </c>
+          <t>王RICK</t>
+        </is>
+      </c>
+      <c r="C320" s="4"/>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>0937124082</t>
+          <t>0930106976</t>
         </is>
       </c>
       <c r="E320" s="4"/>
@@ -9538,18 +9538,22 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>M2601020001</t>
+          <t>M2510240006</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>王仁澤</t>
-        </is>
-      </c>
-      <c r="C321" s="4"/>
+          <t>王中南</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區快速路166號3樓</t>
+        </is>
+      </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>0976503359</t>
+          <t>0937124082</t>
         </is>
       </c>
       <c r="E321" s="4"/>
@@ -9567,18 +9571,18 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>M2603010004</t>
+          <t>M2601020001</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>王又杰</t>
+          <t>王仁澤</t>
         </is>
       </c>
       <c r="C322" s="4"/>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>0909771449</t>
+          <t>0976503359</t>
         </is>
       </c>
       <c r="E322" s="4"/>
@@ -9596,22 +9600,26 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>M2601080001</t>
+          <t>M2603010004</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>王家文</t>
+          <t>王又杰</t>
         </is>
       </c>
       <c r="C323" s="4"/>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>0908176140</t>
+          <t>0909771449</t>
         </is>
       </c>
       <c r="E323" s="4"/>
-      <c r="F323" s="4"/>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -9621,26 +9629,22 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>M2602080001</t>
+          <t>M2601080001</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>王巽璋</t>
+          <t>王家文</t>
         </is>
       </c>
       <c r="C324" s="4"/>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>0932943159</t>
+          <t>0908176140</t>
         </is>
       </c>
       <c r="E324" s="4"/>
-      <c r="F324" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F324" s="4"/>
       <c r="G324" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -9650,18 +9654,18 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>M2512230001</t>
+          <t>M2602080001</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>王志維</t>
+          <t>王巽璋</t>
         </is>
       </c>
       <c r="C325" s="4"/>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>0931262170</t>
+          <t>0932943159</t>
         </is>
       </c>
       <c r="E325" s="4"/>
@@ -9679,18 +9683,18 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>M2511180003</t>
+          <t>M2512230001</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>王明輝</t>
+          <t>王志維</t>
         </is>
       </c>
       <c r="C326" s="4"/>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>0937002585</t>
+          <t>0931262170</t>
         </is>
       </c>
       <c r="E326" s="4"/>
@@ -9708,18 +9712,18 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>M2510140007</t>
+          <t>M2511180003</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>王羿佳</t>
+          <t>王明輝</t>
         </is>
       </c>
       <c r="C327" s="4"/>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>0968831773</t>
+          <t>0937002585</t>
         </is>
       </c>
       <c r="E327" s="4"/>
@@ -9737,22 +9741,18 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>M2509260013</t>
+          <t>M2510140007</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>王舜平</t>
-        </is>
-      </c>
-      <c r="C328" s="4" t="inlineStr">
-        <is>
-          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
-        </is>
-      </c>
+          <t>王羿佳</t>
+        </is>
+      </c>
+      <c r="C328" s="4"/>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>0917215021</t>
+          <t>0968831773</t>
         </is>
       </c>
       <c r="E328" s="4"/>
@@ -9770,18 +9770,22 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>M2601170002</t>
+          <t>M2509260013</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>王閔弘</t>
-        </is>
-      </c>
-      <c r="C329" s="4"/>
+          <t>王舜平</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
+        </is>
+      </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>0931056292</t>
+          <t>0917215021</t>
         </is>
       </c>
       <c r="E329" s="4"/>
@@ -9799,18 +9803,18 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>M2511230003</t>
+          <t>M2601170002</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>王靜芸</t>
+          <t>王閔弘</t>
         </is>
       </c>
       <c r="C330" s="4"/>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>0970224238</t>
+          <t>0931056292</t>
         </is>
       </c>
       <c r="E330" s="4"/>
@@ -9828,18 +9832,18 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>M2510040009</t>
+          <t>M2511230003</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>王駿宏</t>
+          <t>王靜芸</t>
         </is>
       </c>
       <c r="C331" s="4"/>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>0919336854</t>
+          <t>0970224238</t>
         </is>
       </c>
       <c r="E331" s="4"/>
@@ -9857,18 +9861,18 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>M2601010001</t>
+          <t>M2510040009</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>甘玨瑋</t>
+          <t>王駿宏</t>
         </is>
       </c>
       <c r="C332" s="4"/>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>0987214102</t>
+          <t>0919336854</t>
         </is>
       </c>
       <c r="E332" s="4"/>
@@ -9886,22 +9890,18 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>M2510290002</t>
+          <t>M2601010001</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>生生</t>
-        </is>
-      </c>
-      <c r="C333" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街427號</t>
-        </is>
-      </c>
+          <t>甘玨瑋</t>
+        </is>
+      </c>
+      <c r="C333" s="4"/>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>0919001722</t>
+          <t>0987214102</t>
         </is>
       </c>
       <c r="E333" s="4"/>
@@ -9919,18 +9919,22 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>M2509260050</t>
+          <t>M2510290002</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>甩爪</t>
-        </is>
-      </c>
-      <c r="C334" s="4"/>
+          <t>生生</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街427號</t>
+        </is>
+      </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>0970754804</t>
+          <t>0919001722</t>
         </is>
       </c>
       <c r="E334" s="4"/>
@@ -9948,18 +9952,18 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>M2509270005</t>
+          <t>M2509260050</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>甯偉</t>
+          <t>甩爪</t>
         </is>
       </c>
       <c r="C335" s="4"/>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>0955617290</t>
+          <t>0970754804</t>
         </is>
       </c>
       <c r="E335" s="4"/>
@@ -9977,18 +9981,18 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>M2510240007</t>
+          <t>M2509270005</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>盧其辰</t>
+          <t>甯偉</t>
         </is>
       </c>
       <c r="C336" s="4"/>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>0982119779</t>
+          <t>0955617290</t>
         </is>
       </c>
       <c r="E336" s="4"/>
@@ -10006,20 +10010,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>V0013</t>
+          <t>M2510240007</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>真大帥</t>
+          <t>盧其辰</t>
         </is>
       </c>
       <c r="C337" s="4"/>
-      <c r="D337" s="4"/>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>0982119779</t>
+        </is>
+      </c>
       <c r="E337" s="4"/>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -10031,24 +10039,20 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>M2510310002</t>
+          <t>V0013</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>祁麟</t>
+          <t>真大帥</t>
         </is>
       </c>
       <c r="C338" s="4"/>
-      <c r="D338" s="4" t="inlineStr">
-        <is>
-          <t>0982883101</t>
-        </is>
-      </c>
+      <c r="D338" s="4"/>
       <c r="E338" s="4"/>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -10060,18 +10064,18 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>M2602130001</t>
+          <t>M2510310002</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>祐</t>
+          <t>祁麟</t>
         </is>
       </c>
       <c r="C339" s="4"/>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>0983407890</t>
+          <t>0982883101</t>
         </is>
       </c>
       <c r="E339" s="4"/>
@@ -10089,18 +10093,18 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>M2510050001</t>
+          <t>M2602130001</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>程sir/Ashbur</t>
+          <t>祐</t>
         </is>
       </c>
       <c r="C340" s="4"/>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>0963612395</t>
+          <t>0983407890</t>
         </is>
       </c>
       <c r="E340" s="4"/>
@@ -10118,18 +10122,18 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>M2510300001</t>
+          <t>M2510050001</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>程品勝</t>
+          <t>程sir/Ashbur</t>
         </is>
       </c>
       <c r="C341" s="4"/>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>0913780727</t>
+          <t>0963612395</t>
         </is>
       </c>
       <c r="E341" s="4"/>
@@ -10147,18 +10151,18 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>M2601270002</t>
+          <t>M2510300001</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>程建智</t>
+          <t>程品勝</t>
         </is>
       </c>
       <c r="C342" s="4"/>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>0988919027</t>
+          <t>0913780727</t>
         </is>
       </c>
       <c r="E342" s="4"/>
@@ -10176,18 +10180,18 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>M2603120004</t>
+          <t>M2601270002</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>程郁勛</t>
+          <t>程建智</t>
         </is>
       </c>
       <c r="C343" s="4"/>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>0955671407</t>
+          <t>0988919027</t>
         </is>
       </c>
       <c r="E343" s="4"/>
@@ -10205,22 +10209,18 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>M2509160001</t>
+          <t>M2603120004</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>穆莉茹</t>
-        </is>
-      </c>
-      <c r="C344" s="4" t="inlineStr">
-        <is>
-          <t>桃園平鎮區上海路169號</t>
-        </is>
-      </c>
+          <t>程郁勛</t>
+        </is>
+      </c>
+      <c r="C344" s="4"/>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>0955777312</t>
+          <t>0955671407</t>
         </is>
       </c>
       <c r="E344" s="4"/>
@@ -10238,18 +10238,22 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>M2511160003</t>
+          <t>M2509160001</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>簡士傑</t>
-        </is>
-      </c>
-      <c r="C345" s="4"/>
+          <t>穆莉茹</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>桃園平鎮區上海路169號</t>
+        </is>
+      </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>0963817398</t>
+          <t>0955777312</t>
         </is>
       </c>
       <c r="E345" s="4"/>
@@ -10267,18 +10271,18 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>M2509300013</t>
+          <t>M2511160003</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>簡子偉</t>
+          <t>簡士傑</t>
         </is>
       </c>
       <c r="C346" s="4"/>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>0955462926</t>
+          <t>0963817398</t>
         </is>
       </c>
       <c r="E346" s="4"/>
@@ -10296,18 +10300,18 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>M2602280002</t>
+          <t>M2509300013</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>簡子洋</t>
+          <t>簡子偉</t>
         </is>
       </c>
       <c r="C347" s="4"/>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>0933921933</t>
+          <t>0955462926</t>
         </is>
       </c>
       <c r="E347" s="4"/>
@@ -10325,18 +10329,18 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>M2510040003</t>
+          <t>M2602280002</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>簡小琪</t>
+          <t>簡子洋</t>
         </is>
       </c>
       <c r="C348" s="4"/>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>0930033829</t>
+          <t>0933921933</t>
         </is>
       </c>
       <c r="E348" s="4"/>
@@ -10354,18 +10358,18 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>M2510260002</t>
+          <t>M2510040003</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>簡揚城</t>
+          <t>簡小琪</t>
         </is>
       </c>
       <c r="C349" s="4"/>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>0913153353</t>
+          <t>0930033829</t>
         </is>
       </c>
       <c r="E349" s="4"/>
@@ -10383,18 +10387,18 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>M2509300001</t>
+          <t>M2510260002</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>簡瑋成</t>
+          <t>簡揚城</t>
         </is>
       </c>
       <c r="C350" s="4"/>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>0936389969</t>
+          <t>0913153353</t>
         </is>
       </c>
       <c r="E350" s="4"/>
@@ -10412,18 +10416,18 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>M2509290020</t>
+          <t>M2509300001</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>簡茂州</t>
+          <t>簡瑋成</t>
         </is>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>0985217379</t>
+          <t>0936389969</t>
         </is>
       </c>
       <c r="E351" s="4"/>
@@ -10441,18 +10445,18 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>M2512130001</t>
+          <t>M2509290020</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>紀彥銘</t>
+          <t>簡茂州</t>
         </is>
       </c>
       <c r="C352" s="4"/>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>0988752337</t>
+          <t>0985217379</t>
         </is>
       </c>
       <c r="E352" s="4"/>
@@ -10470,20 +10474,24 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>V0001</t>
+          <t>M2512130001</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>統有企業</t>
+          <t>紀彥銘</t>
         </is>
       </c>
       <c r="C353" s="4"/>
-      <c r="D353" s="4"/>
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>0988752337</t>
+        </is>
+      </c>
       <c r="E353" s="4"/>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -10495,24 +10503,20 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>M2509280008</t>
+          <t>V0001</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>維克斯</t>
+          <t>統有企業</t>
         </is>
       </c>
       <c r="C354" s="4"/>
-      <c r="D354" s="4" t="inlineStr">
-        <is>
-          <t>0917771787</t>
-        </is>
-      </c>
+      <c r="D354" s="4"/>
       <c r="E354" s="4"/>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -10524,18 +10528,18 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>M2510170002</t>
+          <t>M2509280008</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>練鎮宇</t>
+          <t>維克斯</t>
         </is>
       </c>
       <c r="C355" s="4"/>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>0952288706</t>
+          <t>0917771787</t>
         </is>
       </c>
       <c r="E355" s="4"/>
@@ -10553,18 +10557,18 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>M2602220003</t>
+          <t>M2510170002</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>羅丁一夫</t>
+          <t>練鎮宇</t>
         </is>
       </c>
       <c r="C356" s="4"/>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>0919339614</t>
+          <t>0952288706</t>
         </is>
       </c>
       <c r="E356" s="4"/>
@@ -10582,18 +10586,18 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>M2510180002</t>
+          <t>M2602220003</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>羅元隆</t>
+          <t>羅丁一夫</t>
         </is>
       </c>
       <c r="C357" s="4"/>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>0975866635</t>
+          <t>0919339614</t>
         </is>
       </c>
       <c r="E357" s="4"/>
@@ -10611,25 +10615,21 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>M2510090003</t>
+          <t>M2510180002</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>羅嘉銘</t>
+          <t>羅元隆</t>
         </is>
       </c>
       <c r="C358" s="4"/>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>0928093385</t>
-        </is>
-      </c>
-      <c r="E358" s="4" t="inlineStr">
-        <is>
-          <t>0985866052</t>
-        </is>
-      </c>
+          <t>0975866635</t>
+        </is>
+      </c>
+      <c r="E358" s="4"/>
       <c r="F358" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -10644,22 +10644,30 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>M2602240001</t>
+          <t>M2510090003</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>羅浩中</t>
+          <t>羅嘉銘</t>
         </is>
       </c>
       <c r="C359" s="4"/>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>0970905092</t>
-        </is>
-      </c>
-      <c r="E359" s="4"/>
-      <c r="F359" s="4"/>
+          <t>0928093385</t>
+        </is>
+      </c>
+      <c r="E359" s="4" t="inlineStr">
+        <is>
+          <t>0985866052</t>
+        </is>
+      </c>
+      <c r="F359" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G359" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -10669,26 +10677,22 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>M2511060003</t>
+          <t>M2602240001</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>翁名勳</t>
+          <t>羅浩中</t>
         </is>
       </c>
       <c r="C360" s="4"/>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>0955083317</t>
+          <t>0970905092</t>
         </is>
       </c>
       <c r="E360" s="4"/>
-      <c r="F360" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F360" s="4"/>
       <c r="G360" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -10698,18 +10702,18 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>M2509260057</t>
+          <t>M2511060003</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>翁國昌</t>
+          <t>翁名勳</t>
         </is>
       </c>
       <c r="C361" s="4"/>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>0918718772</t>
+          <t>0955083317</t>
         </is>
       </c>
       <c r="E361" s="4"/>
@@ -10727,22 +10731,18 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>M2511290001</t>
+          <t>M2509260057</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>翁國祥</t>
-        </is>
-      </c>
-      <c r="C362" s="4" t="inlineStr">
-        <is>
-          <t>新北新莊中信街65號1樓賣菜攤</t>
-        </is>
-      </c>
+          <t>翁國昌</t>
+        </is>
+      </c>
+      <c r="C362" s="4"/>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>0983900052</t>
+          <t>0918718772</t>
         </is>
       </c>
       <c r="E362" s="4"/>
@@ -10760,22 +10760,22 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>M2510010009</t>
+          <t>M2511290001</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩</t>
+          <t>翁國祥</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>未決定</t>
+          <t>新北新莊中信街65號1樓賣菜攤</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>0972757015</t>
+          <t>0983900052</t>
         </is>
       </c>
       <c r="E363" s="4"/>
@@ -10793,53 +10793,53 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
+          <t>M2510010009</t>
+        </is>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>翁敬恩</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr">
+        <is>
+          <t>未決定</t>
+        </is>
+      </c>
+      <c r="D364" s="4" t="inlineStr">
+        <is>
+          <t>0972757015</t>
+        </is>
+      </c>
+      <c r="E364" s="4"/>
+      <c r="F364" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G364" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="inlineStr">
+        <is>
           <t>M2510010009-4</t>
         </is>
       </c>
-      <c r="B364" s="4" t="inlineStr">
+      <c r="B365" s="4" t="inlineStr">
         <is>
           <t>翁敬恩-文山</t>
         </is>
       </c>
-      <c r="C364" s="6" t="inlineStr">
+      <c r="C365" s="6" t="inlineStr">
         <is>
           <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
 收件聯絡電話:0937462412</t>
         </is>
       </c>
-      <c r="D364" s="4" t="inlineStr">
-        <is>
-          <t>0972757015</t>
-        </is>
-      </c>
-      <c r="E364" s="4"/>
-      <c r="F364" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
-      <c r="G364" s="5" t="inlineStr">
-        <is>
-          <t>附件管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="4" t="inlineStr">
-        <is>
-          <t>M2510010009-2</t>
-        </is>
-      </c>
-      <c r="B365" s="4" t="inlineStr">
-        <is>
-          <t>翁敬恩-樂華</t>
-        </is>
-      </c>
-      <c r="C365" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
-        </is>
-      </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
           <t>0972757015</t>
@@ -10860,17 +10860,17 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-3</t>
+          <t>M2510010009-2</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-永和</t>
+          <t>翁敬恩-樂華</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
+          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -10893,22 +10893,22 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-1</t>
+          <t>M2510010009-3</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-饒河</t>
+          <t>翁敬恩-永和</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>0975953978</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E367" s="4"/>
@@ -10926,18 +10926,22 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>M2510140004</t>
+          <t>M2510010009-1</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>翁漢忠</t>
-        </is>
-      </c>
-      <c r="C368" s="4"/>
+          <t>翁敬恩-饒河</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+        </is>
+      </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>0916150750</t>
+          <t>0975953978</t>
         </is>
       </c>
       <c r="E368" s="4"/>
@@ -10955,18 +10959,18 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>M2509260037</t>
+          <t>M2510140004</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>翁翌禎</t>
+          <t>翁漢忠</t>
         </is>
       </c>
       <c r="C369" s="4"/>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>0902308293</t>
+          <t>0916150750</t>
         </is>
       </c>
       <c r="E369" s="4"/>
@@ -10984,18 +10988,18 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>M2509280002</t>
+          <t>M2509260037</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>聶大中</t>
+          <t>翁翌禎</t>
         </is>
       </c>
       <c r="C370" s="4"/>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>0955059148</t>
+          <t>0902308293</t>
         </is>
       </c>
       <c r="E370" s="4"/>
@@ -11013,18 +11017,18 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>M2510220001</t>
+          <t>M2509280002</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>胡HU</t>
+          <t>聶大中</t>
         </is>
       </c>
       <c r="C371" s="4"/>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>0988603554</t>
+          <t>0955059148</t>
         </is>
       </c>
       <c r="E371" s="4"/>
@@ -11042,18 +11046,18 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>M2510100011</t>
+          <t>M2510220001</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>胡凱傑</t>
+          <t>胡HU</t>
         </is>
       </c>
       <c r="C372" s="4"/>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>0955888840</t>
+          <t>0988603554</t>
         </is>
       </c>
       <c r="E372" s="4"/>
@@ -11071,18 +11075,18 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>M2510090005</t>
+          <t>M2510100011</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>胡家榮</t>
+          <t>胡凱傑</t>
         </is>
       </c>
       <c r="C373" s="4"/>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>0933059025</t>
+          <t>0955888840</t>
         </is>
       </c>
       <c r="E373" s="4"/>
@@ -11100,18 +11104,18 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>M2511150001</t>
+          <t>M2510090005</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>胡家銘</t>
+          <t>胡家榮</t>
         </is>
       </c>
       <c r="C374" s="4"/>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>0986362263</t>
+          <t>0933059025</t>
         </is>
       </c>
       <c r="E374" s="4"/>
@@ -11129,18 +11133,18 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>M2511290003</t>
+          <t>M2511150001</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>胡峻強</t>
+          <t>胡家銘</t>
         </is>
       </c>
       <c r="C375" s="4"/>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>0953088041</t>
+          <t>0986362263</t>
         </is>
       </c>
       <c r="E375" s="4"/>
@@ -11158,18 +11162,18 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>M2603010001</t>
+          <t>M2511290003</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>胡辰煜</t>
+          <t>胡峻強</t>
         </is>
       </c>
       <c r="C376" s="4"/>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>0963903685</t>
+          <t>0953088041</t>
         </is>
       </c>
       <c r="E376" s="4"/>
@@ -11187,18 +11191,18 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>M2510040002</t>
+          <t>M2603010001</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>胡辰軒</t>
+          <t>胡辰煜</t>
         </is>
       </c>
       <c r="C377" s="4"/>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>0972094622</t>
+          <t>0963903685</t>
         </is>
       </c>
       <c r="E377" s="4"/>
@@ -11216,18 +11220,18 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>M2602280001</t>
+          <t>M2510040002</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>胡閎翔</t>
+          <t>胡辰軒</t>
         </is>
       </c>
       <c r="C378" s="4"/>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>0970556309</t>
+          <t>0972094622</t>
         </is>
       </c>
       <c r="E378" s="4"/>
@@ -11245,18 +11249,18 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>M2511290002</t>
+          <t>M2602280001</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>舒老闆</t>
+          <t>胡閎翔</t>
         </is>
       </c>
       <c r="C379" s="4"/>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>0979788818</t>
+          <t>0970556309</t>
         </is>
       </c>
       <c r="E379" s="4"/>
@@ -11274,19 +11278,15 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-2</t>
+          <t>M2511290002</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣</t>
-        </is>
-      </c>
-      <c r="C380" s="4" t="inlineStr">
-        <is>
-          <t>台北市松山區八德路三段12巷51弄46號</t>
-        </is>
-      </c>
+          <t>舒老闆</t>
+        </is>
+      </c>
+      <c r="C380" s="4"/>
       <c r="D380" s="4" t="inlineStr">
         <is>
           <t>0979788818</t>
@@ -11307,17 +11307,17 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-1</t>
+          <t>M2511290002-2</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧</t>
+          <t>舒老闆-夾鬥陣</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+          <t>台北市松山區八德路三段12巷51弄46號</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -11340,18 +11340,22 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>M2510140002</t>
+          <t>M2511290002-1</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>范姜敏中</t>
-        </is>
-      </c>
-      <c r="C382" s="4"/>
+          <t>舒老闆-寧寧</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+        </is>
+      </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>0937464692</t>
+          <t>0979788818</t>
         </is>
       </c>
       <c r="E382" s="4"/>
@@ -11369,18 +11373,18 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>M2510140003</t>
+          <t>M2510140002</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>范姜群成</t>
+          <t>范姜敏中</t>
         </is>
       </c>
       <c r="C383" s="4"/>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>0920565234</t>
+          <t>0937464692</t>
         </is>
       </c>
       <c r="E383" s="4"/>
@@ -11398,22 +11402,18 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>M2511300003</t>
+          <t>M2510140003</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>莊正當</t>
-        </is>
-      </c>
-      <c r="C384" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區建安街27號3樓</t>
-        </is>
-      </c>
+          <t>范姜群成</t>
+        </is>
+      </c>
+      <c r="C384" s="4"/>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>0983337218</t>
+          <t>0920565234</t>
         </is>
       </c>
       <c r="E384" s="4"/>
@@ -11431,22 +11431,22 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>M2510270004</t>
+          <t>M2511300003</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>莊淑玲</t>
+          <t>莊正當</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>新北市新莊區五工三路78巷36號</t>
+          <t>新北市新莊區建安街27號3樓</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>0922277383</t>
+          <t>0983337218</t>
         </is>
       </c>
       <c r="E385" s="4"/>
@@ -11464,18 +11464,22 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>M2510190002</t>
+          <t>M2510270004</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>莊耿華</t>
-        </is>
-      </c>
-      <c r="C386" s="4"/>
+          <t>莊淑玲</t>
+        </is>
+      </c>
+      <c r="C386" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工三路78巷36號</t>
+        </is>
+      </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>0938600334</t>
+          <t>0922277383</t>
         </is>
       </c>
       <c r="E386" s="4"/>
@@ -11493,18 +11497,18 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>M2509260005</t>
+          <t>M2510190002</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>莊莊</t>
+          <t>莊耿華</t>
         </is>
       </c>
       <c r="C387" s="4"/>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>0955985557</t>
+          <t>0938600334</t>
         </is>
       </c>
       <c r="E387" s="4"/>
@@ -11522,18 +11526,18 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>M2510100007</t>
+          <t>M2509260005</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>莊閔丞</t>
+          <t>莊莊</t>
         </is>
       </c>
       <c r="C388" s="4"/>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>0963320370</t>
+          <t>0955985557</t>
         </is>
       </c>
       <c r="E388" s="4"/>
@@ -11551,22 +11555,26 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>M2602240002</t>
+          <t>M2510100007</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>萬宗霖</t>
+          <t>莊閔丞</t>
         </is>
       </c>
       <c r="C389" s="4"/>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>0977082365</t>
+          <t>0963320370</t>
         </is>
       </c>
       <c r="E389" s="4"/>
-      <c r="F389" s="4"/>
+      <c r="F389" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G389" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -11576,26 +11584,22 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>M2510160001</t>
+          <t>M2602240002</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>葉力瑋</t>
+          <t>萬宗霖</t>
         </is>
       </c>
       <c r="C390" s="4"/>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>0979611911</t>
+          <t>0977082365</t>
         </is>
       </c>
       <c r="E390" s="4"/>
-      <c r="F390" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F390" s="4"/>
       <c r="G390" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -11605,18 +11609,18 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>M2510030002</t>
+          <t>M2510160001</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>葉家睿</t>
+          <t>葉力瑋</t>
         </is>
       </c>
       <c r="C391" s="4"/>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>0928112227</t>
+          <t>0979611911</t>
         </is>
       </c>
       <c r="E391" s="4"/>
@@ -11634,18 +11638,18 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2511050003</t>
+          <t>M2510030002</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>葉庭綸</t>
+          <t>葉家睿</t>
         </is>
       </c>
       <c r="C392" s="4"/>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>0966638685</t>
+          <t>0928112227</t>
         </is>
       </c>
       <c r="E392" s="4"/>
@@ -11663,18 +11667,18 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>M2510180001</t>
+          <t>M2511050003</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>葉建財</t>
+          <t>葉庭綸</t>
         </is>
       </c>
       <c r="C393" s="4"/>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>0989713349</t>
+          <t>0966638685</t>
         </is>
       </c>
       <c r="E393" s="4"/>
@@ -11692,18 +11696,18 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>M2510150001</t>
+          <t>M2510180001</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>葉彥均</t>
+          <t>葉建財</t>
         </is>
       </c>
       <c r="C394" s="4"/>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>0921436111</t>
+          <t>0989713349</t>
         </is>
       </c>
       <c r="E394" s="4"/>
@@ -11721,18 +11725,18 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>M2601220001</t>
+          <t>M2510150001</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>葉方奕</t>
+          <t>葉彥均</t>
         </is>
       </c>
       <c r="C395" s="4"/>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>0918386488</t>
+          <t>0921436111</t>
         </is>
       </c>
       <c r="E395" s="4"/>
@@ -11750,18 +11754,18 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>M2510260005</t>
+          <t>M2601220001</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>葉祈賢</t>
+          <t>葉方奕</t>
         </is>
       </c>
       <c r="C396" s="4"/>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>0955313212</t>
+          <t>0918386488</t>
         </is>
       </c>
       <c r="E396" s="4"/>
@@ -11779,18 +11783,18 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>M2509290012</t>
+          <t>M2510260005</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>葉維霆</t>
+          <t>葉祈賢</t>
         </is>
       </c>
       <c r="C397" s="4"/>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>0905120835</t>
+          <t>0955313212</t>
         </is>
       </c>
       <c r="E397" s="4"/>
@@ -11808,18 +11812,18 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>M2603050001</t>
+          <t>M2509290012</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>蔡仲凱</t>
+          <t>葉維霆</t>
         </is>
       </c>
       <c r="C398" s="4"/>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>0910733748</t>
+          <t>0905120835</t>
         </is>
       </c>
       <c r="E398" s="4"/>
@@ -11837,18 +11841,18 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>M2511080009</t>
+          <t>M2603050001</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>蔡伯鼎</t>
+          <t>蔡仲凱</t>
         </is>
       </c>
       <c r="C399" s="4"/>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>0933842593</t>
+          <t>0910733748</t>
         </is>
       </c>
       <c r="E399" s="4"/>
@@ -11866,18 +11870,18 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>M2512100001</t>
+          <t>M2511080009</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>蔡其騰</t>
+          <t>蔡伯鼎</t>
         </is>
       </c>
       <c r="C400" s="4"/>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>0988556732</t>
+          <t>0933842593</t>
         </is>
       </c>
       <c r="E400" s="4"/>
@@ -11895,22 +11899,18 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>M2603220001</t>
+          <t>M2512100001</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>蔡嘉章</t>
-        </is>
-      </c>
-      <c r="C401" s="4" t="inlineStr">
-        <is>
-          <t>樹林區太平路150巷8號娃娃機</t>
-        </is>
-      </c>
+          <t>蔡其騰</t>
+        </is>
+      </c>
+      <c r="C401" s="4"/>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>0973658657</t>
+          <t>0988556732</t>
         </is>
       </c>
       <c r="E401" s="4"/>
@@ -11928,18 +11928,22 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>M2509280001</t>
+          <t>M2603220001</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>蔡康志</t>
-        </is>
-      </c>
-      <c r="C402" s="4"/>
+          <t>蔡嘉章</t>
+        </is>
+      </c>
+      <c r="C402" s="4" t="inlineStr">
+        <is>
+          <t>樹林區太平路150巷8號娃娃機</t>
+        </is>
+      </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>0933942089</t>
+          <t>0973658657</t>
         </is>
       </c>
       <c r="E402" s="4"/>
@@ -11957,18 +11961,18 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>M2509260052</t>
+          <t>M2509280001</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>蔡志海</t>
+          <t>蔡康志</t>
         </is>
       </c>
       <c r="C403" s="4"/>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>0926616521</t>
+          <t>0933942089</t>
         </is>
       </c>
       <c r="E403" s="4"/>
@@ -11986,18 +11990,18 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>M2602120003</t>
+          <t>M2509260052</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>蔡承勳</t>
+          <t>蔡志海</t>
         </is>
       </c>
       <c r="C404" s="4"/>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>0979975919</t>
+          <t>0926616521</t>
         </is>
       </c>
       <c r="E404" s="4"/>
@@ -12015,18 +12019,18 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>M2509290002</t>
+          <t>M2602120003</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>蔡振元</t>
+          <t>蔡承勳</t>
         </is>
       </c>
       <c r="C405" s="4"/>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>0908590858</t>
+          <t>0979975919</t>
         </is>
       </c>
       <c r="E405" s="4"/>
@@ -12044,18 +12048,18 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>M2601090001</t>
+          <t>M2509290002</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>蔡昌翔</t>
+          <t>蔡振元</t>
         </is>
       </c>
       <c r="C406" s="4"/>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>0973324888</t>
+          <t>0908590858</t>
         </is>
       </c>
       <c r="E406" s="4"/>
@@ -12073,22 +12077,18 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>M2509260011</t>
+          <t>M2601090001</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>蔡智全</t>
-        </is>
-      </c>
-      <c r="C407" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區雙園街110號1樓</t>
-        </is>
-      </c>
+          <t>蔡昌翔</t>
+        </is>
+      </c>
+      <c r="C407" s="4"/>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>0930167280</t>
+          <t>0973324888</t>
         </is>
       </c>
       <c r="E407" s="4"/>
@@ -12106,22 +12106,22 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>M2509260049</t>
+          <t>M2509260011</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>蔡瀚霆</t>
+          <t>蔡智全</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區保平路207號</t>
+          <t>台北市萬華區雙園街110號1樓</t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>0932014776</t>
+          <t>0930167280</t>
         </is>
       </c>
       <c r="E408" s="4"/>
@@ -12139,18 +12139,22 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>M2510010007</t>
+          <t>M2509260049</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>蔡秉橋</t>
-        </is>
-      </c>
-      <c r="C409" s="4"/>
+          <t>蔡瀚霆</t>
+        </is>
+      </c>
+      <c r="C409" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區保平路207號</t>
+        </is>
+      </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>0987000184</t>
+          <t>0932014776</t>
         </is>
       </c>
       <c r="E409" s="4"/>
@@ -12168,18 +12172,18 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>M2509270009</t>
+          <t>M2510010007</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>蔡育昇</t>
+          <t>蔡秉橋</t>
         </is>
       </c>
       <c r="C410" s="4"/>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>0918058903</t>
+          <t>0987000184</t>
         </is>
       </c>
       <c r="E410" s="4"/>
@@ -12197,18 +12201,18 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>M2603180001</t>
+          <t>M2509270009</t>
         </is>
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>蔡貞瑜</t>
+          <t>蔡育昇</t>
         </is>
       </c>
       <c r="C411" s="4"/>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>0917372131</t>
+          <t>0918058903</t>
         </is>
       </c>
       <c r="E411" s="4"/>
@@ -12226,18 +12230,18 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>M2510070001</t>
+          <t>M2603180001</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>蔡辰旻</t>
+          <t>蔡貞瑜</t>
         </is>
       </c>
       <c r="C412" s="4"/>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>0982621245</t>
+          <t>0917372131</t>
         </is>
       </c>
       <c r="E412" s="4"/>
@@ -12255,7 +12259,7 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>M2602010003</t>
+          <t>M2510070001</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
@@ -12266,7 +12270,7 @@
       <c r="C413" s="4"/>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>0903162818</t>
+          <t>0982621245</t>
         </is>
       </c>
       <c r="E413" s="4"/>
@@ -12284,18 +12288,18 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>M2511270001</t>
+          <t>M2602010003</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>蔡進盛</t>
+          <t>蔡辰旻</t>
         </is>
       </c>
       <c r="C414" s="4"/>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>0989387966</t>
+          <t>0903162818</t>
         </is>
       </c>
       <c r="E414" s="4"/>
@@ -12313,18 +12317,18 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>M2511030001</t>
+          <t>M2511270001</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>蔡鳳來</t>
+          <t>蔡進盛</t>
         </is>
       </c>
       <c r="C415" s="4"/>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>0963550931</t>
+          <t>0989387966</t>
         </is>
       </c>
       <c r="E415" s="4"/>
@@ -12342,18 +12346,18 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>M2509270016</t>
+          <t>M2511030001</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>蕭仲安</t>
+          <t>蔡鳳來</t>
         </is>
       </c>
       <c r="C416" s="4"/>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>0930601899</t>
+          <t>0963550931</t>
         </is>
       </c>
       <c r="E416" s="4"/>
@@ -12371,18 +12375,18 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>M2509270017</t>
+          <t>M2509270016</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>蕭又瑋</t>
+          <t>蕭仲安</t>
         </is>
       </c>
       <c r="C417" s="4"/>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>0922675798</t>
+          <t>0930601899</t>
         </is>
       </c>
       <c r="E417" s="4"/>
@@ -12400,18 +12404,18 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>M2509280009</t>
+          <t>M2509270017</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>蕭宇傑</t>
+          <t>蕭又瑋</t>
         </is>
       </c>
       <c r="C418" s="4"/>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>0989977822</t>
+          <t>0922675798</t>
         </is>
       </c>
       <c r="E418" s="4"/>
@@ -12429,18 +12433,18 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>M2510190006</t>
+          <t>M2509280009</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>蕭毓</t>
+          <t>蕭宇傑</t>
         </is>
       </c>
       <c r="C419" s="4"/>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>0975199046</t>
+          <t>0989977822</t>
         </is>
       </c>
       <c r="E419" s="4"/>
@@ -12458,22 +12462,18 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>M2510090006</t>
+          <t>M2510190006</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>蕭燁鴻</t>
-        </is>
-      </c>
-      <c r="C420" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區金龍路183號1樓</t>
-        </is>
-      </c>
+          <t>蕭毓</t>
+        </is>
+      </c>
+      <c r="C420" s="4"/>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>0917882269</t>
+          <t>0975199046</t>
         </is>
       </c>
       <c r="E420" s="4"/>
@@ -12491,18 +12491,22 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>M2510160008</t>
+          <t>M2510090006</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>蕭韻文</t>
-        </is>
-      </c>
-      <c r="C421" s="4"/>
+          <t>蕭燁鴻</t>
+        </is>
+      </c>
+      <c r="C421" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區金龍路183號1樓</t>
+        </is>
+      </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>0911297473</t>
+          <t>0917882269</t>
         </is>
       </c>
       <c r="E421" s="4"/>
@@ -12520,18 +12524,18 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>M2509300014</t>
+          <t>M2510160008</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>藍駿偉</t>
+          <t>蕭韻文</t>
         </is>
       </c>
       <c r="C422" s="4"/>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>0936152586</t>
+          <t>0911297473</t>
         </is>
       </c>
       <c r="E422" s="4"/>
@@ -12549,18 +12553,18 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>M2511080007</t>
+          <t>M2509300014</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>蘇嘉蓉</t>
+          <t>藍駿偉</t>
         </is>
       </c>
       <c r="C423" s="4"/>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>0937074336</t>
+          <t>0936152586</t>
         </is>
       </c>
       <c r="E423" s="4"/>
@@ -12578,18 +12582,18 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>M2511060002</t>
+          <t>M2511080007</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>蘇國貿</t>
+          <t>蘇嘉蓉</t>
         </is>
       </c>
       <c r="C424" s="4"/>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>0922250285</t>
+          <t>0937074336</t>
         </is>
       </c>
       <c r="E424" s="4"/>
@@ -12607,18 +12611,18 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>M2511280004</t>
+          <t>M2511060002</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>蘇家明</t>
+          <t>蘇國貿</t>
         </is>
       </c>
       <c r="C425" s="4"/>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>0916836765</t>
+          <t>0922250285</t>
         </is>
       </c>
       <c r="E425" s="4"/>
@@ -12636,18 +12640,18 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>M2510300002</t>
+          <t>M2511280004</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>蘇小好</t>
+          <t>蘇家明</t>
         </is>
       </c>
       <c r="C426" s="4"/>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>0981870981</t>
+          <t>0916836765</t>
         </is>
       </c>
       <c r="E426" s="4"/>
@@ -12665,18 +12669,18 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>M2509260021</t>
+          <t>M2510300002</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>蘇彥彰</t>
+          <t>蘇小好</t>
         </is>
       </c>
       <c r="C427" s="4"/>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>0983060026</t>
+          <t>0981870981</t>
         </is>
       </c>
       <c r="E427" s="4"/>
@@ -12694,22 +12698,18 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>M2510240001</t>
+          <t>M2509260021</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>蘇志勇</t>
-        </is>
-      </c>
-      <c r="C428" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
-        </is>
-      </c>
+          <t>蘇彥彰</t>
+        </is>
+      </c>
+      <c r="C428" s="4"/>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>0910051586</t>
+          <t>0983060026</t>
         </is>
       </c>
       <c r="E428" s="4"/>
@@ -12727,18 +12727,22 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>M2602150002</t>
+          <t>M2510240001</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>蘇昱銘</t>
-        </is>
-      </c>
-      <c r="C429" s="4"/>
+          <t>蘇志勇</t>
+        </is>
+      </c>
+      <c r="C429" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
+        </is>
+      </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>0916324119</t>
+          <t>0910051586</t>
         </is>
       </c>
       <c r="E429" s="4"/>
@@ -12756,18 +12760,18 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>M2510050003</t>
+          <t>M2602150002</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>蘇睿慶</t>
+          <t>蘇昱銘</t>
         </is>
       </c>
       <c r="C430" s="4"/>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>0937766339</t>
+          <t>0916324119</t>
         </is>
       </c>
       <c r="E430" s="4"/>
@@ -12785,18 +12789,18 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>M2601180001</t>
+          <t>M2510050003</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>蠟筆</t>
+          <t>蘇睿慶</t>
         </is>
       </c>
       <c r="C431" s="4"/>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>0976321321</t>
+          <t>0937766339</t>
         </is>
       </c>
       <c r="E431" s="4"/>
@@ -12814,18 +12818,18 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>M2512160002</t>
+          <t>M2601180001</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>褚朕誠</t>
+          <t>蠟筆</t>
         </is>
       </c>
       <c r="C432" s="4"/>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>0972217495</t>
+          <t>0976321321</t>
         </is>
       </c>
       <c r="E432" s="4"/>
@@ -12843,18 +12847,18 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>M2512200002</t>
+          <t>M2512160002</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>褚銘漢</t>
+          <t>褚朕誠</t>
         </is>
       </c>
       <c r="C433" s="4"/>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>0925886065</t>
+          <t>0972217495</t>
         </is>
       </c>
       <c r="E433" s="4"/>
@@ -12872,18 +12876,18 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>M2512170002</t>
+          <t>M2512200002</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>許俊鴻</t>
+          <t>褚銘漢</t>
         </is>
       </c>
       <c r="C434" s="4"/>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>0973630391</t>
+          <t>0925886065</t>
         </is>
       </c>
       <c r="E434" s="4"/>
@@ -12901,18 +12905,18 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>M2510050013</t>
+          <t>M2512170002</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>許凱傑</t>
+          <t>許俊鴻</t>
         </is>
       </c>
       <c r="C435" s="4"/>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>0955306971</t>
+          <t>0973630391</t>
         </is>
       </c>
       <c r="E435" s="4"/>
@@ -12930,18 +12934,18 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>M2511110001</t>
+          <t>M2510050013</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>許哲豪</t>
+          <t>許凱傑</t>
         </is>
       </c>
       <c r="C436" s="4"/>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>0985191149</t>
+          <t>0955306971</t>
         </is>
       </c>
       <c r="E436" s="4"/>
@@ -12959,18 +12963,18 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>M2602030001</t>
+          <t>M2511110001</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>許士彥</t>
+          <t>許哲豪</t>
         </is>
       </c>
       <c r="C437" s="4"/>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>0913558692</t>
+          <t>0985191149</t>
         </is>
       </c>
       <c r="E437" s="4"/>
@@ -12988,18 +12992,18 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>M2509290018</t>
+          <t>M2602030001</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>許天寶</t>
+          <t>許士彥</t>
         </is>
       </c>
       <c r="C438" s="4"/>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>0936088850</t>
+          <t>0913558692</t>
         </is>
       </c>
       <c r="E438" s="4"/>
@@ -13017,18 +13021,18 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>M2510160005</t>
+          <t>M2509290018</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>許宥蓁</t>
+          <t>許天寶</t>
         </is>
       </c>
       <c r="C439" s="4"/>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>0938473255</t>
+          <t>0936088850</t>
         </is>
       </c>
       <c r="E439" s="4"/>
@@ -13046,18 +13050,18 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>M2512020001</t>
+          <t>M2510160005</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>許家豪</t>
+          <t>許宥蓁</t>
         </is>
       </c>
       <c r="C440" s="4"/>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>0983215242</t>
+          <t>0938473255</t>
         </is>
       </c>
       <c r="E440" s="4"/>
@@ -13075,18 +13079,18 @@
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>M2510110007</t>
+          <t>M2512020001</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>許峻銓</t>
+          <t>許家豪</t>
         </is>
       </c>
       <c r="C441" s="4"/>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>0979770033</t>
+          <t>0983215242</t>
         </is>
       </c>
       <c r="E441" s="4"/>
@@ -13104,18 +13108,18 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>M2511260001</t>
+          <t>M2510110007</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>許志帆</t>
+          <t>許峻銓</t>
         </is>
       </c>
       <c r="C442" s="4"/>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>0936639358</t>
+          <t>0979770033</t>
         </is>
       </c>
       <c r="E442" s="4"/>
@@ -13133,18 +13137,18 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>M2510310001</t>
+          <t>M2511260001</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>許志豪</t>
+          <t>許志帆</t>
         </is>
       </c>
       <c r="C443" s="4"/>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>0971080606</t>
+          <t>0936639358</t>
         </is>
       </c>
       <c r="E443" s="4"/>
@@ -13162,18 +13166,18 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>M2601040001</t>
+          <t>M2510310001</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>許惠笙</t>
+          <t>許志豪</t>
         </is>
       </c>
       <c r="C444" s="4"/>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>0987890463</t>
+          <t>0971080606</t>
         </is>
       </c>
       <c r="E444" s="4"/>
@@ -13191,18 +13195,18 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>M2603080002</t>
+          <t>M2601040001</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>許汶瑋</t>
+          <t>許惠笙</t>
         </is>
       </c>
       <c r="C445" s="4"/>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>0988166792</t>
+          <t>0987890463</t>
         </is>
       </c>
       <c r="E445" s="4"/>
@@ -13220,22 +13224,18 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>M2509140001</t>
+          <t>M2603080002</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>許煥杰</t>
-        </is>
-      </c>
-      <c r="C446" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區藝文二街88號8樓</t>
-        </is>
-      </c>
+          <t>許汶瑋</t>
+        </is>
+      </c>
+      <c r="C446" s="4"/>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>0913785888</t>
+          <t>0988166792</t>
         </is>
       </c>
       <c r="E446" s="4"/>
@@ -13253,18 +13253,22 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>M2510010001</t>
+          <t>M2509140001</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>許硯棠</t>
-        </is>
-      </c>
-      <c r="C447" s="4"/>
+          <t>許煥杰</t>
+        </is>
+      </c>
+      <c r="C447" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區藝文二街88號8樓</t>
+        </is>
+      </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>0983238652</t>
+          <t>0913785888</t>
         </is>
       </c>
       <c r="E447" s="4"/>
@@ -13282,18 +13286,18 @@
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>M2509270001</t>
+          <t>M2510010001</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>許竣榤</t>
+          <t>許硯棠</t>
         </is>
       </c>
       <c r="C448" s="4"/>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>0955598097</t>
+          <t>0983238652</t>
         </is>
       </c>
       <c r="E448" s="4"/>
@@ -13311,18 +13315,18 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>M2510240002</t>
+          <t>M2509270001</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>許芫睿</t>
+          <t>許竣榤</t>
         </is>
       </c>
       <c r="C449" s="4"/>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>0975057699</t>
+          <t>0955598097</t>
         </is>
       </c>
       <c r="E449" s="4"/>
@@ -13340,18 +13344,18 @@
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>M2509290013</t>
+          <t>M2510240002</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>許雅蓁</t>
+          <t>許芫睿</t>
         </is>
       </c>
       <c r="C450" s="4"/>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>0982339939</t>
+          <t>0975057699</t>
         </is>
       </c>
       <c r="E450" s="4"/>
@@ -13369,18 +13373,18 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>M2509260055</t>
+          <t>M2509290013</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>許靜蔆</t>
+          <t>許雅蓁</t>
         </is>
       </c>
       <c r="C451" s="4"/>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>0928060395</t>
+          <t>0982339939</t>
         </is>
       </c>
       <c r="E451" s="4"/>
@@ -13398,18 +13402,18 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>M2509260027</t>
+          <t>M2509260055</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>詹傑克</t>
+          <t>許靜蔆</t>
         </is>
       </c>
       <c r="C452" s="4"/>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>0968688080</t>
+          <t>0928060395</t>
         </is>
       </c>
       <c r="E452" s="4"/>
@@ -13427,18 +13431,18 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>M2602010004</t>
+          <t>M2509260027</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>詹凱翔</t>
+          <t>詹傑克</t>
         </is>
       </c>
       <c r="C453" s="4"/>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>0963496660</t>
+          <t>0968688080</t>
         </is>
       </c>
       <c r="E453" s="4"/>
@@ -13456,18 +13460,18 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>M2601270001</t>
+          <t>M2602010004</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>詹朝輝</t>
+          <t>詹凱翔</t>
         </is>
       </c>
       <c r="C454" s="4"/>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>0968490321</t>
+          <t>0963496660</t>
         </is>
       </c>
       <c r="E454" s="4"/>
@@ -13485,18 +13489,18 @@
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>M2601170004</t>
+          <t>M2601270001</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>詹煜騰</t>
+          <t>詹朝輝</t>
         </is>
       </c>
       <c r="C455" s="4"/>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>0939919344</t>
+          <t>0968490321</t>
         </is>
       </c>
       <c r="E455" s="4"/>
@@ -13514,18 +13518,18 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>M2509280003</t>
+          <t>M2601170004</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>詹皇</t>
+          <t>詹煜騰</t>
         </is>
       </c>
       <c r="C456" s="4"/>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>0916037915</t>
+          <t>0939919344</t>
         </is>
       </c>
       <c r="E456" s="4"/>
@@ -13543,18 +13547,18 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>M2510030001</t>
+          <t>M2509280003</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>詹皇宥</t>
+          <t>詹皇</t>
         </is>
       </c>
       <c r="C457" s="4"/>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>0919367080</t>
+          <t>0916037915</t>
         </is>
       </c>
       <c r="E457" s="4"/>
@@ -13572,22 +13576,18 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>M2509290016</t>
+          <t>M2510030001</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>詹育銘</t>
-        </is>
-      </c>
-      <c r="C458" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區撫順街25號1樓</t>
-        </is>
-      </c>
+          <t>詹皇宥</t>
+        </is>
+      </c>
+      <c r="C458" s="4"/>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>0926962322</t>
+          <t>0919367080</t>
         </is>
       </c>
       <c r="E458" s="4"/>
@@ -13605,22 +13605,22 @@
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>M2510270001</t>
+          <t>M2509290016</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>謝亞倫</t>
+          <t>詹育銘</t>
         </is>
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>新北市淡水區北投里北投子49-1號</t>
+          <t>台北市中山區撫順街25號1樓</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>0922409070</t>
+          <t>0926962322</t>
         </is>
       </c>
       <c r="E459" s="4"/>
@@ -13638,18 +13638,22 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>M2510040004</t>
+          <t>M2510270001</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>謝佳蓉</t>
-        </is>
-      </c>
-      <c r="C460" s="4"/>
+          <t>謝亞倫</t>
+        </is>
+      </c>
+      <c r="C460" s="4" t="inlineStr">
+        <is>
+          <t>新北市淡水區北投里北投子49-1號</t>
+        </is>
+      </c>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>0976958679</t>
+          <t>0922409070</t>
         </is>
       </c>
       <c r="E460" s="4"/>
@@ -13667,18 +13671,18 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>M2509300019</t>
+          <t>M2510040004</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>謝光明</t>
+          <t>謝佳蓉</t>
         </is>
       </c>
       <c r="C461" s="4"/>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>0983011754</t>
+          <t>0976958679</t>
         </is>
       </c>
       <c r="E461" s="4"/>
@@ -13696,22 +13700,18 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>M2512140002</t>
+          <t>M2509300019</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>謝孟辰</t>
-        </is>
-      </c>
-      <c r="C462" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
-        </is>
-      </c>
+          <t>謝光明</t>
+        </is>
+      </c>
+      <c r="C462" s="4"/>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>0953900309</t>
+          <t>0983011754</t>
         </is>
       </c>
       <c r="E462" s="4"/>
@@ -13729,18 +13729,22 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>M2509270007</t>
+          <t>M2512140002</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>謝建衫</t>
-        </is>
-      </c>
-      <c r="C463" s="4"/>
+          <t>謝孟辰</t>
+        </is>
+      </c>
+      <c r="C463" s="4" t="inlineStr">
+        <is>
+          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
+        </is>
+      </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>0918238090</t>
+          <t>0953900309</t>
         </is>
       </c>
       <c r="E463" s="4"/>
@@ -13758,18 +13762,18 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>M2510150005</t>
+          <t>M2509270007</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>謝文懷</t>
+          <t>謝建衫</t>
         </is>
       </c>
       <c r="C464" s="4"/>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>0989813659</t>
+          <t>0918238090</t>
         </is>
       </c>
       <c r="E464" s="4"/>
@@ -13787,18 +13791,18 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>M2510130004</t>
+          <t>M2510150005</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>謝桂仁</t>
+          <t>謝文懷</t>
         </is>
       </c>
       <c r="C465" s="4"/>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>0938357603</t>
+          <t>0989813659</t>
         </is>
       </c>
       <c r="E465" s="4"/>
@@ -13816,18 +13820,18 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>M2510050002</t>
+          <t>M2510130004</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>謝舒帆</t>
+          <t>謝桂仁</t>
         </is>
       </c>
       <c r="C466" s="4"/>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>0980699503</t>
+          <t>0938357603</t>
         </is>
       </c>
       <c r="E466" s="4"/>
@@ -13845,18 +13849,18 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>M2510040008</t>
+          <t>M2510050002</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>謝荌核</t>
+          <t>謝舒帆</t>
         </is>
       </c>
       <c r="C467" s="4"/>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>0988302836</t>
+          <t>0980699503</t>
         </is>
       </c>
       <c r="E467" s="4"/>
@@ -13874,18 +13878,18 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>M2511300006</t>
+          <t>M2510040008</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>謝詠全</t>
+          <t>謝荌核</t>
         </is>
       </c>
       <c r="C468" s="4"/>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>0977077044</t>
+          <t>0988302836</t>
         </is>
       </c>
       <c r="E468" s="4"/>
@@ -13903,18 +13907,18 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>M2603200003</t>
+          <t>M2511300006</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>譚淵修</t>
+          <t>謝詠全</t>
         </is>
       </c>
       <c r="C469" s="4"/>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>0910322500</t>
+          <t>0977077044</t>
         </is>
       </c>
       <c r="E469" s="4"/>
@@ -13932,18 +13936,18 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>M2510040011</t>
+          <t>M2603200003</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>賴先生</t>
+          <t>譚淵修</t>
         </is>
       </c>
       <c r="C470" s="4"/>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>0965351801</t>
+          <t>0910322500</t>
         </is>
       </c>
       <c r="E470" s="4"/>
@@ -13961,18 +13965,18 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>M2603080001</t>
+          <t>M2510040011</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>賴品豪</t>
+          <t>賴先生</t>
         </is>
       </c>
       <c r="C471" s="4"/>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>0981379127</t>
+          <t>0965351801</t>
         </is>
       </c>
       <c r="E471" s="4"/>
@@ -13990,18 +13994,18 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>M2511010005</t>
+          <t>M2603080001</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>賴彥安</t>
+          <t>賴品豪</t>
         </is>
       </c>
       <c r="C472" s="4"/>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>0913102110</t>
+          <t>0981379127</t>
         </is>
       </c>
       <c r="E472" s="4"/>
@@ -14019,22 +14023,18 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>M2603280001</t>
+          <t>M2511010005</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>賴柏舟</t>
-        </is>
-      </c>
-      <c r="C473" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股五福路11號</t>
-        </is>
-      </c>
+          <t>賴彥安</t>
+        </is>
+      </c>
+      <c r="C473" s="4"/>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>0979131818</t>
+          <t>0913102110</t>
         </is>
       </c>
       <c r="E473" s="4"/>
@@ -14052,18 +14052,22 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
-        </is>
-      </c>
-      <c r="C474" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C474" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E474" s="4"/>
@@ -14081,18 +14085,18 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
+          <t>賴珊珊</t>
         </is>
       </c>
       <c r="C475" s="4"/>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E475" s="4"/>
@@ -14110,22 +14114,18 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C476" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C476" s="4"/>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E476" s="4"/>
@@ -14143,22 +14143,22 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E477" s="4"/>
@@ -14176,22 +14176,22 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>趙云璟</t>
         </is>
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
         </is>
       </c>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E478" s="4"/>
@@ -14209,18 +14209,22 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C479" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C479" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E479" s="4"/>
@@ -14238,18 +14242,18 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C480" s="4"/>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E480" s="4"/>
@@ -14267,18 +14271,18 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C481" s="4"/>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0986258793</t>
         </is>
       </c>
       <c r="E481" s="4"/>
@@ -14296,20 +14300,24 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C482" s="4"/>
-      <c r="D482" s="4"/>
+      <c r="D482" s="4" t="inlineStr">
+        <is>
+          <t>0982484963</t>
+        </is>
+      </c>
       <c r="E482" s="4"/>
       <c r="F482" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G482" s="5" t="inlineStr">
@@ -14321,24 +14329,20 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C483" s="4"/>
-      <c r="D483" s="4" t="inlineStr">
-        <is>
-          <t>0981898339</t>
-        </is>
-      </c>
+      <c r="D483" s="4"/>
       <c r="E483" s="4"/>
       <c r="F483" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G483" s="5" t="inlineStr">
@@ -14350,18 +14354,18 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C484" s="4"/>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>0903921531</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E484" s="4"/>
@@ -14379,18 +14383,18 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C485" s="4"/>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E485" s="4"/>
@@ -14408,18 +14412,18 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C486" s="4"/>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E486" s="4"/>
@@ -14437,18 +14441,18 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C487" s="4"/>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E487" s="4"/>
@@ -14466,18 +14470,18 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱振為</t>
         </is>
       </c>
       <c r="C488" s="4"/>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E488" s="4"/>
@@ -14495,22 +14499,18 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C489" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱政傑</t>
+        </is>
+      </c>
+      <c r="C489" s="4"/>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E489" s="4"/>
@@ -14528,18 +14528,22 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
-        </is>
-      </c>
-      <c r="C490" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C490" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E490" s="4"/>
@@ -14557,18 +14561,18 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C491" s="4"/>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E491" s="4"/>
@@ -14586,18 +14590,18 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C492" s="4"/>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E492" s="4"/>
@@ -14615,7 +14619,7 @@
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B493" s="4" t="inlineStr">
@@ -14644,18 +14648,18 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B494" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C494" s="4"/>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E494" s="4"/>
@@ -14673,16 +14677,20 @@
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C495" s="4"/>
-      <c r="D495" s="4"/>
+      <c r="D495" s="4" t="inlineStr">
+        <is>
+          <t>0935329653</t>
+        </is>
+      </c>
       <c r="E495" s="4"/>
       <c r="F495" s="4" t="inlineStr">
         <is>
@@ -14698,20 +14706,16 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C496" s="4"/>
-      <c r="D496" s="4" t="inlineStr">
-        <is>
-          <t>0976588171</t>
-        </is>
-      </c>
+      <c r="D496" s="4"/>
       <c r="E496" s="4"/>
       <c r="F496" s="4" t="inlineStr">
         <is>
@@ -14727,18 +14731,18 @@
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C497" s="4"/>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>0972128080</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E497" s="4"/>
@@ -14756,18 +14760,18 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C498" s="4"/>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E498" s="4"/>
@@ -14785,18 +14789,18 @@
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C499" s="4"/>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E499" s="4"/>
@@ -14814,18 +14818,18 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C500" s="4"/>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E500" s="4"/>
@@ -14843,18 +14847,18 @@
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C501" s="4"/>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E501" s="4"/>
@@ -14872,18 +14876,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14901,18 +14905,18 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C503" s="4"/>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E503" s="4"/>
@@ -14930,18 +14934,18 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭鼎昇</t>
         </is>
       </c>
       <c r="C504" s="4"/>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -14959,22 +14963,18 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C505" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>鄒育燁</t>
+        </is>
+      </c>
+      <c r="C505" s="4"/>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E505" s="4"/>
@@ -14992,18 +14992,22 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
-        </is>
-      </c>
-      <c r="C506" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C506" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15021,18 +15025,18 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C507" s="4"/>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15050,18 +15054,18 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C508" s="4"/>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E508" s="4"/>
@@ -15079,18 +15083,18 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C509" s="4"/>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E509" s="4"/>
@@ -15108,18 +15112,18 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C510" s="4"/>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E510" s="4"/>
@@ -15137,18 +15141,18 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C511" s="4"/>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E511" s="4"/>
@@ -15166,18 +15170,18 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭秉霖</t>
         </is>
       </c>
       <c r="C512" s="4"/>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E512" s="4"/>
@@ -15195,22 +15199,18 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C513" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C513" s="4"/>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E513" s="4"/>
@@ -15228,26 +15228,30 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>鄭雁宇</t>
+          <t>鄭鉅耀</t>
         </is>
       </c>
       <c r="C514" s="4" t="inlineStr">
         <is>
-          <t>桃園區國聖二街145號5樓之1</t>
+          <t>新北市五股區成泰路二段208號</t>
         </is>
       </c>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E514" s="4"/>
-      <c r="F514" s="4"/>
+      <c r="F514" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G514" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15257,26 +15261,26 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C515" s="4"/>
+          <t>鄭雁宇</t>
+        </is>
+      </c>
+      <c r="C515" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E515" s="4"/>
-      <c r="F515" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F515" s="4"/>
       <c r="G515" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15286,18 +15290,18 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C516" s="4"/>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E516" s="4"/>
@@ -15315,18 +15319,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15344,18 +15348,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C518" s="4"/>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E518" s="4"/>
@@ -15373,18 +15377,18 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾銘峰</t>
         </is>
       </c>
       <c r="C519" s="4"/>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E519" s="4"/>
@@ -15402,22 +15406,18 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C520" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鐘國禎</t>
+        </is>
+      </c>
+      <c r="C520" s="4"/>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E520" s="4"/>
@@ -15435,24 +15435,28 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2603270001</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>鐘駿霆</t>
-        </is>
-      </c>
-      <c r="C521" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C521" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>0919331886</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E521" s="4"/>
       <c r="F521" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G521" s="5" t="inlineStr">
@@ -15464,24 +15468,24 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
+          <t>鐘駿霆</t>
         </is>
       </c>
       <c r="C522" s="4"/>
       <c r="D522" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E522" s="4"/>
       <c r="F522" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G522" s="5" t="inlineStr">
@@ -15493,22 +15497,18 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C523" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>阮海德</t>
+        </is>
+      </c>
+      <c r="C523" s="4"/>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E523" s="4"/>
@@ -15526,18 +15526,22 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
-        </is>
-      </c>
-      <c r="C524" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C524" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E524" s="4"/>
@@ -15555,18 +15559,18 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
+          <t>阿源</t>
         </is>
       </c>
       <c r="C525" s="4"/>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E525" s="4"/>
@@ -15584,22 +15588,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C526" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿良</t>
+        </is>
+      </c>
+      <c r="C526" s="4"/>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15617,18 +15617,22 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
-        </is>
-      </c>
-      <c r="C527" s="4"/>
+          <t>陳仲盟</t>
+        </is>
+      </c>
+      <c r="C527" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
+        </is>
+      </c>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15646,22 +15650,18 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
-        </is>
-      </c>
-      <c r="C528" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區日和街7號22樓</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C528" s="4"/>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15679,22 +15679,22 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
+          <t>陳俊安</t>
         </is>
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>板橋大觀路1段28巷118-1號</t>
+          <t>新北市土城區日和街7號22樓</t>
         </is>
       </c>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15712,18 +15712,22 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C530" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C530" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15741,18 +15745,18 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C531" s="4"/>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15770,18 +15774,18 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C532" s="4"/>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15799,18 +15803,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C533" s="4"/>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15828,18 +15832,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E534" s="4"/>
@@ -15857,18 +15861,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C535" s="4"/>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15886,22 +15890,26 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C536" s="4"/>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E536" s="4"/>
-      <c r="F536" s="4"/>
+      <c r="F536" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G536" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15911,26 +15919,22 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C537" s="4"/>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E537" s="4"/>
-      <c r="F537" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F537" s="4"/>
       <c r="G537" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15940,18 +15944,18 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C538" s="4"/>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E538" s="4"/>
@@ -15969,18 +15973,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳奕融</t>
         </is>
       </c>
       <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E539" s="4"/>
@@ -15998,22 +16002,18 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C540" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕閔</t>
+        </is>
+      </c>
+      <c r="C540" s="4"/>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16031,18 +16031,22 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2603260001</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>陳威宇</t>
-        </is>
-      </c>
-      <c r="C541" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C541" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0958186337</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16060,18 +16064,18 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C542" s="4"/>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E542" s="4"/>
@@ -16089,18 +16093,18 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C543" s="4"/>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16118,18 +16122,18 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C544" s="4"/>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E544" s="4"/>
@@ -16147,18 +16151,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
+          <t>陳子杰</t>
         </is>
       </c>
       <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16176,18 +16180,18 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
+          <t>陳宏文</t>
         </is>
       </c>
       <c r="C546" s="4"/>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16205,22 +16209,18 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C547" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳宏達</t>
+        </is>
+      </c>
+      <c r="C547" s="4"/>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E547" s="4"/>
@@ -16238,18 +16238,22 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
-        </is>
-      </c>
-      <c r="C548" s="4"/>
+          <t>陳家偉</t>
+        </is>
+      </c>
+      <c r="C548" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市神農路一段72號</t>
+        </is>
+      </c>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E548" s="4"/>
@@ -16267,18 +16271,18 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
+          <t>陳小雨</t>
         </is>
       </c>
       <c r="C549" s="4"/>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E549" s="4"/>
@@ -16296,22 +16300,18 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
-        </is>
-      </c>
-      <c r="C550" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
-        </is>
-      </c>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="C550" s="4"/>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E550" s="4"/>
@@ -16329,22 +16329,22 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
+          <t>陳建宏(花蓮)</t>
         </is>
       </c>
       <c r="C551" s="4" t="inlineStr">
         <is>
-          <t>新北市三重區仁美街125號</t>
+          <t>花蓮縣新城鄉佳林31之19號</t>
         </is>
       </c>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E551" s="4"/>
@@ -16362,18 +16362,22 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
-        </is>
-      </c>
-      <c r="C552" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16391,18 +16395,18 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C553" s="4"/>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16420,18 +16424,18 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C554" s="4"/>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16449,18 +16453,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C555" s="4"/>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16478,18 +16482,18 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳怡如(彥鈞)</t>
         </is>
       </c>
       <c r="C556" s="4"/>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16507,18 +16511,18 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳慶壎</t>
         </is>
       </c>
       <c r="C557" s="4"/>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16536,22 +16540,18 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C558" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳敬惟</t>
+        </is>
+      </c>
+      <c r="C558" s="4"/>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16569,18 +16569,22 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
-        </is>
-      </c>
-      <c r="C559" s="4"/>
+          <t>陳智盛</t>
+        </is>
+      </c>
+      <c r="C559" s="4" t="inlineStr">
+        <is>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
+        </is>
+      </c>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16598,22 +16602,18 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
-        </is>
-      </c>
-      <c r="C560" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區星雲街30號</t>
-        </is>
-      </c>
+          <t>陳朋堅</t>
+        </is>
+      </c>
+      <c r="C560" s="4"/>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16631,22 +16631,22 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
+          <t>陳松廉</t>
         </is>
       </c>
       <c r="C561" s="4" t="inlineStr">
         <is>
-          <t>桃園市南豐街258號</t>
+          <t>台北市內湖區星雲街30號</t>
         </is>
       </c>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16664,18 +16664,22 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
-        </is>
-      </c>
-      <c r="C562" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C562" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16693,18 +16697,18 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C563" s="4"/>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16722,7 +16726,7 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
@@ -16733,7 +16737,7 @@
       <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16751,18 +16755,18 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C565" s="4"/>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16780,22 +16784,18 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C566" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳正傑</t>
+        </is>
+      </c>
+      <c r="C566" s="4"/>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16813,18 +16813,22 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
-        </is>
-      </c>
-      <c r="C567" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C567" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16842,18 +16846,18 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C568" s="4"/>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16871,18 +16875,18 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
+          <t>陳琇珊</t>
         </is>
       </c>
       <c r="C569" s="4"/>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16900,18 +16904,18 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳琬瑜</t>
         </is>
       </c>
       <c r="C570" s="4"/>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16929,22 +16933,18 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C571" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳璽文</t>
+        </is>
+      </c>
+      <c r="C571" s="4"/>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -16962,18 +16962,22 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
-        </is>
-      </c>
-      <c r="C572" s="4"/>
+          <t>陳益銓</t>
+        </is>
+      </c>
+      <c r="C572" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區民生街15巷10號3樓</t>
+        </is>
+      </c>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -16991,22 +16995,18 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
-        </is>
-      </c>
-      <c r="C573" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
-        </is>
-      </c>
+          <t>陳秋蓉</t>
+        </is>
+      </c>
+      <c r="C573" s="4"/>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17024,18 +17024,22 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
-        </is>
-      </c>
-      <c r="C574" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17053,18 +17057,18 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
+          <t>陳貴源</t>
         </is>
       </c>
       <c r="C575" s="4"/>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17082,18 +17086,18 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
+          <t>陳達鋒</t>
         </is>
       </c>
       <c r="C576" s="4"/>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17111,22 +17115,18 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C577" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C577" s="4"/>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17144,22 +17144,22 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
+          <t>陳長志</t>
         </is>
       </c>
       <c r="C578" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+          <t>新北市新店區安康路</t>
         </is>
       </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17177,22 +17177,22 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
+          <t>陳雯瑄</t>
         </is>
       </c>
       <c r="C579" s="4" t="inlineStr">
         <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
         </is>
       </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17210,18 +17210,22 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C580" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C580" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17239,18 +17243,18 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C581" s="4"/>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17268,18 +17272,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17297,18 +17301,18 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C583" s="4"/>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17326,18 +17330,18 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C584" s="4"/>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17355,18 +17359,18 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C585" s="4"/>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17384,18 +17388,18 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C586" s="4"/>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17413,18 +17417,18 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C587" s="4"/>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17442,18 +17446,18 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C588" s="4"/>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17471,18 +17475,18 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C589" s="4"/>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17500,18 +17504,18 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C590" s="4"/>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17529,18 +17533,18 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏宏坤</t>
         </is>
       </c>
       <c r="C591" s="4"/>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17558,22 +17562,18 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C592" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>馬迪</t>
+        </is>
+      </c>
+      <c r="C592" s="4"/>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17591,18 +17591,22 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
-        </is>
-      </c>
-      <c r="C593" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C593" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17620,18 +17624,18 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C594" s="4"/>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17649,18 +17653,18 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C595" s="4"/>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17678,18 +17682,18 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C596" s="4"/>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17707,18 +17711,18 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C597" s="4"/>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17736,18 +17740,18 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C598" s="4"/>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17765,18 +17769,18 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高聖景</t>
         </is>
       </c>
       <c r="C599" s="4"/>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17794,22 +17798,18 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C600" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高莉婷</t>
+        </is>
+      </c>
+      <c r="C600" s="4"/>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E600" s="4"/>
@@ -17827,18 +17827,22 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
-        </is>
-      </c>
-      <c r="C601" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17856,18 +17860,18 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C602" s="4"/>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0937742352</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17885,16 +17889,20 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C603" s="4"/>
-      <c r="D603" s="4"/>
+      <c r="D603" s="4" t="inlineStr">
+        <is>
+          <t>0989116588</t>
+        </is>
+      </c>
       <c r="E603" s="4"/>
       <c r="F603" s="4" t="inlineStr">
         <is>
@@ -17910,20 +17918,16 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>鴻</t>
         </is>
       </c>
       <c r="C604" s="4"/>
-      <c r="D604" s="4" t="inlineStr">
-        <is>
-          <t>0958180882</t>
-        </is>
-      </c>
+      <c r="D604" s="4"/>
       <c r="E604" s="4"/>
       <c r="F604" s="4" t="inlineStr">
         <is>
@@ -17939,22 +17943,18 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C605" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
+          <t>黃俊翰</t>
+        </is>
+      </c>
+      <c r="C605" s="4"/>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>0903975921</t>
+          <t>0958180882</t>
         </is>
       </c>
       <c r="E605" s="4"/>
@@ -17972,16 +17972,24 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
-        </is>
-      </c>
-      <c r="C606" s="4"/>
-      <c r="D606" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C606" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
+      <c r="D606" s="4" t="inlineStr">
+        <is>
+          <t>0903975921</t>
+        </is>
+      </c>
       <c r="E606" s="4"/>
       <c r="F606" s="4" t="inlineStr">
         <is>
@@ -17997,20 +18005,16 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C607" s="4"/>
-      <c r="D607" s="4" t="inlineStr">
-        <is>
-          <t>0938722217</t>
-        </is>
-      </c>
+      <c r="D607" s="4"/>
       <c r="E607" s="4"/>
       <c r="F607" s="4" t="inlineStr">
         <is>
@@ -18026,18 +18030,18 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C608" s="4"/>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>0989628136</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E608" s="4"/>
@@ -18055,18 +18059,18 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C609" s="4"/>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18084,18 +18088,18 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C610" s="4"/>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18113,18 +18117,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18142,18 +18146,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18171,18 +18175,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18200,18 +18204,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18229,22 +18233,18 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C615" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃庠豪</t>
+        </is>
+      </c>
+      <c r="C615" s="4"/>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18262,18 +18262,22 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
-        </is>
-      </c>
-      <c r="C616" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C616" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18291,18 +18295,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18320,18 +18324,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18349,18 +18353,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18378,18 +18382,18 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C620" s="4"/>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18407,18 +18411,18 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C621" s="4"/>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18436,18 +18440,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18465,18 +18469,18 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C623" s="4"/>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E623" s="4"/>
@@ -18494,18 +18498,18 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C624" s="4"/>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E624" s="4"/>
@@ -18523,18 +18527,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18552,22 +18556,26 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E626" s="4"/>
-      <c r="F626" s="4"/>
+      <c r="F626" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G626" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -18577,26 +18585,22 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E627" s="4"/>
-      <c r="F627" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F627" s="4"/>
       <c r="G627" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -18606,18 +18610,18 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C628" s="4"/>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18635,18 +18639,18 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C629" s="4"/>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E629" s="4"/>
@@ -18664,18 +18668,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18693,18 +18697,18 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C631" s="4"/>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E631" s="4"/>
@@ -18722,18 +18726,18 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2510020007</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃鴻麒</t>
         </is>
       </c>
       <c r="C632" s="4"/>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0930571975</t>
         </is>
       </c>
       <c r="E632" s="4"/>
@@ -18751,18 +18755,18 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2602270002</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黎信宏</t>
         </is>
       </c>
       <c r="C633" s="4"/>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0911024337</t>
         </is>
       </c>
       <c r="E633" s="4"/>
@@ -18778,9 +18782,38 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>2026/03/28  13:00:09</t>
+      <c r="A634" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B634" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C634" s="4"/>
+      <c r="D634" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E634" s="4"/>
+      <c r="F634" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G634" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026/03/28  14:20:53</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -8278,16 +8278,20 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>V0020</t>
+          <t>M2603280003</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>榮豪</t>
+          <t>楊鎮良</t>
         </is>
       </c>
       <c r="C277" s="4"/>
-      <c r="D277" s="4"/>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>0976121606</t>
+        </is>
+      </c>
       <c r="E277" s="4"/>
       <c r="F277" s="4" t="inlineStr">
         <is>
@@ -8303,20 +8307,16 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>M2602130002</t>
+          <t>V0020</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>榮豪-許</t>
+          <t>榮豪</t>
         </is>
       </c>
       <c r="C278" s="4"/>
-      <c r="D278" s="4" t="inlineStr">
-        <is>
-          <t>0931100879</t>
-        </is>
-      </c>
+      <c r="D278" s="4"/>
       <c r="E278" s="4"/>
       <c r="F278" s="4" t="inlineStr">
         <is>
@@ -8332,18 +8332,18 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>M2602080007</t>
+          <t>M2602130002</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>樓俊瑋</t>
+          <t>榮豪-許</t>
         </is>
       </c>
       <c r="C279" s="4"/>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>0910900256</t>
+          <t>0931100879</t>
         </is>
       </c>
       <c r="E279" s="4"/>
@@ -8361,22 +8361,18 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>M2511010001</t>
+          <t>M2602080007</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>武林</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區集美街222號5樓</t>
-        </is>
-      </c>
+          <t>樓俊瑋</t>
+        </is>
+      </c>
+      <c r="C280" s="4"/>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>0913211688</t>
+          <t>0910900256</t>
         </is>
       </c>
       <c r="E280" s="4"/>
@@ -8394,18 +8390,22 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>M2511080005</t>
+          <t>M2511010001</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>毛毛</t>
-        </is>
-      </c>
-      <c r="C281" s="4"/>
+          <t>武林</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區集美街222號5樓</t>
+        </is>
+      </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>0919286386</t>
+          <t>0913211688</t>
         </is>
       </c>
       <c r="E281" s="4"/>
@@ -8423,24 +8423,24 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>Z0001</t>
+          <t>M2511080005</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>民享店</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
-        </is>
-      </c>
-      <c r="D282" s="4"/>
+          <t>毛毛</t>
+        </is>
+      </c>
+      <c r="C282" s="4"/>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>0919286386</t>
+        </is>
+      </c>
       <c r="E282" s="4"/>
       <c r="F282" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -8452,15 +8452,19 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>V0014</t>
+          <t>Z0001</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>民享房東</t>
-        </is>
-      </c>
-      <c r="C283" s="4"/>
+          <t>民享店</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
+        </is>
+      </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
       <c r="F283" s="4" t="inlineStr">
@@ -8477,12 +8481,12 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>V0019</t>
+          <t>V0014</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>永豐餘</t>
+          <t>民享房東</t>
         </is>
       </c>
       <c r="C284" s="4"/>
@@ -8490,7 +8494,7 @@
       <c r="E284" s="4"/>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -8502,24 +8506,20 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>M2509260041</t>
+          <t>V0019</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>江世隆(新莊區)</t>
+          <t>永豐餘</t>
         </is>
       </c>
       <c r="C285" s="4"/>
-      <c r="D285" s="4" t="inlineStr">
-        <is>
-          <t>0981243133</t>
-        </is>
-      </c>
+      <c r="D285" s="4"/>
       <c r="E285" s="4"/>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -8531,18 +8531,18 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>M2510050010</t>
+          <t>M2509260041</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>江仁堂</t>
+          <t>江世隆(新莊區)</t>
         </is>
       </c>
       <c r="C286" s="4"/>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>0986696777</t>
+          <t>0981243133</t>
         </is>
       </c>
       <c r="E286" s="4"/>
@@ -8560,18 +8560,18 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>M2511220002</t>
+          <t>M2510050010</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>江凱逸</t>
+          <t>江仁堂</t>
         </is>
       </c>
       <c r="C287" s="4"/>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>0912312896</t>
+          <t>0986696777</t>
         </is>
       </c>
       <c r="E287" s="4"/>
@@ -8589,16 +8589,20 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>M2509120001</t>
+          <t>M2511220002</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>江哥</t>
+          <t>江凱逸</t>
         </is>
       </c>
       <c r="C288" s="4"/>
-      <c r="D288" s="4"/>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>0912312896</t>
+        </is>
+      </c>
       <c r="E288" s="4"/>
       <c r="F288" s="4" t="inlineStr">
         <is>
@@ -8614,20 +8618,16 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>M2509280006</t>
+          <t>M2509120001</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>江宏恩</t>
+          <t>江哥</t>
         </is>
       </c>
       <c r="C289" s="4"/>
-      <c r="D289" s="4" t="inlineStr">
-        <is>
-          <t>0988677410</t>
-        </is>
-      </c>
+      <c r="D289" s="4"/>
       <c r="E289" s="4"/>
       <c r="F289" s="4" t="inlineStr">
         <is>
@@ -8643,18 +8643,18 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>M2510160009</t>
+          <t>M2509280006</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>江育哲</t>
+          <t>江宏恩</t>
         </is>
       </c>
       <c r="C290" s="4"/>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>0916586618</t>
+          <t>0988677410</t>
         </is>
       </c>
       <c r="E290" s="4"/>
@@ -8672,18 +8672,18 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>M2511060005</t>
+          <t>M2510160009</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>池沛潔</t>
+          <t>江育哲</t>
         </is>
       </c>
       <c r="C291" s="4"/>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>0963900636</t>
+          <t>0916586618</t>
         </is>
       </c>
       <c r="E291" s="4"/>
@@ -8701,18 +8701,18 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>M2510240003</t>
+          <t>M2511060005</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>汪鈺修</t>
+          <t>池沛潔</t>
         </is>
       </c>
       <c r="C292" s="4"/>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>0971792952</t>
+          <t>0963900636</t>
         </is>
       </c>
       <c r="E292" s="4"/>
@@ -8730,18 +8730,18 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>M2601030003</t>
+          <t>M2510240003</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>沈大哥</t>
+          <t>汪鈺修</t>
         </is>
       </c>
       <c r="C293" s="4"/>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>0978562818</t>
+          <t>0971792952</t>
         </is>
       </c>
       <c r="E293" s="4"/>
@@ -8759,18 +8759,18 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>M2509300002</t>
+          <t>M2601030003</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>沈明鋒</t>
+          <t>沈大哥</t>
         </is>
       </c>
       <c r="C294" s="4"/>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>0908356227</t>
+          <t>0978562818</t>
         </is>
       </c>
       <c r="E294" s="4"/>
@@ -8788,20 +8788,24 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>V0005</t>
+          <t>M2509300002</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>波蜜企業</t>
+          <t>沈明鋒</t>
         </is>
       </c>
       <c r="C295" s="4"/>
-      <c r="D295" s="4"/>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>0908356227</t>
+        </is>
+      </c>
       <c r="E295" s="4"/>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -8813,24 +8817,20 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>M2512200004</t>
+          <t>V0005</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>洪丞鍇</t>
+          <t>波蜜企業</t>
         </is>
       </c>
       <c r="C296" s="4"/>
-      <c r="D296" s="4" t="inlineStr">
-        <is>
-          <t>0952119213</t>
-        </is>
-      </c>
+      <c r="D296" s="4"/>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -8842,18 +8842,18 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>M2602270003</t>
+          <t>M2512200004</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>洪儒明</t>
+          <t>洪丞鍇</t>
         </is>
       </c>
       <c r="C297" s="4"/>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>0960097097</t>
+          <t>0952119213</t>
         </is>
       </c>
       <c r="E297" s="4"/>
@@ -8871,18 +8871,18 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>M2509280012</t>
+          <t>M2602270003</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>洪勝忠</t>
+          <t>洪儒明</t>
         </is>
       </c>
       <c r="C298" s="4"/>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>0917962020</t>
+          <t>0960097097</t>
         </is>
       </c>
       <c r="E298" s="4"/>
@@ -8900,18 +8900,18 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>M2510060001</t>
+          <t>M2509280012</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>洪文輝</t>
+          <t>洪勝忠</t>
         </is>
       </c>
       <c r="C299" s="4"/>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>0909183013</t>
+          <t>0917962020</t>
         </is>
       </c>
       <c r="E299" s="4"/>
@@ -8929,18 +8929,18 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>M2510300003</t>
+          <t>M2510060001</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>洪毅平</t>
+          <t>洪文輝</t>
         </is>
       </c>
       <c r="C300" s="4"/>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>0958266132</t>
+          <t>0909183013</t>
         </is>
       </c>
       <c r="E300" s="4"/>
@@ -8958,18 +8958,18 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>M2510240005</t>
+          <t>M2510300003</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>洪浩鈞</t>
+          <t>洪毅平</t>
         </is>
       </c>
       <c r="C301" s="4"/>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>0939553096</t>
+          <t>0958266132</t>
         </is>
       </c>
       <c r="E301" s="4"/>
@@ -8987,18 +8987,18 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>M2509260019</t>
+          <t>M2510240005</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>洪秋麗</t>
+          <t>洪浩鈞</t>
         </is>
       </c>
       <c r="C302" s="4"/>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>0922210223</t>
+          <t>0939553096</t>
         </is>
       </c>
       <c r="E302" s="4"/>
@@ -9016,18 +9016,18 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>M2512140001</t>
+          <t>M2509260019</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>洪翊珊</t>
+          <t>洪秋麗</t>
         </is>
       </c>
       <c r="C303" s="4"/>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>0968884119</t>
+          <t>0922210223</t>
         </is>
       </c>
       <c r="E303" s="4"/>
@@ -9045,22 +9045,18 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>M2510060006</t>
+          <t>M2512140001</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>洪金賢</t>
-        </is>
-      </c>
-      <c r="C304" s="4" t="inlineStr">
-        <is>
-          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
-        </is>
-      </c>
+          <t>洪翊珊</t>
+        </is>
+      </c>
+      <c r="C304" s="4"/>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>0933702515</t>
+          <t>0968884119</t>
         </is>
       </c>
       <c r="E304" s="4"/>
@@ -9078,22 +9074,22 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>M2602040001</t>
+          <t>M2510060006</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>涂宏忠</t>
+          <t>洪金賢</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>高雄市開發路15-3號</t>
+          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>0963222826</t>
+          <t>0933702515</t>
         </is>
       </c>
       <c r="E305" s="4"/>
@@ -9111,18 +9107,22 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>M2510090009</t>
+          <t>M2602040001</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>游仲強</t>
-        </is>
-      </c>
-      <c r="C306" s="4"/>
+          <t>涂宏忠</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>高雄市開發路15-3號</t>
+        </is>
+      </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>0910671480</t>
+          <t>0963222826</t>
         </is>
       </c>
       <c r="E306" s="4"/>
@@ -9140,18 +9140,18 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>M2602030002</t>
+          <t>M2510090009</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>游凱翔</t>
+          <t>游仲強</t>
         </is>
       </c>
       <c r="C307" s="4"/>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>0978317186</t>
+          <t>0910671480</t>
         </is>
       </c>
       <c r="E307" s="4"/>
@@ -9169,18 +9169,18 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>M2601290001</t>
+          <t>M2602030002</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>游家誠</t>
+          <t>游凱翔</t>
         </is>
       </c>
       <c r="C308" s="4"/>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>0920727320</t>
+          <t>0978317186</t>
         </is>
       </c>
       <c r="E308" s="4"/>
@@ -9198,18 +9198,18 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>M2510090002</t>
+          <t>M2601290001</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>游煥清</t>
+          <t>游家誠</t>
         </is>
       </c>
       <c r="C309" s="4"/>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>0932139705</t>
+          <t>0920727320</t>
         </is>
       </c>
       <c r="E309" s="4"/>
@@ -9227,18 +9227,18 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>M2510100004</t>
+          <t>M2510090002</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>潘文展</t>
+          <t>游煥清</t>
         </is>
       </c>
       <c r="C310" s="4"/>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>0930842995</t>
+          <t>0932139705</t>
         </is>
       </c>
       <c r="E310" s="4"/>
@@ -9256,22 +9256,18 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>M2511230004</t>
+          <t>M2510100004</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>潘正霖(瘋爪子)</t>
-        </is>
-      </c>
-      <c r="C311" s="4" t="inlineStr">
-        <is>
-          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
-        </is>
-      </c>
+          <t>潘文展</t>
+        </is>
+      </c>
+      <c r="C311" s="4"/>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>0983777818</t>
+          <t>0930842995</t>
         </is>
       </c>
       <c r="E311" s="4"/>
@@ -9289,18 +9285,22 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>M2509280010</t>
+          <t>M2511230004</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>潘秀茹</t>
-        </is>
-      </c>
-      <c r="C312" s="4"/>
+          <t>潘正霖(瘋爪子)</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
+        </is>
+      </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>0911900520</t>
+          <t>0983777818</t>
         </is>
       </c>
       <c r="E312" s="4"/>
@@ -9318,18 +9318,18 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>M2601200002</t>
+          <t>M2509280010</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>潘糖糖</t>
+          <t>潘秀茹</t>
         </is>
       </c>
       <c r="C313" s="4"/>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>0976297272</t>
+          <t>0911900520</t>
         </is>
       </c>
       <c r="E313" s="4"/>
@@ -9347,18 +9347,18 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>M2509300016</t>
+          <t>M2601200002</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>潘鳯斌</t>
+          <t>潘糖糖</t>
         </is>
       </c>
       <c r="C314" s="4"/>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>0935502290</t>
+          <t>0976297272</t>
         </is>
       </c>
       <c r="E314" s="4"/>
@@ -9376,16 +9376,20 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>M2509290010</t>
+          <t>M2509300016</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>火牛-批發</t>
+          <t>潘鳯斌</t>
         </is>
       </c>
       <c r="C315" s="4"/>
-      <c r="D315" s="4"/>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>0935502290</t>
+        </is>
+      </c>
       <c r="E315" s="4"/>
       <c r="F315" s="4" t="inlineStr">
         <is>
@@ -9401,12 +9405,12 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>M2512180002</t>
+          <t>M2509290010</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>火牛-老秦</t>
+          <t>火牛-批發</t>
         </is>
       </c>
       <c r="C316" s="4"/>
@@ -9426,12 +9430,12 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>M2512180001</t>
+          <t>M2512180002</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>火牛-阿昌</t>
+          <t>火牛-老秦</t>
         </is>
       </c>
       <c r="C317" s="4"/>
@@ -9451,20 +9455,16 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>M2602140002</t>
+          <t>M2512180001</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>灰灰</t>
+          <t>火牛-阿昌</t>
         </is>
       </c>
       <c r="C318" s="4"/>
-      <c r="D318" s="4" t="inlineStr">
-        <is>
-          <t>0987829134</t>
-        </is>
-      </c>
+      <c r="D318" s="4"/>
       <c r="E318" s="4"/>
       <c r="F318" s="4" t="inlineStr">
         <is>
@@ -9480,18 +9480,18 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>M2509300011</t>
+          <t>M2602140002</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>熊駿天(大熊)</t>
+          <t>灰灰</t>
         </is>
       </c>
       <c r="C319" s="4"/>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>0933131800</t>
+          <t>0987829134</t>
         </is>
       </c>
       <c r="E319" s="4"/>
@@ -9509,18 +9509,18 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>M2602070001</t>
+          <t>M2509300011</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>王RICK</t>
+          <t>熊駿天(大熊)</t>
         </is>
       </c>
       <c r="C320" s="4"/>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>0930106976</t>
+          <t>0933131800</t>
         </is>
       </c>
       <c r="E320" s="4"/>
@@ -9538,22 +9538,18 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>M2510240006</t>
+          <t>M2602070001</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>王中南</t>
-        </is>
-      </c>
-      <c r="C321" s="4" t="inlineStr">
-        <is>
-          <t>桃園市平鎮區快速路166號3樓</t>
-        </is>
-      </c>
+          <t>王RICK</t>
+        </is>
+      </c>
+      <c r="C321" s="4"/>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>0937124082</t>
+          <t>0930106976</t>
         </is>
       </c>
       <c r="E321" s="4"/>
@@ -9571,18 +9567,22 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>M2601020001</t>
+          <t>M2510240006</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>王仁澤</t>
-        </is>
-      </c>
-      <c r="C322" s="4"/>
+          <t>王中南</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區快速路166號3樓</t>
+        </is>
+      </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>0976503359</t>
+          <t>0937124082</t>
         </is>
       </c>
       <c r="E322" s="4"/>
@@ -9600,18 +9600,18 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>M2603010004</t>
+          <t>M2601020001</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>王又杰</t>
+          <t>王仁澤</t>
         </is>
       </c>
       <c r="C323" s="4"/>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>0909771449</t>
+          <t>0976503359</t>
         </is>
       </c>
       <c r="E323" s="4"/>
@@ -9629,22 +9629,26 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>M2601080001</t>
+          <t>M2603010004</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>王家文</t>
+          <t>王又杰</t>
         </is>
       </c>
       <c r="C324" s="4"/>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>0908176140</t>
+          <t>0909771449</t>
         </is>
       </c>
       <c r="E324" s="4"/>
-      <c r="F324" s="4"/>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -9654,26 +9658,22 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>M2602080001</t>
+          <t>M2601080001</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>王巽璋</t>
+          <t>王家文</t>
         </is>
       </c>
       <c r="C325" s="4"/>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>0932943159</t>
+          <t>0908176140</t>
         </is>
       </c>
       <c r="E325" s="4"/>
-      <c r="F325" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F325" s="4"/>
       <c r="G325" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -9683,18 +9683,18 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>M2512230001</t>
+          <t>M2602080001</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>王志維</t>
+          <t>王巽璋</t>
         </is>
       </c>
       <c r="C326" s="4"/>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>0931262170</t>
+          <t>0932943159</t>
         </is>
       </c>
       <c r="E326" s="4"/>
@@ -9712,18 +9712,18 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>M2511180003</t>
+          <t>M2512230001</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>王明輝</t>
+          <t>王志維</t>
         </is>
       </c>
       <c r="C327" s="4"/>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>0937002585</t>
+          <t>0931262170</t>
         </is>
       </c>
       <c r="E327" s="4"/>
@@ -9741,18 +9741,18 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>M2510140007</t>
+          <t>M2511180003</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>王羿佳</t>
+          <t>王明輝</t>
         </is>
       </c>
       <c r="C328" s="4"/>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>0968831773</t>
+          <t>0937002585</t>
         </is>
       </c>
       <c r="E328" s="4"/>
@@ -9770,22 +9770,18 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>M2509260013</t>
+          <t>M2510140007</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>王舜平</t>
-        </is>
-      </c>
-      <c r="C329" s="4" t="inlineStr">
-        <is>
-          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
-        </is>
-      </c>
+          <t>王羿佳</t>
+        </is>
+      </c>
+      <c r="C329" s="4"/>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>0917215021</t>
+          <t>0968831773</t>
         </is>
       </c>
       <c r="E329" s="4"/>
@@ -9803,18 +9799,22 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>M2601170002</t>
+          <t>M2509260013</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>王閔弘</t>
-        </is>
-      </c>
-      <c r="C330" s="4"/>
+          <t>王舜平</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
+        </is>
+      </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>0931056292</t>
+          <t>0917215021</t>
         </is>
       </c>
       <c r="E330" s="4"/>
@@ -9832,18 +9832,18 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>M2511230003</t>
+          <t>M2601170002</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>王靜芸</t>
+          <t>王閔弘</t>
         </is>
       </c>
       <c r="C331" s="4"/>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>0970224238</t>
+          <t>0931056292</t>
         </is>
       </c>
       <c r="E331" s="4"/>
@@ -9861,18 +9861,18 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>M2510040009</t>
+          <t>M2511230003</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>王駿宏</t>
+          <t>王靜芸</t>
         </is>
       </c>
       <c r="C332" s="4"/>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>0919336854</t>
+          <t>0970224238</t>
         </is>
       </c>
       <c r="E332" s="4"/>
@@ -9890,18 +9890,18 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>M2601010001</t>
+          <t>M2510040009</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>甘玨瑋</t>
+          <t>王駿宏</t>
         </is>
       </c>
       <c r="C333" s="4"/>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>0987214102</t>
+          <t>0919336854</t>
         </is>
       </c>
       <c r="E333" s="4"/>
@@ -9919,22 +9919,18 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>M2510290002</t>
+          <t>M2601010001</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>生生</t>
-        </is>
-      </c>
-      <c r="C334" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街427號</t>
-        </is>
-      </c>
+          <t>甘玨瑋</t>
+        </is>
+      </c>
+      <c r="C334" s="4"/>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>0919001722</t>
+          <t>0987214102</t>
         </is>
       </c>
       <c r="E334" s="4"/>
@@ -9952,18 +9948,22 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>M2509260050</t>
+          <t>M2510290002</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>甩爪</t>
-        </is>
-      </c>
-      <c r="C335" s="4"/>
+          <t>生生</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街427號</t>
+        </is>
+      </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>0970754804</t>
+          <t>0919001722</t>
         </is>
       </c>
       <c r="E335" s="4"/>
@@ -9981,18 +9981,18 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>M2509270005</t>
+          <t>M2509260050</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>甯偉</t>
+          <t>甩爪</t>
         </is>
       </c>
       <c r="C336" s="4"/>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>0955617290</t>
+          <t>0970754804</t>
         </is>
       </c>
       <c r="E336" s="4"/>
@@ -10010,18 +10010,18 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>M2510240007</t>
+          <t>M2509270005</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>盧其辰</t>
+          <t>甯偉</t>
         </is>
       </c>
       <c r="C337" s="4"/>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>0982119779</t>
+          <t>0955617290</t>
         </is>
       </c>
       <c r="E337" s="4"/>
@@ -10039,20 +10039,24 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>V0013</t>
+          <t>M2510240007</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>真大帥</t>
+          <t>盧其辰</t>
         </is>
       </c>
       <c r="C338" s="4"/>
-      <c r="D338" s="4"/>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>0982119779</t>
+        </is>
+      </c>
       <c r="E338" s="4"/>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
@@ -10064,24 +10068,20 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>M2510310002</t>
+          <t>V0013</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>祁麟</t>
+          <t>真大帥</t>
         </is>
       </c>
       <c r="C339" s="4"/>
-      <c r="D339" s="4" t="inlineStr">
-        <is>
-          <t>0982883101</t>
-        </is>
-      </c>
+      <c r="D339" s="4"/>
       <c r="E339" s="4"/>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -10093,18 +10093,18 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>M2602130001</t>
+          <t>M2510310002</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>祐</t>
+          <t>祁麟</t>
         </is>
       </c>
       <c r="C340" s="4"/>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>0983407890</t>
+          <t>0982883101</t>
         </is>
       </c>
       <c r="E340" s="4"/>
@@ -10122,18 +10122,18 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>M2510050001</t>
+          <t>M2602130001</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>程sir/Ashbur</t>
+          <t>祐</t>
         </is>
       </c>
       <c r="C341" s="4"/>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>0963612395</t>
+          <t>0983407890</t>
         </is>
       </c>
       <c r="E341" s="4"/>
@@ -10151,18 +10151,18 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>M2510300001</t>
+          <t>M2510050001</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>程品勝</t>
+          <t>程sir/Ashbur</t>
         </is>
       </c>
       <c r="C342" s="4"/>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>0913780727</t>
+          <t>0963612395</t>
         </is>
       </c>
       <c r="E342" s="4"/>
@@ -10180,18 +10180,18 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>M2601270002</t>
+          <t>M2510300001</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>程建智</t>
+          <t>程品勝</t>
         </is>
       </c>
       <c r="C343" s="4"/>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>0988919027</t>
+          <t>0913780727</t>
         </is>
       </c>
       <c r="E343" s="4"/>
@@ -10209,18 +10209,18 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>M2603120004</t>
+          <t>M2601270002</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>程郁勛</t>
+          <t>程建智</t>
         </is>
       </c>
       <c r="C344" s="4"/>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>0955671407</t>
+          <t>0988919027</t>
         </is>
       </c>
       <c r="E344" s="4"/>
@@ -10238,22 +10238,18 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>M2509160001</t>
+          <t>M2603120004</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>穆莉茹</t>
-        </is>
-      </c>
-      <c r="C345" s="4" t="inlineStr">
-        <is>
-          <t>桃園平鎮區上海路169號</t>
-        </is>
-      </c>
+          <t>程郁勛</t>
+        </is>
+      </c>
+      <c r="C345" s="4"/>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>0955777312</t>
+          <t>0955671407</t>
         </is>
       </c>
       <c r="E345" s="4"/>
@@ -10271,18 +10267,22 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>M2511160003</t>
+          <t>M2509160001</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>簡士傑</t>
-        </is>
-      </c>
-      <c r="C346" s="4"/>
+          <t>穆莉茹</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>桃園平鎮區上海路169號</t>
+        </is>
+      </c>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>0963817398</t>
+          <t>0955777312</t>
         </is>
       </c>
       <c r="E346" s="4"/>
@@ -10300,18 +10300,18 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>M2509300013</t>
+          <t>M2511160003</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>簡子偉</t>
+          <t>簡士傑</t>
         </is>
       </c>
       <c r="C347" s="4"/>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>0955462926</t>
+          <t>0963817398</t>
         </is>
       </c>
       <c r="E347" s="4"/>
@@ -10329,18 +10329,18 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>M2602280002</t>
+          <t>M2509300013</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>簡子洋</t>
+          <t>簡子偉</t>
         </is>
       </c>
       <c r="C348" s="4"/>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>0933921933</t>
+          <t>0955462926</t>
         </is>
       </c>
       <c r="E348" s="4"/>
@@ -10358,18 +10358,18 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>M2510040003</t>
+          <t>M2602280002</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>簡小琪</t>
+          <t>簡子洋</t>
         </is>
       </c>
       <c r="C349" s="4"/>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>0930033829</t>
+          <t>0933921933</t>
         </is>
       </c>
       <c r="E349" s="4"/>
@@ -10387,18 +10387,18 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>M2510260002</t>
+          <t>M2510040003</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>簡揚城</t>
+          <t>簡小琪</t>
         </is>
       </c>
       <c r="C350" s="4"/>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>0913153353</t>
+          <t>0930033829</t>
         </is>
       </c>
       <c r="E350" s="4"/>
@@ -10416,18 +10416,18 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>M2509300001</t>
+          <t>M2510260002</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>簡瑋成</t>
+          <t>簡揚城</t>
         </is>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>0936389969</t>
+          <t>0913153353</t>
         </is>
       </c>
       <c r="E351" s="4"/>
@@ -10445,18 +10445,18 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>M2509290020</t>
+          <t>M2509300001</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>簡茂州</t>
+          <t>簡瑋成</t>
         </is>
       </c>
       <c r="C352" s="4"/>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>0985217379</t>
+          <t>0936389969</t>
         </is>
       </c>
       <c r="E352" s="4"/>
@@ -10474,18 +10474,18 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>M2512130001</t>
+          <t>M2509290020</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>紀彥銘</t>
+          <t>簡茂州</t>
         </is>
       </c>
       <c r="C353" s="4"/>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>0988752337</t>
+          <t>0985217379</t>
         </is>
       </c>
       <c r="E353" s="4"/>
@@ -10503,20 +10503,24 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>V0001</t>
+          <t>M2512130001</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>統有企業</t>
+          <t>紀彥銘</t>
         </is>
       </c>
       <c r="C354" s="4"/>
-      <c r="D354" s="4"/>
+      <c r="D354" s="4" t="inlineStr">
+        <is>
+          <t>0988752337</t>
+        </is>
+      </c>
       <c r="E354" s="4"/>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -10528,24 +10532,20 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>M2509280008</t>
+          <t>V0001</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>維克斯</t>
+          <t>統有企業</t>
         </is>
       </c>
       <c r="C355" s="4"/>
-      <c r="D355" s="4" t="inlineStr">
-        <is>
-          <t>0917771787</t>
-        </is>
-      </c>
+      <c r="D355" s="4"/>
       <c r="E355" s="4"/>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -10557,18 +10557,18 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>M2510170002</t>
+          <t>M2509280008</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>練鎮宇</t>
+          <t>維克斯</t>
         </is>
       </c>
       <c r="C356" s="4"/>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>0952288706</t>
+          <t>0917771787</t>
         </is>
       </c>
       <c r="E356" s="4"/>
@@ -10586,18 +10586,18 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>M2602220003</t>
+          <t>M2510170002</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>羅丁一夫</t>
+          <t>練鎮宇</t>
         </is>
       </c>
       <c r="C357" s="4"/>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>0919339614</t>
+          <t>0952288706</t>
         </is>
       </c>
       <c r="E357" s="4"/>
@@ -10615,18 +10615,18 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>M2510180002</t>
+          <t>M2602220003</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>羅元隆</t>
+          <t>羅丁一夫</t>
         </is>
       </c>
       <c r="C358" s="4"/>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>0975866635</t>
+          <t>0919339614</t>
         </is>
       </c>
       <c r="E358" s="4"/>
@@ -10644,25 +10644,21 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>M2510090003</t>
+          <t>M2510180002</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>羅嘉銘</t>
+          <t>羅元隆</t>
         </is>
       </c>
       <c r="C359" s="4"/>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>0928093385</t>
-        </is>
-      </c>
-      <c r="E359" s="4" t="inlineStr">
-        <is>
-          <t>0985866052</t>
-        </is>
-      </c>
+          <t>0975866635</t>
+        </is>
+      </c>
+      <c r="E359" s="4"/>
       <c r="F359" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -10677,22 +10673,30 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>M2602240001</t>
+          <t>M2510090003</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>羅浩中</t>
+          <t>羅嘉銘</t>
         </is>
       </c>
       <c r="C360" s="4"/>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>0970905092</t>
-        </is>
-      </c>
-      <c r="E360" s="4"/>
-      <c r="F360" s="4"/>
+          <t>0928093385</t>
+        </is>
+      </c>
+      <c r="E360" s="4" t="inlineStr">
+        <is>
+          <t>0985866052</t>
+        </is>
+      </c>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G360" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -10702,26 +10706,22 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>M2511060003</t>
+          <t>M2602240001</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>翁名勳</t>
+          <t>羅浩中</t>
         </is>
       </c>
       <c r="C361" s="4"/>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>0955083317</t>
+          <t>0970905092</t>
         </is>
       </c>
       <c r="E361" s="4"/>
-      <c r="F361" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F361" s="4"/>
       <c r="G361" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -10731,18 +10731,18 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>M2509260057</t>
+          <t>M2511060003</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>翁國昌</t>
+          <t>翁名勳</t>
         </is>
       </c>
       <c r="C362" s="4"/>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>0918718772</t>
+          <t>0955083317</t>
         </is>
       </c>
       <c r="E362" s="4"/>
@@ -10760,22 +10760,18 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>M2511290001</t>
+          <t>M2509260057</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>翁國祥</t>
-        </is>
-      </c>
-      <c r="C363" s="4" t="inlineStr">
-        <is>
-          <t>新北新莊中信街65號1樓賣菜攤</t>
-        </is>
-      </c>
+          <t>翁國昌</t>
+        </is>
+      </c>
+      <c r="C363" s="4"/>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>0983900052</t>
+          <t>0918718772</t>
         </is>
       </c>
       <c r="E363" s="4"/>
@@ -10793,22 +10789,22 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>M2510010009</t>
+          <t>M2511290001</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩</t>
+          <t>翁國祥</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>未決定</t>
+          <t>新北新莊中信街65號1樓賣菜攤</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>0972757015</t>
+          <t>0983900052</t>
         </is>
       </c>
       <c r="E364" s="4"/>
@@ -10826,53 +10822,53 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
+          <t>M2510010009</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>翁敬恩</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>未決定</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>0972757015</t>
+        </is>
+      </c>
+      <c r="E365" s="4"/>
+      <c r="F365" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G365" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="4" t="inlineStr">
+        <is>
           <t>M2510010009-4</t>
         </is>
       </c>
-      <c r="B365" s="4" t="inlineStr">
+      <c r="B366" s="4" t="inlineStr">
         <is>
           <t>翁敬恩-文山</t>
         </is>
       </c>
-      <c r="C365" s="6" t="inlineStr">
+      <c r="C366" s="6" t="inlineStr">
         <is>
           <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
 收件聯絡電話:0937462412</t>
         </is>
       </c>
-      <c r="D365" s="4" t="inlineStr">
-        <is>
-          <t>0972757015</t>
-        </is>
-      </c>
-      <c r="E365" s="4"/>
-      <c r="F365" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
-      <c r="G365" s="5" t="inlineStr">
-        <is>
-          <t>附件管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="4" t="inlineStr">
-        <is>
-          <t>M2510010009-2</t>
-        </is>
-      </c>
-      <c r="B366" s="4" t="inlineStr">
-        <is>
-          <t>翁敬恩-樂華</t>
-        </is>
-      </c>
-      <c r="C366" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
-        </is>
-      </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
           <t>0972757015</t>
@@ -10893,17 +10889,17 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-3</t>
+          <t>M2510010009-2</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-永和</t>
+          <t>翁敬恩-樂華</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
+          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -10926,22 +10922,22 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-1</t>
+          <t>M2510010009-3</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-饒河</t>
+          <t>翁敬恩-永和</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>0975953978</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E368" s="4"/>
@@ -10959,18 +10955,22 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>M2510140004</t>
+          <t>M2510010009-1</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>翁漢忠</t>
-        </is>
-      </c>
-      <c r="C369" s="4"/>
+          <t>翁敬恩-饒河</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+        </is>
+      </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>0916150750</t>
+          <t>0975953978</t>
         </is>
       </c>
       <c r="E369" s="4"/>
@@ -10988,18 +10988,18 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>M2509260037</t>
+          <t>M2510140004</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>翁翌禎</t>
+          <t>翁漢忠</t>
         </is>
       </c>
       <c r="C370" s="4"/>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>0902308293</t>
+          <t>0916150750</t>
         </is>
       </c>
       <c r="E370" s="4"/>
@@ -11017,18 +11017,18 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>M2509280002</t>
+          <t>M2509260037</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>聶大中</t>
+          <t>翁翌禎</t>
         </is>
       </c>
       <c r="C371" s="4"/>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>0955059148</t>
+          <t>0902308293</t>
         </is>
       </c>
       <c r="E371" s="4"/>
@@ -11046,18 +11046,18 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>M2510220001</t>
+          <t>M2509280002</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>胡HU</t>
+          <t>聶大中</t>
         </is>
       </c>
       <c r="C372" s="4"/>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>0988603554</t>
+          <t>0955059148</t>
         </is>
       </c>
       <c r="E372" s="4"/>
@@ -11075,18 +11075,18 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>M2510100011</t>
+          <t>M2510220001</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>胡凱傑</t>
+          <t>胡HU</t>
         </is>
       </c>
       <c r="C373" s="4"/>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>0955888840</t>
+          <t>0988603554</t>
         </is>
       </c>
       <c r="E373" s="4"/>
@@ -11104,18 +11104,18 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>M2510090005</t>
+          <t>M2510100011</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>胡家榮</t>
+          <t>胡凱傑</t>
         </is>
       </c>
       <c r="C374" s="4"/>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>0933059025</t>
+          <t>0955888840</t>
         </is>
       </c>
       <c r="E374" s="4"/>
@@ -11133,18 +11133,18 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>M2511150001</t>
+          <t>M2510090005</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>胡家銘</t>
+          <t>胡家榮</t>
         </is>
       </c>
       <c r="C375" s="4"/>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>0986362263</t>
+          <t>0933059025</t>
         </is>
       </c>
       <c r="E375" s="4"/>
@@ -11162,18 +11162,18 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>M2511290003</t>
+          <t>M2511150001</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>胡峻強</t>
+          <t>胡家銘</t>
         </is>
       </c>
       <c r="C376" s="4"/>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>0953088041</t>
+          <t>0986362263</t>
         </is>
       </c>
       <c r="E376" s="4"/>
@@ -11191,18 +11191,18 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>M2603010001</t>
+          <t>M2511290003</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>胡辰煜</t>
+          <t>胡峻強</t>
         </is>
       </c>
       <c r="C377" s="4"/>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>0963903685</t>
+          <t>0953088041</t>
         </is>
       </c>
       <c r="E377" s="4"/>
@@ -11220,18 +11220,18 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>M2510040002</t>
+          <t>M2603010001</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>胡辰軒</t>
+          <t>胡辰煜</t>
         </is>
       </c>
       <c r="C378" s="4"/>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>0972094622</t>
+          <t>0963903685</t>
         </is>
       </c>
       <c r="E378" s="4"/>
@@ -11249,18 +11249,18 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>M2602280001</t>
+          <t>M2510040002</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>胡閎翔</t>
+          <t>胡辰軒</t>
         </is>
       </c>
       <c r="C379" s="4"/>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>0970556309</t>
+          <t>0972094622</t>
         </is>
       </c>
       <c r="E379" s="4"/>
@@ -11278,18 +11278,18 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>M2511290002</t>
+          <t>M2602280001</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>舒老闆</t>
+          <t>胡閎翔</t>
         </is>
       </c>
       <c r="C380" s="4"/>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>0979788818</t>
+          <t>0970556309</t>
         </is>
       </c>
       <c r="E380" s="4"/>
@@ -11307,19 +11307,15 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-2</t>
+          <t>M2511290002</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣</t>
-        </is>
-      </c>
-      <c r="C381" s="4" t="inlineStr">
-        <is>
-          <t>台北市松山區八德路三段12巷51弄46號</t>
-        </is>
-      </c>
+          <t>舒老闆</t>
+        </is>
+      </c>
+      <c r="C381" s="4"/>
       <c r="D381" s="4" t="inlineStr">
         <is>
           <t>0979788818</t>
@@ -11340,17 +11336,17 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-1</t>
+          <t>M2511290002-2</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧</t>
+          <t>舒老闆-夾鬥陣</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+          <t>台北市松山區八德路三段12巷51弄46號</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
@@ -11373,18 +11369,22 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>M2510140002</t>
+          <t>M2511290002-1</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>范姜敏中</t>
-        </is>
-      </c>
-      <c r="C383" s="4"/>
+          <t>舒老闆-寧寧</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+        </is>
+      </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>0937464692</t>
+          <t>0979788818</t>
         </is>
       </c>
       <c r="E383" s="4"/>
@@ -11402,18 +11402,18 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>M2510140003</t>
+          <t>M2510140002</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>范姜群成</t>
+          <t>范姜敏中</t>
         </is>
       </c>
       <c r="C384" s="4"/>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>0920565234</t>
+          <t>0937464692</t>
         </is>
       </c>
       <c r="E384" s="4"/>
@@ -11431,22 +11431,18 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>M2511300003</t>
+          <t>M2510140003</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>莊正當</t>
-        </is>
-      </c>
-      <c r="C385" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區建安街27號3樓</t>
-        </is>
-      </c>
+          <t>范姜群成</t>
+        </is>
+      </c>
+      <c r="C385" s="4"/>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>0983337218</t>
+          <t>0920565234</t>
         </is>
       </c>
       <c r="E385" s="4"/>
@@ -11464,22 +11460,22 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>M2510270004</t>
+          <t>M2511300003</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>莊淑玲</t>
+          <t>莊正當</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>新北市新莊區五工三路78巷36號</t>
+          <t>新北市新莊區建安街27號3樓</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>0922277383</t>
+          <t>0983337218</t>
         </is>
       </c>
       <c r="E386" s="4"/>
@@ -11497,18 +11493,22 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>M2510190002</t>
+          <t>M2510270004</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>莊耿華</t>
-        </is>
-      </c>
-      <c r="C387" s="4"/>
+          <t>莊淑玲</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工三路78巷36號</t>
+        </is>
+      </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>0938600334</t>
+          <t>0922277383</t>
         </is>
       </c>
       <c r="E387" s="4"/>
@@ -11526,18 +11526,18 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>M2509260005</t>
+          <t>M2510190002</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>莊莊</t>
+          <t>莊耿華</t>
         </is>
       </c>
       <c r="C388" s="4"/>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>0955985557</t>
+          <t>0938600334</t>
         </is>
       </c>
       <c r="E388" s="4"/>
@@ -11555,18 +11555,18 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>M2510100007</t>
+          <t>M2509260005</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>莊閔丞</t>
+          <t>莊莊</t>
         </is>
       </c>
       <c r="C389" s="4"/>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>0963320370</t>
+          <t>0955985557</t>
         </is>
       </c>
       <c r="E389" s="4"/>
@@ -11584,22 +11584,26 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>M2602240002</t>
+          <t>M2510100007</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>萬宗霖</t>
+          <t>莊閔丞</t>
         </is>
       </c>
       <c r="C390" s="4"/>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>0977082365</t>
+          <t>0963320370</t>
         </is>
       </c>
       <c r="E390" s="4"/>
-      <c r="F390" s="4"/>
+      <c r="F390" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G390" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -11609,26 +11613,22 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>M2510160001</t>
+          <t>M2602240002</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>葉力瑋</t>
+          <t>萬宗霖</t>
         </is>
       </c>
       <c r="C391" s="4"/>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>0979611911</t>
+          <t>0977082365</t>
         </is>
       </c>
       <c r="E391" s="4"/>
-      <c r="F391" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F391" s="4"/>
       <c r="G391" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -11638,18 +11638,18 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2510030002</t>
+          <t>M2510160001</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>葉家睿</t>
+          <t>葉力瑋</t>
         </is>
       </c>
       <c r="C392" s="4"/>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>0928112227</t>
+          <t>0979611911</t>
         </is>
       </c>
       <c r="E392" s="4"/>
@@ -11667,18 +11667,18 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>M2511050003</t>
+          <t>M2510030002</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>葉庭綸</t>
+          <t>葉家睿</t>
         </is>
       </c>
       <c r="C393" s="4"/>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>0966638685</t>
+          <t>0928112227</t>
         </is>
       </c>
       <c r="E393" s="4"/>
@@ -11696,18 +11696,18 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>M2510180001</t>
+          <t>M2511050003</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>葉建財</t>
+          <t>葉庭綸</t>
         </is>
       </c>
       <c r="C394" s="4"/>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>0989713349</t>
+          <t>0966638685</t>
         </is>
       </c>
       <c r="E394" s="4"/>
@@ -11725,18 +11725,18 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>M2510150001</t>
+          <t>M2510180001</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>葉彥均</t>
+          <t>葉建財</t>
         </is>
       </c>
       <c r="C395" s="4"/>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>0921436111</t>
+          <t>0989713349</t>
         </is>
       </c>
       <c r="E395" s="4"/>
@@ -11754,18 +11754,18 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>M2601220001</t>
+          <t>M2510150001</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>葉方奕</t>
+          <t>葉彥均</t>
         </is>
       </c>
       <c r="C396" s="4"/>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>0918386488</t>
+          <t>0921436111</t>
         </is>
       </c>
       <c r="E396" s="4"/>
@@ -11783,18 +11783,18 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>M2510260005</t>
+          <t>M2601220001</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>葉祈賢</t>
+          <t>葉方奕</t>
         </is>
       </c>
       <c r="C397" s="4"/>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>0955313212</t>
+          <t>0918386488</t>
         </is>
       </c>
       <c r="E397" s="4"/>
@@ -11812,18 +11812,18 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>M2509290012</t>
+          <t>M2510260005</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>葉維霆</t>
+          <t>葉祈賢</t>
         </is>
       </c>
       <c r="C398" s="4"/>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>0905120835</t>
+          <t>0955313212</t>
         </is>
       </c>
       <c r="E398" s="4"/>
@@ -11841,18 +11841,18 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>M2603050001</t>
+          <t>M2509290012</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>蔡仲凱</t>
+          <t>葉維霆</t>
         </is>
       </c>
       <c r="C399" s="4"/>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>0910733748</t>
+          <t>0905120835</t>
         </is>
       </c>
       <c r="E399" s="4"/>
@@ -11870,18 +11870,18 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>M2511080009</t>
+          <t>M2603050001</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>蔡伯鼎</t>
+          <t>蔡仲凱</t>
         </is>
       </c>
       <c r="C400" s="4"/>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>0933842593</t>
+          <t>0910733748</t>
         </is>
       </c>
       <c r="E400" s="4"/>
@@ -11899,18 +11899,18 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>M2512100001</t>
+          <t>M2511080009</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>蔡其騰</t>
+          <t>蔡伯鼎</t>
         </is>
       </c>
       <c r="C401" s="4"/>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>0988556732</t>
+          <t>0933842593</t>
         </is>
       </c>
       <c r="E401" s="4"/>
@@ -11928,22 +11928,18 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>M2603220001</t>
+          <t>M2512100001</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>蔡嘉章</t>
-        </is>
-      </c>
-      <c r="C402" s="4" t="inlineStr">
-        <is>
-          <t>樹林區太平路150巷8號娃娃機</t>
-        </is>
-      </c>
+          <t>蔡其騰</t>
+        </is>
+      </c>
+      <c r="C402" s="4"/>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>0973658657</t>
+          <t>0988556732</t>
         </is>
       </c>
       <c r="E402" s="4"/>
@@ -11961,18 +11957,22 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>M2509280001</t>
+          <t>M2603220001</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>蔡康志</t>
-        </is>
-      </c>
-      <c r="C403" s="4"/>
+          <t>蔡嘉章</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>樹林區太平路150巷8號娃娃機</t>
+        </is>
+      </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>0933942089</t>
+          <t>0973658657</t>
         </is>
       </c>
       <c r="E403" s="4"/>
@@ -11990,18 +11990,18 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>M2509260052</t>
+          <t>M2509280001</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>蔡志海</t>
+          <t>蔡康志</t>
         </is>
       </c>
       <c r="C404" s="4"/>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>0926616521</t>
+          <t>0933942089</t>
         </is>
       </c>
       <c r="E404" s="4"/>
@@ -12019,18 +12019,18 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>M2602120003</t>
+          <t>M2509260052</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>蔡承勳</t>
+          <t>蔡志海</t>
         </is>
       </c>
       <c r="C405" s="4"/>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>0979975919</t>
+          <t>0926616521</t>
         </is>
       </c>
       <c r="E405" s="4"/>
@@ -12048,18 +12048,18 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>M2509290002</t>
+          <t>M2602120003</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>蔡振元</t>
+          <t>蔡承勳</t>
         </is>
       </c>
       <c r="C406" s="4"/>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>0908590858</t>
+          <t>0979975919</t>
         </is>
       </c>
       <c r="E406" s="4"/>
@@ -12077,18 +12077,18 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>M2601090001</t>
+          <t>M2509290002</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>蔡昌翔</t>
+          <t>蔡振元</t>
         </is>
       </c>
       <c r="C407" s="4"/>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>0973324888</t>
+          <t>0908590858</t>
         </is>
       </c>
       <c r="E407" s="4"/>
@@ -12106,22 +12106,18 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>M2509260011</t>
+          <t>M2601090001</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>蔡智全</t>
-        </is>
-      </c>
-      <c r="C408" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區雙園街110號1樓</t>
-        </is>
-      </c>
+          <t>蔡昌翔</t>
+        </is>
+      </c>
+      <c r="C408" s="4"/>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>0930167280</t>
+          <t>0973324888</t>
         </is>
       </c>
       <c r="E408" s="4"/>
@@ -12139,22 +12135,22 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>M2509260049</t>
+          <t>M2509260011</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>蔡瀚霆</t>
+          <t>蔡智全</t>
         </is>
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區保平路207號</t>
+          <t>台北市萬華區雙園街110號1樓</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>0932014776</t>
+          <t>0930167280</t>
         </is>
       </c>
       <c r="E409" s="4"/>
@@ -12172,18 +12168,22 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>M2510010007</t>
+          <t>M2509260049</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>蔡秉橋</t>
-        </is>
-      </c>
-      <c r="C410" s="4"/>
+          <t>蔡瀚霆</t>
+        </is>
+      </c>
+      <c r="C410" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區保平路207號</t>
+        </is>
+      </c>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>0987000184</t>
+          <t>0932014776</t>
         </is>
       </c>
       <c r="E410" s="4"/>
@@ -12201,18 +12201,18 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>M2509270009</t>
+          <t>M2510010007</t>
         </is>
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>蔡育昇</t>
+          <t>蔡秉橋</t>
         </is>
       </c>
       <c r="C411" s="4"/>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>0918058903</t>
+          <t>0987000184</t>
         </is>
       </c>
       <c r="E411" s="4"/>
@@ -12230,18 +12230,18 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>M2603180001</t>
+          <t>M2509270009</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>蔡貞瑜</t>
+          <t>蔡育昇</t>
         </is>
       </c>
       <c r="C412" s="4"/>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>0917372131</t>
+          <t>0918058903</t>
         </is>
       </c>
       <c r="E412" s="4"/>
@@ -12259,18 +12259,18 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>M2510070001</t>
+          <t>M2603180001</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>蔡辰旻</t>
+          <t>蔡貞瑜</t>
         </is>
       </c>
       <c r="C413" s="4"/>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>0982621245</t>
+          <t>0917372131</t>
         </is>
       </c>
       <c r="E413" s="4"/>
@@ -12288,7 +12288,7 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>M2602010003</t>
+          <t>M2510070001</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
@@ -12299,7 +12299,7 @@
       <c r="C414" s="4"/>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>0903162818</t>
+          <t>0982621245</t>
         </is>
       </c>
       <c r="E414" s="4"/>
@@ -12317,18 +12317,18 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>M2511270001</t>
+          <t>M2602010003</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>蔡進盛</t>
+          <t>蔡辰旻</t>
         </is>
       </c>
       <c r="C415" s="4"/>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>0989387966</t>
+          <t>0903162818</t>
         </is>
       </c>
       <c r="E415" s="4"/>
@@ -12346,18 +12346,18 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>M2511030001</t>
+          <t>M2511270001</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>蔡鳳來</t>
+          <t>蔡進盛</t>
         </is>
       </c>
       <c r="C416" s="4"/>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>0963550931</t>
+          <t>0989387966</t>
         </is>
       </c>
       <c r="E416" s="4"/>
@@ -12375,18 +12375,18 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>M2509270016</t>
+          <t>M2511030001</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>蕭仲安</t>
+          <t>蔡鳳來</t>
         </is>
       </c>
       <c r="C417" s="4"/>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>0930601899</t>
+          <t>0963550931</t>
         </is>
       </c>
       <c r="E417" s="4"/>
@@ -12404,18 +12404,18 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>M2509270017</t>
+          <t>M2509270016</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>蕭又瑋</t>
+          <t>蕭仲安</t>
         </is>
       </c>
       <c r="C418" s="4"/>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>0922675798</t>
+          <t>0930601899</t>
         </is>
       </c>
       <c r="E418" s="4"/>
@@ -12433,18 +12433,18 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>M2509280009</t>
+          <t>M2509270017</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>蕭宇傑</t>
+          <t>蕭又瑋</t>
         </is>
       </c>
       <c r="C419" s="4"/>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>0989977822</t>
+          <t>0922675798</t>
         </is>
       </c>
       <c r="E419" s="4"/>
@@ -12462,18 +12462,18 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>M2510190006</t>
+          <t>M2509280009</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>蕭毓</t>
+          <t>蕭宇傑</t>
         </is>
       </c>
       <c r="C420" s="4"/>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>0975199046</t>
+          <t>0989977822</t>
         </is>
       </c>
       <c r="E420" s="4"/>
@@ -12491,22 +12491,18 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>M2510090006</t>
+          <t>M2510190006</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>蕭燁鴻</t>
-        </is>
-      </c>
-      <c r="C421" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區金龍路183號1樓</t>
-        </is>
-      </c>
+          <t>蕭毓</t>
+        </is>
+      </c>
+      <c r="C421" s="4"/>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>0917882269</t>
+          <t>0975199046</t>
         </is>
       </c>
       <c r="E421" s="4"/>
@@ -12524,18 +12520,22 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>M2510160008</t>
+          <t>M2510090006</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>蕭韻文</t>
-        </is>
-      </c>
-      <c r="C422" s="4"/>
+          <t>蕭燁鴻</t>
+        </is>
+      </c>
+      <c r="C422" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區金龍路183號1樓</t>
+        </is>
+      </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>0911297473</t>
+          <t>0917882269</t>
         </is>
       </c>
       <c r="E422" s="4"/>
@@ -12553,18 +12553,18 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>M2509300014</t>
+          <t>M2510160008</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>藍駿偉</t>
+          <t>蕭韻文</t>
         </is>
       </c>
       <c r="C423" s="4"/>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>0936152586</t>
+          <t>0911297473</t>
         </is>
       </c>
       <c r="E423" s="4"/>
@@ -12582,18 +12582,18 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>M2511080007</t>
+          <t>M2509300014</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>蘇嘉蓉</t>
+          <t>藍駿偉</t>
         </is>
       </c>
       <c r="C424" s="4"/>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>0937074336</t>
+          <t>0936152586</t>
         </is>
       </c>
       <c r="E424" s="4"/>
@@ -12611,18 +12611,18 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>M2511060002</t>
+          <t>M2511080007</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>蘇國貿</t>
+          <t>蘇嘉蓉</t>
         </is>
       </c>
       <c r="C425" s="4"/>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>0922250285</t>
+          <t>0937074336</t>
         </is>
       </c>
       <c r="E425" s="4"/>
@@ -12640,18 +12640,18 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>M2511280004</t>
+          <t>M2511060002</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>蘇家明</t>
+          <t>蘇國貿</t>
         </is>
       </c>
       <c r="C426" s="4"/>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>0916836765</t>
+          <t>0922250285</t>
         </is>
       </c>
       <c r="E426" s="4"/>
@@ -12669,18 +12669,18 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>M2510300002</t>
+          <t>M2511280004</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>蘇小好</t>
+          <t>蘇家明</t>
         </is>
       </c>
       <c r="C427" s="4"/>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>0981870981</t>
+          <t>0916836765</t>
         </is>
       </c>
       <c r="E427" s="4"/>
@@ -12698,18 +12698,18 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>M2509260021</t>
+          <t>M2510300002</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>蘇彥彰</t>
+          <t>蘇小好</t>
         </is>
       </c>
       <c r="C428" s="4"/>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>0983060026</t>
+          <t>0981870981</t>
         </is>
       </c>
       <c r="E428" s="4"/>
@@ -12727,22 +12727,18 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>M2510240001</t>
+          <t>M2509260021</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>蘇志勇</t>
-        </is>
-      </c>
-      <c r="C429" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
-        </is>
-      </c>
+          <t>蘇彥彰</t>
+        </is>
+      </c>
+      <c r="C429" s="4"/>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>0910051586</t>
+          <t>0983060026</t>
         </is>
       </c>
       <c r="E429" s="4"/>
@@ -12760,18 +12756,22 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>M2602150002</t>
+          <t>M2510240001</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>蘇昱銘</t>
-        </is>
-      </c>
-      <c r="C430" s="4"/>
+          <t>蘇志勇</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
+        </is>
+      </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>0916324119</t>
+          <t>0910051586</t>
         </is>
       </c>
       <c r="E430" s="4"/>
@@ -12789,18 +12789,18 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>M2510050003</t>
+          <t>M2602150002</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>蘇睿慶</t>
+          <t>蘇昱銘</t>
         </is>
       </c>
       <c r="C431" s="4"/>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>0937766339</t>
+          <t>0916324119</t>
         </is>
       </c>
       <c r="E431" s="4"/>
@@ -12818,18 +12818,18 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>M2601180001</t>
+          <t>M2510050003</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>蠟筆</t>
+          <t>蘇睿慶</t>
         </is>
       </c>
       <c r="C432" s="4"/>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>0976321321</t>
+          <t>0937766339</t>
         </is>
       </c>
       <c r="E432" s="4"/>
@@ -12847,18 +12847,18 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>M2512160002</t>
+          <t>M2601180001</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>褚朕誠</t>
+          <t>蠟筆</t>
         </is>
       </c>
       <c r="C433" s="4"/>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>0972217495</t>
+          <t>0976321321</t>
         </is>
       </c>
       <c r="E433" s="4"/>
@@ -12876,18 +12876,18 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>M2512200002</t>
+          <t>M2512160002</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>褚銘漢</t>
+          <t>褚朕誠</t>
         </is>
       </c>
       <c r="C434" s="4"/>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>0925886065</t>
+          <t>0972217495</t>
         </is>
       </c>
       <c r="E434" s="4"/>
@@ -12905,18 +12905,18 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>M2512170002</t>
+          <t>M2512200002</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>許俊鴻</t>
+          <t>褚銘漢</t>
         </is>
       </c>
       <c r="C435" s="4"/>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>0973630391</t>
+          <t>0925886065</t>
         </is>
       </c>
       <c r="E435" s="4"/>
@@ -12934,18 +12934,18 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>M2510050013</t>
+          <t>M2512170002</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>許凱傑</t>
+          <t>許俊鴻</t>
         </is>
       </c>
       <c r="C436" s="4"/>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>0955306971</t>
+          <t>0973630391</t>
         </is>
       </c>
       <c r="E436" s="4"/>
@@ -12963,18 +12963,18 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>M2511110001</t>
+          <t>M2510050013</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>許哲豪</t>
+          <t>許凱傑</t>
         </is>
       </c>
       <c r="C437" s="4"/>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>0985191149</t>
+          <t>0955306971</t>
         </is>
       </c>
       <c r="E437" s="4"/>
@@ -12992,18 +12992,18 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>M2602030001</t>
+          <t>M2511110001</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>許士彥</t>
+          <t>許哲豪</t>
         </is>
       </c>
       <c r="C438" s="4"/>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>0913558692</t>
+          <t>0985191149</t>
         </is>
       </c>
       <c r="E438" s="4"/>
@@ -13021,18 +13021,18 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>M2509290018</t>
+          <t>M2602030001</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>許天寶</t>
+          <t>許士彥</t>
         </is>
       </c>
       <c r="C439" s="4"/>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>0936088850</t>
+          <t>0913558692</t>
         </is>
       </c>
       <c r="E439" s="4"/>
@@ -13050,18 +13050,18 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>M2510160005</t>
+          <t>M2509290018</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>許宥蓁</t>
+          <t>許天寶</t>
         </is>
       </c>
       <c r="C440" s="4"/>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>0938473255</t>
+          <t>0936088850</t>
         </is>
       </c>
       <c r="E440" s="4"/>
@@ -13079,18 +13079,18 @@
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>M2512020001</t>
+          <t>M2510160005</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>許家豪</t>
+          <t>許宥蓁</t>
         </is>
       </c>
       <c r="C441" s="4"/>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>0983215242</t>
+          <t>0938473255</t>
         </is>
       </c>
       <c r="E441" s="4"/>
@@ -13108,18 +13108,18 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>M2510110007</t>
+          <t>M2512020001</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>許峻銓</t>
+          <t>許家豪</t>
         </is>
       </c>
       <c r="C442" s="4"/>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>0979770033</t>
+          <t>0983215242</t>
         </is>
       </c>
       <c r="E442" s="4"/>
@@ -13137,18 +13137,18 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>M2511260001</t>
+          <t>M2510110007</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>許志帆</t>
+          <t>許峻銓</t>
         </is>
       </c>
       <c r="C443" s="4"/>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>0936639358</t>
+          <t>0979770033</t>
         </is>
       </c>
       <c r="E443" s="4"/>
@@ -13166,18 +13166,18 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>M2510310001</t>
+          <t>M2511260001</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>許志豪</t>
+          <t>許志帆</t>
         </is>
       </c>
       <c r="C444" s="4"/>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>0971080606</t>
+          <t>0936639358</t>
         </is>
       </c>
       <c r="E444" s="4"/>
@@ -13195,18 +13195,18 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>M2601040001</t>
+          <t>M2510310001</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>許惠笙</t>
+          <t>許志豪</t>
         </is>
       </c>
       <c r="C445" s="4"/>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>0987890463</t>
+          <t>0971080606</t>
         </is>
       </c>
       <c r="E445" s="4"/>
@@ -13224,18 +13224,18 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>M2603080002</t>
+          <t>M2601040001</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>許汶瑋</t>
+          <t>許惠笙</t>
         </is>
       </c>
       <c r="C446" s="4"/>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>0988166792</t>
+          <t>0987890463</t>
         </is>
       </c>
       <c r="E446" s="4"/>
@@ -13253,22 +13253,18 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>M2509140001</t>
+          <t>M2603080002</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>許煥杰</t>
-        </is>
-      </c>
-      <c r="C447" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區藝文二街88號8樓</t>
-        </is>
-      </c>
+          <t>許汶瑋</t>
+        </is>
+      </c>
+      <c r="C447" s="4"/>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>0913785888</t>
+          <t>0988166792</t>
         </is>
       </c>
       <c r="E447" s="4"/>
@@ -13286,18 +13282,22 @@
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>M2510010001</t>
+          <t>M2509140001</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>許硯棠</t>
-        </is>
-      </c>
-      <c r="C448" s="4"/>
+          <t>許煥杰</t>
+        </is>
+      </c>
+      <c r="C448" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區藝文二街88號8樓</t>
+        </is>
+      </c>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>0983238652</t>
+          <t>0913785888</t>
         </is>
       </c>
       <c r="E448" s="4"/>
@@ -13315,18 +13315,18 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>M2509270001</t>
+          <t>M2510010001</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>許竣榤</t>
+          <t>許硯棠</t>
         </is>
       </c>
       <c r="C449" s="4"/>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>0955598097</t>
+          <t>0983238652</t>
         </is>
       </c>
       <c r="E449" s="4"/>
@@ -13344,18 +13344,18 @@
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>M2510240002</t>
+          <t>M2509270001</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>許芫睿</t>
+          <t>許竣榤</t>
         </is>
       </c>
       <c r="C450" s="4"/>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>0975057699</t>
+          <t>0955598097</t>
         </is>
       </c>
       <c r="E450" s="4"/>
@@ -13373,18 +13373,18 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>M2509290013</t>
+          <t>M2510240002</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>許雅蓁</t>
+          <t>許芫睿</t>
         </is>
       </c>
       <c r="C451" s="4"/>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>0982339939</t>
+          <t>0975057699</t>
         </is>
       </c>
       <c r="E451" s="4"/>
@@ -13402,18 +13402,18 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>M2509260055</t>
+          <t>M2509290013</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>許靜蔆</t>
+          <t>許雅蓁</t>
         </is>
       </c>
       <c r="C452" s="4"/>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>0928060395</t>
+          <t>0982339939</t>
         </is>
       </c>
       <c r="E452" s="4"/>
@@ -13431,18 +13431,18 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>M2509260027</t>
+          <t>M2509260055</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>詹傑克</t>
+          <t>許靜蔆</t>
         </is>
       </c>
       <c r="C453" s="4"/>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>0968688080</t>
+          <t>0928060395</t>
         </is>
       </c>
       <c r="E453" s="4"/>
@@ -13460,18 +13460,18 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>M2602010004</t>
+          <t>M2509260027</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>詹凱翔</t>
+          <t>詹傑克</t>
         </is>
       </c>
       <c r="C454" s="4"/>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>0963496660</t>
+          <t>0968688080</t>
         </is>
       </c>
       <c r="E454" s="4"/>
@@ -13489,18 +13489,18 @@
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>M2601270001</t>
+          <t>M2602010004</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>詹朝輝</t>
+          <t>詹凱翔</t>
         </is>
       </c>
       <c r="C455" s="4"/>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>0968490321</t>
+          <t>0963496660</t>
         </is>
       </c>
       <c r="E455" s="4"/>
@@ -13518,18 +13518,18 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>M2601170004</t>
+          <t>M2601270001</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>詹煜騰</t>
+          <t>詹朝輝</t>
         </is>
       </c>
       <c r="C456" s="4"/>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>0939919344</t>
+          <t>0968490321</t>
         </is>
       </c>
       <c r="E456" s="4"/>
@@ -13547,18 +13547,18 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>M2509280003</t>
+          <t>M2601170004</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>詹皇</t>
+          <t>詹煜騰</t>
         </is>
       </c>
       <c r="C457" s="4"/>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>0916037915</t>
+          <t>0939919344</t>
         </is>
       </c>
       <c r="E457" s="4"/>
@@ -13576,18 +13576,18 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>M2510030001</t>
+          <t>M2509280003</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>詹皇宥</t>
+          <t>詹皇</t>
         </is>
       </c>
       <c r="C458" s="4"/>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>0919367080</t>
+          <t>0916037915</t>
         </is>
       </c>
       <c r="E458" s="4"/>
@@ -13605,22 +13605,18 @@
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>M2509290016</t>
+          <t>M2510030001</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>詹育銘</t>
-        </is>
-      </c>
-      <c r="C459" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區撫順街25號1樓</t>
-        </is>
-      </c>
+          <t>詹皇宥</t>
+        </is>
+      </c>
+      <c r="C459" s="4"/>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>0926962322</t>
+          <t>0919367080</t>
         </is>
       </c>
       <c r="E459" s="4"/>
@@ -13638,22 +13634,22 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>M2510270001</t>
+          <t>M2509290016</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>謝亞倫</t>
+          <t>詹育銘</t>
         </is>
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>新北市淡水區北投里北投子49-1號</t>
+          <t>台北市中山區撫順街25號1樓</t>
         </is>
       </c>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>0922409070</t>
+          <t>0926962322</t>
         </is>
       </c>
       <c r="E460" s="4"/>
@@ -13671,18 +13667,22 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>M2510040004</t>
+          <t>M2510270001</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>謝佳蓉</t>
-        </is>
-      </c>
-      <c r="C461" s="4"/>
+          <t>謝亞倫</t>
+        </is>
+      </c>
+      <c r="C461" s="4" t="inlineStr">
+        <is>
+          <t>新北市淡水區北投里北投子49-1號</t>
+        </is>
+      </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>0976958679</t>
+          <t>0922409070</t>
         </is>
       </c>
       <c r="E461" s="4"/>
@@ -13700,18 +13700,18 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>M2509300019</t>
+          <t>M2510040004</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>謝光明</t>
+          <t>謝佳蓉</t>
         </is>
       </c>
       <c r="C462" s="4"/>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>0983011754</t>
+          <t>0976958679</t>
         </is>
       </c>
       <c r="E462" s="4"/>
@@ -13729,22 +13729,18 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>M2512140002</t>
+          <t>M2509300019</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>謝孟辰</t>
-        </is>
-      </c>
-      <c r="C463" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
-        </is>
-      </c>
+          <t>謝光明</t>
+        </is>
+      </c>
+      <c r="C463" s="4"/>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>0953900309</t>
+          <t>0983011754</t>
         </is>
       </c>
       <c r="E463" s="4"/>
@@ -13762,18 +13758,22 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>M2509270007</t>
+          <t>M2512140002</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>謝建衫</t>
-        </is>
-      </c>
-      <c r="C464" s="4"/>
+          <t>謝孟辰</t>
+        </is>
+      </c>
+      <c r="C464" s="4" t="inlineStr">
+        <is>
+          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
+        </is>
+      </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>0918238090</t>
+          <t>0953900309</t>
         </is>
       </c>
       <c r="E464" s="4"/>
@@ -13791,18 +13791,18 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>M2510150005</t>
+          <t>M2509270007</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>謝文懷</t>
+          <t>謝建衫</t>
         </is>
       </c>
       <c r="C465" s="4"/>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>0989813659</t>
+          <t>0918238090</t>
         </is>
       </c>
       <c r="E465" s="4"/>
@@ -13820,18 +13820,18 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>M2510130004</t>
+          <t>M2510150005</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>謝桂仁</t>
+          <t>謝文懷</t>
         </is>
       </c>
       <c r="C466" s="4"/>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>0938357603</t>
+          <t>0989813659</t>
         </is>
       </c>
       <c r="E466" s="4"/>
@@ -13849,18 +13849,18 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>M2510050002</t>
+          <t>M2510130004</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>謝舒帆</t>
+          <t>謝桂仁</t>
         </is>
       </c>
       <c r="C467" s="4"/>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>0980699503</t>
+          <t>0938357603</t>
         </is>
       </c>
       <c r="E467" s="4"/>
@@ -13878,18 +13878,18 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>M2510040008</t>
+          <t>M2510050002</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>謝荌核</t>
+          <t>謝舒帆</t>
         </is>
       </c>
       <c r="C468" s="4"/>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>0988302836</t>
+          <t>0980699503</t>
         </is>
       </c>
       <c r="E468" s="4"/>
@@ -13907,18 +13907,18 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>M2511300006</t>
+          <t>M2510040008</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>謝詠全</t>
+          <t>謝荌核</t>
         </is>
       </c>
       <c r="C469" s="4"/>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>0977077044</t>
+          <t>0988302836</t>
         </is>
       </c>
       <c r="E469" s="4"/>
@@ -13936,18 +13936,18 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>M2603200003</t>
+          <t>M2511300006</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>譚淵修</t>
+          <t>謝詠全</t>
         </is>
       </c>
       <c r="C470" s="4"/>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>0910322500</t>
+          <t>0977077044</t>
         </is>
       </c>
       <c r="E470" s="4"/>
@@ -13965,18 +13965,18 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>M2510040011</t>
+          <t>M2603200003</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>賴先生</t>
+          <t>譚淵修</t>
         </is>
       </c>
       <c r="C471" s="4"/>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>0965351801</t>
+          <t>0910322500</t>
         </is>
       </c>
       <c r="E471" s="4"/>
@@ -13994,18 +13994,18 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>M2603080001</t>
+          <t>M2510040011</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>賴品豪</t>
+          <t>賴先生</t>
         </is>
       </c>
       <c r="C472" s="4"/>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>0981379127</t>
+          <t>0965351801</t>
         </is>
       </c>
       <c r="E472" s="4"/>
@@ -14023,18 +14023,18 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>M2511010005</t>
+          <t>M2603080001</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>賴彥安</t>
+          <t>賴品豪</t>
         </is>
       </c>
       <c r="C473" s="4"/>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>0913102110</t>
+          <t>0981379127</t>
         </is>
       </c>
       <c r="E473" s="4"/>
@@ -14052,22 +14052,18 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>M2603280001</t>
+          <t>M2511010005</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>賴柏舟</t>
-        </is>
-      </c>
-      <c r="C474" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股五福路11號</t>
-        </is>
-      </c>
+          <t>賴彥安</t>
+        </is>
+      </c>
+      <c r="C474" s="4"/>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>0979131818</t>
+          <t>0913102110</t>
         </is>
       </c>
       <c r="E474" s="4"/>
@@ -14085,18 +14081,22 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
-        </is>
-      </c>
-      <c r="C475" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C475" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E475" s="4"/>
@@ -14114,18 +14114,18 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
+          <t>賴珊珊</t>
         </is>
       </c>
       <c r="C476" s="4"/>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E476" s="4"/>
@@ -14143,22 +14143,18 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C477" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C477" s="4"/>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E477" s="4"/>
@@ -14176,22 +14172,22 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E478" s="4"/>
@@ -14209,22 +14205,22 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>趙云璟</t>
         </is>
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E479" s="4"/>
@@ -14242,18 +14238,22 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C480" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C480" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E480" s="4"/>
@@ -14271,18 +14271,18 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C481" s="4"/>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E481" s="4"/>
@@ -14300,18 +14300,18 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C482" s="4"/>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0986258793</t>
         </is>
       </c>
       <c r="E482" s="4"/>
@@ -14329,20 +14329,24 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C483" s="4"/>
-      <c r="D483" s="4"/>
+      <c r="D483" s="4" t="inlineStr">
+        <is>
+          <t>0982484963</t>
+        </is>
+      </c>
       <c r="E483" s="4"/>
       <c r="F483" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G483" s="5" t="inlineStr">
@@ -14354,24 +14358,20 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C484" s="4"/>
-      <c r="D484" s="4" t="inlineStr">
-        <is>
-          <t>0981898339</t>
-        </is>
-      </c>
+      <c r="D484" s="4"/>
       <c r="E484" s="4"/>
       <c r="F484" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G484" s="5" t="inlineStr">
@@ -14383,18 +14383,18 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C485" s="4"/>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>0903921531</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E485" s="4"/>
@@ -14412,18 +14412,18 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C486" s="4"/>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E486" s="4"/>
@@ -14441,18 +14441,18 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C487" s="4"/>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E487" s="4"/>
@@ -14470,18 +14470,18 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C488" s="4"/>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E488" s="4"/>
@@ -14499,18 +14499,18 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱振為</t>
         </is>
       </c>
       <c r="C489" s="4"/>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E489" s="4"/>
@@ -14528,22 +14528,18 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C490" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱政傑</t>
+        </is>
+      </c>
+      <c r="C490" s="4"/>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E490" s="4"/>
@@ -14561,18 +14557,22 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
-        </is>
-      </c>
-      <c r="C491" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C491" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E491" s="4"/>
@@ -14590,18 +14590,18 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C492" s="4"/>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E492" s="4"/>
@@ -14619,18 +14619,18 @@
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C493" s="4"/>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E493" s="4"/>
@@ -14648,7 +14648,7 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B494" s="4" t="inlineStr">
@@ -14677,18 +14677,18 @@
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C495" s="4"/>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E495" s="4"/>
@@ -14706,16 +14706,20 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C496" s="4"/>
-      <c r="D496" s="4"/>
+      <c r="D496" s="4" t="inlineStr">
+        <is>
+          <t>0935329653</t>
+        </is>
+      </c>
       <c r="E496" s="4"/>
       <c r="F496" s="4" t="inlineStr">
         <is>
@@ -14731,20 +14735,16 @@
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C497" s="4"/>
-      <c r="D497" s="4" t="inlineStr">
-        <is>
-          <t>0976588171</t>
-        </is>
-      </c>
+      <c r="D497" s="4"/>
       <c r="E497" s="4"/>
       <c r="F497" s="4" t="inlineStr">
         <is>
@@ -14760,18 +14760,18 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C498" s="4"/>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>0972128080</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E498" s="4"/>
@@ -14789,18 +14789,18 @@
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C499" s="4"/>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E499" s="4"/>
@@ -14818,18 +14818,18 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C500" s="4"/>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E500" s="4"/>
@@ -14847,18 +14847,18 @@
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C501" s="4"/>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E501" s="4"/>
@@ -14876,18 +14876,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14905,18 +14905,18 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C503" s="4"/>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E503" s="4"/>
@@ -14934,18 +14934,18 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C504" s="4"/>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -14963,18 +14963,18 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭鼎昇</t>
         </is>
       </c>
       <c r="C505" s="4"/>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E505" s="4"/>
@@ -14992,22 +14992,18 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C506" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>鄒育燁</t>
+        </is>
+      </c>
+      <c r="C506" s="4"/>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15025,18 +15021,22 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
-        </is>
-      </c>
-      <c r="C507" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C507" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15054,18 +15054,18 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C508" s="4"/>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E508" s="4"/>
@@ -15083,18 +15083,18 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C509" s="4"/>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E509" s="4"/>
@@ -15112,18 +15112,18 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C510" s="4"/>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E510" s="4"/>
@@ -15141,18 +15141,18 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C511" s="4"/>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E511" s="4"/>
@@ -15170,18 +15170,18 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C512" s="4"/>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E512" s="4"/>
@@ -15199,18 +15199,18 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭秉霖</t>
         </is>
       </c>
       <c r="C513" s="4"/>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E513" s="4"/>
@@ -15228,22 +15228,18 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C514" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C514" s="4"/>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E514" s="4"/>
@@ -15261,26 +15257,30 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>鄭雁宇</t>
+          <t>鄭鉅耀</t>
         </is>
       </c>
       <c r="C515" s="4" t="inlineStr">
         <is>
-          <t>桃園區國聖二街145號5樓之1</t>
+          <t>新北市五股區成泰路二段208號</t>
         </is>
       </c>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E515" s="4"/>
-      <c r="F515" s="4"/>
+      <c r="F515" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G515" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15290,26 +15290,26 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C516" s="4"/>
+          <t>鄭雁宇</t>
+        </is>
+      </c>
+      <c r="C516" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E516" s="4"/>
-      <c r="F516" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F516" s="4"/>
       <c r="G516" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15319,18 +15319,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15348,18 +15348,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C518" s="4"/>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E518" s="4"/>
@@ -15377,18 +15377,18 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C519" s="4"/>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E519" s="4"/>
@@ -15406,18 +15406,18 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾銘峰</t>
         </is>
       </c>
       <c r="C520" s="4"/>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E520" s="4"/>
@@ -15435,22 +15435,18 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C521" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鐘國禎</t>
+        </is>
+      </c>
+      <c r="C521" s="4"/>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E521" s="4"/>
@@ -15468,24 +15464,28 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2603270001</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>鐘駿霆</t>
-        </is>
-      </c>
-      <c r="C522" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C522" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D522" s="4" t="inlineStr">
         <is>
-          <t>0919331886</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E522" s="4"/>
       <c r="F522" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G522" s="5" t="inlineStr">
@@ -15497,24 +15497,24 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
+          <t>鐘駿霆</t>
         </is>
       </c>
       <c r="C523" s="4"/>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E523" s="4"/>
       <c r="F523" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G523" s="5" t="inlineStr">
@@ -15526,22 +15526,18 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C524" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>阮海德</t>
+        </is>
+      </c>
+      <c r="C524" s="4"/>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E524" s="4"/>
@@ -15559,18 +15555,22 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
-        </is>
-      </c>
-      <c r="C525" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C525" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E525" s="4"/>
@@ -15588,18 +15588,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
+          <t>阿源</t>
         </is>
       </c>
       <c r="C526" s="4"/>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15617,22 +15617,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C527" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿良</t>
+        </is>
+      </c>
+      <c r="C527" s="4"/>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15650,18 +15646,22 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
-        </is>
-      </c>
-      <c r="C528" s="4"/>
+          <t>陳仲盟</t>
+        </is>
+      </c>
+      <c r="C528" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
+        </is>
+      </c>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15679,22 +15679,18 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
-        </is>
-      </c>
-      <c r="C529" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區日和街7號22樓</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C529" s="4"/>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15712,22 +15708,22 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
+          <t>陳俊安</t>
         </is>
       </c>
       <c r="C530" s="4" t="inlineStr">
         <is>
-          <t>板橋大觀路1段28巷118-1號</t>
+          <t>新北市土城區日和街7號22樓</t>
         </is>
       </c>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15745,18 +15741,22 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C531" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C531" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15774,18 +15774,18 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C532" s="4"/>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15803,18 +15803,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C533" s="4"/>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15832,18 +15832,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E534" s="4"/>
@@ -15861,18 +15861,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C535" s="4"/>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15890,18 +15890,18 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C536" s="4"/>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E536" s="4"/>
@@ -15919,22 +15919,26 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C537" s="4"/>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E537" s="4"/>
-      <c r="F537" s="4"/>
+      <c r="F537" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G537" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15944,26 +15948,22 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C538" s="4"/>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E538" s="4"/>
-      <c r="F538" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F538" s="4"/>
       <c r="G538" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -15973,18 +15973,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E539" s="4"/>
@@ -16002,18 +16002,18 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳奕融</t>
         </is>
       </c>
       <c r="C540" s="4"/>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16031,22 +16031,18 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C541" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕閔</t>
+        </is>
+      </c>
+      <c r="C541" s="4"/>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16064,18 +16060,22 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2603260001</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>陳威宇</t>
-        </is>
-      </c>
-      <c r="C542" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C542" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0958186337</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E542" s="4"/>
@@ -16093,18 +16093,18 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C543" s="4"/>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16122,18 +16122,18 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C544" s="4"/>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E544" s="4"/>
@@ -16151,18 +16151,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16180,18 +16180,18 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
+          <t>陳子杰</t>
         </is>
       </c>
       <c r="C546" s="4"/>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16209,18 +16209,18 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
+          <t>陳宏文</t>
         </is>
       </c>
       <c r="C547" s="4"/>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E547" s="4"/>
@@ -16238,22 +16238,18 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C548" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳宏達</t>
+        </is>
+      </c>
+      <c r="C548" s="4"/>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E548" s="4"/>
@@ -16271,18 +16267,22 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
-        </is>
-      </c>
-      <c r="C549" s="4"/>
+          <t>陳家偉</t>
+        </is>
+      </c>
+      <c r="C549" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市神農路一段72號</t>
+        </is>
+      </c>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E549" s="4"/>
@@ -16300,18 +16300,18 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
+          <t>陳小雨</t>
         </is>
       </c>
       <c r="C550" s="4"/>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E550" s="4"/>
@@ -16329,22 +16329,18 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
-        </is>
-      </c>
-      <c r="C551" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
-        </is>
-      </c>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="C551" s="4"/>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E551" s="4"/>
@@ -16362,22 +16358,22 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
+          <t>陳建宏(花蓮)</t>
         </is>
       </c>
       <c r="C552" s="4" t="inlineStr">
         <is>
-          <t>新北市三重區仁美街125號</t>
+          <t>花蓮縣新城鄉佳林31之19號</t>
         </is>
       </c>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16395,18 +16391,22 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
-        </is>
-      </c>
-      <c r="C553" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16424,18 +16424,18 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C554" s="4"/>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16453,18 +16453,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C555" s="4"/>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16482,18 +16482,18 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C556" s="4"/>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16511,18 +16511,18 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳怡如(彥鈞)</t>
         </is>
       </c>
       <c r="C557" s="4"/>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16540,18 +16540,18 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳慶壎</t>
         </is>
       </c>
       <c r="C558" s="4"/>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16569,22 +16569,18 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C559" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳敬惟</t>
+        </is>
+      </c>
+      <c r="C559" s="4"/>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16602,18 +16598,22 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
-        </is>
-      </c>
-      <c r="C560" s="4"/>
+          <t>陳智盛</t>
+        </is>
+      </c>
+      <c r="C560" s="4" t="inlineStr">
+        <is>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
+        </is>
+      </c>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16631,22 +16631,18 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
-        </is>
-      </c>
-      <c r="C561" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區星雲街30號</t>
-        </is>
-      </c>
+          <t>陳朋堅</t>
+        </is>
+      </c>
+      <c r="C561" s="4"/>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16664,22 +16660,22 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
+          <t>陳松廉</t>
         </is>
       </c>
       <c r="C562" s="4" t="inlineStr">
         <is>
-          <t>桃園市南豐街258號</t>
+          <t>台北市內湖區星雲街30號</t>
         </is>
       </c>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16697,18 +16693,22 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
-        </is>
-      </c>
-      <c r="C563" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C563" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16726,18 +16726,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16755,7 +16755,7 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
@@ -16766,7 +16766,7 @@
       <c r="C565" s="4"/>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16784,18 +16784,18 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C566" s="4"/>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16813,22 +16813,18 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C567" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳正傑</t>
+        </is>
+      </c>
+      <c r="C567" s="4"/>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16846,18 +16842,22 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
-        </is>
-      </c>
-      <c r="C568" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C568" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16875,18 +16875,18 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C569" s="4"/>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16904,18 +16904,18 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
+          <t>陳琇珊</t>
         </is>
       </c>
       <c r="C570" s="4"/>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16933,18 +16933,18 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳琬瑜</t>
         </is>
       </c>
       <c r="C571" s="4"/>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -16962,22 +16962,18 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C572" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳璽文</t>
+        </is>
+      </c>
+      <c r="C572" s="4"/>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -16995,18 +16991,22 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
-        </is>
-      </c>
-      <c r="C573" s="4"/>
+          <t>陳益銓</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區民生街15巷10號3樓</t>
+        </is>
+      </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17024,22 +17024,18 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
-        </is>
-      </c>
-      <c r="C574" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
-        </is>
-      </c>
+          <t>陳秋蓉</t>
+        </is>
+      </c>
+      <c r="C574" s="4"/>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17057,18 +17053,22 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
-        </is>
-      </c>
-      <c r="C575" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17086,18 +17086,18 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
+          <t>陳貴源</t>
         </is>
       </c>
       <c r="C576" s="4"/>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17115,18 +17115,18 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
+          <t>陳達鋒</t>
         </is>
       </c>
       <c r="C577" s="4"/>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17144,22 +17144,18 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C578" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C578" s="4"/>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17177,22 +17173,22 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
+          <t>陳長志</t>
         </is>
       </c>
       <c r="C579" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+          <t>新北市新店區安康路</t>
         </is>
       </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17210,22 +17206,22 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
+          <t>陳雯瑄</t>
         </is>
       </c>
       <c r="C580" s="4" t="inlineStr">
         <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
         </is>
       </c>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17243,18 +17239,22 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C581" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17272,18 +17272,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17301,18 +17301,18 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C583" s="4"/>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17330,18 +17330,18 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C584" s="4"/>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17359,18 +17359,18 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C585" s="4"/>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17388,18 +17388,18 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C586" s="4"/>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17417,18 +17417,18 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C587" s="4"/>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17446,18 +17446,18 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C588" s="4"/>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17475,18 +17475,18 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C589" s="4"/>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17504,18 +17504,18 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C590" s="4"/>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17533,18 +17533,18 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C591" s="4"/>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17562,18 +17562,18 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏宏坤</t>
         </is>
       </c>
       <c r="C592" s="4"/>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17591,22 +17591,18 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C593" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>馬迪</t>
+        </is>
+      </c>
+      <c r="C593" s="4"/>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17624,18 +17620,22 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
-        </is>
-      </c>
-      <c r="C594" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C594" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17653,18 +17653,18 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C595" s="4"/>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17682,18 +17682,18 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C596" s="4"/>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17711,18 +17711,18 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C597" s="4"/>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17740,18 +17740,18 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C598" s="4"/>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17769,18 +17769,18 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C599" s="4"/>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17798,18 +17798,18 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高聖景</t>
         </is>
       </c>
       <c r="C600" s="4"/>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E600" s="4"/>
@@ -17827,22 +17827,18 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C601" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高莉婷</t>
+        </is>
+      </c>
+      <c r="C601" s="4"/>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17860,18 +17856,22 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
-        </is>
-      </c>
-      <c r="C602" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C602" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17889,18 +17889,18 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C603" s="4"/>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0937742352</t>
         </is>
       </c>
       <c r="E603" s="4"/>
@@ -17918,16 +17918,20 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C604" s="4"/>
-      <c r="D604" s="4"/>
+      <c r="D604" s="4" t="inlineStr">
+        <is>
+          <t>0989116588</t>
+        </is>
+      </c>
       <c r="E604" s="4"/>
       <c r="F604" s="4" t="inlineStr">
         <is>
@@ -17943,20 +17947,16 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>鴻</t>
         </is>
       </c>
       <c r="C605" s="4"/>
-      <c r="D605" s="4" t="inlineStr">
-        <is>
-          <t>0958180882</t>
-        </is>
-      </c>
+      <c r="D605" s="4"/>
       <c r="E605" s="4"/>
       <c r="F605" s="4" t="inlineStr">
         <is>
@@ -17972,22 +17972,18 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C606" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
+          <t>黃俊翰</t>
+        </is>
+      </c>
+      <c r="C606" s="4"/>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>0903975921</t>
+          <t>0958180882</t>
         </is>
       </c>
       <c r="E606" s="4"/>
@@ -18005,16 +18001,24 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
-        </is>
-      </c>
-      <c r="C607" s="4"/>
-      <c r="D607" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C607" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
+      <c r="D607" s="4" t="inlineStr">
+        <is>
+          <t>0903975921</t>
+        </is>
+      </c>
       <c r="E607" s="4"/>
       <c r="F607" s="4" t="inlineStr">
         <is>
@@ -18030,20 +18034,16 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C608" s="4"/>
-      <c r="D608" s="4" t="inlineStr">
-        <is>
-          <t>0938722217</t>
-        </is>
-      </c>
+      <c r="D608" s="4"/>
       <c r="E608" s="4"/>
       <c r="F608" s="4" t="inlineStr">
         <is>
@@ -18059,18 +18059,18 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C609" s="4"/>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0989628136</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18088,18 +18088,18 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C610" s="4"/>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18117,18 +18117,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18146,18 +18146,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18175,18 +18175,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18204,18 +18204,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18233,18 +18233,18 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C615" s="4"/>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18262,22 +18262,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C616" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃庠豪</t>
+        </is>
+      </c>
+      <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18295,18 +18291,22 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
-        </is>
-      </c>
-      <c r="C617" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C617" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18324,18 +18324,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18353,18 +18353,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18382,18 +18382,18 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C620" s="4"/>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18411,18 +18411,18 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C621" s="4"/>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18440,18 +18440,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18469,18 +18469,18 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C623" s="4"/>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E623" s="4"/>
@@ -18498,18 +18498,18 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C624" s="4"/>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E624" s="4"/>
@@ -18527,18 +18527,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18556,18 +18556,18 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E626" s="4"/>
@@ -18585,22 +18585,26 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E627" s="4"/>
-      <c r="F627" s="4"/>
+      <c r="F627" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
       <c r="G627" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -18610,26 +18614,22 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C628" s="4"/>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E628" s="4"/>
-      <c r="F628" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F628" s="4"/>
       <c r="G628" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -18639,18 +18639,18 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C629" s="4"/>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E629" s="4"/>
@@ -18668,18 +18668,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18697,18 +18697,18 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C631" s="4"/>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E631" s="4"/>
@@ -18726,18 +18726,18 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C632" s="4"/>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E632" s="4"/>
@@ -18755,18 +18755,18 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2510020007</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃鴻麒</t>
         </is>
       </c>
       <c r="C633" s="4"/>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0930571975</t>
         </is>
       </c>
       <c r="E633" s="4"/>
@@ -18784,18 +18784,18 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2602270002</t>
         </is>
       </c>
       <c r="B634" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黎信宏</t>
         </is>
       </c>
       <c r="C634" s="4"/>
       <c r="D634" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0911024337</t>
         </is>
       </c>
       <c r="E634" s="4"/>
@@ -18811,9 +18811,38 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>2026/03/28  14:20:53</t>
+      <c r="A635" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B635" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C635" s="4"/>
+      <c r="D635" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E635" s="4"/>
+      <c r="F635" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G635" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026/03/29  13:00:11</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -19353,7 +19353,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026/04/10  13:00:19</t>
+          <t>2026/04/11  13:00:23</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -10357,20 +10357,24 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>V0013</t>
+          <t>M2604110001</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>真大帥</t>
+          <t>盧炳宏</t>
         </is>
       </c>
       <c r="C348" s="4"/>
-      <c r="D348" s="4"/>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>0921062300</t>
+        </is>
+      </c>
       <c r="E348" s="4"/>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -10382,24 +10386,20 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>M2510310002</t>
+          <t>V0013</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>祁麟</t>
+          <t>真大帥</t>
         </is>
       </c>
       <c r="C349" s="4"/>
-      <c r="D349" s="4" t="inlineStr">
-        <is>
-          <t>0982883101</t>
-        </is>
-      </c>
+      <c r="D349" s="4"/>
       <c r="E349" s="4"/>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -10411,18 +10411,18 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>M2602130001</t>
+          <t>M2510310002</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>祐</t>
+          <t>祁麟</t>
         </is>
       </c>
       <c r="C350" s="4"/>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>0983407890</t>
+          <t>0982883101</t>
         </is>
       </c>
       <c r="E350" s="4"/>
@@ -10440,18 +10440,18 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>M2510050001</t>
+          <t>M2602130001</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>程sir/Ashbur</t>
+          <t>祐</t>
         </is>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>0963612395</t>
+          <t>0983407890</t>
         </is>
       </c>
       <c r="E351" s="4"/>
@@ -10469,18 +10469,18 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>M2510300001</t>
+          <t>M2510050001</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>程品勝</t>
+          <t>程sir/Ashbur</t>
         </is>
       </c>
       <c r="C352" s="4"/>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>0913780727</t>
+          <t>0963612395</t>
         </is>
       </c>
       <c r="E352" s="4"/>
@@ -10498,18 +10498,18 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>M2601270002</t>
+          <t>M2510300001</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>程建智</t>
+          <t>程品勝</t>
         </is>
       </c>
       <c r="C353" s="4"/>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>0988919027</t>
+          <t>0913780727</t>
         </is>
       </c>
       <c r="E353" s="4"/>
@@ -10527,18 +10527,18 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>M2603120004</t>
+          <t>M2601270002</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>程郁勛</t>
+          <t>程建智</t>
         </is>
       </c>
       <c r="C354" s="4"/>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>0955671407</t>
+          <t>0988919027</t>
         </is>
       </c>
       <c r="E354" s="4"/>
@@ -10556,22 +10556,18 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>M2509160001</t>
+          <t>M2603120004</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>穆莉茹</t>
-        </is>
-      </c>
-      <c r="C355" s="4" t="inlineStr">
-        <is>
-          <t>桃園平鎮區上海路169號</t>
-        </is>
-      </c>
+          <t>程郁勛</t>
+        </is>
+      </c>
+      <c r="C355" s="4"/>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>0955777312</t>
+          <t>0955671407</t>
         </is>
       </c>
       <c r="E355" s="4"/>
@@ -10589,18 +10585,22 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>M2511160003</t>
+          <t>M2509160001</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>簡士傑</t>
-        </is>
-      </c>
-      <c r="C356" s="4"/>
+          <t>穆莉茹</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>桃園平鎮區上海路169號</t>
+        </is>
+      </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>0963817398</t>
+          <t>0955777312</t>
         </is>
       </c>
       <c r="E356" s="4"/>
@@ -10618,18 +10618,18 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>M2509300013</t>
+          <t>M2511160003</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>簡子偉</t>
+          <t>簡士傑</t>
         </is>
       </c>
       <c r="C357" s="4"/>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>0955462926</t>
+          <t>0963817398</t>
         </is>
       </c>
       <c r="E357" s="4"/>
@@ -10647,18 +10647,18 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>M2602280002</t>
+          <t>M2509300013</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>簡子洋</t>
+          <t>簡子偉</t>
         </is>
       </c>
       <c r="C358" s="4"/>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>0933921933</t>
+          <t>0955462926</t>
         </is>
       </c>
       <c r="E358" s="4"/>
@@ -10676,18 +10676,18 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>M2510040003</t>
+          <t>M2602280002</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>簡小琪</t>
+          <t>簡子洋</t>
         </is>
       </c>
       <c r="C359" s="4"/>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>0930033829</t>
+          <t>0933921933</t>
         </is>
       </c>
       <c r="E359" s="4"/>
@@ -10705,18 +10705,18 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>M2510260002</t>
+          <t>M2510040003</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>簡揚城</t>
+          <t>簡小琪</t>
         </is>
       </c>
       <c r="C360" s="4"/>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>0913153353</t>
+          <t>0930033829</t>
         </is>
       </c>
       <c r="E360" s="4"/>
@@ -10734,18 +10734,18 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>M2509300001</t>
+          <t>M2510260002</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>簡瑋成</t>
+          <t>簡揚城</t>
         </is>
       </c>
       <c r="C361" s="4"/>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>0936389969</t>
+          <t>0913153353</t>
         </is>
       </c>
       <c r="E361" s="4"/>
@@ -10763,18 +10763,18 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>M2509290020</t>
+          <t>M2509300001</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>簡茂州</t>
+          <t>簡瑋成</t>
         </is>
       </c>
       <c r="C362" s="4"/>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>0985217379</t>
+          <t>0936389969</t>
         </is>
       </c>
       <c r="E362" s="4"/>
@@ -10792,18 +10792,18 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>M2512130001</t>
+          <t>M2509290020</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>紀彥銘</t>
+          <t>簡茂州</t>
         </is>
       </c>
       <c r="C363" s="4"/>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>0988752337</t>
+          <t>0985217379</t>
         </is>
       </c>
       <c r="E363" s="4"/>
@@ -10821,20 +10821,24 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>V0001</t>
+          <t>M2512130001</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>統有企業</t>
+          <t>紀彥銘</t>
         </is>
       </c>
       <c r="C364" s="4"/>
-      <c r="D364" s="4"/>
+      <c r="D364" s="4" t="inlineStr">
+        <is>
+          <t>0988752337</t>
+        </is>
+      </c>
       <c r="E364" s="4"/>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -10846,24 +10850,20 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>M2509280008</t>
+          <t>V0001</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>維克斯</t>
+          <t>統有企業</t>
         </is>
       </c>
       <c r="C365" s="4"/>
-      <c r="D365" s="4" t="inlineStr">
-        <is>
-          <t>0917771787</t>
-        </is>
-      </c>
+      <c r="D365" s="4"/>
       <c r="E365" s="4"/>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G365" s="5" t="inlineStr">
@@ -10875,18 +10875,18 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>M2510170002</t>
+          <t>M2509280008</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>練鎮宇</t>
+          <t>維克斯</t>
         </is>
       </c>
       <c r="C366" s="4"/>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>0952288706</t>
+          <t>0917771787</t>
         </is>
       </c>
       <c r="E366" s="4"/>
@@ -10904,22 +10904,18 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>M2602220003</t>
+          <t>M2510170002</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>羅丁一夫</t>
-        </is>
-      </c>
-      <c r="C367" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
-        </is>
-      </c>
+          <t>練鎮宇</t>
+        </is>
+      </c>
+      <c r="C367" s="4"/>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>0919339614</t>
+          <t>0952288706</t>
         </is>
       </c>
       <c r="E367" s="4"/>
@@ -10937,18 +10933,22 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>M2510180002</t>
+          <t>M2602220003</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>羅元隆</t>
-        </is>
-      </c>
-      <c r="C368" s="4"/>
+          <t>羅丁一夫</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
+        </is>
+      </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>0975866635</t>
+          <t>0919339614</t>
         </is>
       </c>
       <c r="E368" s="4"/>
@@ -10966,25 +10966,21 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>M2510090003</t>
+          <t>M2510180002</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>羅嘉銘</t>
+          <t>羅元隆</t>
         </is>
       </c>
       <c r="C369" s="4"/>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>0928093385</t>
-        </is>
-      </c>
-      <c r="E369" s="4" t="inlineStr">
-        <is>
-          <t>0985866052</t>
-        </is>
-      </c>
+          <t>0975866635</t>
+        </is>
+      </c>
+      <c r="E369" s="4"/>
       <c r="F369" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -10999,21 +10995,25 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>M2602240001</t>
+          <t>M2510090003</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>羅浩中</t>
+          <t>羅嘉銘</t>
         </is>
       </c>
       <c r="C370" s="4"/>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>0970905092</t>
-        </is>
-      </c>
-      <c r="E370" s="4"/>
+          <t>0928093385</t>
+        </is>
+      </c>
+      <c r="E370" s="4" t="inlineStr">
+        <is>
+          <t>0985866052</t>
+        </is>
+      </c>
       <c r="F370" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11028,18 +11028,18 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>M2511060003</t>
+          <t>M2602240001</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>翁名勳</t>
+          <t>羅浩中</t>
         </is>
       </c>
       <c r="C371" s="4"/>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>0955083317</t>
+          <t>0970905092</t>
         </is>
       </c>
       <c r="E371" s="4"/>
@@ -11057,18 +11057,18 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>M2509260057</t>
+          <t>M2511060003</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>翁國昌</t>
+          <t>翁名勳</t>
         </is>
       </c>
       <c r="C372" s="4"/>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>0918718772</t>
+          <t>0955083317</t>
         </is>
       </c>
       <c r="E372" s="4"/>
@@ -11086,22 +11086,18 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>M2511290001</t>
+          <t>M2509260057</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>翁國祥</t>
-        </is>
-      </c>
-      <c r="C373" s="4" t="inlineStr">
-        <is>
-          <t>新北新莊中信街65號1樓賣菜攤</t>
-        </is>
-      </c>
+          <t>翁國昌</t>
+        </is>
+      </c>
+      <c r="C373" s="4"/>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>0983900052</t>
+          <t>0918718772</t>
         </is>
       </c>
       <c r="E373" s="4"/>
@@ -11119,22 +11115,22 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>M2510010009</t>
+          <t>M2511290001</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩</t>
+          <t>翁國祥</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>未決定</t>
+          <t>新北新莊中信街65號1樓賣菜攤</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>0972757015</t>
+          <t>0983900052</t>
         </is>
       </c>
       <c r="E374" s="4"/>
@@ -11152,53 +11148,53 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
+          <t>M2510010009</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>翁敬恩</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="inlineStr">
+        <is>
+          <t>未決定</t>
+        </is>
+      </c>
+      <c r="D375" s="4" t="inlineStr">
+        <is>
+          <t>0972757015</t>
+        </is>
+      </c>
+      <c r="E375" s="4"/>
+      <c r="F375" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G375" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="inlineStr">
+        <is>
           <t>M2510010009-4</t>
         </is>
       </c>
-      <c r="B375" s="4" t="inlineStr">
+      <c r="B376" s="4" t="inlineStr">
         <is>
           <t>翁敬恩-文山</t>
         </is>
       </c>
-      <c r="C375" s="6" t="inlineStr">
+      <c r="C376" s="6" t="inlineStr">
         <is>
           <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
 收件聯絡電話:0937462412</t>
         </is>
       </c>
-      <c r="D375" s="4" t="inlineStr">
-        <is>
-          <t>0972757015</t>
-        </is>
-      </c>
-      <c r="E375" s="4"/>
-      <c r="F375" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
-      <c r="G375" s="5" t="inlineStr">
-        <is>
-          <t>附件管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="4" t="inlineStr">
-        <is>
-          <t>M2510010009-2</t>
-        </is>
-      </c>
-      <c r="B376" s="4" t="inlineStr">
-        <is>
-          <t>翁敬恩-樂華</t>
-        </is>
-      </c>
-      <c r="C376" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
-        </is>
-      </c>
       <c r="D376" s="4" t="inlineStr">
         <is>
           <t>0972757015</t>
@@ -11219,17 +11215,17 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-3</t>
+          <t>M2510010009-2</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-永和</t>
+          <t>翁敬恩-樂華</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
+          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -11252,22 +11248,22 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-1</t>
+          <t>M2510010009-3</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-饒河</t>
+          <t>翁敬恩-永和</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>0975953978</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E378" s="4"/>
@@ -11285,18 +11281,22 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>M2510140004</t>
+          <t>M2510010009-1</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>翁漢忠</t>
-        </is>
-      </c>
-      <c r="C379" s="4"/>
+          <t>翁敬恩-饒河</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+        </is>
+      </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>0916150750</t>
+          <t>0975953978</t>
         </is>
       </c>
       <c r="E379" s="4"/>
@@ -11314,18 +11314,18 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>M2509260037</t>
+          <t>M2510140004</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>翁翌禎</t>
+          <t>翁漢忠</t>
         </is>
       </c>
       <c r="C380" s="4"/>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>0902308293</t>
+          <t>0916150750</t>
         </is>
       </c>
       <c r="E380" s="4"/>
@@ -11343,18 +11343,18 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>M2509280002</t>
+          <t>M2509260037</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>聶大中</t>
+          <t>翁翌禎</t>
         </is>
       </c>
       <c r="C381" s="4"/>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>0955059148</t>
+          <t>0902308293</t>
         </is>
       </c>
       <c r="E381" s="4"/>
@@ -11372,18 +11372,18 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>M2510220001</t>
+          <t>M2509280002</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>胡HU</t>
+          <t>聶大中</t>
         </is>
       </c>
       <c r="C382" s="4"/>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>0988603554</t>
+          <t>0955059148</t>
         </is>
       </c>
       <c r="E382" s="4"/>
@@ -11401,18 +11401,18 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>M2510100011</t>
+          <t>M2510220001</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>胡凱傑</t>
+          <t>胡HU</t>
         </is>
       </c>
       <c r="C383" s="4"/>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>0955888840</t>
+          <t>0988603554</t>
         </is>
       </c>
       <c r="E383" s="4"/>
@@ -11430,18 +11430,18 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>M2510090005</t>
+          <t>M2510100011</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>胡家榮</t>
+          <t>胡凱傑</t>
         </is>
       </c>
       <c r="C384" s="4"/>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>0933059025</t>
+          <t>0955888840</t>
         </is>
       </c>
       <c r="E384" s="4"/>
@@ -11459,18 +11459,18 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>M2511150001</t>
+          <t>M2510090005</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>胡家銘</t>
+          <t>胡家榮</t>
         </is>
       </c>
       <c r="C385" s="4"/>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>0986362263</t>
+          <t>0933059025</t>
         </is>
       </c>
       <c r="E385" s="4"/>
@@ -11488,18 +11488,18 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>M2511290003</t>
+          <t>M2511150001</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>胡峻強</t>
+          <t>胡家銘</t>
         </is>
       </c>
       <c r="C386" s="4"/>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>0953088041</t>
+          <t>0986362263</t>
         </is>
       </c>
       <c r="E386" s="4"/>
@@ -11517,18 +11517,18 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>M2603010001</t>
+          <t>M2511290003</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>胡辰煜</t>
+          <t>胡峻強</t>
         </is>
       </c>
       <c r="C387" s="4"/>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>0963903685</t>
+          <t>0953088041</t>
         </is>
       </c>
       <c r="E387" s="4"/>
@@ -11546,18 +11546,18 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>M2510040002</t>
+          <t>M2603010001</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>胡辰軒</t>
+          <t>胡辰煜</t>
         </is>
       </c>
       <c r="C388" s="4"/>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>0972094622</t>
+          <t>0963903685</t>
         </is>
       </c>
       <c r="E388" s="4"/>
@@ -11575,18 +11575,18 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>M2602280001</t>
+          <t>M2510040002</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>胡閎翔</t>
+          <t>胡辰軒</t>
         </is>
       </c>
       <c r="C389" s="4"/>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>0970556309</t>
+          <t>0972094622</t>
         </is>
       </c>
       <c r="E389" s="4"/>
@@ -11604,18 +11604,18 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>M2511290002</t>
+          <t>M2602280001</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>舒老闆</t>
+          <t>胡閎翔</t>
         </is>
       </c>
       <c r="C390" s="4"/>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>0979788818</t>
+          <t>0970556309</t>
         </is>
       </c>
       <c r="E390" s="4"/>
@@ -11633,19 +11633,15 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-6</t>
+          <t>M2511290002</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-冬冬/虎林</t>
-        </is>
-      </c>
-      <c r="C391" s="4" t="inlineStr">
-        <is>
-          <t>台北市信義區虎林街164巷60弄19號</t>
-        </is>
-      </c>
+          <t>舒老闆</t>
+        </is>
+      </c>
+      <c r="C391" s="4"/>
       <c r="D391" s="4" t="inlineStr">
         <is>
           <t>0979788818</t>
@@ -11666,17 +11662,17 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-8</t>
+          <t>M2511290002-6</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德17號</t>
+          <t>舒老闆-冬冬/虎林</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區八德路三段155巷17號</t>
+          <t>台北市信義區虎林街164巷60弄19號</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
@@ -11699,17 +11695,17 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-2</t>
+          <t>M2511290002-8</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德46號</t>
+          <t>舒老闆-夾鬥陣/八德17號</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區八德路三段12巷51弄46號</t>
+          <t>台北市松山區八德路三段155巷17號</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -11732,17 +11728,17 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-7</t>
+          <t>M2511290002-2</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/臥龍</t>
+          <t>舒老闆-夾鬥陣/八德46號</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>台北市大安區臥龍街254號</t>
+          <t>台北市松山區八德路三段12巷51弄46號</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
@@ -11765,17 +11761,17 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-4</t>
+          <t>M2511290002-7</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/中正</t>
+          <t>舒老闆-夾鬥陣/臥龍</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路14號</t>
+          <t>台北市大安區臥龍街254號</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -11798,17 +11794,17 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-5</t>
+          <t>M2511290002-4</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/吳興</t>
+          <t>舒老闆-寧寧/中正</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>台北市信義區吳興街342號</t>
+          <t>新北市永和區中正路14號</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -11831,17 +11827,17 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-3</t>
+          <t>M2511290002-5</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/智光</t>
+          <t>舒老闆-寧寧/吳興</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區智光街98號</t>
+          <t>台北市信義區吳興街342號</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -11864,17 +11860,17 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-1</t>
+          <t>M2511290002-3</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/秀朗</t>
+          <t>舒老闆-寧寧/智光</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+          <t>新北市永和區智光街98號</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -11897,18 +11893,22 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>M2510140002</t>
+          <t>M2511290002-1</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>范姜敏中</t>
-        </is>
-      </c>
-      <c r="C399" s="4"/>
+          <t>舒老闆-寧寧/秀朗</t>
+        </is>
+      </c>
+      <c r="C399" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+        </is>
+      </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>0937464692</t>
+          <t>0979788818</t>
         </is>
       </c>
       <c r="E399" s="4"/>
@@ -11926,18 +11926,18 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>M2510140003</t>
+          <t>M2510140002</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>范姜群成</t>
+          <t>范姜敏中</t>
         </is>
       </c>
       <c r="C400" s="4"/>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>0920565234</t>
+          <t>0937464692</t>
         </is>
       </c>
       <c r="E400" s="4"/>
@@ -11955,22 +11955,18 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>M2511300003</t>
+          <t>M2510140003</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>莊正當</t>
-        </is>
-      </c>
-      <c r="C401" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區建安街27號3樓</t>
-        </is>
-      </c>
+          <t>范姜群成</t>
+        </is>
+      </c>
+      <c r="C401" s="4"/>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>0983337218</t>
+          <t>0920565234</t>
         </is>
       </c>
       <c r="E401" s="4"/>
@@ -11988,22 +11984,22 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>M2510270004</t>
+          <t>M2511300003</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>莊淑玲</t>
+          <t>莊正當</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>新北市新莊區五工三路78巷36號</t>
+          <t>新北市新莊區建安街27號3樓</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>0922277383</t>
+          <t>0983337218</t>
         </is>
       </c>
       <c r="E402" s="4"/>
@@ -12021,18 +12017,22 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>M2510190002</t>
+          <t>M2510270004</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>莊耿華</t>
-        </is>
-      </c>
-      <c r="C403" s="4"/>
+          <t>莊淑玲</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工三路78巷36號</t>
+        </is>
+      </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>0938600334</t>
+          <t>0922277383</t>
         </is>
       </c>
       <c r="E403" s="4"/>
@@ -12050,18 +12050,18 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>M2509260005</t>
+          <t>M2510190002</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>莊莊</t>
+          <t>莊耿華</t>
         </is>
       </c>
       <c r="C404" s="4"/>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>0955985557</t>
+          <t>0938600334</t>
         </is>
       </c>
       <c r="E404" s="4"/>
@@ -12079,18 +12079,18 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>M2510100007</t>
+          <t>M2509260005</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>莊閔丞</t>
+          <t>莊莊</t>
         </is>
       </c>
       <c r="C405" s="4"/>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>0963320370</t>
+          <t>0955985557</t>
         </is>
       </c>
       <c r="E405" s="4"/>
@@ -12108,18 +12108,18 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>M2602240002</t>
+          <t>M2510100007</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>萬宗霖</t>
+          <t>莊閔丞</t>
         </is>
       </c>
       <c r="C406" s="4"/>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>0977082365</t>
+          <t>0963320370</t>
         </is>
       </c>
       <c r="E406" s="4"/>
@@ -12137,18 +12137,18 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>M2510160001</t>
+          <t>M2602240002</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>葉力瑋</t>
+          <t>萬宗霖</t>
         </is>
       </c>
       <c r="C407" s="4"/>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>0979611911</t>
+          <t>0977082365</t>
         </is>
       </c>
       <c r="E407" s="4"/>
@@ -12166,18 +12166,18 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>M2510030002</t>
+          <t>M2510160001</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>葉家睿</t>
+          <t>葉力瑋</t>
         </is>
       </c>
       <c r="C408" s="4"/>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>0928112227</t>
+          <t>0979611911</t>
         </is>
       </c>
       <c r="E408" s="4"/>
@@ -12195,18 +12195,18 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>M2511050003</t>
+          <t>M2510030002</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>葉庭綸</t>
+          <t>葉家睿</t>
         </is>
       </c>
       <c r="C409" s="4"/>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>0966638685</t>
+          <t>0928112227</t>
         </is>
       </c>
       <c r="E409" s="4"/>
@@ -12224,18 +12224,18 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>M2510180001</t>
+          <t>M2511050003</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>葉建財</t>
+          <t>葉庭綸</t>
         </is>
       </c>
       <c r="C410" s="4"/>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>0989713349</t>
+          <t>0966638685</t>
         </is>
       </c>
       <c r="E410" s="4"/>
@@ -12253,18 +12253,18 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>M2510150001</t>
+          <t>M2510180001</t>
         </is>
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>葉彥均</t>
+          <t>葉建財</t>
         </is>
       </c>
       <c r="C411" s="4"/>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>0921436111</t>
+          <t>0989713349</t>
         </is>
       </c>
       <c r="E411" s="4"/>
@@ -12282,18 +12282,18 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>M2601220001</t>
+          <t>M2510150001</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>葉方奕</t>
+          <t>葉彥均</t>
         </is>
       </c>
       <c r="C412" s="4"/>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>0918386488</t>
+          <t>0921436111</t>
         </is>
       </c>
       <c r="E412" s="4"/>
@@ -12311,18 +12311,18 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>M2510260005</t>
+          <t>M2601220001</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>葉祈賢</t>
+          <t>葉方奕</t>
         </is>
       </c>
       <c r="C413" s="4"/>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>0955313212</t>
+          <t>0918386488</t>
         </is>
       </c>
       <c r="E413" s="4"/>
@@ -12340,18 +12340,18 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>M2509290012</t>
+          <t>M2510260005</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>葉維霆</t>
+          <t>葉祈賢</t>
         </is>
       </c>
       <c r="C414" s="4"/>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>0905120835</t>
+          <t>0955313212</t>
         </is>
       </c>
       <c r="E414" s="4"/>
@@ -12369,18 +12369,18 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>M2603050001</t>
+          <t>M2509290012</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>蔡仲凱</t>
+          <t>葉維霆</t>
         </is>
       </c>
       <c r="C415" s="4"/>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>0910733748</t>
+          <t>0905120835</t>
         </is>
       </c>
       <c r="E415" s="4"/>
@@ -12398,18 +12398,18 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>M2511080009</t>
+          <t>M2603050001</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>蔡伯鼎</t>
+          <t>蔡仲凱</t>
         </is>
       </c>
       <c r="C416" s="4"/>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>0933842593</t>
+          <t>0910733748</t>
         </is>
       </c>
       <c r="E416" s="4"/>
@@ -12427,18 +12427,18 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>M2512100001</t>
+          <t>M2511080009</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>蔡其騰</t>
+          <t>蔡伯鼎</t>
         </is>
       </c>
       <c r="C417" s="4"/>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>0988556732</t>
+          <t>0933842593</t>
         </is>
       </c>
       <c r="E417" s="4"/>
@@ -12456,22 +12456,18 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>M2603220001</t>
+          <t>M2512100001</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>蔡嘉章</t>
-        </is>
-      </c>
-      <c r="C418" s="4" t="inlineStr">
-        <is>
-          <t>樹林區太平路150巷8號娃娃機</t>
-        </is>
-      </c>
+          <t>蔡其騰</t>
+        </is>
+      </c>
+      <c r="C418" s="4"/>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>0973658657</t>
+          <t>0988556732</t>
         </is>
       </c>
       <c r="E418" s="4"/>
@@ -12489,18 +12485,22 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>M2509280001</t>
+          <t>M2603220001</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>蔡康志</t>
-        </is>
-      </c>
-      <c r="C419" s="4"/>
+          <t>蔡嘉章</t>
+        </is>
+      </c>
+      <c r="C419" s="4" t="inlineStr">
+        <is>
+          <t>樹林區太平路150巷8號娃娃機</t>
+        </is>
+      </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>0933942089</t>
+          <t>0973658657</t>
         </is>
       </c>
       <c r="E419" s="4"/>
@@ -12518,18 +12518,18 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>M2509260052</t>
+          <t>M2509280001</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>蔡志海</t>
+          <t>蔡康志</t>
         </is>
       </c>
       <c r="C420" s="4"/>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>0926616521</t>
+          <t>0933942089</t>
         </is>
       </c>
       <c r="E420" s="4"/>
@@ -12547,18 +12547,18 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>M2602120003</t>
+          <t>M2509260052</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>蔡承勳</t>
+          <t>蔡志海</t>
         </is>
       </c>
       <c r="C421" s="4"/>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>0979975919</t>
+          <t>0926616521</t>
         </is>
       </c>
       <c r="E421" s="4"/>
@@ -12576,18 +12576,18 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>M2509290002</t>
+          <t>M2602120003</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>蔡振元</t>
+          <t>蔡承勳</t>
         </is>
       </c>
       <c r="C422" s="4"/>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>0908590858</t>
+          <t>0979975919</t>
         </is>
       </c>
       <c r="E422" s="4"/>
@@ -12605,18 +12605,18 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>M2601090001</t>
+          <t>M2509290002</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>蔡昌翔</t>
+          <t>蔡振元</t>
         </is>
       </c>
       <c r="C423" s="4"/>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>0973324888</t>
+          <t>0908590858</t>
         </is>
       </c>
       <c r="E423" s="4"/>
@@ -12634,22 +12634,18 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>M2509260011</t>
+          <t>M2601090001</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>蔡智全</t>
-        </is>
-      </c>
-      <c r="C424" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區雙園街110號1樓</t>
-        </is>
-      </c>
+          <t>蔡昌翔</t>
+        </is>
+      </c>
+      <c r="C424" s="4"/>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>0930167280</t>
+          <t>0973324888</t>
         </is>
       </c>
       <c r="E424" s="4"/>
@@ -12667,22 +12663,22 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>M2509260049</t>
+          <t>M2509260011</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>蔡瀚霆</t>
+          <t>蔡智全</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區保平路207號</t>
+          <t>台北市萬華區雙園街110號1樓</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>0932014776</t>
+          <t>0930167280</t>
         </is>
       </c>
       <c r="E425" s="4"/>
@@ -12700,18 +12696,22 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>M2510010007</t>
+          <t>M2509260049</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>蔡秉橋</t>
-        </is>
-      </c>
-      <c r="C426" s="4"/>
+          <t>蔡瀚霆</t>
+        </is>
+      </c>
+      <c r="C426" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區保平路207號</t>
+        </is>
+      </c>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>0987000184</t>
+          <t>0932014776</t>
         </is>
       </c>
       <c r="E426" s="4"/>
@@ -12729,18 +12729,18 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>M2509270009</t>
+          <t>M2510010007</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>蔡育昇</t>
+          <t>蔡秉橋</t>
         </is>
       </c>
       <c r="C427" s="4"/>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>0918058903</t>
+          <t>0987000184</t>
         </is>
       </c>
       <c r="E427" s="4"/>
@@ -12758,18 +12758,18 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>M2603180001</t>
+          <t>M2509270009</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>蔡貞瑜</t>
+          <t>蔡育昇</t>
         </is>
       </c>
       <c r="C428" s="4"/>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>0917372131</t>
+          <t>0918058903</t>
         </is>
       </c>
       <c r="E428" s="4"/>
@@ -12787,18 +12787,18 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>M2510070001</t>
+          <t>M2603180001</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>蔡辰旻</t>
+          <t>蔡貞瑜</t>
         </is>
       </c>
       <c r="C429" s="4"/>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>0982621245</t>
+          <t>0917372131</t>
         </is>
       </c>
       <c r="E429" s="4"/>
@@ -12816,7 +12816,7 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>M2602010003</t>
+          <t>M2510070001</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
@@ -12827,7 +12827,7 @@
       <c r="C430" s="4"/>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>0903162818</t>
+          <t>0982621245</t>
         </is>
       </c>
       <c r="E430" s="4"/>
@@ -12845,18 +12845,18 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>M2511270001</t>
+          <t>M2602010003</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>蔡進盛</t>
+          <t>蔡辰旻</t>
         </is>
       </c>
       <c r="C431" s="4"/>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>0989387966</t>
+          <t>0903162818</t>
         </is>
       </c>
       <c r="E431" s="4"/>
@@ -12874,18 +12874,18 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>M2511030001</t>
+          <t>M2511270001</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>蔡鳳來</t>
+          <t>蔡進盛</t>
         </is>
       </c>
       <c r="C432" s="4"/>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>0963550931</t>
+          <t>0989387966</t>
         </is>
       </c>
       <c r="E432" s="4"/>
@@ -12903,18 +12903,18 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>M2509270016</t>
+          <t>M2511030001</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>蕭仲安</t>
+          <t>蔡鳳來</t>
         </is>
       </c>
       <c r="C433" s="4"/>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>0930601899</t>
+          <t>0963550931</t>
         </is>
       </c>
       <c r="E433" s="4"/>
@@ -12932,18 +12932,18 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>M2509270017</t>
+          <t>M2509270016</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>蕭又瑋</t>
+          <t>蕭仲安</t>
         </is>
       </c>
       <c r="C434" s="4"/>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>0922675798</t>
+          <t>0930601899</t>
         </is>
       </c>
       <c r="E434" s="4"/>
@@ -12961,18 +12961,18 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>M2509280009</t>
+          <t>M2509270017</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>蕭宇傑</t>
+          <t>蕭又瑋</t>
         </is>
       </c>
       <c r="C435" s="4"/>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>0989977822</t>
+          <t>0922675798</t>
         </is>
       </c>
       <c r="E435" s="4"/>
@@ -12990,18 +12990,18 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>M2510190006</t>
+          <t>M2509280009</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>蕭毓</t>
+          <t>蕭宇傑</t>
         </is>
       </c>
       <c r="C436" s="4"/>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>0975199046</t>
+          <t>0989977822</t>
         </is>
       </c>
       <c r="E436" s="4"/>
@@ -13019,22 +13019,18 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>M2510090006</t>
+          <t>M2510190006</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>蕭燁鴻</t>
-        </is>
-      </c>
-      <c r="C437" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區金龍路183號1樓</t>
-        </is>
-      </c>
+          <t>蕭毓</t>
+        </is>
+      </c>
+      <c r="C437" s="4"/>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>0917882269</t>
+          <t>0975199046</t>
         </is>
       </c>
       <c r="E437" s="4"/>
@@ -13052,18 +13048,22 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>M2510160008</t>
+          <t>M2510090006</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>蕭韻文</t>
-        </is>
-      </c>
-      <c r="C438" s="4"/>
+          <t>蕭燁鴻</t>
+        </is>
+      </c>
+      <c r="C438" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區金龍路183號1樓</t>
+        </is>
+      </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>0911297473</t>
+          <t>0917882269</t>
         </is>
       </c>
       <c r="E438" s="4"/>
@@ -13081,18 +13081,18 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>M2509300014</t>
+          <t>M2510160008</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>藍駿偉</t>
+          <t>蕭韻文</t>
         </is>
       </c>
       <c r="C439" s="4"/>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>0936152586</t>
+          <t>0911297473</t>
         </is>
       </c>
       <c r="E439" s="4"/>
@@ -13110,18 +13110,18 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>M2511080007</t>
+          <t>M2509300014</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>蘇嘉蓉</t>
+          <t>藍駿偉</t>
         </is>
       </c>
       <c r="C440" s="4"/>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>0937074336</t>
+          <t>0936152586</t>
         </is>
       </c>
       <c r="E440" s="4"/>
@@ -13139,18 +13139,18 @@
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>M2511060002</t>
+          <t>M2511080007</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>蘇國貿</t>
+          <t>蘇嘉蓉</t>
         </is>
       </c>
       <c r="C441" s="4"/>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>0922250285</t>
+          <t>0937074336</t>
         </is>
       </c>
       <c r="E441" s="4"/>
@@ -13168,18 +13168,18 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>M2511280004</t>
+          <t>M2511060002</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>蘇家明</t>
+          <t>蘇國貿</t>
         </is>
       </c>
       <c r="C442" s="4"/>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>0916836765</t>
+          <t>0922250285</t>
         </is>
       </c>
       <c r="E442" s="4"/>
@@ -13197,18 +13197,18 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>M2510300002</t>
+          <t>M2511280004</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>蘇小好</t>
+          <t>蘇家明</t>
         </is>
       </c>
       <c r="C443" s="4"/>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>0981870981</t>
+          <t>0916836765</t>
         </is>
       </c>
       <c r="E443" s="4"/>
@@ -13226,18 +13226,18 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>M2509260021</t>
+          <t>M2510300002</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>蘇彥彰</t>
+          <t>蘇小好</t>
         </is>
       </c>
       <c r="C444" s="4"/>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>0983060026</t>
+          <t>0981870981</t>
         </is>
       </c>
       <c r="E444" s="4"/>
@@ -13255,22 +13255,18 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>M2510240001</t>
+          <t>M2509260021</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>蘇志勇</t>
-        </is>
-      </c>
-      <c r="C445" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
-        </is>
-      </c>
+          <t>蘇彥彰</t>
+        </is>
+      </c>
+      <c r="C445" s="4"/>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>0910051586</t>
+          <t>0983060026</t>
         </is>
       </c>
       <c r="E445" s="4"/>
@@ -13288,18 +13284,22 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>M2602150002</t>
+          <t>M2510240001</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>蘇昱銘</t>
-        </is>
-      </c>
-      <c r="C446" s="4"/>
+          <t>蘇志勇</t>
+        </is>
+      </c>
+      <c r="C446" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
+        </is>
+      </c>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>0916324119</t>
+          <t>0910051586</t>
         </is>
       </c>
       <c r="E446" s="4"/>
@@ -13317,18 +13317,18 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>M2510050003</t>
+          <t>M2602150002</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>蘇睿慶</t>
+          <t>蘇昱銘</t>
         </is>
       </c>
       <c r="C447" s="4"/>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>0937766339</t>
+          <t>0916324119</t>
         </is>
       </c>
       <c r="E447" s="4"/>
@@ -13346,18 +13346,18 @@
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>M2601180001</t>
+          <t>M2510050003</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>蠟筆</t>
+          <t>蘇睿慶</t>
         </is>
       </c>
       <c r="C448" s="4"/>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>0976321321</t>
+          <t>0937766339</t>
         </is>
       </c>
       <c r="E448" s="4"/>
@@ -13375,18 +13375,18 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>M2512160002</t>
+          <t>M2601180001</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>褚朕誠</t>
+          <t>蠟筆</t>
         </is>
       </c>
       <c r="C449" s="4"/>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>0972217495</t>
+          <t>0976321321</t>
         </is>
       </c>
       <c r="E449" s="4"/>
@@ -13404,18 +13404,18 @@
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>M2512200002</t>
+          <t>M2512160002</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>褚銘漢</t>
+          <t>褚朕誠</t>
         </is>
       </c>
       <c r="C450" s="4"/>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>0925886065</t>
+          <t>0972217495</t>
         </is>
       </c>
       <c r="E450" s="4"/>
@@ -13433,18 +13433,18 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>M2512170002</t>
+          <t>M2512200002</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>許俊鴻</t>
+          <t>褚銘漢</t>
         </is>
       </c>
       <c r="C451" s="4"/>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>0973630391</t>
+          <t>0925886065</t>
         </is>
       </c>
       <c r="E451" s="4"/>
@@ -13462,18 +13462,18 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>M2510050013</t>
+          <t>M2512170002</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>許凱傑</t>
+          <t>許俊鴻</t>
         </is>
       </c>
       <c r="C452" s="4"/>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>0955306971</t>
+          <t>0973630391</t>
         </is>
       </c>
       <c r="E452" s="4"/>
@@ -13491,18 +13491,18 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>M2511110001</t>
+          <t>M2510050013</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>許哲豪</t>
+          <t>許凱傑</t>
         </is>
       </c>
       <c r="C453" s="4"/>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>0985191149</t>
+          <t>0955306971</t>
         </is>
       </c>
       <c r="E453" s="4"/>
@@ -13520,18 +13520,18 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>M2602030001</t>
+          <t>M2511110001</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>許士彥</t>
+          <t>許哲豪</t>
         </is>
       </c>
       <c r="C454" s="4"/>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>0913558692</t>
+          <t>0985191149</t>
         </is>
       </c>
       <c r="E454" s="4"/>
@@ -13549,18 +13549,18 @@
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>M2509290018</t>
+          <t>M2602030001</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>許天寶</t>
+          <t>許士彥</t>
         </is>
       </c>
       <c r="C455" s="4"/>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>0936088850</t>
+          <t>0913558692</t>
         </is>
       </c>
       <c r="E455" s="4"/>
@@ -13578,18 +13578,18 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>M2510160005</t>
+          <t>M2509290018</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>許宥蓁</t>
+          <t>許天寶</t>
         </is>
       </c>
       <c r="C456" s="4"/>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>0938473255</t>
+          <t>0936088850</t>
         </is>
       </c>
       <c r="E456" s="4"/>
@@ -13607,18 +13607,18 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>M2512020001</t>
+          <t>M2510160005</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>許家豪</t>
+          <t>許宥蓁</t>
         </is>
       </c>
       <c r="C457" s="4"/>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>0983215242</t>
+          <t>0938473255</t>
         </is>
       </c>
       <c r="E457" s="4"/>
@@ -13636,18 +13636,18 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>M2510110007</t>
+          <t>M2512020001</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>許峻銓</t>
+          <t>許家豪</t>
         </is>
       </c>
       <c r="C458" s="4"/>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>0979770033</t>
+          <t>0983215242</t>
         </is>
       </c>
       <c r="E458" s="4"/>
@@ -13665,18 +13665,18 @@
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>M2511260001</t>
+          <t>M2510110007</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>許志帆</t>
+          <t>許峻銓</t>
         </is>
       </c>
       <c r="C459" s="4"/>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>0936639358</t>
+          <t>0979770033</t>
         </is>
       </c>
       <c r="E459" s="4"/>
@@ -13694,18 +13694,18 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>M2510310001</t>
+          <t>M2511260001</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>許志豪</t>
+          <t>許志帆</t>
         </is>
       </c>
       <c r="C460" s="4"/>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>0971080606</t>
+          <t>0936639358</t>
         </is>
       </c>
       <c r="E460" s="4"/>
@@ -13723,18 +13723,18 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>M2601040001</t>
+          <t>M2510310001</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>許惠笙</t>
+          <t>許志豪</t>
         </is>
       </c>
       <c r="C461" s="4"/>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>0987890463</t>
+          <t>0971080606</t>
         </is>
       </c>
       <c r="E461" s="4"/>
@@ -13752,18 +13752,18 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>M2603080002</t>
+          <t>M2601040001</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>許汶瑋</t>
+          <t>許惠笙</t>
         </is>
       </c>
       <c r="C462" s="4"/>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>0988166792</t>
+          <t>0987890463</t>
         </is>
       </c>
       <c r="E462" s="4"/>
@@ -13781,22 +13781,18 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>M2509140001</t>
+          <t>M2603080002</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>許煥杰</t>
-        </is>
-      </c>
-      <c r="C463" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區藝文二街88號8樓</t>
-        </is>
-      </c>
+          <t>許汶瑋</t>
+        </is>
+      </c>
+      <c r="C463" s="4"/>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>0913785888</t>
+          <t>0988166792</t>
         </is>
       </c>
       <c r="E463" s="4"/>
@@ -13814,18 +13810,22 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>M2510010001</t>
+          <t>M2509140001</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>許硯棠</t>
-        </is>
-      </c>
-      <c r="C464" s="4"/>
+          <t>許煥杰</t>
+        </is>
+      </c>
+      <c r="C464" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區藝文二街88號8樓</t>
+        </is>
+      </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>0983238652</t>
+          <t>0913785888</t>
         </is>
       </c>
       <c r="E464" s="4"/>
@@ -13843,18 +13843,18 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>M2509270001</t>
+          <t>M2510010001</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>許竣榤</t>
+          <t>許硯棠</t>
         </is>
       </c>
       <c r="C465" s="4"/>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>0955598097</t>
+          <t>0983238652</t>
         </is>
       </c>
       <c r="E465" s="4"/>
@@ -13872,18 +13872,18 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>M2510240002</t>
+          <t>M2509270001</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>許芫睿</t>
+          <t>許竣榤</t>
         </is>
       </c>
       <c r="C466" s="4"/>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>0975057699</t>
+          <t>0955598097</t>
         </is>
       </c>
       <c r="E466" s="4"/>
@@ -13901,18 +13901,18 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>M2509290013</t>
+          <t>M2510240002</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>許雅蓁</t>
+          <t>許芫睿</t>
         </is>
       </c>
       <c r="C467" s="4"/>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>0982339939</t>
+          <t>0975057699</t>
         </is>
       </c>
       <c r="E467" s="4"/>
@@ -13930,18 +13930,18 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>M2509260055</t>
+          <t>M2509290013</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>許靜蔆</t>
+          <t>許雅蓁</t>
         </is>
       </c>
       <c r="C468" s="4"/>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>0928060395</t>
+          <t>0982339939</t>
         </is>
       </c>
       <c r="E468" s="4"/>
@@ -13959,18 +13959,18 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>M2509260027</t>
+          <t>M2509260055</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>詹傑克</t>
+          <t>許靜蔆</t>
         </is>
       </c>
       <c r="C469" s="4"/>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>0968688080</t>
+          <t>0928060395</t>
         </is>
       </c>
       <c r="E469" s="4"/>
@@ -13988,18 +13988,18 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>M2602010004</t>
+          <t>M2509260027</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>詹凱翔</t>
+          <t>詹傑克</t>
         </is>
       </c>
       <c r="C470" s="4"/>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>0963496660</t>
+          <t>0968688080</t>
         </is>
       </c>
       <c r="E470" s="4"/>
@@ -14017,18 +14017,18 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>M2601270001</t>
+          <t>M2602010004</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>詹朝輝</t>
+          <t>詹凱翔</t>
         </is>
       </c>
       <c r="C471" s="4"/>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>0968490321</t>
+          <t>0963496660</t>
         </is>
       </c>
       <c r="E471" s="4"/>
@@ -14046,18 +14046,18 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>M2601170004</t>
+          <t>M2601270001</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>詹煜騰</t>
+          <t>詹朝輝</t>
         </is>
       </c>
       <c r="C472" s="4"/>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>0939919344</t>
+          <t>0968490321</t>
         </is>
       </c>
       <c r="E472" s="4"/>
@@ -14075,18 +14075,18 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>M2509280003</t>
+          <t>M2601170004</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>詹皇</t>
+          <t>詹煜騰</t>
         </is>
       </c>
       <c r="C473" s="4"/>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>0916037915</t>
+          <t>0939919344</t>
         </is>
       </c>
       <c r="E473" s="4"/>
@@ -14104,18 +14104,18 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>M2510030001</t>
+          <t>M2509280003</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>詹皇宥</t>
+          <t>詹皇</t>
         </is>
       </c>
       <c r="C474" s="4"/>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>0919367080</t>
+          <t>0916037915</t>
         </is>
       </c>
       <c r="E474" s="4"/>
@@ -14133,22 +14133,18 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>M2509290016</t>
+          <t>M2510030001</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>詹育銘</t>
-        </is>
-      </c>
-      <c r="C475" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區撫順街25號1樓</t>
-        </is>
-      </c>
+          <t>詹皇宥</t>
+        </is>
+      </c>
+      <c r="C475" s="4"/>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>0926962322</t>
+          <t>0919367080</t>
         </is>
       </c>
       <c r="E475" s="4"/>
@@ -14166,22 +14162,22 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>M2510270001</t>
+          <t>M2509290016</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>謝亞倫</t>
+          <t>詹育銘</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>新北市淡水區北投里北投子49-1號</t>
+          <t>台北市中山區撫順街25號1樓</t>
         </is>
       </c>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>0922409070</t>
+          <t>0926962322</t>
         </is>
       </c>
       <c r="E476" s="4"/>
@@ -14199,18 +14195,22 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>M2510040004</t>
+          <t>M2510270001</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>謝佳蓉</t>
-        </is>
-      </c>
-      <c r="C477" s="4"/>
+          <t>謝亞倫</t>
+        </is>
+      </c>
+      <c r="C477" s="4" t="inlineStr">
+        <is>
+          <t>新北市淡水區北投里北投子49-1號</t>
+        </is>
+      </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>0976958679</t>
+          <t>0922409070</t>
         </is>
       </c>
       <c r="E477" s="4"/>
@@ -14228,18 +14228,18 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>M2509300019</t>
+          <t>M2510040004</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>謝光明</t>
+          <t>謝佳蓉</t>
         </is>
       </c>
       <c r="C478" s="4"/>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>0983011754</t>
+          <t>0976958679</t>
         </is>
       </c>
       <c r="E478" s="4"/>
@@ -14257,22 +14257,18 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>M2512140002</t>
+          <t>M2509300019</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>謝孟辰</t>
-        </is>
-      </c>
-      <c r="C479" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
-        </is>
-      </c>
+          <t>謝光明</t>
+        </is>
+      </c>
+      <c r="C479" s="4"/>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>0953900309</t>
+          <t>0983011754</t>
         </is>
       </c>
       <c r="E479" s="4"/>
@@ -14290,18 +14286,22 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>M2509270007</t>
+          <t>M2512140002</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>謝建衫</t>
-        </is>
-      </c>
-      <c r="C480" s="4"/>
+          <t>謝孟辰</t>
+        </is>
+      </c>
+      <c r="C480" s="4" t="inlineStr">
+        <is>
+          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
+        </is>
+      </c>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>0918238090</t>
+          <t>0953900309</t>
         </is>
       </c>
       <c r="E480" s="4"/>
@@ -14319,18 +14319,18 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>M2510150005</t>
+          <t>M2509270007</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>謝文懷</t>
+          <t>謝建衫</t>
         </is>
       </c>
       <c r="C481" s="4"/>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>0989813659</t>
+          <t>0918238090</t>
         </is>
       </c>
       <c r="E481" s="4"/>
@@ -14348,18 +14348,18 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>M2510130004</t>
+          <t>M2510150005</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>謝桂仁</t>
+          <t>謝文懷</t>
         </is>
       </c>
       <c r="C482" s="4"/>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>0938357603</t>
+          <t>0989813659</t>
         </is>
       </c>
       <c r="E482" s="4"/>
@@ -14377,18 +14377,18 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>M2510050002</t>
+          <t>M2510130004</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>謝舒帆</t>
+          <t>謝桂仁</t>
         </is>
       </c>
       <c r="C483" s="4"/>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>0980699503</t>
+          <t>0938357603</t>
         </is>
       </c>
       <c r="E483" s="4"/>
@@ -14406,18 +14406,18 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>M2510040008</t>
+          <t>M2510050002</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>謝荌核</t>
+          <t>謝舒帆</t>
         </is>
       </c>
       <c r="C484" s="4"/>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>0988302836</t>
+          <t>0980699503</t>
         </is>
       </c>
       <c r="E484" s="4"/>
@@ -14435,18 +14435,18 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>M2511300006</t>
+          <t>M2510040008</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>謝詠全</t>
+          <t>謝荌核</t>
         </is>
       </c>
       <c r="C485" s="4"/>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>0977077044</t>
+          <t>0988302836</t>
         </is>
       </c>
       <c r="E485" s="4"/>
@@ -14464,18 +14464,18 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>M2603200003</t>
+          <t>M2511300006</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>譚淵修</t>
+          <t>謝詠全</t>
         </is>
       </c>
       <c r="C486" s="4"/>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>0910322500</t>
+          <t>0977077044</t>
         </is>
       </c>
       <c r="E486" s="4"/>
@@ -14493,18 +14493,18 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>M2510040011</t>
+          <t>M2603200003</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>賴先生</t>
+          <t>譚淵修</t>
         </is>
       </c>
       <c r="C487" s="4"/>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>0965351801</t>
+          <t>0910322500</t>
         </is>
       </c>
       <c r="E487" s="4"/>
@@ -14522,18 +14522,18 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>M2603080001</t>
+          <t>M2510040011</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>賴品豪</t>
+          <t>賴先生</t>
         </is>
       </c>
       <c r="C488" s="4"/>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>0981379127</t>
+          <t>0965351801</t>
         </is>
       </c>
       <c r="E488" s="4"/>
@@ -14551,18 +14551,18 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>M2511010005</t>
+          <t>M2603080001</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>賴彥安</t>
+          <t>賴品豪</t>
         </is>
       </c>
       <c r="C489" s="4"/>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>0913102110</t>
+          <t>0981379127</t>
         </is>
       </c>
       <c r="E489" s="4"/>
@@ -14580,22 +14580,18 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>M2603280001</t>
+          <t>M2511010005</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>賴柏舟</t>
-        </is>
-      </c>
-      <c r="C490" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股五福路11號</t>
-        </is>
-      </c>
+          <t>賴彥安</t>
+        </is>
+      </c>
+      <c r="C490" s="4"/>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>0979131818</t>
+          <t>0913102110</t>
         </is>
       </c>
       <c r="E490" s="4"/>
@@ -14613,18 +14609,22 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
-        </is>
-      </c>
-      <c r="C491" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C491" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E491" s="4"/>
@@ -14642,18 +14642,18 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
+          <t>賴珊珊</t>
         </is>
       </c>
       <c r="C492" s="4"/>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E492" s="4"/>
@@ -14671,22 +14671,18 @@
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C493" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C493" s="4"/>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E493" s="4"/>
@@ -14704,22 +14700,22 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B494" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E494" s="4"/>
@@ -14737,22 +14733,22 @@
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>趙云璟</t>
         </is>
       </c>
       <c r="C495" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E495" s="4"/>
@@ -14770,18 +14766,22 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C496" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C496" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E496" s="4"/>
@@ -14799,18 +14799,18 @@
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C497" s="4"/>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E497" s="4"/>
@@ -14828,18 +14828,18 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C498" s="4"/>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0986258793</t>
         </is>
       </c>
       <c r="E498" s="4"/>
@@ -14857,20 +14857,24 @@
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C499" s="4"/>
-      <c r="D499" s="4"/>
+      <c r="D499" s="4" t="inlineStr">
+        <is>
+          <t>0982484963</t>
+        </is>
+      </c>
       <c r="E499" s="4"/>
       <c r="F499" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G499" s="5" t="inlineStr">
@@ -14882,24 +14886,20 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C500" s="4"/>
-      <c r="D500" s="4" t="inlineStr">
-        <is>
-          <t>0981898339</t>
-        </is>
-      </c>
+      <c r="D500" s="4"/>
       <c r="E500" s="4"/>
       <c r="F500" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G500" s="5" t="inlineStr">
@@ -14911,18 +14911,18 @@
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C501" s="4"/>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>0903921531</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E501" s="4"/>
@@ -14940,18 +14940,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14969,18 +14969,18 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C503" s="4"/>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E503" s="4"/>
@@ -14998,18 +14998,18 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C504" s="4"/>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -15027,18 +15027,18 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱振為</t>
         </is>
       </c>
       <c r="C505" s="4"/>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E505" s="4"/>
@@ -15056,22 +15056,18 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C506" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱政傑</t>
+        </is>
+      </c>
+      <c r="C506" s="4"/>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15089,18 +15085,22 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
-        </is>
-      </c>
-      <c r="C507" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C507" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15118,18 +15118,18 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C508" s="4"/>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E508" s="4"/>
@@ -15147,18 +15147,18 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C509" s="4"/>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E509" s="4"/>
@@ -15176,7 +15176,7 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
@@ -15205,18 +15205,18 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C511" s="4"/>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E511" s="4"/>
@@ -15234,16 +15234,20 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C512" s="4"/>
-      <c r="D512" s="4"/>
+      <c r="D512" s="4" t="inlineStr">
+        <is>
+          <t>0935329653</t>
+        </is>
+      </c>
       <c r="E512" s="4"/>
       <c r="F512" s="4" t="inlineStr">
         <is>
@@ -15259,20 +15263,16 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C513" s="4"/>
-      <c r="D513" s="4" t="inlineStr">
-        <is>
-          <t>0976588171</t>
-        </is>
-      </c>
+      <c r="D513" s="4"/>
       <c r="E513" s="4"/>
       <c r="F513" s="4" t="inlineStr">
         <is>
@@ -15288,18 +15288,18 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C514" s="4"/>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0972128080</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E514" s="4"/>
@@ -15317,18 +15317,18 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C515" s="4"/>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E515" s="4"/>
@@ -15346,18 +15346,18 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C516" s="4"/>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E516" s="4"/>
@@ -15375,18 +15375,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15404,18 +15404,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C518" s="4"/>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E518" s="4"/>
@@ -15433,18 +15433,18 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C519" s="4"/>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E519" s="4"/>
@@ -15462,18 +15462,18 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C520" s="4"/>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E520" s="4"/>
@@ -15491,18 +15491,18 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭鼎昇</t>
         </is>
       </c>
       <c r="C521" s="4"/>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E521" s="4"/>
@@ -15520,22 +15520,18 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C522" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>鄒育燁</t>
+        </is>
+      </c>
+      <c r="C522" s="4"/>
       <c r="D522" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E522" s="4"/>
@@ -15553,18 +15549,22 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
-        </is>
-      </c>
-      <c r="C523" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C523" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E523" s="4"/>
@@ -15582,18 +15582,18 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C524" s="4"/>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E524" s="4"/>
@@ -15611,18 +15611,18 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C525" s="4"/>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E525" s="4"/>
@@ -15640,18 +15640,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C526" s="4"/>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15669,18 +15669,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C527" s="4"/>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15698,18 +15698,18 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C528" s="4"/>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15727,18 +15727,18 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭秉霖</t>
         </is>
       </c>
       <c r="C529" s="4"/>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15756,22 +15756,18 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C530" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C530" s="4"/>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15789,22 +15785,22 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>鄭雁予</t>
+          <t>鄭鉅耀</t>
         </is>
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>桃園區國聖二街145號5樓之1</t>
+          <t>新北市五股區成泰路二段208號</t>
         </is>
       </c>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15822,18 +15818,22 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C532" s="4"/>
+          <t>鄭雁予</t>
+        </is>
+      </c>
+      <c r="C532" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15851,18 +15851,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C533" s="4"/>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15880,18 +15880,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E534" s="4"/>
@@ -15909,18 +15909,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C535" s="4"/>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15938,18 +15938,18 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾銘峰</t>
         </is>
       </c>
       <c r="C536" s="4"/>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E536" s="4"/>
@@ -15967,22 +15967,18 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C537" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鐘國禎</t>
+        </is>
+      </c>
+      <c r="C537" s="4"/>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E537" s="4"/>
@@ -16000,24 +15996,28 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2603270001</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>鐘駿霆</t>
-        </is>
-      </c>
-      <c r="C538" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C538" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0919331886</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E538" s="4"/>
       <c r="F538" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G538" s="5" t="inlineStr">
@@ -16029,24 +16029,24 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
+          <t>鐘駿霆</t>
         </is>
       </c>
       <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E539" s="4"/>
       <c r="F539" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G539" s="5" t="inlineStr">
@@ -16058,22 +16058,18 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C540" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>阮海德</t>
+        </is>
+      </c>
+      <c r="C540" s="4"/>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16091,18 +16087,22 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
-        </is>
-      </c>
-      <c r="C541" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C541" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16120,18 +16120,18 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
+          <t>阿源</t>
         </is>
       </c>
       <c r="C542" s="4"/>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E542" s="4"/>
@@ -16149,22 +16149,18 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C543" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿良</t>
+        </is>
+      </c>
+      <c r="C543" s="4"/>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16182,18 +16178,22 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
-        </is>
-      </c>
-      <c r="C544" s="4"/>
+          <t>陳仲盟</t>
+        </is>
+      </c>
+      <c r="C544" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
+        </is>
+      </c>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E544" s="4"/>
@@ -16211,22 +16211,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
-        </is>
-      </c>
-      <c r="C545" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區日和街7號22樓</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16244,22 +16240,22 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
+          <t>陳俊安</t>
         </is>
       </c>
       <c r="C546" s="4" t="inlineStr">
         <is>
-          <t>板橋大觀路1段28巷118-1號</t>
+          <t>新北市土城區日和街7號22樓</t>
         </is>
       </c>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16277,18 +16273,22 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C547" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E547" s="4"/>
@@ -16306,18 +16306,18 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C548" s="4"/>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E548" s="4"/>
@@ -16335,18 +16335,18 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C549" s="4"/>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E549" s="4"/>
@@ -16364,18 +16364,18 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C550" s="4"/>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E550" s="4"/>
@@ -16393,18 +16393,18 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C551" s="4"/>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E551" s="4"/>
@@ -16422,18 +16422,18 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C552" s="4"/>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16451,18 +16451,18 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C553" s="4"/>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16480,18 +16480,18 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C554" s="4"/>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16509,18 +16509,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C555" s="4"/>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16538,18 +16538,18 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳奕融</t>
         </is>
       </c>
       <c r="C556" s="4"/>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16567,22 +16567,18 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C557" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕閔</t>
+        </is>
+      </c>
+      <c r="C557" s="4"/>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16600,18 +16596,22 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2603260001</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳威宇</t>
-        </is>
-      </c>
-      <c r="C558" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C558" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0958186337</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16629,18 +16629,18 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C559" s="4"/>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16658,18 +16658,18 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C560" s="4"/>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16687,18 +16687,18 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C561" s="4"/>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16716,18 +16716,18 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
+          <t>陳子杰</t>
         </is>
       </c>
       <c r="C562" s="4"/>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16745,18 +16745,18 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
+          <t>陳宏文</t>
         </is>
       </c>
       <c r="C563" s="4"/>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16774,22 +16774,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C564" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳宏達</t>
+        </is>
+      </c>
+      <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16807,18 +16803,22 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
-        </is>
-      </c>
-      <c r="C565" s="4"/>
+          <t>陳家偉</t>
+        </is>
+      </c>
+      <c r="C565" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市神農路一段72號</t>
+        </is>
+      </c>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16836,18 +16836,18 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
+          <t>陳小雨</t>
         </is>
       </c>
       <c r="C566" s="4"/>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16865,22 +16865,18 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
-        </is>
-      </c>
-      <c r="C567" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
-        </is>
-      </c>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="C567" s="4"/>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16898,22 +16894,22 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
+          <t>陳建宏(花蓮)</t>
         </is>
       </c>
       <c r="C568" s="4" t="inlineStr">
         <is>
-          <t>新北市三重區仁美街125號</t>
+          <t>花蓮縣新城鄉佳林31之19號</t>
         </is>
       </c>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16931,18 +16927,22 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
-        </is>
-      </c>
-      <c r="C569" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C569" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16960,18 +16960,18 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C570" s="4"/>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16989,18 +16989,18 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C571" s="4"/>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -17018,18 +17018,18 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C572" s="4"/>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -17047,18 +17047,18 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳怡如(彥鈞)</t>
         </is>
       </c>
       <c r="C573" s="4"/>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17076,18 +17076,18 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳慶壎</t>
         </is>
       </c>
       <c r="C574" s="4"/>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17105,22 +17105,18 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C575" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳敬惟</t>
+        </is>
+      </c>
+      <c r="C575" s="4"/>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17138,18 +17134,22 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
-        </is>
-      </c>
-      <c r="C576" s="4"/>
+          <t>陳智盛</t>
+        </is>
+      </c>
+      <c r="C576" s="4" t="inlineStr">
+        <is>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
+        </is>
+      </c>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17167,22 +17167,18 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
-        </is>
-      </c>
-      <c r="C577" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區星雲街30號</t>
-        </is>
-      </c>
+          <t>陳朋堅</t>
+        </is>
+      </c>
+      <c r="C577" s="4"/>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17200,22 +17196,22 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
+          <t>陳松廉</t>
         </is>
       </c>
       <c r="C578" s="4" t="inlineStr">
         <is>
-          <t>桃園市南豐街258號</t>
+          <t>台北市內湖區星雲街30號</t>
         </is>
       </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17233,18 +17229,22 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
-        </is>
-      </c>
-      <c r="C579" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17262,18 +17262,18 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C580" s="4"/>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17291,7 +17291,7 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
@@ -17302,7 +17302,7 @@
       <c r="C581" s="4"/>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17320,18 +17320,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17349,22 +17349,18 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C583" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳正傑</t>
+        </is>
+      </c>
+      <c r="C583" s="4"/>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17382,18 +17378,22 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
-        </is>
-      </c>
-      <c r="C584" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C584" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17411,18 +17411,18 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C585" s="4"/>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17440,18 +17440,18 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
+          <t>陳琇珊</t>
         </is>
       </c>
       <c r="C586" s="4"/>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17469,18 +17469,18 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳琬瑜</t>
         </is>
       </c>
       <c r="C587" s="4"/>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17498,22 +17498,18 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C588" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳璽文</t>
+        </is>
+      </c>
+      <c r="C588" s="4"/>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17531,18 +17527,22 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
-        </is>
-      </c>
-      <c r="C589" s="4"/>
+          <t>陳益銓</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區民生街15巷10號3樓</t>
+        </is>
+      </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17560,22 +17560,18 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
-        </is>
-      </c>
-      <c r="C590" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
-        </is>
-      </c>
+          <t>陳秋蓉</t>
+        </is>
+      </c>
+      <c r="C590" s="4"/>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17593,18 +17589,22 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
-        </is>
-      </c>
-      <c r="C591" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C591" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17622,18 +17622,18 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
+          <t>陳貴源</t>
         </is>
       </c>
       <c r="C592" s="4"/>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17651,18 +17651,18 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
+          <t>陳達鋒</t>
         </is>
       </c>
       <c r="C593" s="4"/>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17680,22 +17680,18 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C594" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C594" s="4"/>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17713,22 +17709,22 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
+          <t>陳長志</t>
         </is>
       </c>
       <c r="C595" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+          <t>新北市新店區安康路</t>
         </is>
       </c>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17746,22 +17742,22 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
+          <t>陳雯瑄</t>
         </is>
       </c>
       <c r="C596" s="4" t="inlineStr">
         <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
         </is>
       </c>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17779,18 +17775,22 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C597" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C597" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17808,18 +17808,18 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C598" s="4"/>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17837,18 +17837,18 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C599" s="4"/>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17866,18 +17866,18 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C600" s="4"/>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E600" s="4"/>
@@ -17895,18 +17895,18 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C601" s="4"/>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17924,18 +17924,18 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C602" s="4"/>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17953,18 +17953,18 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C603" s="4"/>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E603" s="4"/>
@@ -17982,18 +17982,18 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C604" s="4"/>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E604" s="4"/>
@@ -18011,18 +18011,18 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C605" s="4"/>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E605" s="4"/>
@@ -18040,18 +18040,18 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C606" s="4"/>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E606" s="4"/>
@@ -18069,18 +18069,18 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C607" s="4"/>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E607" s="4"/>
@@ -18098,18 +18098,18 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏宏坤</t>
         </is>
       </c>
       <c r="C608" s="4"/>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E608" s="4"/>
@@ -18127,22 +18127,18 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C609" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>馬迪</t>
+        </is>
+      </c>
+      <c r="C609" s="4"/>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18160,18 +18156,22 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
-        </is>
-      </c>
-      <c r="C610" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C610" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18189,18 +18189,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18218,18 +18218,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18247,18 +18247,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18276,18 +18276,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18305,18 +18305,18 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C615" s="4"/>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18334,18 +18334,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高聖景</t>
         </is>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18363,22 +18363,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C617" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高莉婷</t>
+        </is>
+      </c>
+      <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18396,18 +18392,22 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
-        </is>
-      </c>
-      <c r="C618" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C618" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18425,18 +18425,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0937742352</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18454,16 +18454,20 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C620" s="4"/>
-      <c r="D620" s="4"/>
+      <c r="D620" s="4" t="inlineStr">
+        <is>
+          <t>0989116588</t>
+        </is>
+      </c>
       <c r="E620" s="4"/>
       <c r="F620" s="4" t="inlineStr">
         <is>
@@ -18479,20 +18483,16 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>鴻</t>
         </is>
       </c>
       <c r="C621" s="4"/>
-      <c r="D621" s="4" t="inlineStr">
-        <is>
-          <t>0958180882</t>
-        </is>
-      </c>
+      <c r="D621" s="4"/>
       <c r="E621" s="4"/>
       <c r="F621" s="4" t="inlineStr">
         <is>
@@ -18508,22 +18508,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C622" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
+          <t>黃俊翰</t>
+        </is>
+      </c>
+      <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0903975921</t>
+          <t>0958180882</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18541,16 +18537,24 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
-        </is>
-      </c>
-      <c r="C623" s="4"/>
-      <c r="D623" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C623" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
+      <c r="D623" s="4" t="inlineStr">
+        <is>
+          <t>0903975921</t>
+        </is>
+      </c>
       <c r="E623" s="4"/>
       <c r="F623" s="4" t="inlineStr">
         <is>
@@ -18566,20 +18570,16 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C624" s="4"/>
-      <c r="D624" s="4" t="inlineStr">
-        <is>
-          <t>0938722217</t>
-        </is>
-      </c>
+      <c r="D624" s="4"/>
       <c r="E624" s="4"/>
       <c r="F624" s="4" t="inlineStr">
         <is>
@@ -18595,18 +18595,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0989628136</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18624,18 +18624,18 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E626" s="4"/>
@@ -18653,18 +18653,18 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E627" s="4"/>
@@ -18682,18 +18682,18 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C628" s="4"/>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18711,18 +18711,18 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C629" s="4"/>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E629" s="4"/>
@@ -18740,18 +18740,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18769,18 +18769,18 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C631" s="4"/>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E631" s="4"/>
@@ -18798,22 +18798,18 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C632" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃庠豪</t>
+        </is>
+      </c>
+      <c r="C632" s="4"/>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E632" s="4"/>
@@ -18831,18 +18827,22 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
-        </is>
-      </c>
-      <c r="C633" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C633" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E633" s="4"/>
@@ -18860,18 +18860,18 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B634" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C634" s="4"/>
       <c r="D634" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E634" s="4"/>
@@ -18889,18 +18889,18 @@
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C635" s="4"/>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E635" s="4"/>
@@ -18918,18 +18918,18 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B636" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C636" s="4"/>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E636" s="4"/>
@@ -18947,18 +18947,18 @@
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C637" s="4"/>
       <c r="D637" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E637" s="4"/>
@@ -18976,18 +18976,18 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B638" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C638" s="4"/>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E638" s="4"/>
@@ -19005,18 +19005,18 @@
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C639" s="4"/>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E639" s="4"/>
@@ -19034,18 +19034,18 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B640" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C640" s="4"/>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E640" s="4"/>
@@ -19063,18 +19063,18 @@
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C641" s="4"/>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E641" s="4"/>
@@ -19092,18 +19092,18 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B642" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C642" s="4"/>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E642" s="4"/>
@@ -19121,18 +19121,18 @@
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C643" s="4"/>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E643" s="4"/>
@@ -19150,18 +19150,18 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B644" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C644" s="4"/>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E644" s="4"/>
@@ -19179,18 +19179,18 @@
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C645" s="4"/>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E645" s="4"/>
@@ -19208,18 +19208,18 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B646" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C646" s="4"/>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E646" s="4"/>
@@ -19237,18 +19237,18 @@
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C647" s="4"/>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E647" s="4"/>
@@ -19266,18 +19266,18 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B648" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C648" s="4"/>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E648" s="4"/>
@@ -19295,18 +19295,18 @@
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2510020007</t>
         </is>
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃鴻麒</t>
         </is>
       </c>
       <c r="C649" s="4"/>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0930571975</t>
         </is>
       </c>
       <c r="E649" s="4"/>
@@ -19324,18 +19324,18 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2602270002</t>
         </is>
       </c>
       <c r="B650" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黎信宏</t>
         </is>
       </c>
       <c r="C650" s="4"/>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0911024337</t>
         </is>
       </c>
       <c r="E650" s="4"/>
@@ -19351,9 +19351,38 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>2026/04/11  13:00:23</t>
+      <c r="A651" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B651" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C651" s="4"/>
+      <c r="D651" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E651" s="4"/>
+      <c r="F651" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G651" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026/04/12  13:00:15</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -19461,7 +19461,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026/04/13  13:00:19</t>
+          <t>2026/04/14  13:00:16</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -11948,7 +11948,7 @@
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/秀朗</t>
+          <t>舒老闆-寧寧/秀山</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
@@ -19461,7 +19461,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026/04/14  13:00:16</t>
+          <t>2026/04/14  18:00:20</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -7669,18 +7669,18 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>M2511280003</t>
+          <t>M2604160001</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>林文洋</t>
+          <t>林文傑</t>
         </is>
       </c>
       <c r="C256" s="4"/>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>0955731206</t>
+          <t>0955725512</t>
         </is>
       </c>
       <c r="E256" s="4"/>
@@ -7698,18 +7698,18 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>M2510220003</t>
+          <t>M2511280003</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>林明男</t>
+          <t>林文洋</t>
         </is>
       </c>
       <c r="C257" s="4"/>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>0933209600</t>
+          <t>0955731206</t>
         </is>
       </c>
       <c r="E257" s="4"/>
@@ -7727,18 +7727,18 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>M2511300001</t>
+          <t>M2510220003</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>林柏勳</t>
+          <t>林明男</t>
         </is>
       </c>
       <c r="C258" s="4"/>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>0970619667</t>
+          <t>0933209600</t>
         </is>
       </c>
       <c r="E258" s="4"/>
@@ -7756,18 +7756,18 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>M2511160001</t>
+          <t>M2511300001</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>林柏辰</t>
+          <t>林柏勳</t>
         </is>
       </c>
       <c r="C259" s="4"/>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>0909020600</t>
+          <t>0970619667</t>
         </is>
       </c>
       <c r="E259" s="4"/>
@@ -7785,18 +7785,18 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>M2602270001</t>
+          <t>M2511160001</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>林洧民</t>
+          <t>林柏辰</t>
         </is>
       </c>
       <c r="C260" s="4"/>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>0976716171</t>
+          <t>0909020600</t>
         </is>
       </c>
       <c r="E260" s="4"/>
@@ -7814,18 +7814,18 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>M2601110002</t>
+          <t>M2602270001</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>林淵涼</t>
+          <t>林洧民</t>
         </is>
       </c>
       <c r="C261" s="4"/>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>0911280485</t>
+          <t>0976716171</t>
         </is>
       </c>
       <c r="E261" s="4"/>
@@ -7843,18 +7843,18 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>M2511120003</t>
+          <t>M2601110002</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>林清泉</t>
+          <t>林淵涼</t>
         </is>
       </c>
       <c r="C262" s="4"/>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>0910012065</t>
+          <t>0911280485</t>
         </is>
       </c>
       <c r="E262" s="4"/>
@@ -7872,18 +7872,18 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>M2509260023</t>
+          <t>M2511120003</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>林清雲</t>
+          <t>林清泉</t>
         </is>
       </c>
       <c r="C263" s="4"/>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>0936282363</t>
+          <t>0910012065</t>
         </is>
       </c>
       <c r="E263" s="4"/>
@@ -7901,18 +7901,18 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>M2602050001</t>
+          <t>M2509260023</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>林澤恩</t>
+          <t>林清雲</t>
         </is>
       </c>
       <c r="C264" s="4"/>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>0968319131</t>
+          <t>0936282363</t>
         </is>
       </c>
       <c r="E264" s="4"/>
@@ -7930,18 +7930,18 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>M2511160002</t>
+          <t>M2602050001</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>林瑩昇</t>
+          <t>林澤恩</t>
         </is>
       </c>
       <c r="C265" s="4"/>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>0939577028</t>
+          <t>0968319131</t>
         </is>
       </c>
       <c r="E265" s="4"/>
@@ -7959,18 +7959,18 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>M2509260046</t>
+          <t>M2511160002</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>林甫吉</t>
+          <t>林瑩昇</t>
         </is>
       </c>
       <c r="C266" s="4"/>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>0909520365</t>
+          <t>0939577028</t>
         </is>
       </c>
       <c r="E266" s="4"/>
@@ -7988,22 +7988,18 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>M2603280002</t>
+          <t>M2509260046</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>林秀英</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>台北市士林區中山北路七段81巷16弄11-2號1樓</t>
-        </is>
-      </c>
+          <t>林甫吉</t>
+        </is>
+      </c>
+      <c r="C267" s="4"/>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>0922316858</t>
+          <t>0909520365</t>
         </is>
       </c>
       <c r="E267" s="4"/>
@@ -8021,18 +8017,22 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>M2509260053</t>
+          <t>M2603280002</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>林美雲</t>
-        </is>
-      </c>
-      <c r="C268" s="4"/>
+          <t>林秀英</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區中山北路七段81巷16弄11-2號1樓</t>
+        </is>
+      </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>0920436214</t>
+          <t>0922316858</t>
         </is>
       </c>
       <c r="E268" s="4"/>
@@ -8050,18 +8050,18 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>M2510280002</t>
+          <t>M2509260053</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>林耀武</t>
+          <t>林美雲</t>
         </is>
       </c>
       <c r="C269" s="4"/>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>0911552967</t>
+          <t>0920436214</t>
         </is>
       </c>
       <c r="E269" s="4"/>
@@ -8079,18 +8079,18 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>M2509300005</t>
+          <t>M2510280002</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>林通海</t>
+          <t>林耀武</t>
         </is>
       </c>
       <c r="C270" s="4"/>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>0958589472</t>
+          <t>0911552967</t>
         </is>
       </c>
       <c r="E270" s="4"/>
@@ -8108,18 +8108,22 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>M2511220001</t>
+          <t>M2604160002</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>林鈺倫</t>
-        </is>
-      </c>
-      <c r="C271" s="4"/>
+          <t>林辰奕</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市黎明路323巷31號</t>
+        </is>
+      </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>0988210410</t>
+          <t>0903807636</t>
         </is>
       </c>
       <c r="E271" s="4"/>
@@ -8137,18 +8141,18 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>M2510190005</t>
+          <t>M2509300005</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>林鈺瑩</t>
+          <t>林通海</t>
         </is>
       </c>
       <c r="C272" s="4"/>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>0973789355</t>
+          <t>0958589472</t>
         </is>
       </c>
       <c r="E272" s="4"/>
@@ -8166,18 +8170,18 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>M2603311001</t>
+          <t>M2511220001</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>林銘宇</t>
+          <t>林鈺倫</t>
         </is>
       </c>
       <c r="C273" s="4"/>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>0903101817</t>
+          <t>0988210410</t>
         </is>
       </c>
       <c r="E273" s="4"/>
@@ -8195,18 +8199,18 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>M2511250001</t>
+          <t>M2510190005</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>林雅琦</t>
+          <t>林鈺瑩</t>
         </is>
       </c>
       <c r="C274" s="4"/>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>0917361103</t>
+          <t>0973789355</t>
         </is>
       </c>
       <c r="E274" s="4"/>
@@ -8224,18 +8228,18 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>M2510100002</t>
+          <t>M2603311001</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>林鴻丞</t>
+          <t>林銘宇</t>
         </is>
       </c>
       <c r="C275" s="4"/>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>0989764757</t>
+          <t>0903101817</t>
         </is>
       </c>
       <c r="E275" s="4"/>
@@ -8253,18 +8257,18 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>M2601030004</t>
+          <t>M2511250001</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>柯偉強</t>
+          <t>林雅琦</t>
         </is>
       </c>
       <c r="C276" s="4"/>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>0976720368</t>
+          <t>0917361103</t>
         </is>
       </c>
       <c r="E276" s="4"/>
@@ -8282,18 +8286,18 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>M2510050009</t>
+          <t>M2510100002</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>梁涵鈞</t>
+          <t>林鴻丞</t>
         </is>
       </c>
       <c r="C277" s="4"/>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>0961007059</t>
+          <t>0989764757</t>
         </is>
       </c>
       <c r="E277" s="4"/>
@@ -8311,18 +8315,18 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>M2512210002</t>
+          <t>M2601030004</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>楊啓煌</t>
+          <t>柯偉強</t>
         </is>
       </c>
       <c r="C278" s="4"/>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>0970290888</t>
+          <t>0976720368</t>
         </is>
       </c>
       <c r="E278" s="4"/>
@@ -8340,22 +8344,18 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>M2603240002</t>
+          <t>M2510050009</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>楊啓煌</t>
-        </is>
-      </c>
-      <c r="C279" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區新生北路三段84巷33號2樓</t>
-        </is>
-      </c>
+          <t>梁涵鈞</t>
+        </is>
+      </c>
+      <c r="C279" s="4"/>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>0970290888</t>
+          <t>0961007059</t>
         </is>
       </c>
       <c r="E279" s="4"/>
@@ -8373,18 +8373,18 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>M2509260042</t>
+          <t>M2512210002</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>楊士毅</t>
+          <t>楊啓煌</t>
         </is>
       </c>
       <c r="C280" s="4"/>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>0917523878</t>
+          <t>0970290888</t>
         </is>
       </c>
       <c r="E280" s="4"/>
@@ -8402,18 +8402,22 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>M2510100008</t>
+          <t>M2603240002</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>楊孝斌</t>
-        </is>
-      </c>
-      <c r="C281" s="4"/>
+          <t>楊啓煌</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>台北市中山區新生北路三段84巷33號2樓</t>
+        </is>
+      </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>0916001788</t>
+          <t>0970290888</t>
         </is>
       </c>
       <c r="E281" s="4"/>
@@ -8431,22 +8435,18 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>M2509270002</t>
+          <t>M2509260042</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>楊岱惊</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>桃園市長安街26巷3號</t>
-        </is>
-      </c>
+          <t>楊士毅</t>
+        </is>
+      </c>
+      <c r="C282" s="4"/>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>0989612191</t>
+          <t>0917523878</t>
         </is>
       </c>
       <c r="E282" s="4"/>
@@ -8464,22 +8464,18 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>M2509270011</t>
+          <t>M2510100008</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>楊庭瑋</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中山區復興路151號</t>
-        </is>
-      </c>
+          <t>楊孝斌</t>
+        </is>
+      </c>
+      <c r="C283" s="4"/>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>0963922276</t>
+          <t>0916001788</t>
         </is>
       </c>
       <c r="E283" s="4"/>
@@ -8497,18 +8493,22 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>M2511060001</t>
+          <t>M2509270002</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>楊明晁(四哥)</t>
-        </is>
-      </c>
-      <c r="C284" s="4"/>
+          <t>楊岱惊</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>桃園市長安街26巷3號</t>
+        </is>
+      </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>0968732839</t>
+          <t>0989612191</t>
         </is>
       </c>
       <c r="E284" s="4"/>
@@ -8526,18 +8526,22 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>M2601250001</t>
+          <t>M2509270011</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>楊智傑</t>
-        </is>
-      </c>
-      <c r="C285" s="4"/>
+          <t>楊庭瑋</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區復興路151號</t>
+        </is>
+      </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>0931131821</t>
+          <t>0963922276</t>
         </is>
       </c>
       <c r="E285" s="4"/>
@@ -8555,18 +8559,18 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>M2510030003</t>
+          <t>M2511060001</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>楊智翔</t>
+          <t>楊明晁(四哥)</t>
         </is>
       </c>
       <c r="C286" s="4"/>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>0975128278</t>
+          <t>0968732839</t>
         </is>
       </c>
       <c r="E286" s="4"/>
@@ -8584,18 +8588,18 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>M2510060004</t>
+          <t>M2601250001</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>楊重九</t>
+          <t>楊智傑</t>
         </is>
       </c>
       <c r="C287" s="4"/>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>0920626999</t>
+          <t>0931131821</t>
         </is>
       </c>
       <c r="E287" s="4"/>
@@ -8613,18 +8617,18 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>M2510080001</t>
+          <t>M2510030003</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>楊錦加</t>
+          <t>楊智翔</t>
         </is>
       </c>
       <c r="C288" s="4"/>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>0918872988</t>
+          <t>0975128278</t>
         </is>
       </c>
       <c r="E288" s="4"/>
@@ -8642,18 +8646,18 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>M2603280003</t>
+          <t>M2510060004</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>楊鎮良</t>
+          <t>楊重九</t>
         </is>
       </c>
       <c r="C289" s="4"/>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>0976121606</t>
+          <t>0920626999</t>
         </is>
       </c>
       <c r="E289" s="4"/>
@@ -8671,16 +8675,20 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>V0020</t>
+          <t>M2510080001</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>榮豪</t>
+          <t>楊錦加</t>
         </is>
       </c>
       <c r="C290" s="4"/>
-      <c r="D290" s="4"/>
+      <c r="D290" s="4" t="inlineStr">
+        <is>
+          <t>0918872988</t>
+        </is>
+      </c>
       <c r="E290" s="4"/>
       <c r="F290" s="4" t="inlineStr">
         <is>
@@ -8696,18 +8704,18 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>M2602130002</t>
+          <t>M2603280003</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>榮豪-許</t>
+          <t>楊鎮良</t>
         </is>
       </c>
       <c r="C291" s="4"/>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>0931100879</t>
+          <t>0976121606</t>
         </is>
       </c>
       <c r="E291" s="4"/>
@@ -8725,20 +8733,16 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>M2602080007</t>
+          <t>V0020</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>樓俊瑋</t>
+          <t>榮豪</t>
         </is>
       </c>
       <c r="C292" s="4"/>
-      <c r="D292" s="4" t="inlineStr">
-        <is>
-          <t>0910900256</t>
-        </is>
-      </c>
+      <c r="D292" s="4"/>
       <c r="E292" s="4"/>
       <c r="F292" s="4" t="inlineStr">
         <is>
@@ -8754,22 +8758,18 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>M2511010001</t>
+          <t>M2602130002</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>武林</t>
-        </is>
-      </c>
-      <c r="C293" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區集美街222號5樓</t>
-        </is>
-      </c>
+          <t>榮豪-許</t>
+        </is>
+      </c>
+      <c r="C293" s="4"/>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>0913211688</t>
+          <t>0931100879</t>
         </is>
       </c>
       <c r="E293" s="4"/>
@@ -8787,18 +8787,18 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>M2511080005</t>
+          <t>M2602080007</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>毛毛</t>
+          <t>樓俊瑋</t>
         </is>
       </c>
       <c r="C294" s="4"/>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>0919286386</t>
+          <t>0910900256</t>
         </is>
       </c>
       <c r="E294" s="4"/>
@@ -8816,24 +8816,28 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>Z0001</t>
+          <t>M2511010001</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>民享店</t>
+          <t>武林</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
-        </is>
-      </c>
-      <c r="D295" s="4"/>
+          <t>新北市三重區集美街222號5樓</t>
+        </is>
+      </c>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>0913211688</t>
+        </is>
+      </c>
       <c r="E295" s="4"/>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -8845,20 +8849,24 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>V0014</t>
+          <t>M2511080005</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>民享房東</t>
+          <t>毛毛</t>
         </is>
       </c>
       <c r="C296" s="4"/>
-      <c r="D296" s="4"/>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>0919286386</t>
+        </is>
+      </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G296" s="5" t="inlineStr">
@@ -8870,20 +8878,24 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>V0019</t>
+          <t>Z0001</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>永豐餘</t>
-        </is>
-      </c>
-      <c r="C297" s="4"/>
+          <t>民享店</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
+        </is>
+      </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -8895,24 +8907,20 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>M2509260041</t>
+          <t>V0014</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>江世隆(新莊區)</t>
+          <t>民享房東</t>
         </is>
       </c>
       <c r="C298" s="4"/>
-      <c r="D298" s="4" t="inlineStr">
-        <is>
-          <t>0981243133</t>
-        </is>
-      </c>
+      <c r="D298" s="4"/>
       <c r="E298" s="4"/>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
@@ -8924,24 +8932,20 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>M2510050010</t>
+          <t>V0019</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>江仁堂</t>
+          <t>永豐餘</t>
         </is>
       </c>
       <c r="C299" s="4"/>
-      <c r="D299" s="4" t="inlineStr">
-        <is>
-          <t>0986696777</t>
-        </is>
-      </c>
+      <c r="D299" s="4"/>
       <c r="E299" s="4"/>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -8953,18 +8957,18 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>M2511220002</t>
+          <t>M2509260041</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>江凱逸</t>
+          <t>江世隆(新莊區)</t>
         </is>
       </c>
       <c r="C300" s="4"/>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>0912312896</t>
+          <t>0981243133</t>
         </is>
       </c>
       <c r="E300" s="4"/>
@@ -8982,16 +8986,20 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>M2509120001</t>
+          <t>M2510050010</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>江哥</t>
+          <t>江仁堂</t>
         </is>
       </c>
       <c r="C301" s="4"/>
-      <c r="D301" s="4"/>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>0986696777</t>
+        </is>
+      </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4" t="inlineStr">
         <is>
@@ -9007,18 +9015,18 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>M2509280006</t>
+          <t>M2511220002</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>江宏恩</t>
+          <t>江凱逸</t>
         </is>
       </c>
       <c r="C302" s="4"/>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>0988677410</t>
+          <t>0912312896</t>
         </is>
       </c>
       <c r="E302" s="4"/>
@@ -9036,20 +9044,16 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>M2510160009</t>
+          <t>M2509120001</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>江育哲</t>
+          <t>江哥</t>
         </is>
       </c>
       <c r="C303" s="4"/>
-      <c r="D303" s="4" t="inlineStr">
-        <is>
-          <t>0916586618</t>
-        </is>
-      </c>
+      <c r="D303" s="4"/>
       <c r="E303" s="4"/>
       <c r="F303" s="4" t="inlineStr">
         <is>
@@ -9065,18 +9069,18 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>M2511060005</t>
+          <t>M2509280006</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>池沛潔</t>
+          <t>江宏恩</t>
         </is>
       </c>
       <c r="C304" s="4"/>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>0963900636</t>
+          <t>0988677410</t>
         </is>
       </c>
       <c r="E304" s="4"/>
@@ -9094,18 +9098,18 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>M2510240003</t>
+          <t>M2510160009</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>汪鈺修</t>
+          <t>江育哲</t>
         </is>
       </c>
       <c r="C305" s="4"/>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>0971792952</t>
+          <t>0916586618</t>
         </is>
       </c>
       <c r="E305" s="4"/>
@@ -9123,18 +9127,18 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>M2601030003</t>
+          <t>M2511060005</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>沈大哥</t>
+          <t>池沛潔</t>
         </is>
       </c>
       <c r="C306" s="4"/>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>0978562818</t>
+          <t>0963900636</t>
         </is>
       </c>
       <c r="E306" s="4"/>
@@ -9152,18 +9156,18 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>M2509300002</t>
+          <t>M2510240003</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>沈明鋒</t>
+          <t>汪鈺修</t>
         </is>
       </c>
       <c r="C307" s="4"/>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>0908356227</t>
+          <t>0971792952</t>
         </is>
       </c>
       <c r="E307" s="4"/>
@@ -9181,20 +9185,24 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>V0005</t>
+          <t>M2601030003</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>波蜜企業</t>
+          <t>沈大哥</t>
         </is>
       </c>
       <c r="C308" s="4"/>
-      <c r="D308" s="4"/>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>0978562818</t>
+        </is>
+      </c>
       <c r="E308" s="4"/>
       <c r="F308" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -9206,18 +9214,18 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>M2512200004</t>
+          <t>M2509300002</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>洪丞鍇</t>
+          <t>沈明鋒</t>
         </is>
       </c>
       <c r="C309" s="4"/>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>0952119213</t>
+          <t>0908356227</t>
         </is>
       </c>
       <c r="E309" s="4"/>
@@ -9235,24 +9243,20 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>M2602270003</t>
+          <t>V0005</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>洪儒明</t>
+          <t>波蜜企業</t>
         </is>
       </c>
       <c r="C310" s="4"/>
-      <c r="D310" s="4" t="inlineStr">
-        <is>
-          <t>0960097097</t>
-        </is>
-      </c>
+      <c r="D310" s="4"/>
       <c r="E310" s="4"/>
       <c r="F310" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -9264,18 +9268,18 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>M2509280012</t>
+          <t>M2512200004</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>洪勝忠</t>
+          <t>洪丞鍇</t>
         </is>
       </c>
       <c r="C311" s="4"/>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>0917962020</t>
+          <t>0952119213</t>
         </is>
       </c>
       <c r="E311" s="4"/>
@@ -9293,18 +9297,18 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>M2510060001</t>
+          <t>M2602270003</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>洪文輝</t>
+          <t>洪儒明</t>
         </is>
       </c>
       <c r="C312" s="4"/>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>0909183013</t>
+          <t>0960097097</t>
         </is>
       </c>
       <c r="E312" s="4"/>
@@ -9322,18 +9326,18 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>M2510300003</t>
+          <t>M2509280012</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>洪毅平</t>
+          <t>洪勝忠</t>
         </is>
       </c>
       <c r="C313" s="4"/>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>0958266132</t>
+          <t>0917962020</t>
         </is>
       </c>
       <c r="E313" s="4"/>
@@ -9351,18 +9355,18 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>M2510240005</t>
+          <t>M2510060001</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>洪浩鈞</t>
+          <t>洪文輝</t>
         </is>
       </c>
       <c r="C314" s="4"/>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>0939553096</t>
+          <t>0909183013</t>
         </is>
       </c>
       <c r="E314" s="4"/>
@@ -9380,18 +9384,18 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>M2509260019</t>
+          <t>M2510300003</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>洪秋麗</t>
+          <t>洪毅平</t>
         </is>
       </c>
       <c r="C315" s="4"/>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>0922210223</t>
+          <t>0958266132</t>
         </is>
       </c>
       <c r="E315" s="4"/>
@@ -9409,18 +9413,18 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>M2512140001</t>
+          <t>M2510240005</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>洪翊珊</t>
+          <t>洪浩鈞</t>
         </is>
       </c>
       <c r="C316" s="4"/>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>0968884119</t>
+          <t>0939553096</t>
         </is>
       </c>
       <c r="E316" s="4"/>
@@ -9438,22 +9442,18 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>M2510060006</t>
+          <t>M2509260019</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>洪金賢</t>
-        </is>
-      </c>
-      <c r="C317" s="4" t="inlineStr">
-        <is>
-          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
-        </is>
-      </c>
+          <t>洪秋麗</t>
+        </is>
+      </c>
+      <c r="C317" s="4"/>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>0933702515</t>
+          <t>0922210223</t>
         </is>
       </c>
       <c r="E317" s="4"/>
@@ -9471,22 +9471,18 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>M2602040001</t>
+          <t>M2512140001</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>涂宏忠</t>
-        </is>
-      </c>
-      <c r="C318" s="4" t="inlineStr">
-        <is>
-          <t>高雄市開發路15-3號</t>
-        </is>
-      </c>
+          <t>洪翊珊</t>
+        </is>
+      </c>
+      <c r="C318" s="4"/>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>0963222826</t>
+          <t>0968884119</t>
         </is>
       </c>
       <c r="E318" s="4"/>
@@ -9504,18 +9500,22 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>M2510090009</t>
+          <t>M2510060006</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>游仲強</t>
-        </is>
-      </c>
-      <c r="C319" s="4"/>
+          <t>洪金賢</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
+        </is>
+      </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>0910671480</t>
+          <t>0933702515</t>
         </is>
       </c>
       <c r="E319" s="4"/>
@@ -9533,18 +9533,22 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>M2602030002</t>
+          <t>M2602040001</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>游凱翔</t>
-        </is>
-      </c>
-      <c r="C320" s="4"/>
+          <t>涂宏忠</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>高雄市開發路15-3號</t>
+        </is>
+      </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>0978317186</t>
+          <t>0963222826</t>
         </is>
       </c>
       <c r="E320" s="4"/>
@@ -9562,18 +9566,18 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>M2601290001</t>
+          <t>M2510090009</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>游家誠</t>
+          <t>游仲強</t>
         </is>
       </c>
       <c r="C321" s="4"/>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>0920727320</t>
+          <t>0910671480</t>
         </is>
       </c>
       <c r="E321" s="4"/>
@@ -9591,18 +9595,18 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>M2510090002</t>
+          <t>M2602030002</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>游煥清</t>
+          <t>游凱翔</t>
         </is>
       </c>
       <c r="C322" s="4"/>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>0932139705</t>
+          <t>0978317186</t>
         </is>
       </c>
       <c r="E322" s="4"/>
@@ -9620,18 +9624,18 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>M2510100004</t>
+          <t>M2601290001</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>潘文展</t>
+          <t>游家誠</t>
         </is>
       </c>
       <c r="C323" s="4"/>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>0930842995</t>
+          <t>0920727320</t>
         </is>
       </c>
       <c r="E323" s="4"/>
@@ -9649,22 +9653,18 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>M2511230004</t>
+          <t>M2510090002</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>潘正霖(瘋爪子)</t>
-        </is>
-      </c>
-      <c r="C324" s="4" t="inlineStr">
-        <is>
-          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
-        </is>
-      </c>
+          <t>游煥清</t>
+        </is>
+      </c>
+      <c r="C324" s="4"/>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>0983777818</t>
+          <t>0932139705</t>
         </is>
       </c>
       <c r="E324" s="4"/>
@@ -9682,18 +9682,18 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>M2509280010</t>
+          <t>M2510100004</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>潘秀茹</t>
+          <t>潘文展</t>
         </is>
       </c>
       <c r="C325" s="4"/>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>0911900520</t>
+          <t>0930842995</t>
         </is>
       </c>
       <c r="E325" s="4"/>
@@ -9711,18 +9711,22 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>M2601200002</t>
+          <t>M2511230004</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>潘糖糖</t>
-        </is>
-      </c>
-      <c r="C326" s="4"/>
+          <t>潘正霖(瘋爪子)</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
+        </is>
+      </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>0976297272</t>
+          <t>0983777818</t>
         </is>
       </c>
       <c r="E326" s="4"/>
@@ -9740,18 +9744,18 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>M2509300016</t>
+          <t>M2509280010</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>潘鳯斌</t>
+          <t>潘秀茹</t>
         </is>
       </c>
       <c r="C327" s="4"/>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>0935502290</t>
+          <t>0911900520</t>
         </is>
       </c>
       <c r="E327" s="4"/>
@@ -9769,16 +9773,20 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>M2509290010</t>
+          <t>M2601200002</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>火牛-批發</t>
+          <t>潘糖糖</t>
         </is>
       </c>
       <c r="C328" s="4"/>
-      <c r="D328" s="4"/>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>0976297272</t>
+        </is>
+      </c>
       <c r="E328" s="4"/>
       <c r="F328" s="4" t="inlineStr">
         <is>
@@ -9794,16 +9802,20 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>M2512180002</t>
+          <t>M2509300016</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>火牛-老秦</t>
+          <t>潘鳯斌</t>
         </is>
       </c>
       <c r="C329" s="4"/>
-      <c r="D329" s="4"/>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>0935502290</t>
+        </is>
+      </c>
       <c r="E329" s="4"/>
       <c r="F329" s="4" t="inlineStr">
         <is>
@@ -9819,12 +9831,12 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>M2512180001</t>
+          <t>M2509290010</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>火牛-阿昌</t>
+          <t>火牛-批發</t>
         </is>
       </c>
       <c r="C330" s="4"/>
@@ -9844,20 +9856,16 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>M2602140002</t>
+          <t>M2512180002</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>灰灰</t>
+          <t>火牛-老秦</t>
         </is>
       </c>
       <c r="C331" s="4"/>
-      <c r="D331" s="4" t="inlineStr">
-        <is>
-          <t>0987829134</t>
-        </is>
-      </c>
+      <c r="D331" s="4"/>
       <c r="E331" s="4"/>
       <c r="F331" s="4" t="inlineStr">
         <is>
@@ -9873,20 +9881,16 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>M2509300011</t>
+          <t>M2512180001</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>熊駿天(大熊)</t>
+          <t>火牛-阿昌</t>
         </is>
       </c>
       <c r="C332" s="4"/>
-      <c r="D332" s="4" t="inlineStr">
-        <is>
-          <t>0933131800</t>
-        </is>
-      </c>
+      <c r="D332" s="4"/>
       <c r="E332" s="4"/>
       <c r="F332" s="4" t="inlineStr">
         <is>
@@ -9902,18 +9906,18 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>M2602070001</t>
+          <t>M2602140002</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>王RICK</t>
+          <t>灰灰</t>
         </is>
       </c>
       <c r="C333" s="4"/>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>0930106976</t>
+          <t>0987829134</t>
         </is>
       </c>
       <c r="E333" s="4"/>
@@ -9931,22 +9935,18 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>M2510240006</t>
+          <t>M2509300011</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>王中南</t>
-        </is>
-      </c>
-      <c r="C334" s="4" t="inlineStr">
-        <is>
-          <t>桃園市平鎮區快速路166號3樓</t>
-        </is>
-      </c>
+          <t>熊駿天(大熊)</t>
+        </is>
+      </c>
+      <c r="C334" s="4"/>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>0937124082</t>
+          <t>0933131800</t>
         </is>
       </c>
       <c r="E334" s="4"/>
@@ -9964,18 +9964,18 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>M2601020001</t>
+          <t>M2602070001</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>王仁澤</t>
+          <t>王RICK</t>
         </is>
       </c>
       <c r="C335" s="4"/>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>0976503359</t>
+          <t>0930106976</t>
         </is>
       </c>
       <c r="E335" s="4"/>
@@ -9993,18 +9993,22 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>M2603010004</t>
+          <t>M2510240006</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>王又杰</t>
-        </is>
-      </c>
-      <c r="C336" s="4"/>
+          <t>王中南</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區快速路166號3樓</t>
+        </is>
+      </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>0909771449</t>
+          <t>0937124082</t>
         </is>
       </c>
       <c r="E336" s="4"/>
@@ -10022,18 +10026,18 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>M2601080001</t>
+          <t>M2601020001</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>王家文</t>
+          <t>王仁澤</t>
         </is>
       </c>
       <c r="C337" s="4"/>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>0908176140</t>
+          <t>0976503359</t>
         </is>
       </c>
       <c r="E337" s="4"/>
@@ -10051,18 +10055,18 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>M2602080001</t>
+          <t>M2603010004</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>王巽璋</t>
+          <t>王又杰</t>
         </is>
       </c>
       <c r="C338" s="4"/>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>0932943159</t>
+          <t>0909771449</t>
         </is>
       </c>
       <c r="E338" s="4"/>
@@ -10080,18 +10084,18 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>M2512230001</t>
+          <t>M2601080001</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>王志維</t>
+          <t>王家文</t>
         </is>
       </c>
       <c r="C339" s="4"/>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>0931262170</t>
+          <t>0908176140</t>
         </is>
       </c>
       <c r="E339" s="4"/>
@@ -10109,18 +10113,18 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>M2511180003</t>
+          <t>M2602080001</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>王明輝</t>
+          <t>王巽璋</t>
         </is>
       </c>
       <c r="C340" s="4"/>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>0937002585</t>
+          <t>0932943159</t>
         </is>
       </c>
       <c r="E340" s="4"/>
@@ -10138,18 +10142,18 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>M2510140007</t>
+          <t>M2512230001</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>王羿佳</t>
+          <t>王志維</t>
         </is>
       </c>
       <c r="C341" s="4"/>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>0968831773</t>
+          <t>0931262170</t>
         </is>
       </c>
       <c r="E341" s="4"/>
@@ -10167,22 +10171,18 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>M2509260013</t>
+          <t>M2511180003</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>王舜平</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
-        </is>
-      </c>
+          <t>王明輝</t>
+        </is>
+      </c>
+      <c r="C342" s="4"/>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>0917215021</t>
+          <t>0937002585</t>
         </is>
       </c>
       <c r="E342" s="4"/>
@@ -10200,18 +10200,18 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>M2601170002</t>
+          <t>M2510140007</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>王閔弘</t>
+          <t>王羿佳</t>
         </is>
       </c>
       <c r="C343" s="4"/>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>0931056292</t>
+          <t>0968831773</t>
         </is>
       </c>
       <c r="E343" s="4"/>
@@ -10229,18 +10229,22 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>M2511230003</t>
+          <t>M2509260013</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>王靜芸</t>
-        </is>
-      </c>
-      <c r="C344" s="4"/>
+          <t>王舜平</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
+        </is>
+      </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>0970224238</t>
+          <t>0917215021</t>
         </is>
       </c>
       <c r="E344" s="4"/>
@@ -10258,18 +10262,18 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>M2510040009</t>
+          <t>M2601170002</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>王駿宏</t>
+          <t>王閔弘</t>
         </is>
       </c>
       <c r="C345" s="4"/>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>0919336854</t>
+          <t>0931056292</t>
         </is>
       </c>
       <c r="E345" s="4"/>
@@ -10287,18 +10291,18 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>M2601010001</t>
+          <t>M2511230003</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>甘玨瑋</t>
+          <t>王靜芸</t>
         </is>
       </c>
       <c r="C346" s="4"/>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>0987214102</t>
+          <t>0970224238</t>
         </is>
       </c>
       <c r="E346" s="4"/>
@@ -10316,22 +10320,18 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>M2510290002</t>
+          <t>M2510040009</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>生生</t>
-        </is>
-      </c>
-      <c r="C347" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街427號</t>
-        </is>
-      </c>
+          <t>王駿宏</t>
+        </is>
+      </c>
+      <c r="C347" s="4"/>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>0919001722</t>
+          <t>0919336854</t>
         </is>
       </c>
       <c r="E347" s="4"/>
@@ -10349,18 +10349,18 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>M2509260050</t>
+          <t>M2601010001</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>甩爪</t>
+          <t>甘玨瑋</t>
         </is>
       </c>
       <c r="C348" s="4"/>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>0970754804</t>
+          <t>0987214102</t>
         </is>
       </c>
       <c r="E348" s="4"/>
@@ -10378,18 +10378,22 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>M2509270005</t>
+          <t>M2510290002</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>甯偉</t>
-        </is>
-      </c>
-      <c r="C349" s="4"/>
+          <t>生生</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街427號</t>
+        </is>
+      </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>0955617290</t>
+          <t>0919001722</t>
         </is>
       </c>
       <c r="E349" s="4"/>
@@ -10407,18 +10411,18 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>M2510240007</t>
+          <t>M2509260050</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>盧其辰</t>
+          <t>甩爪</t>
         </is>
       </c>
       <c r="C350" s="4"/>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>0982119779</t>
+          <t>0970754804</t>
         </is>
       </c>
       <c r="E350" s="4"/>
@@ -10436,18 +10440,18 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>M2604110001</t>
+          <t>M2509270005</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>盧炳宏</t>
+          <t>甯偉</t>
         </is>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>0921062300</t>
+          <t>0955617290</t>
         </is>
       </c>
       <c r="E351" s="4"/>
@@ -10465,20 +10469,24 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>V0013</t>
+          <t>M2510240007</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>真大帥</t>
+          <t>盧其辰</t>
         </is>
       </c>
       <c r="C352" s="4"/>
-      <c r="D352" s="4"/>
+      <c r="D352" s="4" t="inlineStr">
+        <is>
+          <t>0982119779</t>
+        </is>
+      </c>
       <c r="E352" s="4"/>
       <c r="F352" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -10490,18 +10498,18 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>M2510310002</t>
+          <t>M2604110001</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>祁麟</t>
+          <t>盧炳宏</t>
         </is>
       </c>
       <c r="C353" s="4"/>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>0982883101</t>
+          <t>0921062300</t>
         </is>
       </c>
       <c r="E353" s="4"/>
@@ -10519,24 +10527,20 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>M2602130001</t>
+          <t>V0013</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>祐</t>
+          <t>真大帥</t>
         </is>
       </c>
       <c r="C354" s="4"/>
-      <c r="D354" s="4" t="inlineStr">
-        <is>
-          <t>0983407890</t>
-        </is>
-      </c>
+      <c r="D354" s="4"/>
       <c r="E354" s="4"/>
       <c r="F354" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -10548,18 +10552,18 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>M2510050001</t>
+          <t>M2510310002</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>程sir/Ashbur</t>
+          <t>祁麟</t>
         </is>
       </c>
       <c r="C355" s="4"/>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>0963612395</t>
+          <t>0982883101</t>
         </is>
       </c>
       <c r="E355" s="4"/>
@@ -10577,18 +10581,18 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>M2510300001</t>
+          <t>M2602130001</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>程品勝</t>
+          <t>祐</t>
         </is>
       </c>
       <c r="C356" s="4"/>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>0913780727</t>
+          <t>0983407890</t>
         </is>
       </c>
       <c r="E356" s="4"/>
@@ -10606,18 +10610,18 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>M2601270002</t>
+          <t>M2510050001</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>程建智</t>
+          <t>程sir/Ashbur</t>
         </is>
       </c>
       <c r="C357" s="4"/>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>0988919027</t>
+          <t>0963612395</t>
         </is>
       </c>
       <c r="E357" s="4"/>
@@ -10635,18 +10639,18 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>M2603120004</t>
+          <t>M2510300001</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>程郁勛</t>
+          <t>程品勝</t>
         </is>
       </c>
       <c r="C358" s="4"/>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>0955671407</t>
+          <t>0913780727</t>
         </is>
       </c>
       <c r="E358" s="4"/>
@@ -10664,22 +10668,18 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>M2509160001</t>
+          <t>M2601270002</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>穆莉茹</t>
-        </is>
-      </c>
-      <c r="C359" s="4" t="inlineStr">
-        <is>
-          <t>桃園平鎮區上海路169號</t>
-        </is>
-      </c>
+          <t>程建智</t>
+        </is>
+      </c>
+      <c r="C359" s="4"/>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>0955777312</t>
+          <t>0988919027</t>
         </is>
       </c>
       <c r="E359" s="4"/>
@@ -10697,18 +10697,18 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>M2511160003</t>
+          <t>M2603120004</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>簡士傑</t>
+          <t>程郁勛</t>
         </is>
       </c>
       <c r="C360" s="4"/>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>0963817398</t>
+          <t>0955671407</t>
         </is>
       </c>
       <c r="E360" s="4"/>
@@ -10726,18 +10726,22 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>M2509300013</t>
+          <t>M2509160001</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>簡子偉</t>
-        </is>
-      </c>
-      <c r="C361" s="4"/>
+          <t>穆莉茹</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>桃園平鎮區上海路169號</t>
+        </is>
+      </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>0955462926</t>
+          <t>0955777312</t>
         </is>
       </c>
       <c r="E361" s="4"/>
@@ -10755,18 +10759,18 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>M2602280002</t>
+          <t>M2511160003</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>簡子洋</t>
+          <t>簡士傑</t>
         </is>
       </c>
       <c r="C362" s="4"/>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>0933921933</t>
+          <t>0963817398</t>
         </is>
       </c>
       <c r="E362" s="4"/>
@@ -10784,18 +10788,18 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>M2510040003</t>
+          <t>M2509300013</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>簡小琪</t>
+          <t>簡子偉</t>
         </is>
       </c>
       <c r="C363" s="4"/>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>0930033829</t>
+          <t>0955462926</t>
         </is>
       </c>
       <c r="E363" s="4"/>
@@ -10813,18 +10817,18 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>M2510260002</t>
+          <t>M2602280002</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>簡揚城</t>
+          <t>簡子洋</t>
         </is>
       </c>
       <c r="C364" s="4"/>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>0913153353</t>
+          <t>0933921933</t>
         </is>
       </c>
       <c r="E364" s="4"/>
@@ -10842,18 +10846,18 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>M2509300001</t>
+          <t>M2510040003</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>簡瑋成</t>
+          <t>簡小琪</t>
         </is>
       </c>
       <c r="C365" s="4"/>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>0936389969</t>
+          <t>0930033829</t>
         </is>
       </c>
       <c r="E365" s="4"/>
@@ -10871,18 +10875,18 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>M2509290020</t>
+          <t>M2510260002</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>簡茂州</t>
+          <t>簡揚城</t>
         </is>
       </c>
       <c r="C366" s="4"/>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>0985217379</t>
+          <t>0913153353</t>
         </is>
       </c>
       <c r="E366" s="4"/>
@@ -10900,18 +10904,18 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>M2512130001</t>
+          <t>M2509300001</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>紀彥銘</t>
+          <t>簡瑋成</t>
         </is>
       </c>
       <c r="C367" s="4"/>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>0988752337</t>
+          <t>0936389969</t>
         </is>
       </c>
       <c r="E367" s="4"/>
@@ -10929,20 +10933,24 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>V0001</t>
+          <t>M2509290020</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>統有企業</t>
+          <t>簡茂州</t>
         </is>
       </c>
       <c r="C368" s="4"/>
-      <c r="D368" s="4"/>
+      <c r="D368" s="4" t="inlineStr">
+        <is>
+          <t>0985217379</t>
+        </is>
+      </c>
       <c r="E368" s="4"/>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G368" s="5" t="inlineStr">
@@ -10954,18 +10962,18 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>M2509280008</t>
+          <t>M2512130001</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>維克斯</t>
+          <t>紀彥銘</t>
         </is>
       </c>
       <c r="C369" s="4"/>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>0917771787</t>
+          <t>0988752337</t>
         </is>
       </c>
       <c r="E369" s="4"/>
@@ -10983,24 +10991,20 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>M2510170002</t>
+          <t>V0001</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>練鎮宇</t>
+          <t>統有企業</t>
         </is>
       </c>
       <c r="C370" s="4"/>
-      <c r="D370" s="4" t="inlineStr">
-        <is>
-          <t>0952288706</t>
-        </is>
-      </c>
+      <c r="D370" s="4"/>
       <c r="E370" s="4"/>
       <c r="F370" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G370" s="5" t="inlineStr">
@@ -11012,22 +11016,18 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>M2602220003</t>
+          <t>M2509280008</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>羅丁一夫</t>
-        </is>
-      </c>
-      <c r="C371" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
-        </is>
-      </c>
+          <t>維克斯</t>
+        </is>
+      </c>
+      <c r="C371" s="4"/>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>0919339614</t>
+          <t>0917771787</t>
         </is>
       </c>
       <c r="E371" s="4"/>
@@ -11045,18 +11045,18 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>M2510180002</t>
+          <t>M2510170002</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>羅元隆</t>
+          <t>練鎮宇</t>
         </is>
       </c>
       <c r="C372" s="4"/>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>0975866635</t>
+          <t>0952288706</t>
         </is>
       </c>
       <c r="E372" s="4"/>
@@ -11074,25 +11074,25 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>M2510090003</t>
+          <t>M2602220003</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>羅嘉銘</t>
-        </is>
-      </c>
-      <c r="C373" s="4"/>
+          <t>羅丁一夫</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
+        </is>
+      </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>0928093385</t>
-        </is>
-      </c>
-      <c r="E373" s="4" t="inlineStr">
-        <is>
-          <t>0985866052</t>
-        </is>
-      </c>
+          <t>0919339614</t>
+        </is>
+      </c>
+      <c r="E373" s="4"/>
       <c r="F373" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11107,18 +11107,18 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>M2602240001</t>
+          <t>M2510180002</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>羅浩中</t>
+          <t>羅元隆</t>
         </is>
       </c>
       <c r="C374" s="4"/>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>0970905092</t>
+          <t>0975866635</t>
         </is>
       </c>
       <c r="E374" s="4"/>
@@ -11136,21 +11136,25 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>M2511060003</t>
+          <t>M2510090003</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>翁名勳</t>
+          <t>羅嘉銘</t>
         </is>
       </c>
       <c r="C375" s="4"/>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>0955083317</t>
-        </is>
-      </c>
-      <c r="E375" s="4"/>
+          <t>0928093385</t>
+        </is>
+      </c>
+      <c r="E375" s="4" t="inlineStr">
+        <is>
+          <t>0985866052</t>
+        </is>
+      </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11165,18 +11169,18 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>M2509260057</t>
+          <t>M2602240001</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>翁國昌</t>
+          <t>羅浩中</t>
         </is>
       </c>
       <c r="C376" s="4"/>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>0918718772</t>
+          <t>0970905092</t>
         </is>
       </c>
       <c r="E376" s="4"/>
@@ -11194,22 +11198,18 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>M2511290001</t>
+          <t>M2511060003</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>翁國祥</t>
-        </is>
-      </c>
-      <c r="C377" s="4" t="inlineStr">
-        <is>
-          <t>新北新莊中信街65號1樓賣菜攤</t>
-        </is>
-      </c>
+          <t>翁名勳</t>
+        </is>
+      </c>
+      <c r="C377" s="4"/>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>0983900052</t>
+          <t>0955083317</t>
         </is>
       </c>
       <c r="E377" s="4"/>
@@ -11227,22 +11227,18 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>M2510010009</t>
+          <t>M2509260057</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩</t>
-        </is>
-      </c>
-      <c r="C378" s="4" t="inlineStr">
-        <is>
-          <t>未決定</t>
-        </is>
-      </c>
+          <t>翁國昌</t>
+        </is>
+      </c>
+      <c r="C378" s="4"/>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>0972757015</t>
+          <t>0918718772</t>
         </is>
       </c>
       <c r="E378" s="4"/>
@@ -11260,86 +11256,86 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
+          <t>M2511290001</t>
+        </is>
+      </c>
+      <c r="B379" s="4" t="inlineStr">
+        <is>
+          <t>翁國祥</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>新北新莊中信街65號1樓賣菜攤</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>0983900052</t>
+        </is>
+      </c>
+      <c r="E379" s="4"/>
+      <c r="F379" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G379" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="4" t="inlineStr">
+        <is>
+          <t>M2510010009</t>
+        </is>
+      </c>
+      <c r="B380" s="4" t="inlineStr">
+        <is>
+          <t>翁敬恩</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="inlineStr">
+        <is>
+          <t>未決定</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>0972757015</t>
+        </is>
+      </c>
+      <c r="E380" s="4"/>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G380" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="4" t="inlineStr">
+        <is>
           <t>M2510010009-4</t>
         </is>
       </c>
-      <c r="B379" s="4" t="inlineStr">
+      <c r="B381" s="4" t="inlineStr">
         <is>
           <t>翁敬恩-文山</t>
         </is>
       </c>
-      <c r="C379" s="6" t="inlineStr">
+      <c r="C381" s="6" t="inlineStr">
         <is>
           <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
 收件聯絡電話:0937462412</t>
         </is>
       </c>
-      <c r="D379" s="4" t="inlineStr">
-        <is>
-          <t>0972757015</t>
-        </is>
-      </c>
-      <c r="E379" s="4"/>
-      <c r="F379" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
-      <c r="G379" s="5" t="inlineStr">
-        <is>
-          <t>附件管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="4" t="inlineStr">
-        <is>
-          <t>M2510010009-2</t>
-        </is>
-      </c>
-      <c r="B380" s="4" t="inlineStr">
-        <is>
-          <t>翁敬恩-樂華</t>
-        </is>
-      </c>
-      <c r="C380" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
-        </is>
-      </c>
-      <c r="D380" s="4" t="inlineStr">
-        <is>
-          <t>0972757015</t>
-        </is>
-      </c>
-      <c r="E380" s="4"/>
-      <c r="F380" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
-      <c r="G380" s="5" t="inlineStr">
-        <is>
-          <t>附件管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="4" t="inlineStr">
-        <is>
-          <t>M2510010009-3</t>
-        </is>
-      </c>
-      <c r="B381" s="4" t="inlineStr">
-        <is>
-          <t>翁敬恩-永和</t>
-        </is>
-      </c>
-      <c r="C381" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
-        </is>
-      </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
           <t>0972757015</t>
@@ -11360,22 +11356,22 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-1</t>
+          <t>M2510010009-2</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-饒河</t>
+          <t>翁敬恩-樂華</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>0975953978</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E382" s="4"/>
@@ -11393,18 +11389,22 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>M2510140004</t>
+          <t>M2510010009-3</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>翁漢忠</t>
-        </is>
-      </c>
-      <c r="C383" s="4"/>
+          <t>翁敬恩-永和</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
+        </is>
+      </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>0916150750</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E383" s="4"/>
@@ -11422,18 +11422,22 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>M2509260037</t>
+          <t>M2510010009-1</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>翁翌禎</t>
-        </is>
-      </c>
-      <c r="C384" s="4"/>
+          <t>翁敬恩-饒河</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr">
+        <is>
+          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+        </is>
+      </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>0902308293</t>
+          <t>0975953978</t>
         </is>
       </c>
       <c r="E384" s="4"/>
@@ -11451,18 +11455,18 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>M2509280002</t>
+          <t>M2510140004</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>聶大中</t>
+          <t>翁漢忠</t>
         </is>
       </c>
       <c r="C385" s="4"/>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>0955059148</t>
+          <t>0916150750</t>
         </is>
       </c>
       <c r="E385" s="4"/>
@@ -11480,18 +11484,18 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>M2510220001</t>
+          <t>M2509260037</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>胡HU</t>
+          <t>翁翌禎</t>
         </is>
       </c>
       <c r="C386" s="4"/>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>0988603554</t>
+          <t>0902308293</t>
         </is>
       </c>
       <c r="E386" s="4"/>
@@ -11509,18 +11513,18 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>M2510100011</t>
+          <t>M2509280002</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>胡凱傑</t>
+          <t>聶大中</t>
         </is>
       </c>
       <c r="C387" s="4"/>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>0955888840</t>
+          <t>0955059148</t>
         </is>
       </c>
       <c r="E387" s="4"/>
@@ -11538,18 +11542,18 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>M2510090005</t>
+          <t>M2510220001</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>胡家榮</t>
+          <t>胡HU</t>
         </is>
       </c>
       <c r="C388" s="4"/>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>0933059025</t>
+          <t>0988603554</t>
         </is>
       </c>
       <c r="E388" s="4"/>
@@ -11567,18 +11571,18 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>M2511150001</t>
+          <t>M2510100011</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>胡家銘</t>
+          <t>胡凱傑</t>
         </is>
       </c>
       <c r="C389" s="4"/>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>0986362263</t>
+          <t>0955888840</t>
         </is>
       </c>
       <c r="E389" s="4"/>
@@ -11596,18 +11600,18 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>M2511290003</t>
+          <t>M2510090005</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>胡峻強</t>
+          <t>胡家榮</t>
         </is>
       </c>
       <c r="C390" s="4"/>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>0953088041</t>
+          <t>0933059025</t>
         </is>
       </c>
       <c r="E390" s="4"/>
@@ -11625,18 +11629,18 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>M2603010001</t>
+          <t>M2511150001</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>胡辰煜</t>
+          <t>胡家銘</t>
         </is>
       </c>
       <c r="C391" s="4"/>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>0963903685</t>
+          <t>0986362263</t>
         </is>
       </c>
       <c r="E391" s="4"/>
@@ -11654,18 +11658,18 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2510040002</t>
+          <t>M2511290003</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>胡辰軒</t>
+          <t>胡峻強</t>
         </is>
       </c>
       <c r="C392" s="4"/>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>0972094622</t>
+          <t>0953088041</t>
         </is>
       </c>
       <c r="E392" s="4"/>
@@ -11683,18 +11687,18 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>M2602280001</t>
+          <t>M2603010001</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>胡閎翔</t>
+          <t>胡辰煜</t>
         </is>
       </c>
       <c r="C393" s="4"/>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>0970556309</t>
+          <t>0963903685</t>
         </is>
       </c>
       <c r="E393" s="4"/>
@@ -11712,18 +11716,18 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>M2511290002</t>
+          <t>M2510040002</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>舒老闆</t>
+          <t>胡辰軒</t>
         </is>
       </c>
       <c r="C394" s="4"/>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>0979788818</t>
+          <t>0972094622</t>
         </is>
       </c>
       <c r="E394" s="4"/>
@@ -11741,22 +11745,18 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-6</t>
+          <t>M2602280001</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-冬冬/虎林</t>
-        </is>
-      </c>
-      <c r="C395" s="4" t="inlineStr">
-        <is>
-          <t>台北市信義區虎林街164巷60弄19號</t>
-        </is>
-      </c>
+          <t>胡閎翔</t>
+        </is>
+      </c>
+      <c r="C395" s="4"/>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>0979788818</t>
+          <t>0970556309</t>
         </is>
       </c>
       <c r="E395" s="4"/>
@@ -11774,19 +11774,15 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-8</t>
+          <t>M2511290002</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德17號</t>
-        </is>
-      </c>
-      <c r="C396" s="4" t="inlineStr">
-        <is>
-          <t>台北市松山區八德路三段155巷17號</t>
-        </is>
-      </c>
+          <t>舒老闆</t>
+        </is>
+      </c>
+      <c r="C396" s="4"/>
       <c r="D396" s="4" t="inlineStr">
         <is>
           <t>0979788818</t>
@@ -11807,17 +11803,17 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-2</t>
+          <t>M2511290002-6</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德46號</t>
+          <t>舒老闆-冬冬/虎林</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區八德路三段12巷51弄46號</t>
+          <t>台北市信義區虎林街164巷60弄19號</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -11840,17 +11836,17 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-7</t>
+          <t>M2511290002-8</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/臥龍</t>
+          <t>舒老闆-夾鬥陣/八德17號</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>台北市大安區臥龍街254號</t>
+          <t>台北市松山區八德路三段155巷17號</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -11873,17 +11869,17 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-4</t>
+          <t>M2511290002-2</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/中正</t>
+          <t>舒老闆-夾鬥陣/八德46號</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路14號</t>
+          <t>台北市松山區八德路三段12巷51弄46號</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -11906,17 +11902,17 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-5</t>
+          <t>M2511290002-7</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/吳興</t>
+          <t>舒老闆-夾鬥陣/臥龍</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>台北市信義區吳興街342號</t>
+          <t>台北市大安區臥龍街254號</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
@@ -11939,17 +11935,17 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-3</t>
+          <t>M2511290002-4</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/智光</t>
+          <t>舒老闆-寧寧/中正</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區智光街98號</t>
+          <t>新北市永和區中正路14號</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -11972,17 +11968,17 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-1</t>
+          <t>M2511290002-5</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/秀山</t>
+          <t>舒老闆-寧寧/吳興</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+          <t>台北市信義區吳興街342號</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
@@ -12005,18 +12001,22 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>M2510140002</t>
+          <t>M2511290002-3</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>范姜敏中</t>
-        </is>
-      </c>
-      <c r="C403" s="4"/>
+          <t>舒老闆-寧寧/智光</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區智光街98號</t>
+        </is>
+      </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>0937464692</t>
+          <t>0979788818</t>
         </is>
       </c>
       <c r="E403" s="4"/>
@@ -12034,18 +12034,22 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>M2510140003</t>
+          <t>M2511290002-1</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>范姜群成</t>
-        </is>
-      </c>
-      <c r="C404" s="4"/>
+          <t>舒老闆-寧寧/秀山</t>
+        </is>
+      </c>
+      <c r="C404" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+        </is>
+      </c>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>0920565234</t>
+          <t>0979788818</t>
         </is>
       </c>
       <c r="E404" s="4"/>
@@ -12063,22 +12067,18 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>M2511300003</t>
+          <t>M2510140002</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>莊正當</t>
-        </is>
-      </c>
-      <c r="C405" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區建安街27號3樓</t>
-        </is>
-      </c>
+          <t>范姜敏中</t>
+        </is>
+      </c>
+      <c r="C405" s="4"/>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>0983337218</t>
+          <t>0937464692</t>
         </is>
       </c>
       <c r="E405" s="4"/>
@@ -12096,22 +12096,18 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>M2510270004</t>
+          <t>M2510140003</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>莊淑玲</t>
-        </is>
-      </c>
-      <c r="C406" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區五工三路78巷36號</t>
-        </is>
-      </c>
+          <t>范姜群成</t>
+        </is>
+      </c>
+      <c r="C406" s="4"/>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>0922277383</t>
+          <t>0920565234</t>
         </is>
       </c>
       <c r="E406" s="4"/>
@@ -12129,18 +12125,22 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>M2510190002</t>
+          <t>M2511300003</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>莊耿華</t>
-        </is>
-      </c>
-      <c r="C407" s="4"/>
+          <t>莊正當</t>
+        </is>
+      </c>
+      <c r="C407" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區建安街27號3樓</t>
+        </is>
+      </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>0938600334</t>
+          <t>0983337218</t>
         </is>
       </c>
       <c r="E407" s="4"/>
@@ -12158,18 +12158,22 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>M2509260005</t>
+          <t>M2510270004</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>莊莊</t>
-        </is>
-      </c>
-      <c r="C408" s="4"/>
+          <t>莊淑玲</t>
+        </is>
+      </c>
+      <c r="C408" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工三路78巷36號</t>
+        </is>
+      </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>0955985557</t>
+          <t>0922277383</t>
         </is>
       </c>
       <c r="E408" s="4"/>
@@ -12187,18 +12191,18 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>M2510100007</t>
+          <t>M2510190002</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>莊閔丞</t>
+          <t>莊耿華</t>
         </is>
       </c>
       <c r="C409" s="4"/>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>0963320370</t>
+          <t>0938600334</t>
         </is>
       </c>
       <c r="E409" s="4"/>
@@ -12216,18 +12220,18 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>M2602240002</t>
+          <t>M2509260005</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>萬宗霖</t>
+          <t>莊莊</t>
         </is>
       </c>
       <c r="C410" s="4"/>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>0977082365</t>
+          <t>0955985557</t>
         </is>
       </c>
       <c r="E410" s="4"/>
@@ -12245,18 +12249,18 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>M2510160001</t>
+          <t>M2510100007</t>
         </is>
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>葉力瑋</t>
+          <t>莊閔丞</t>
         </is>
       </c>
       <c r="C411" s="4"/>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>0979611911</t>
+          <t>0963320370</t>
         </is>
       </c>
       <c r="E411" s="4"/>
@@ -12274,18 +12278,18 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>M2510030002</t>
+          <t>M2602240002</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>葉家睿</t>
+          <t>萬宗霖</t>
         </is>
       </c>
       <c r="C412" s="4"/>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>0928112227</t>
+          <t>0977082365</t>
         </is>
       </c>
       <c r="E412" s="4"/>
@@ -12303,18 +12307,18 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>M2511050003</t>
+          <t>M2510160001</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>葉庭綸</t>
+          <t>葉力瑋</t>
         </is>
       </c>
       <c r="C413" s="4"/>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>0966638685</t>
+          <t>0979611911</t>
         </is>
       </c>
       <c r="E413" s="4"/>
@@ -12332,18 +12336,18 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>M2510180001</t>
+          <t>M2510030002</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>葉建財</t>
+          <t>葉家睿</t>
         </is>
       </c>
       <c r="C414" s="4"/>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>0989713349</t>
+          <t>0928112227</t>
         </is>
       </c>
       <c r="E414" s="4"/>
@@ -12361,18 +12365,18 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>M2510150001</t>
+          <t>M2511050003</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>葉彥均</t>
+          <t>葉庭綸</t>
         </is>
       </c>
       <c r="C415" s="4"/>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>0921436111</t>
+          <t>0966638685</t>
         </is>
       </c>
       <c r="E415" s="4"/>
@@ -12390,18 +12394,18 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>M2601220001</t>
+          <t>M2510180001</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>葉方奕</t>
+          <t>葉建財</t>
         </is>
       </c>
       <c r="C416" s="4"/>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>0918386488</t>
+          <t>0989713349</t>
         </is>
       </c>
       <c r="E416" s="4"/>
@@ -12419,18 +12423,18 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>M2510260005</t>
+          <t>M2510150001</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>葉祈賢</t>
+          <t>葉彥均</t>
         </is>
       </c>
       <c r="C417" s="4"/>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>0955313212</t>
+          <t>0921436111</t>
         </is>
       </c>
       <c r="E417" s="4"/>
@@ -12448,18 +12452,18 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>M2509290012</t>
+          <t>M2601220001</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>葉維霆</t>
+          <t>葉方奕</t>
         </is>
       </c>
       <c r="C418" s="4"/>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>0905120835</t>
+          <t>0918386488</t>
         </is>
       </c>
       <c r="E418" s="4"/>
@@ -12477,18 +12481,18 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>M2603050001</t>
+          <t>M2510260005</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>蔡仲凱</t>
+          <t>葉祈賢</t>
         </is>
       </c>
       <c r="C419" s="4"/>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>0910733748</t>
+          <t>0955313212</t>
         </is>
       </c>
       <c r="E419" s="4"/>
@@ -12506,18 +12510,18 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>M2511080009</t>
+          <t>M2509290012</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>蔡伯鼎</t>
+          <t>葉維霆</t>
         </is>
       </c>
       <c r="C420" s="4"/>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>0933842593</t>
+          <t>0905120835</t>
         </is>
       </c>
       <c r="E420" s="4"/>
@@ -12535,18 +12539,18 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>M2512100001</t>
+          <t>M2603050001</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>蔡其騰</t>
+          <t>蔡仲凱</t>
         </is>
       </c>
       <c r="C421" s="4"/>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>0988556732</t>
+          <t>0910733748</t>
         </is>
       </c>
       <c r="E421" s="4"/>
@@ -12564,22 +12568,18 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>M2603220001</t>
+          <t>M2511080009</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>蔡嘉章</t>
-        </is>
-      </c>
-      <c r="C422" s="4" t="inlineStr">
-        <is>
-          <t>樹林區太平路150巷8號娃娃機</t>
-        </is>
-      </c>
+          <t>蔡伯鼎</t>
+        </is>
+      </c>
+      <c r="C422" s="4"/>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>0973658657</t>
+          <t>0933842593</t>
         </is>
       </c>
       <c r="E422" s="4"/>
@@ -12597,18 +12597,18 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>M2509280001</t>
+          <t>M2512100001</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>蔡康志</t>
+          <t>蔡其騰</t>
         </is>
       </c>
       <c r="C423" s="4"/>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>0933942089</t>
+          <t>0988556732</t>
         </is>
       </c>
       <c r="E423" s="4"/>
@@ -12626,18 +12626,22 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>M2509260052</t>
+          <t>M2603220001</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>蔡志海</t>
-        </is>
-      </c>
-      <c r="C424" s="4"/>
+          <t>蔡嘉章</t>
+        </is>
+      </c>
+      <c r="C424" s="4" t="inlineStr">
+        <is>
+          <t>樹林區太平路150巷8號娃娃機</t>
+        </is>
+      </c>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>0926616521</t>
+          <t>0973658657</t>
         </is>
       </c>
       <c r="E424" s="4"/>
@@ -12655,18 +12659,18 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>M2602120003</t>
+          <t>M2509280001</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>蔡承勳</t>
+          <t>蔡康志</t>
         </is>
       </c>
       <c r="C425" s="4"/>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>0979975919</t>
+          <t>0933942089</t>
         </is>
       </c>
       <c r="E425" s="4"/>
@@ -12684,18 +12688,18 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>M2509290002</t>
+          <t>M2509260052</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>蔡振元</t>
+          <t>蔡志海</t>
         </is>
       </c>
       <c r="C426" s="4"/>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>0908590858</t>
+          <t>0926616521</t>
         </is>
       </c>
       <c r="E426" s="4"/>
@@ -12713,18 +12717,18 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>M2601090001</t>
+          <t>M2602120003</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>蔡昌翔</t>
+          <t>蔡承勳</t>
         </is>
       </c>
       <c r="C427" s="4"/>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>0973324888</t>
+          <t>0979975919</t>
         </is>
       </c>
       <c r="E427" s="4"/>
@@ -12742,22 +12746,18 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>M2509260011</t>
+          <t>M2509290002</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>蔡智全</t>
-        </is>
-      </c>
-      <c r="C428" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區雙園街110號1樓</t>
-        </is>
-      </c>
+          <t>蔡振元</t>
+        </is>
+      </c>
+      <c r="C428" s="4"/>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>0930167280</t>
+          <t>0908590858</t>
         </is>
       </c>
       <c r="E428" s="4"/>
@@ -12775,22 +12775,18 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>M2509260049</t>
+          <t>M2601090001</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>蔡瀚霆</t>
-        </is>
-      </c>
-      <c r="C429" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區保平路207號</t>
-        </is>
-      </c>
+          <t>蔡昌翔</t>
+        </is>
+      </c>
+      <c r="C429" s="4"/>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>0932014776</t>
+          <t>0973324888</t>
         </is>
       </c>
       <c r="E429" s="4"/>
@@ -12808,18 +12804,22 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>M2510010007</t>
+          <t>M2509260011</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>蔡秉橋</t>
-        </is>
-      </c>
-      <c r="C430" s="4"/>
+          <t>蔡智全</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="inlineStr">
+        <is>
+          <t>台北市萬華區雙園街110號1樓</t>
+        </is>
+      </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>0987000184</t>
+          <t>0930167280</t>
         </is>
       </c>
       <c r="E430" s="4"/>
@@ -12837,18 +12837,22 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>M2509270009</t>
+          <t>M2509260049</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>蔡育昇</t>
-        </is>
-      </c>
-      <c r="C431" s="4"/>
+          <t>蔡瀚霆</t>
+        </is>
+      </c>
+      <c r="C431" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區保平路207號</t>
+        </is>
+      </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>0918058903</t>
+          <t>0932014776</t>
         </is>
       </c>
       <c r="E431" s="4"/>
@@ -12866,18 +12870,18 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>M2603180001</t>
+          <t>M2510010007</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>蔡貞瑜</t>
+          <t>蔡秉橋</t>
         </is>
       </c>
       <c r="C432" s="4"/>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>0917372131</t>
+          <t>0987000184</t>
         </is>
       </c>
       <c r="E432" s="4"/>
@@ -12895,18 +12899,18 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>M2510070001</t>
+          <t>M2509270009</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>蔡辰旻</t>
+          <t>蔡育昇</t>
         </is>
       </c>
       <c r="C433" s="4"/>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>0982621245</t>
+          <t>0918058903</t>
         </is>
       </c>
       <c r="E433" s="4"/>
@@ -12924,18 +12928,18 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>M2602010003</t>
+          <t>M2603180001</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>蔡辰旻</t>
+          <t>蔡貞瑜</t>
         </is>
       </c>
       <c r="C434" s="4"/>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>0903162818</t>
+          <t>0917372131</t>
         </is>
       </c>
       <c r="E434" s="4"/>
@@ -12953,18 +12957,18 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>M2511270001</t>
+          <t>M2510070001</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>蔡進盛</t>
+          <t>蔡辰旻</t>
         </is>
       </c>
       <c r="C435" s="4"/>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>0989387966</t>
+          <t>0982621245</t>
         </is>
       </c>
       <c r="E435" s="4"/>
@@ -12982,18 +12986,18 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>M2511030001</t>
+          <t>M2602010003</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>蔡鳳來</t>
+          <t>蔡辰旻</t>
         </is>
       </c>
       <c r="C436" s="4"/>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>0963550931</t>
+          <t>0903162818</t>
         </is>
       </c>
       <c r="E436" s="4"/>
@@ -13011,18 +13015,18 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>M2509270016</t>
+          <t>M2511270001</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>蕭仲安</t>
+          <t>蔡進盛</t>
         </is>
       </c>
       <c r="C437" s="4"/>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>0930601899</t>
+          <t>0989387966</t>
         </is>
       </c>
       <c r="E437" s="4"/>
@@ -13040,18 +13044,18 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>M2509270017</t>
+          <t>M2511030001</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>蕭又瑋</t>
+          <t>蔡鳳來</t>
         </is>
       </c>
       <c r="C438" s="4"/>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>0922675798</t>
+          <t>0963550931</t>
         </is>
       </c>
       <c r="E438" s="4"/>
@@ -13069,18 +13073,18 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>M2509280009</t>
+          <t>M2509270016</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>蕭宇傑</t>
+          <t>蕭仲安</t>
         </is>
       </c>
       <c r="C439" s="4"/>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>0989977822</t>
+          <t>0930601899</t>
         </is>
       </c>
       <c r="E439" s="4"/>
@@ -13098,18 +13102,18 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>M2510190006</t>
+          <t>M2509270017</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>蕭毓</t>
+          <t>蕭又瑋</t>
         </is>
       </c>
       <c r="C440" s="4"/>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>0975199046</t>
+          <t>0922675798</t>
         </is>
       </c>
       <c r="E440" s="4"/>
@@ -13127,22 +13131,18 @@
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>M2510090006</t>
+          <t>M2509280009</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>蕭燁鴻</t>
-        </is>
-      </c>
-      <c r="C441" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區金龍路183號1樓</t>
-        </is>
-      </c>
+          <t>蕭宇傑</t>
+        </is>
+      </c>
+      <c r="C441" s="4"/>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>0917882269</t>
+          <t>0989977822</t>
         </is>
       </c>
       <c r="E441" s="4"/>
@@ -13160,18 +13160,18 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>M2510160008</t>
+          <t>M2510190006</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>蕭韻文</t>
+          <t>蕭毓</t>
         </is>
       </c>
       <c r="C442" s="4"/>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>0911297473</t>
+          <t>0975199046</t>
         </is>
       </c>
       <c r="E442" s="4"/>
@@ -13189,18 +13189,22 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>M2509300014</t>
+          <t>M2510090006</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>藍駿偉</t>
-        </is>
-      </c>
-      <c r="C443" s="4"/>
+          <t>蕭燁鴻</t>
+        </is>
+      </c>
+      <c r="C443" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區金龍路183號1樓</t>
+        </is>
+      </c>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>0936152586</t>
+          <t>0917882269</t>
         </is>
       </c>
       <c r="E443" s="4"/>
@@ -13218,18 +13222,18 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>M2511080007</t>
+          <t>M2510160008</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>蘇嘉蓉</t>
+          <t>蕭韻文</t>
         </is>
       </c>
       <c r="C444" s="4"/>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>0937074336</t>
+          <t>0911297473</t>
         </is>
       </c>
       <c r="E444" s="4"/>
@@ -13247,18 +13251,18 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>M2511060002</t>
+          <t>M2509300014</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>蘇國貿</t>
+          <t>藍駿偉</t>
         </is>
       </c>
       <c r="C445" s="4"/>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>0922250285</t>
+          <t>0936152586</t>
         </is>
       </c>
       <c r="E445" s="4"/>
@@ -13276,18 +13280,18 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>M2511280004</t>
+          <t>M2511080007</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>蘇家明</t>
+          <t>蘇嘉蓉</t>
         </is>
       </c>
       <c r="C446" s="4"/>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>0916836765</t>
+          <t>0937074336</t>
         </is>
       </c>
       <c r="E446" s="4"/>
@@ -13305,18 +13309,18 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>M2510300002</t>
+          <t>M2511060002</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>蘇小好</t>
+          <t>蘇國貿</t>
         </is>
       </c>
       <c r="C447" s="4"/>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>0981870981</t>
+          <t>0922250285</t>
         </is>
       </c>
       <c r="E447" s="4"/>
@@ -13334,18 +13338,18 @@
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>M2509260021</t>
+          <t>M2511280004</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>蘇彥彰</t>
+          <t>蘇家明</t>
         </is>
       </c>
       <c r="C448" s="4"/>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>0983060026</t>
+          <t>0916836765</t>
         </is>
       </c>
       <c r="E448" s="4"/>
@@ -13363,22 +13367,18 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>M2510240001</t>
+          <t>M2510300002</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>蘇志勇</t>
-        </is>
-      </c>
-      <c r="C449" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
-        </is>
-      </c>
+          <t>蘇小好</t>
+        </is>
+      </c>
+      <c r="C449" s="4"/>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>0910051586</t>
+          <t>0981870981</t>
         </is>
       </c>
       <c r="E449" s="4"/>
@@ -13396,18 +13396,18 @@
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>M2602150002</t>
+          <t>M2509260021</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>蘇昱銘</t>
+          <t>蘇彥彰</t>
         </is>
       </c>
       <c r="C450" s="4"/>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>0916324119</t>
+          <t>0983060026</t>
         </is>
       </c>
       <c r="E450" s="4"/>
@@ -13425,18 +13425,22 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>M2510050003</t>
+          <t>M2510240001</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>蘇睿慶</t>
-        </is>
-      </c>
-      <c r="C451" s="4"/>
+          <t>蘇志勇</t>
+        </is>
+      </c>
+      <c r="C451" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
+        </is>
+      </c>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>0937766339</t>
+          <t>0910051586</t>
         </is>
       </c>
       <c r="E451" s="4"/>
@@ -13454,18 +13458,18 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>M2601180001</t>
+          <t>M2602150002</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>蠟筆</t>
+          <t>蘇昱銘</t>
         </is>
       </c>
       <c r="C452" s="4"/>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>0976321321</t>
+          <t>0916324119</t>
         </is>
       </c>
       <c r="E452" s="4"/>
@@ -13483,18 +13487,18 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>M2512160002</t>
+          <t>M2510050003</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>褚朕誠</t>
+          <t>蘇睿慶</t>
         </is>
       </c>
       <c r="C453" s="4"/>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>0972217495</t>
+          <t>0937766339</t>
         </is>
       </c>
       <c r="E453" s="4"/>
@@ -13512,18 +13516,18 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>M2512200002</t>
+          <t>M2601180001</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>褚銘漢</t>
+          <t>蠟筆</t>
         </is>
       </c>
       <c r="C454" s="4"/>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>0925886065</t>
+          <t>0976321321</t>
         </is>
       </c>
       <c r="E454" s="4"/>
@@ -13541,18 +13545,18 @@
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>M2512170002</t>
+          <t>M2512160002</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>許俊鴻</t>
+          <t>褚朕誠</t>
         </is>
       </c>
       <c r="C455" s="4"/>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>0973630391</t>
+          <t>0972217495</t>
         </is>
       </c>
       <c r="E455" s="4"/>
@@ -13570,18 +13574,18 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>M2510050013</t>
+          <t>M2512200002</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>許凱傑</t>
+          <t>褚銘漢</t>
         </is>
       </c>
       <c r="C456" s="4"/>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>0955306971</t>
+          <t>0925886065</t>
         </is>
       </c>
       <c r="E456" s="4"/>
@@ -13599,18 +13603,18 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>M2511110001</t>
+          <t>M2512170002</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>許哲豪</t>
+          <t>許俊鴻</t>
         </is>
       </c>
       <c r="C457" s="4"/>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>0985191149</t>
+          <t>0973630391</t>
         </is>
       </c>
       <c r="E457" s="4"/>
@@ -13628,18 +13632,18 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>M2602030001</t>
+          <t>M2510050013</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>許士彥</t>
+          <t>許凱傑</t>
         </is>
       </c>
       <c r="C458" s="4"/>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>0913558692</t>
+          <t>0955306971</t>
         </is>
       </c>
       <c r="E458" s="4"/>
@@ -13657,18 +13661,18 @@
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>M2509290018</t>
+          <t>M2511110001</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>許天寶</t>
+          <t>許哲豪</t>
         </is>
       </c>
       <c r="C459" s="4"/>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>0936088850</t>
+          <t>0985191149</t>
         </is>
       </c>
       <c r="E459" s="4"/>
@@ -13686,18 +13690,18 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>M2510160005</t>
+          <t>M2602030001</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>許宥蓁</t>
+          <t>許士彥</t>
         </is>
       </c>
       <c r="C460" s="4"/>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>0938473255</t>
+          <t>0913558692</t>
         </is>
       </c>
       <c r="E460" s="4"/>
@@ -13715,18 +13719,18 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>M2512020001</t>
+          <t>M2509290018</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>許家豪</t>
+          <t>許天寶</t>
         </is>
       </c>
       <c r="C461" s="4"/>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>0983215242</t>
+          <t>0936088850</t>
         </is>
       </c>
       <c r="E461" s="4"/>
@@ -13744,18 +13748,18 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>M2510110007</t>
+          <t>M2510160005</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>許峻銓</t>
+          <t>許宥蓁</t>
         </is>
       </c>
       <c r="C462" s="4"/>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>0979770033</t>
+          <t>0938473255</t>
         </is>
       </c>
       <c r="E462" s="4"/>
@@ -13773,18 +13777,18 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>M2511260001</t>
+          <t>M2512020001</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>許志帆</t>
+          <t>許家豪</t>
         </is>
       </c>
       <c r="C463" s="4"/>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>0936639358</t>
+          <t>0983215242</t>
         </is>
       </c>
       <c r="E463" s="4"/>
@@ -13802,18 +13806,18 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>M2510310001</t>
+          <t>M2510110007</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>許志豪</t>
+          <t>許峻銓</t>
         </is>
       </c>
       <c r="C464" s="4"/>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>0971080606</t>
+          <t>0979770033</t>
         </is>
       </c>
       <c r="E464" s="4"/>
@@ -13831,18 +13835,18 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>M2601040001</t>
+          <t>M2511260001</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>許惠笙</t>
+          <t>許志帆</t>
         </is>
       </c>
       <c r="C465" s="4"/>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>0987890463</t>
+          <t>0936639358</t>
         </is>
       </c>
       <c r="E465" s="4"/>
@@ -13860,18 +13864,18 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>M2603080002</t>
+          <t>M2510310001</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>許汶瑋</t>
+          <t>許志豪</t>
         </is>
       </c>
       <c r="C466" s="4"/>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>0988166792</t>
+          <t>0971080606</t>
         </is>
       </c>
       <c r="E466" s="4"/>
@@ -13889,22 +13893,18 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>M2509140001</t>
+          <t>M2601040001</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>許煥杰</t>
-        </is>
-      </c>
-      <c r="C467" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區藝文二街88號8樓</t>
-        </is>
-      </c>
+          <t>許惠笙</t>
+        </is>
+      </c>
+      <c r="C467" s="4"/>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>0913785888</t>
+          <t>0987890463</t>
         </is>
       </c>
       <c r="E467" s="4"/>
@@ -13922,18 +13922,18 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>M2510010001</t>
+          <t>M2603080002</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>許硯棠</t>
+          <t>許汶瑋</t>
         </is>
       </c>
       <c r="C468" s="4"/>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>0983238652</t>
+          <t>0988166792</t>
         </is>
       </c>
       <c r="E468" s="4"/>
@@ -13951,18 +13951,22 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>M2509270001</t>
+          <t>M2509140001</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>許竣榤</t>
-        </is>
-      </c>
-      <c r="C469" s="4"/>
+          <t>許煥杰</t>
+        </is>
+      </c>
+      <c r="C469" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區藝文二街88號8樓</t>
+        </is>
+      </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>0955598097</t>
+          <t>0913785888</t>
         </is>
       </c>
       <c r="E469" s="4"/>
@@ -13980,18 +13984,18 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>M2510240002</t>
+          <t>M2510010001</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>許芫睿</t>
+          <t>許硯棠</t>
         </is>
       </c>
       <c r="C470" s="4"/>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>0975057699</t>
+          <t>0983238652</t>
         </is>
       </c>
       <c r="E470" s="4"/>
@@ -14009,18 +14013,18 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>M2509290013</t>
+          <t>M2509270001</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>許雅蓁</t>
+          <t>許竣榤</t>
         </is>
       </c>
       <c r="C471" s="4"/>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>0982339939</t>
+          <t>0955598097</t>
         </is>
       </c>
       <c r="E471" s="4"/>
@@ -14038,18 +14042,18 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>M2509260055</t>
+          <t>M2510240002</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>許靜蔆</t>
+          <t>許芫睿</t>
         </is>
       </c>
       <c r="C472" s="4"/>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>0928060395</t>
+          <t>0975057699</t>
         </is>
       </c>
       <c r="E472" s="4"/>
@@ -14067,18 +14071,18 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>M2509260027</t>
+          <t>M2509290013</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>詹傑克</t>
+          <t>許雅蓁</t>
         </is>
       </c>
       <c r="C473" s="4"/>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>0968688080</t>
+          <t>0982339939</t>
         </is>
       </c>
       <c r="E473" s="4"/>
@@ -14096,18 +14100,18 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>M2602010004</t>
+          <t>M2509260055</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>詹凱翔</t>
+          <t>許靜蔆</t>
         </is>
       </c>
       <c r="C474" s="4"/>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>0963496660</t>
+          <t>0928060395</t>
         </is>
       </c>
       <c r="E474" s="4"/>
@@ -14125,18 +14129,18 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>M2601270001</t>
+          <t>M2509260027</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>詹朝輝</t>
+          <t>詹傑克</t>
         </is>
       </c>
       <c r="C475" s="4"/>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>0968490321</t>
+          <t>0968688080</t>
         </is>
       </c>
       <c r="E475" s="4"/>
@@ -14154,18 +14158,18 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>M2601170004</t>
+          <t>M2602010004</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>詹煜騰</t>
+          <t>詹凱翔</t>
         </is>
       </c>
       <c r="C476" s="4"/>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>0939919344</t>
+          <t>0963496660</t>
         </is>
       </c>
       <c r="E476" s="4"/>
@@ -14183,18 +14187,18 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>M2509280003</t>
+          <t>M2601270001</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>詹皇</t>
+          <t>詹朝輝</t>
         </is>
       </c>
       <c r="C477" s="4"/>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>0916037915</t>
+          <t>0968490321</t>
         </is>
       </c>
       <c r="E477" s="4"/>
@@ -14212,18 +14216,18 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>M2510030001</t>
+          <t>M2601170004</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>詹皇宥</t>
+          <t>詹煜騰</t>
         </is>
       </c>
       <c r="C478" s="4"/>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>0919367080</t>
+          <t>0939919344</t>
         </is>
       </c>
       <c r="E478" s="4"/>
@@ -14241,22 +14245,18 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>M2509290016</t>
+          <t>M2509280003</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>詹育銘</t>
-        </is>
-      </c>
-      <c r="C479" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區撫順街25號1樓</t>
-        </is>
-      </c>
+          <t>詹皇</t>
+        </is>
+      </c>
+      <c r="C479" s="4"/>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>0926962322</t>
+          <t>0916037915</t>
         </is>
       </c>
       <c r="E479" s="4"/>
@@ -14274,22 +14274,18 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>M2510270001</t>
+          <t>M2510030001</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>謝亞倫</t>
-        </is>
-      </c>
-      <c r="C480" s="4" t="inlineStr">
-        <is>
-          <t>新北市淡水區北投里北投子49-1號</t>
-        </is>
-      </c>
+          <t>詹皇宥</t>
+        </is>
+      </c>
+      <c r="C480" s="4"/>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>0922409070</t>
+          <t>0919367080</t>
         </is>
       </c>
       <c r="E480" s="4"/>
@@ -14307,18 +14303,22 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>M2510040004</t>
+          <t>M2509290016</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>謝佳蓉</t>
-        </is>
-      </c>
-      <c r="C481" s="4"/>
+          <t>詹育銘</t>
+        </is>
+      </c>
+      <c r="C481" s="4" t="inlineStr">
+        <is>
+          <t>台北市中山區撫順街25號1樓</t>
+        </is>
+      </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>0976958679</t>
+          <t>0926962322</t>
         </is>
       </c>
       <c r="E481" s="4"/>
@@ -14336,18 +14336,22 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>M2509300019</t>
+          <t>M2510270001</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>謝光明</t>
-        </is>
-      </c>
-      <c r="C482" s="4"/>
+          <t>謝亞倫</t>
+        </is>
+      </c>
+      <c r="C482" s="4" t="inlineStr">
+        <is>
+          <t>新北市淡水區北投里北投子49-1號</t>
+        </is>
+      </c>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>0983011754</t>
+          <t>0922409070</t>
         </is>
       </c>
       <c r="E482" s="4"/>
@@ -14365,22 +14369,18 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>M2512140002</t>
+          <t>M2510040004</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>謝孟辰</t>
-        </is>
-      </c>
-      <c r="C483" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
-        </is>
-      </c>
+          <t>謝佳蓉</t>
+        </is>
+      </c>
+      <c r="C483" s="4"/>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>0953900309</t>
+          <t>0976958679</t>
         </is>
       </c>
       <c r="E483" s="4"/>
@@ -14398,18 +14398,18 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>M2509270007</t>
+          <t>M2509300019</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>謝建衫</t>
+          <t>謝光明</t>
         </is>
       </c>
       <c r="C484" s="4"/>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>0918238090</t>
+          <t>0983011754</t>
         </is>
       </c>
       <c r="E484" s="4"/>
@@ -14427,18 +14427,22 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>M2510150005</t>
+          <t>M2512140002</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>謝文懷</t>
-        </is>
-      </c>
-      <c r="C485" s="4"/>
+          <t>謝孟辰</t>
+        </is>
+      </c>
+      <c r="C485" s="4" t="inlineStr">
+        <is>
+          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
+        </is>
+      </c>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>0989813659</t>
+          <t>0953900309</t>
         </is>
       </c>
       <c r="E485" s="4"/>
@@ -14456,18 +14460,18 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>M2510130004</t>
+          <t>M2509270007</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>謝桂仁</t>
+          <t>謝建衫</t>
         </is>
       </c>
       <c r="C486" s="4"/>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>0938357603</t>
+          <t>0918238090</t>
         </is>
       </c>
       <c r="E486" s="4"/>
@@ -14485,18 +14489,18 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>M2510050002</t>
+          <t>M2510150005</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>謝舒帆</t>
+          <t>謝文懷</t>
         </is>
       </c>
       <c r="C487" s="4"/>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>0980699503</t>
+          <t>0989813659</t>
         </is>
       </c>
       <c r="E487" s="4"/>
@@ -14514,18 +14518,18 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>M2510040008</t>
+          <t>M2510130004</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>謝荌核</t>
+          <t>謝桂仁</t>
         </is>
       </c>
       <c r="C488" s="4"/>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>0988302836</t>
+          <t>0938357603</t>
         </is>
       </c>
       <c r="E488" s="4"/>
@@ -14543,18 +14547,18 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>M2511300006</t>
+          <t>M2510050002</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>謝詠全</t>
+          <t>謝舒帆</t>
         </is>
       </c>
       <c r="C489" s="4"/>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>0977077044</t>
+          <t>0980699503</t>
         </is>
       </c>
       <c r="E489" s="4"/>
@@ -14572,18 +14576,18 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>M2603200003</t>
+          <t>M2510040008</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>譚淵修</t>
+          <t>謝荌核</t>
         </is>
       </c>
       <c r="C490" s="4"/>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>0910322500</t>
+          <t>0988302836</t>
         </is>
       </c>
       <c r="E490" s="4"/>
@@ -14601,18 +14605,18 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>M2510040011</t>
+          <t>M2511300006</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>賴先生</t>
+          <t>謝詠全</t>
         </is>
       </c>
       <c r="C491" s="4"/>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>0965351801</t>
+          <t>0977077044</t>
         </is>
       </c>
       <c r="E491" s="4"/>
@@ -14630,18 +14634,18 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>M2603080001</t>
+          <t>M2603200003</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>賴品豪</t>
+          <t>譚淵修</t>
         </is>
       </c>
       <c r="C492" s="4"/>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>0981379127</t>
+          <t>0910322500</t>
         </is>
       </c>
       <c r="E492" s="4"/>
@@ -14659,18 +14663,18 @@
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>M2511010005</t>
+          <t>M2510040011</t>
         </is>
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>賴彥安</t>
+          <t>賴先生</t>
         </is>
       </c>
       <c r="C493" s="4"/>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>0913102110</t>
+          <t>0965351801</t>
         </is>
       </c>
       <c r="E493" s="4"/>
@@ -14688,22 +14692,18 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>M2603280001</t>
+          <t>M2603080001</t>
         </is>
       </c>
       <c r="B494" s="4" t="inlineStr">
         <is>
-          <t>賴柏舟</t>
-        </is>
-      </c>
-      <c r="C494" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股五福路11號</t>
-        </is>
-      </c>
+          <t>賴品豪</t>
+        </is>
+      </c>
+      <c r="C494" s="4"/>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>0979131818</t>
+          <t>0981379127</t>
         </is>
       </c>
       <c r="E494" s="4"/>
@@ -14721,18 +14721,18 @@
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2511010005</t>
         </is>
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
+          <t>賴彥安</t>
         </is>
       </c>
       <c r="C495" s="4"/>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0913102110</t>
         </is>
       </c>
       <c r="E495" s="4"/>
@@ -14750,18 +14750,22 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
-        </is>
-      </c>
-      <c r="C496" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C496" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E496" s="4"/>
@@ -14779,22 +14783,18 @@
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C497" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴珊珊</t>
+        </is>
+      </c>
+      <c r="C497" s="4"/>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E497" s="4"/>
@@ -14812,22 +14812,18 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
-        </is>
-      </c>
-      <c r="C498" s="4" t="inlineStr">
-        <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C498" s="4"/>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E498" s="4"/>
@@ -14845,22 +14841,22 @@
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C499" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E499" s="4"/>
@@ -14878,18 +14874,22 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C500" s="4"/>
+          <t>趙云璟</t>
+        </is>
+      </c>
+      <c r="C500" s="4" t="inlineStr">
+        <is>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+        </is>
+      </c>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E500" s="4"/>
@@ -14907,18 +14907,22 @@
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
-        </is>
-      </c>
-      <c r="C501" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C501" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E501" s="4"/>
@@ -14936,18 +14940,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14965,20 +14969,24 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C503" s="4"/>
-      <c r="D503" s="4"/>
+      <c r="D503" s="4" t="inlineStr">
+        <is>
+          <t>0986258793</t>
+        </is>
+      </c>
       <c r="E503" s="4"/>
       <c r="F503" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G503" s="5" t="inlineStr">
@@ -14990,18 +14998,18 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C504" s="4"/>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0981898339</t>
+          <t>0982484963</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -15019,24 +15027,20 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C505" s="4"/>
-      <c r="D505" s="4" t="inlineStr">
-        <is>
-          <t>0903921531</t>
-        </is>
-      </c>
+      <c r="D505" s="4"/>
       <c r="E505" s="4"/>
       <c r="F505" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G505" s="5" t="inlineStr">
@@ -15048,18 +15052,18 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C506" s="4"/>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15077,18 +15081,18 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C507" s="4"/>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15106,18 +15110,18 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C508" s="4"/>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E508" s="4"/>
@@ -15135,18 +15139,18 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C509" s="4"/>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E509" s="4"/>
@@ -15164,22 +15168,18 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C510" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱振為</t>
+        </is>
+      </c>
+      <c r="C510" s="4"/>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E510" s="4"/>
@@ -15197,18 +15197,18 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
+          <t>邱政傑</t>
         </is>
       </c>
       <c r="C511" s="4"/>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E511" s="4"/>
@@ -15226,18 +15226,22 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
-        </is>
-      </c>
-      <c r="C512" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C512" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E512" s="4"/>
@@ -15255,18 +15259,18 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C513" s="4"/>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E513" s="4"/>
@@ -15284,18 +15288,18 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C514" s="4"/>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E514" s="4"/>
@@ -15313,18 +15317,18 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C515" s="4"/>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E515" s="4"/>
@@ -15342,16 +15346,20 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C516" s="4"/>
-      <c r="D516" s="4"/>
+      <c r="D516" s="4" t="inlineStr">
+        <is>
+          <t>0908227630</t>
+        </is>
+      </c>
       <c r="E516" s="4"/>
       <c r="F516" s="4" t="inlineStr">
         <is>
@@ -15367,18 +15375,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0976588171</t>
+          <t>0935329653</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15396,20 +15404,16 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C518" s="4"/>
-      <c r="D518" s="4" t="inlineStr">
-        <is>
-          <t>0972128080</t>
-        </is>
-      </c>
+      <c r="D518" s="4"/>
       <c r="E518" s="4"/>
       <c r="F518" s="4" t="inlineStr">
         <is>
@@ -15425,18 +15429,18 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C519" s="4"/>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E519" s="4"/>
@@ -15454,18 +15458,18 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C520" s="4"/>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E520" s="4"/>
@@ -15483,18 +15487,18 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C521" s="4"/>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E521" s="4"/>
@@ -15512,18 +15516,18 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C522" s="4"/>
       <c r="D522" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E522" s="4"/>
@@ -15541,18 +15545,18 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C523" s="4"/>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E523" s="4"/>
@@ -15570,18 +15574,18 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C524" s="4"/>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E524" s="4"/>
@@ -15599,18 +15603,18 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C525" s="4"/>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E525" s="4"/>
@@ -15628,22 +15632,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C526" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>郭鼎昇</t>
+        </is>
+      </c>
+      <c r="C526" s="4"/>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15661,18 +15661,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
+          <t>鄒育燁</t>
         </is>
       </c>
       <c r="C527" s="4"/>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15690,18 +15690,22 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
-        </is>
-      </c>
-      <c r="C528" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C528" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15719,18 +15723,18 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C529" s="4"/>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15748,18 +15752,18 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C530" s="4"/>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15777,18 +15781,18 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C531" s="4"/>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15806,18 +15810,18 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C532" s="4"/>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15835,18 +15839,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C533" s="4"/>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15864,22 +15868,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C534" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭秉霖</t>
+        </is>
+      </c>
+      <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E534" s="4"/>
@@ -15897,22 +15897,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>鄭雁予</t>
-        </is>
-      </c>
-      <c r="C535" s="4" t="inlineStr">
-        <is>
-          <t>桃園區國聖二街145號5樓之1</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C535" s="4"/>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15930,18 +15926,22 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C536" s="4"/>
+          <t>鄭鉅耀</t>
+        </is>
+      </c>
+      <c r="C536" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股區成泰路二段208號</t>
+        </is>
+      </c>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E536" s="4"/>
@@ -15959,18 +15959,22 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
-        </is>
-      </c>
-      <c r="C537" s="4"/>
+          <t>鄭雁予</t>
+        </is>
+      </c>
+      <c r="C537" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E537" s="4"/>
@@ -15988,18 +15992,18 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C538" s="4"/>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E538" s="4"/>
@@ -16017,18 +16021,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E539" s="4"/>
@@ -16046,18 +16050,18 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C540" s="4"/>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16075,22 +16079,18 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C541" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鍾銘峰</t>
+        </is>
+      </c>
+      <c r="C541" s="4"/>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16108,24 +16108,24 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2603270001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>鐘駿霆</t>
+          <t>鐘國禎</t>
         </is>
       </c>
       <c r="C542" s="4"/>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0919331886</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E542" s="4"/>
       <c r="F542" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G542" s="5" t="inlineStr">
@@ -16137,18 +16137,22 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
-        </is>
-      </c>
-      <c r="C543" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C543" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16166,28 +16170,24 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C544" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>鐘駿霆</t>
+        </is>
+      </c>
+      <c r="C544" s="4"/>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E544" s="4"/>
       <c r="F544" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G544" s="5" t="inlineStr">
@@ -16199,18 +16199,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
+          <t>阮海德</t>
         </is>
       </c>
       <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16228,18 +16228,22 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
-        </is>
-      </c>
-      <c r="C546" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C546" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16257,22 +16261,18 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C547" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿源</t>
+        </is>
+      </c>
+      <c r="C547" s="4"/>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E547" s="4"/>
@@ -16290,18 +16290,18 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
+          <t>阿良</t>
         </is>
       </c>
       <c r="C548" s="4"/>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E548" s="4"/>
@@ -16319,22 +16319,22 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
+          <t>陳仲盟</t>
         </is>
       </c>
       <c r="C549" s="4" t="inlineStr">
         <is>
-          <t>新北市土城區日和街7號22樓</t>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
         </is>
       </c>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E549" s="4"/>
@@ -16352,22 +16352,18 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
-        </is>
-      </c>
-      <c r="C550" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路1段28巷118-1號</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C550" s="4"/>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E550" s="4"/>
@@ -16385,18 +16381,22 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C551" s="4"/>
+          <t>陳俊安</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區日和街7號22樓</t>
+        </is>
+      </c>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E551" s="4"/>
@@ -16414,18 +16414,22 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
-        </is>
-      </c>
-      <c r="C552" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16443,18 +16447,18 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C553" s="4"/>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16472,18 +16476,18 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C554" s="4"/>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16501,18 +16505,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C555" s="4"/>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16530,18 +16534,18 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C556" s="4"/>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16559,18 +16563,18 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C557" s="4"/>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16588,18 +16592,18 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C558" s="4"/>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16617,18 +16621,18 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C559" s="4"/>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16646,18 +16650,18 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C560" s="4"/>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16675,22 +16679,18 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C561" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕融</t>
+        </is>
+      </c>
+      <c r="C561" s="4"/>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16708,18 +16708,18 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2603260001</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳威宇</t>
+          <t>陳奕閔</t>
         </is>
       </c>
       <c r="C562" s="4"/>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0958186337</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16737,18 +16737,22 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
-        </is>
-      </c>
-      <c r="C563" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C563" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16766,18 +16770,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16795,18 +16799,18 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C565" s="4"/>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16824,18 +16828,18 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C566" s="4"/>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16853,18 +16857,18 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
+          <t>陳子杰</t>
         </is>
       </c>
       <c r="C567" s="4"/>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16882,22 +16886,18 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C568" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳宏文</t>
+        </is>
+      </c>
+      <c r="C568" s="4"/>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16915,18 +16915,18 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
+          <t>陳宏達</t>
         </is>
       </c>
       <c r="C569" s="4"/>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16944,18 +16944,22 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
-        </is>
-      </c>
-      <c r="C570" s="4"/>
+          <t>陳家偉</t>
+        </is>
+      </c>
+      <c r="C570" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市神農路一段72號</t>
+        </is>
+      </c>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16973,22 +16977,18 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
-        </is>
-      </c>
-      <c r="C571" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
-        </is>
-      </c>
+          <t>陳小雨</t>
+        </is>
+      </c>
+      <c r="C571" s="4"/>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -17006,22 +17006,18 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
-        </is>
-      </c>
-      <c r="C572" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁美街125號</t>
-        </is>
-      </c>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="C572" s="4"/>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -17039,18 +17035,22 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
-        </is>
-      </c>
-      <c r="C573" s="4"/>
+          <t>陳建宏(花蓮)</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉佳林31之19號</t>
+        </is>
+      </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17068,18 +17068,22 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
-        </is>
-      </c>
-      <c r="C574" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17097,18 +17101,18 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C575" s="4"/>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17126,18 +17130,18 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C576" s="4"/>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17155,18 +17159,18 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C577" s="4"/>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17184,18 +17188,18 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳怡如(彥鈞)</t>
         </is>
       </c>
       <c r="C578" s="4"/>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17213,22 +17217,18 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C579" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳慶壎</t>
+        </is>
+      </c>
+      <c r="C579" s="4"/>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17246,18 +17246,18 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
+          <t>陳敬惟</t>
         </is>
       </c>
       <c r="C580" s="4"/>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17275,22 +17275,22 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
+          <t>陳智盛</t>
         </is>
       </c>
       <c r="C581" s="4" t="inlineStr">
         <is>
-          <t>台北市內湖區星雲街30號</t>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17308,22 +17308,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
-        </is>
-      </c>
-      <c r="C582" s="4" t="inlineStr">
-        <is>
-          <t>桃園市南豐街258號</t>
-        </is>
-      </c>
+          <t>陳朋堅</t>
+        </is>
+      </c>
+      <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17341,18 +17337,22 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
-        </is>
-      </c>
-      <c r="C583" s="4"/>
+          <t>陳松廉</t>
+        </is>
+      </c>
+      <c r="C583" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區星雲街30號</t>
+        </is>
+      </c>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17370,18 +17370,22 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
-        </is>
-      </c>
-      <c r="C584" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C584" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17399,18 +17403,18 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C585" s="4"/>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17428,18 +17432,18 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C586" s="4"/>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17457,22 +17461,18 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C587" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳柏豪</t>
+        </is>
+      </c>
+      <c r="C587" s="4"/>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17490,18 +17490,18 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
+          <t>陳正傑</t>
         </is>
       </c>
       <c r="C588" s="4"/>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17519,18 +17519,22 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
-        </is>
-      </c>
-      <c r="C589" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17548,18 +17552,18 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C590" s="4"/>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17577,18 +17581,18 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳琇珊</t>
         </is>
       </c>
       <c r="C591" s="4"/>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17606,22 +17610,18 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C592" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳琬瑜</t>
+        </is>
+      </c>
+      <c r="C592" s="4"/>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17639,18 +17639,18 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
+          <t>陳璽文</t>
         </is>
       </c>
       <c r="C593" s="4"/>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17668,22 +17668,22 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
+          <t>陳益銓</t>
         </is>
       </c>
       <c r="C594" s="4" t="inlineStr">
         <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+          <t>新北市新莊區民生街15巷10號3樓</t>
         </is>
       </c>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17701,18 +17701,18 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
+          <t>陳秋蓉</t>
         </is>
       </c>
       <c r="C595" s="4"/>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17730,18 +17730,22 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
-        </is>
-      </c>
-      <c r="C596" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C596" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17759,18 +17763,18 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
+          <t>陳貴源</t>
         </is>
       </c>
       <c r="C597" s="4"/>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17788,22 +17792,18 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C598" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳達鋒</t>
+        </is>
+      </c>
+      <c r="C598" s="4"/>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17821,22 +17821,18 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
-        </is>
-      </c>
-      <c r="C599" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C599" s="4"/>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17854,22 +17850,22 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
+          <t>陳長志</t>
         </is>
       </c>
       <c r="C600" s="4" t="inlineStr">
         <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
+          <t>新北市新店區安康路</t>
         </is>
       </c>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E600" s="4"/>
@@ -17887,18 +17883,22 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C601" s="4"/>
+          <t>陳雯瑄</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+        </is>
+      </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17916,18 +17916,22 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
-        </is>
-      </c>
-      <c r="C602" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C602" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17945,18 +17949,18 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C603" s="4"/>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E603" s="4"/>
@@ -17974,18 +17978,18 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C604" s="4"/>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E604" s="4"/>
@@ -18003,18 +18007,18 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C605" s="4"/>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E605" s="4"/>
@@ -18032,18 +18036,18 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C606" s="4"/>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E606" s="4"/>
@@ -18061,18 +18065,18 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C607" s="4"/>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E607" s="4"/>
@@ -18090,18 +18094,18 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C608" s="4"/>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E608" s="4"/>
@@ -18119,18 +18123,18 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C609" s="4"/>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18148,18 +18152,18 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C610" s="4"/>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18177,18 +18181,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18206,18 +18210,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18235,22 +18239,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C613" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>顏宏坤</t>
+        </is>
+      </c>
+      <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18268,18 +18268,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
+          <t>馬迪</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18297,18 +18297,22 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
-        </is>
-      </c>
-      <c r="C615" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C615" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18326,18 +18330,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18355,18 +18359,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18384,18 +18388,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18413,18 +18417,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18442,18 +18446,18 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C620" s="4"/>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18471,22 +18475,18 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C621" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高聖景</t>
+        </is>
+      </c>
+      <c r="C621" s="4"/>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18504,18 +18504,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
+          <t>高莉婷</t>
         </is>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18533,18 +18533,22 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
-        </is>
-      </c>
-      <c r="C623" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C623" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E623" s="4"/>
@@ -18562,16 +18566,20 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C624" s="4"/>
-      <c r="D624" s="4"/>
+      <c r="D624" s="4" t="inlineStr">
+        <is>
+          <t>0937742352</t>
+        </is>
+      </c>
       <c r="E624" s="4"/>
       <c r="F624" s="4" t="inlineStr">
         <is>
@@ -18587,18 +18595,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0958180882</t>
+          <t>0989116588</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18616,24 +18624,16 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C626" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
-      <c r="D626" s="4" t="inlineStr">
-        <is>
-          <t>0903975921</t>
-        </is>
-      </c>
+          <t>鴻</t>
+        </is>
+      </c>
+      <c r="C626" s="4"/>
+      <c r="D626" s="4"/>
       <c r="E626" s="4"/>
       <c r="F626" s="4" t="inlineStr">
         <is>
@@ -18649,16 +18649,20 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
+          <t>黃俊翰</t>
         </is>
       </c>
       <c r="C627" s="4"/>
-      <c r="D627" s="4"/>
+      <c r="D627" s="4" t="inlineStr">
+        <is>
+          <t>0958180882</t>
+        </is>
+      </c>
       <c r="E627" s="4"/>
       <c r="F627" s="4" t="inlineStr">
         <is>
@@ -18674,18 +18678,22 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
-        </is>
-      </c>
-      <c r="C628" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C628" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0938722217</t>
+          <t>0903975921</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18703,20 +18711,16 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C629" s="4"/>
-      <c r="D629" s="4" t="inlineStr">
-        <is>
-          <t>0989628136</t>
-        </is>
-      </c>
+      <c r="D629" s="4"/>
       <c r="E629" s="4"/>
       <c r="F629" s="4" t="inlineStr">
         <is>
@@ -18732,18 +18736,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18761,18 +18765,18 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C631" s="4"/>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E631" s="4"/>
@@ -18790,18 +18794,18 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C632" s="4"/>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E632" s="4"/>
@@ -18819,18 +18823,18 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C633" s="4"/>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E633" s="4"/>
@@ -18848,18 +18852,18 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>M2604120001</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B634" s="4" t="inlineStr">
         <is>
-          <t>黃宥文</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C634" s="4"/>
       <c r="D634" s="4" t="inlineStr">
         <is>
-          <t>0953082147</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E634" s="4"/>
@@ -18877,18 +18881,18 @@
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C635" s="4"/>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E635" s="4"/>
@@ -18906,18 +18910,18 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2604120001</t>
         </is>
       </c>
       <c r="B636" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃宥文</t>
         </is>
       </c>
       <c r="C636" s="4"/>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0953082147</t>
         </is>
       </c>
       <c r="E636" s="4"/>
@@ -18935,22 +18939,18 @@
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C637" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃家鈺</t>
+        </is>
+      </c>
+      <c r="C637" s="4"/>
       <c r="D637" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E637" s="4"/>
@@ -18968,18 +18968,18 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B638" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
+          <t>黃庠豪</t>
         </is>
       </c>
       <c r="C638" s="4"/>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E638" s="4"/>
@@ -18997,18 +18997,22 @@
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
-        </is>
-      </c>
-      <c r="C639" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C639" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E639" s="4"/>
@@ -19026,18 +19030,18 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B640" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C640" s="4"/>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E640" s="4"/>
@@ -19055,18 +19059,18 @@
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C641" s="4"/>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E641" s="4"/>
@@ -19084,18 +19088,18 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B642" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C642" s="4"/>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E642" s="4"/>
@@ -19113,18 +19117,18 @@
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C643" s="4"/>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E643" s="4"/>
@@ -19142,18 +19146,18 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B644" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C644" s="4"/>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E644" s="4"/>
@@ -19171,18 +19175,18 @@
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C645" s="4"/>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E645" s="4"/>
@@ -19200,18 +19204,18 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B646" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C646" s="4"/>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E646" s="4"/>
@@ -19229,18 +19233,18 @@
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C647" s="4"/>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E647" s="4"/>
@@ -19258,18 +19262,18 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B648" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C648" s="4"/>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E648" s="4"/>
@@ -19287,18 +19291,18 @@
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C649" s="4"/>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E649" s="4"/>
@@ -19316,18 +19320,18 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B650" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C650" s="4"/>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E650" s="4"/>
@@ -19345,18 +19349,18 @@
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B651" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C651" s="4"/>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E651" s="4"/>
@@ -19374,18 +19378,18 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B652" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C652" s="4"/>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E652" s="4"/>
@@ -19403,18 +19407,18 @@
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B653" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C653" s="4"/>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E653" s="4"/>
@@ -19432,18 +19436,18 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B654" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C654" s="4"/>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E654" s="4"/>
@@ -19461,18 +19465,18 @@
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2510020007</t>
         </is>
       </c>
       <c r="B655" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黃鴻麒</t>
         </is>
       </c>
       <c r="C655" s="4"/>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0930571975</t>
         </is>
       </c>
       <c r="E655" s="4"/>
@@ -19488,9 +19492,67 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>2026/04/16  13:00:14</t>
+      <c r="A656" s="4" t="inlineStr">
+        <is>
+          <t>M2602270002</t>
+        </is>
+      </c>
+      <c r="B656" s="4" t="inlineStr">
+        <is>
+          <t>黎信宏</t>
+        </is>
+      </c>
+      <c r="C656" s="4"/>
+      <c r="D656" s="4" t="inlineStr">
+        <is>
+          <t>0911024337</t>
+        </is>
+      </c>
+      <c r="E656" s="4"/>
+      <c r="F656" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G656" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B657" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C657" s="4"/>
+      <c r="D657" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E657" s="4"/>
+      <c r="F657" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G657" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026/04/16  16:05:03</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -19552,7 +19552,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026/04/16  16:05:03</t>
+          <t>2026/04/17  13:00:14</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -8203,22 +8203,18 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>M2604160002</t>
+          <t>M2604190002</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>林辰奕</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市黎明路323巷31號</t>
-        </is>
-      </c>
+          <t>林裕勝</t>
+        </is>
+      </c>
+      <c r="C274" s="4"/>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>0903807636</t>
+          <t>0972220939</t>
         </is>
       </c>
       <c r="E274" s="4"/>
@@ -8236,18 +8232,22 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>M2509300005</t>
+          <t>M2604160002</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>林通海</t>
-        </is>
-      </c>
-      <c r="C275" s="4"/>
+          <t>林辰奕</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市黎明路323巷31號</t>
+        </is>
+      </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>0958589472</t>
+          <t>0903807636</t>
         </is>
       </c>
       <c r="E275" s="4"/>
@@ -8265,18 +8265,18 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>M2511220001</t>
+          <t>M2509300005</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>林鈺倫</t>
+          <t>林通海</t>
         </is>
       </c>
       <c r="C276" s="4"/>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>0988210410</t>
+          <t>0958589472</t>
         </is>
       </c>
       <c r="E276" s="4"/>
@@ -8294,18 +8294,18 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>M2510190005</t>
+          <t>M2511220001</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>林鈺瑩</t>
+          <t>林鈺倫</t>
         </is>
       </c>
       <c r="C277" s="4"/>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>0973789355</t>
+          <t>0988210410</t>
         </is>
       </c>
       <c r="E277" s="4"/>
@@ -8323,18 +8323,18 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>M2603311001</t>
+          <t>M2510190005</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>林銘宇</t>
+          <t>林鈺瑩</t>
         </is>
       </c>
       <c r="C278" s="4"/>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>0903101817</t>
+          <t>0973789355</t>
         </is>
       </c>
       <c r="E278" s="4"/>
@@ -8352,18 +8352,18 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>M2511250001</t>
+          <t>M2603311001</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>林雅琦</t>
+          <t>林銘宇</t>
         </is>
       </c>
       <c r="C279" s="4"/>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>0917361103</t>
+          <t>0903101817</t>
         </is>
       </c>
       <c r="E279" s="4"/>
@@ -8381,18 +8381,18 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>M2510100002</t>
+          <t>M2511250001</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>林鴻丞</t>
+          <t>林雅琦</t>
         </is>
       </c>
       <c r="C280" s="4"/>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>0989764757</t>
+          <t>0917361103</t>
         </is>
       </c>
       <c r="E280" s="4"/>
@@ -8410,18 +8410,18 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>M2601030004</t>
+          <t>M2510100002</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>柯偉強</t>
+          <t>林鴻丞</t>
         </is>
       </c>
       <c r="C281" s="4"/>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>0976720368</t>
+          <t>0989764757</t>
         </is>
       </c>
       <c r="E281" s="4"/>
@@ -8439,18 +8439,18 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>M2510050009</t>
+          <t>M2601030004</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>梁涵鈞</t>
+          <t>柯偉強</t>
         </is>
       </c>
       <c r="C282" s="4"/>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>0961007059</t>
+          <t>0976720368</t>
         </is>
       </c>
       <c r="E282" s="4"/>
@@ -8468,18 +8468,18 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>M2512210002</t>
+          <t>M2510050009</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>楊啓煌</t>
+          <t>梁涵鈞</t>
         </is>
       </c>
       <c r="C283" s="4"/>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>0970290888</t>
+          <t>0961007059</t>
         </is>
       </c>
       <c r="E283" s="4"/>
@@ -8497,7 +8497,7 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>M2603240002</t>
+          <t>M2512210002</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -8505,11 +8505,7 @@
           <t>楊啓煌</t>
         </is>
       </c>
-      <c r="C284" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區新生北路三段84巷33號2樓</t>
-        </is>
-      </c>
+      <c r="C284" s="4"/>
       <c r="D284" s="4" t="inlineStr">
         <is>
           <t>0970290888</t>
@@ -8530,18 +8526,22 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>M2509260042</t>
+          <t>M2603240002</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>楊士毅</t>
-        </is>
-      </c>
-      <c r="C285" s="4"/>
+          <t>楊啓煌</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>台北市中山區新生北路三段84巷33號2樓</t>
+        </is>
+      </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>0917523878</t>
+          <t>0970290888</t>
         </is>
       </c>
       <c r="E285" s="4"/>
@@ -8559,18 +8559,18 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>M2510100008</t>
+          <t>M2509260042</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>楊孝斌</t>
+          <t>楊士毅</t>
         </is>
       </c>
       <c r="C286" s="4"/>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>0916001788</t>
+          <t>0917523878</t>
         </is>
       </c>
       <c r="E286" s="4"/>
@@ -8588,22 +8588,18 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>M2509270002</t>
+          <t>M2510100008</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>楊岱惊</t>
-        </is>
-      </c>
-      <c r="C287" s="4" t="inlineStr">
-        <is>
-          <t>桃園市長安街26巷3號</t>
-        </is>
-      </c>
+          <t>楊孝斌</t>
+        </is>
+      </c>
+      <c r="C287" s="4"/>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>0989612191</t>
+          <t>0916001788</t>
         </is>
       </c>
       <c r="E287" s="4"/>
@@ -8621,22 +8617,22 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>M2509270011</t>
+          <t>M2509270002</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>楊庭瑋</t>
+          <t>楊岱惊</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>基隆市中山區復興路151號</t>
+          <t>桃園市長安街26巷3號</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>0963922276</t>
+          <t>0989612191</t>
         </is>
       </c>
       <c r="E288" s="4"/>
@@ -8654,18 +8650,22 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>M2511060001</t>
+          <t>M2509270011</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>楊明晁(四哥)</t>
-        </is>
-      </c>
-      <c r="C289" s="4"/>
+          <t>楊庭瑋</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區復興路151號</t>
+        </is>
+      </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>0968732839</t>
+          <t>0963922276</t>
         </is>
       </c>
       <c r="E289" s="4"/>
@@ -8683,18 +8683,18 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>M2601250001</t>
+          <t>M2511060001</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>楊智傑</t>
+          <t>楊明晁(四哥)</t>
         </is>
       </c>
       <c r="C290" s="4"/>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>0931131821</t>
+          <t>0968732839</t>
         </is>
       </c>
       <c r="E290" s="4"/>
@@ -8712,18 +8712,18 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>M2510030003</t>
+          <t>M2601250001</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>楊智翔</t>
+          <t>楊智傑</t>
         </is>
       </c>
       <c r="C291" s="4"/>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>0975128278</t>
+          <t>0931131821</t>
         </is>
       </c>
       <c r="E291" s="4"/>
@@ -8741,18 +8741,18 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>M2510060004</t>
+          <t>M2510030003</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>楊重九</t>
+          <t>楊智翔</t>
         </is>
       </c>
       <c r="C292" s="4"/>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>0920626999</t>
+          <t>0975128278</t>
         </is>
       </c>
       <c r="E292" s="4"/>
@@ -8770,18 +8770,18 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>M2510080001</t>
+          <t>M2510060004</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>楊錦加</t>
+          <t>楊重九</t>
         </is>
       </c>
       <c r="C293" s="4"/>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>0918872988</t>
+          <t>0920626999</t>
         </is>
       </c>
       <c r="E293" s="4"/>
@@ -8799,18 +8799,18 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>M2603280003</t>
+          <t>M2510080001</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>楊鎮良</t>
+          <t>楊錦加</t>
         </is>
       </c>
       <c r="C294" s="4"/>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>0976121606</t>
+          <t>0918872988</t>
         </is>
       </c>
       <c r="E294" s="4"/>
@@ -8828,16 +8828,20 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>V0020</t>
+          <t>M2603280003</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>榮豪</t>
+          <t>楊鎮良</t>
         </is>
       </c>
       <c r="C295" s="4"/>
-      <c r="D295" s="4"/>
+      <c r="D295" s="4" t="inlineStr">
+        <is>
+          <t>0976121606</t>
+        </is>
+      </c>
       <c r="E295" s="4"/>
       <c r="F295" s="4" t="inlineStr">
         <is>
@@ -8853,20 +8857,16 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>M2602130002</t>
+          <t>V0020</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>榮豪-許</t>
+          <t>榮豪</t>
         </is>
       </c>
       <c r="C296" s="4"/>
-      <c r="D296" s="4" t="inlineStr">
-        <is>
-          <t>0931100879</t>
-        </is>
-      </c>
+      <c r="D296" s="4"/>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="inlineStr">
         <is>
@@ -8882,18 +8882,18 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>M2602080007</t>
+          <t>M2602130002</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>樓俊瑋</t>
+          <t>榮豪-許</t>
         </is>
       </c>
       <c r="C297" s="4"/>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>0910900256</t>
+          <t>0931100879</t>
         </is>
       </c>
       <c r="E297" s="4"/>
@@ -8911,22 +8911,18 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>M2511010001</t>
+          <t>M2602080007</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>武林</t>
-        </is>
-      </c>
-      <c r="C298" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區集美街222號5樓</t>
-        </is>
-      </c>
+          <t>樓俊瑋</t>
+        </is>
+      </c>
+      <c r="C298" s="4"/>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>0913211688</t>
+          <t>0910900256</t>
         </is>
       </c>
       <c r="E298" s="4"/>
@@ -8944,18 +8940,22 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>M2511080005</t>
+          <t>M2511010001</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>毛毛</t>
-        </is>
-      </c>
-      <c r="C299" s="4"/>
+          <t>武林</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區集美街222號5樓</t>
+        </is>
+      </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>0919286386</t>
+          <t>0913211688</t>
         </is>
       </c>
       <c r="E299" s="4"/>
@@ -8973,24 +8973,24 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>Z0001</t>
+          <t>M2511080005</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>民享店</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="inlineStr">
-        <is>
-          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
-        </is>
-      </c>
-      <c r="D300" s="4"/>
+          <t>毛毛</t>
+        </is>
+      </c>
+      <c r="C300" s="4"/>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>0919286386</t>
+        </is>
+      </c>
       <c r="E300" s="4"/>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
@@ -9002,15 +9002,19 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>V0014</t>
+          <t>Z0001</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>民享房東</t>
-        </is>
-      </c>
-      <c r="C301" s="4"/>
+          <t>民享店</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
+        </is>
+      </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
       <c r="F301" s="4" t="inlineStr">
@@ -9027,12 +9031,12 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>V0019</t>
+          <t>V0014</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>永豐餘</t>
+          <t>民享房東</t>
         </is>
       </c>
       <c r="C302" s="4"/>
@@ -9040,7 +9044,7 @@
       <c r="E302" s="4"/>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G302" s="5" t="inlineStr">
@@ -9052,24 +9056,20 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>M2509260041</t>
+          <t>V0019</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>江世隆(新莊區)</t>
+          <t>永豐餘</t>
         </is>
       </c>
       <c r="C303" s="4"/>
-      <c r="D303" s="4" t="inlineStr">
-        <is>
-          <t>0981243133</t>
-        </is>
-      </c>
+      <c r="D303" s="4"/>
       <c r="E303" s="4"/>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -9081,18 +9081,18 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>M2510050010</t>
+          <t>M2509260041</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>江仁堂</t>
+          <t>江世隆(新莊區)</t>
         </is>
       </c>
       <c r="C304" s="4"/>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>0986696777</t>
+          <t>0981243133</t>
         </is>
       </c>
       <c r="E304" s="4"/>
@@ -9110,18 +9110,18 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>M2511220002</t>
+          <t>M2510050010</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>江凱逸</t>
+          <t>江仁堂</t>
         </is>
       </c>
       <c r="C305" s="4"/>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>0912312896</t>
+          <t>0986696777</t>
         </is>
       </c>
       <c r="E305" s="4"/>
@@ -9139,16 +9139,20 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>M2509120001</t>
+          <t>M2511220002</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>江哥</t>
+          <t>江凱逸</t>
         </is>
       </c>
       <c r="C306" s="4"/>
-      <c r="D306" s="4"/>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>0912312896</t>
+        </is>
+      </c>
       <c r="E306" s="4"/>
       <c r="F306" s="4" t="inlineStr">
         <is>
@@ -9164,20 +9168,16 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>M2509280006</t>
+          <t>M2509120001</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>江宏恩</t>
+          <t>江哥</t>
         </is>
       </c>
       <c r="C307" s="4"/>
-      <c r="D307" s="4" t="inlineStr">
-        <is>
-          <t>0988677410</t>
-        </is>
-      </c>
+      <c r="D307" s="4"/>
       <c r="E307" s="4"/>
       <c r="F307" s="4" t="inlineStr">
         <is>
@@ -9193,18 +9193,18 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>M2510160009</t>
+          <t>M2509280006</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>江育哲</t>
+          <t>江宏恩</t>
         </is>
       </c>
       <c r="C308" s="4"/>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>0916586618</t>
+          <t>0988677410</t>
         </is>
       </c>
       <c r="E308" s="4"/>
@@ -9222,18 +9222,18 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>M2511060005</t>
+          <t>M2510160009</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>池沛潔</t>
+          <t>江育哲</t>
         </is>
       </c>
       <c r="C309" s="4"/>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>0963900636</t>
+          <t>0916586618</t>
         </is>
       </c>
       <c r="E309" s="4"/>
@@ -9251,18 +9251,18 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>M2510240003</t>
+          <t>M2511060005</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>汪鈺修</t>
+          <t>池沛潔</t>
         </is>
       </c>
       <c r="C310" s="4"/>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>0971792952</t>
+          <t>0963900636</t>
         </is>
       </c>
       <c r="E310" s="4"/>
@@ -9280,18 +9280,18 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>M2601030003</t>
+          <t>M2510240003</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>沈大哥</t>
+          <t>汪鈺修</t>
         </is>
       </c>
       <c r="C311" s="4"/>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>0978562818</t>
+          <t>0971792952</t>
         </is>
       </c>
       <c r="E311" s="4"/>
@@ -9309,18 +9309,18 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>M2509300002</t>
+          <t>M2601030003</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>沈明鋒</t>
+          <t>沈大哥</t>
         </is>
       </c>
       <c r="C312" s="4"/>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>0908356227</t>
+          <t>0978562818</t>
         </is>
       </c>
       <c r="E312" s="4"/>
@@ -9338,20 +9338,24 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>V0005</t>
+          <t>M2509300002</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>波蜜企業</t>
+          <t>沈明鋒</t>
         </is>
       </c>
       <c r="C313" s="4"/>
-      <c r="D313" s="4"/>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>0908356227</t>
+        </is>
+      </c>
       <c r="E313" s="4"/>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -9363,24 +9367,20 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>M2512200004</t>
+          <t>V0005</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>洪丞鍇</t>
+          <t>波蜜企業</t>
         </is>
       </c>
       <c r="C314" s="4"/>
-      <c r="D314" s="4" t="inlineStr">
-        <is>
-          <t>0952119213</t>
-        </is>
-      </c>
+      <c r="D314" s="4"/>
       <c r="E314" s="4"/>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -9392,18 +9392,18 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>M2602270003</t>
+          <t>M2512200004</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>洪儒明</t>
+          <t>洪丞鍇</t>
         </is>
       </c>
       <c r="C315" s="4"/>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>0960097097</t>
+          <t>0952119213</t>
         </is>
       </c>
       <c r="E315" s="4"/>
@@ -9421,18 +9421,18 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>M2509280012</t>
+          <t>M2602270003</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>洪勝忠</t>
+          <t>洪儒明</t>
         </is>
       </c>
       <c r="C316" s="4"/>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>0917962020</t>
+          <t>0960097097</t>
         </is>
       </c>
       <c r="E316" s="4"/>
@@ -9450,18 +9450,18 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>M2510060001</t>
+          <t>M2509280012</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>洪文輝</t>
+          <t>洪勝忠</t>
         </is>
       </c>
       <c r="C317" s="4"/>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>0909183013</t>
+          <t>0917962020</t>
         </is>
       </c>
       <c r="E317" s="4"/>
@@ -9479,18 +9479,18 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>M2510300003</t>
+          <t>M2510060001</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>洪毅平</t>
+          <t>洪文輝</t>
         </is>
       </c>
       <c r="C318" s="4"/>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>0958266132</t>
+          <t>0909183013</t>
         </is>
       </c>
       <c r="E318" s="4"/>
@@ -9508,18 +9508,18 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>M2510240005</t>
+          <t>M2510300003</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>洪浩鈞</t>
+          <t>洪毅平</t>
         </is>
       </c>
       <c r="C319" s="4"/>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>0939553096</t>
+          <t>0958266132</t>
         </is>
       </c>
       <c r="E319" s="4"/>
@@ -9537,18 +9537,18 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>M2509260019</t>
+          <t>M2510240005</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>洪秋麗</t>
+          <t>洪浩鈞</t>
         </is>
       </c>
       <c r="C320" s="4"/>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>0922210223</t>
+          <t>0939553096</t>
         </is>
       </c>
       <c r="E320" s="4"/>
@@ -9566,18 +9566,18 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>M2512140001</t>
+          <t>M2509260019</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>洪翊珊</t>
+          <t>洪秋麗</t>
         </is>
       </c>
       <c r="C321" s="4"/>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>0968884119</t>
+          <t>0922210223</t>
         </is>
       </c>
       <c r="E321" s="4"/>
@@ -9595,22 +9595,18 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>M2510060006</t>
+          <t>M2512140001</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>洪金賢</t>
-        </is>
-      </c>
-      <c r="C322" s="4" t="inlineStr">
-        <is>
-          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
-        </is>
-      </c>
+          <t>洪翊珊</t>
+        </is>
+      </c>
+      <c r="C322" s="4"/>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>0933702515</t>
+          <t>0968884119</t>
         </is>
       </c>
       <c r="E322" s="4"/>
@@ -9628,22 +9624,22 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>M2602040001</t>
+          <t>M2510060006</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>涂宏忠</t>
+          <t>洪金賢</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>高雄市開發路15-3號</t>
+          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>0963222826</t>
+          <t>0933702515</t>
         </is>
       </c>
       <c r="E323" s="4"/>
@@ -9661,18 +9657,22 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>M2510090009</t>
+          <t>M2602040001</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>游仲強</t>
-        </is>
-      </c>
-      <c r="C324" s="4"/>
+          <t>涂宏忠</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>高雄市開發路15-3號</t>
+        </is>
+      </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>0910671480</t>
+          <t>0963222826</t>
         </is>
       </c>
       <c r="E324" s="4"/>
@@ -9690,18 +9690,18 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>M2602030002</t>
+          <t>M2510090009</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>游凱翔</t>
+          <t>游仲強</t>
         </is>
       </c>
       <c r="C325" s="4"/>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>0978317186</t>
+          <t>0910671480</t>
         </is>
       </c>
       <c r="E325" s="4"/>
@@ -9719,18 +9719,18 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>M2601290001</t>
+          <t>M2602030002</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>游家誠</t>
+          <t>游凱翔</t>
         </is>
       </c>
       <c r="C326" s="4"/>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>0920727320</t>
+          <t>0978317186</t>
         </is>
       </c>
       <c r="E326" s="4"/>
@@ -9748,18 +9748,18 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>M2510090002</t>
+          <t>M2601290001</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>游煥清</t>
+          <t>游家誠</t>
         </is>
       </c>
       <c r="C327" s="4"/>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>0932139705</t>
+          <t>0920727320</t>
         </is>
       </c>
       <c r="E327" s="4"/>
@@ -9777,18 +9777,18 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>M2510100004</t>
+          <t>M2510090002</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>潘文展</t>
+          <t>游煥清</t>
         </is>
       </c>
       <c r="C328" s="4"/>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>0930842995</t>
+          <t>0932139705</t>
         </is>
       </c>
       <c r="E328" s="4"/>
@@ -9806,22 +9806,18 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>M2511230004</t>
+          <t>M2510100004</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>潘正霖(瘋爪子)</t>
-        </is>
-      </c>
-      <c r="C329" s="4" t="inlineStr">
-        <is>
-          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
-        </is>
-      </c>
+          <t>潘文展</t>
+        </is>
+      </c>
+      <c r="C329" s="4"/>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>0983777818</t>
+          <t>0930842995</t>
         </is>
       </c>
       <c r="E329" s="4"/>
@@ -9839,18 +9835,22 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>M2509280010</t>
+          <t>M2511230004</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>潘秀茹</t>
-        </is>
-      </c>
-      <c r="C330" s="4"/>
+          <t>潘正霖(瘋爪子)</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
+        </is>
+      </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>0911900520</t>
+          <t>0983777818</t>
         </is>
       </c>
       <c r="E330" s="4"/>
@@ -9868,18 +9868,18 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>M2601200002</t>
+          <t>M2509280010</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>潘糖糖</t>
+          <t>潘秀茹</t>
         </is>
       </c>
       <c r="C331" s="4"/>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>0976297272</t>
+          <t>0911900520</t>
         </is>
       </c>
       <c r="E331" s="4"/>
@@ -9897,18 +9897,18 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>M2509300016</t>
+          <t>M2601200002</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>潘鳯斌</t>
+          <t>潘糖糖</t>
         </is>
       </c>
       <c r="C332" s="4"/>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>0935502290</t>
+          <t>0976297272</t>
         </is>
       </c>
       <c r="E332" s="4"/>
@@ -9926,16 +9926,20 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>M2509290010</t>
+          <t>M2509300016</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>火牛-批發</t>
+          <t>潘鳯斌</t>
         </is>
       </c>
       <c r="C333" s="4"/>
-      <c r="D333" s="4"/>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>0935502290</t>
+        </is>
+      </c>
       <c r="E333" s="4"/>
       <c r="F333" s="4" t="inlineStr">
         <is>
@@ -9951,12 +9955,12 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>M2512180002</t>
+          <t>M2509290010</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>火牛-老秦</t>
+          <t>火牛-批發</t>
         </is>
       </c>
       <c r="C334" s="4"/>
@@ -9976,12 +9980,12 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>M2512180001</t>
+          <t>M2512180002</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>火牛-阿昌</t>
+          <t>火牛-老秦</t>
         </is>
       </c>
       <c r="C335" s="4"/>
@@ -10001,20 +10005,16 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>M2602140002</t>
+          <t>M2512180001</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>灰灰</t>
+          <t>火牛-阿昌</t>
         </is>
       </c>
       <c r="C336" s="4"/>
-      <c r="D336" s="4" t="inlineStr">
-        <is>
-          <t>0987829134</t>
-        </is>
-      </c>
+      <c r="D336" s="4"/>
       <c r="E336" s="4"/>
       <c r="F336" s="4" t="inlineStr">
         <is>
@@ -10030,18 +10030,18 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>M2509300011</t>
+          <t>M2602140002</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>熊駿天(大熊)</t>
+          <t>灰灰</t>
         </is>
       </c>
       <c r="C337" s="4"/>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>0933131800</t>
+          <t>0987829134</t>
         </is>
       </c>
       <c r="E337" s="4"/>
@@ -10059,18 +10059,18 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>M2602070001</t>
+          <t>M2509300011</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>王RICK</t>
+          <t>熊駿天(大熊)</t>
         </is>
       </c>
       <c r="C338" s="4"/>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>0930106976</t>
+          <t>0933131800</t>
         </is>
       </c>
       <c r="E338" s="4"/>
@@ -10088,22 +10088,18 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>M2510240006</t>
+          <t>M2602070001</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>王中南</t>
-        </is>
-      </c>
-      <c r="C339" s="4" t="inlineStr">
-        <is>
-          <t>桃園市平鎮區快速路166號3樓</t>
-        </is>
-      </c>
+          <t>王RICK</t>
+        </is>
+      </c>
+      <c r="C339" s="4"/>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>0937124082</t>
+          <t>0930106976</t>
         </is>
       </c>
       <c r="E339" s="4"/>
@@ -10121,18 +10117,22 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>M2601020001</t>
+          <t>M2510240006</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>王仁澤</t>
-        </is>
-      </c>
-      <c r="C340" s="4"/>
+          <t>王中南</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區快速路166號3樓</t>
+        </is>
+      </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>0976503359</t>
+          <t>0937124082</t>
         </is>
       </c>
       <c r="E340" s="4"/>
@@ -10150,18 +10150,18 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>M2603010004</t>
+          <t>M2601020001</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>王又杰</t>
+          <t>王仁澤</t>
         </is>
       </c>
       <c r="C341" s="4"/>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>0909771449</t>
+          <t>0976503359</t>
         </is>
       </c>
       <c r="E341" s="4"/>
@@ -10179,18 +10179,18 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>M2601080001</t>
+          <t>M2603010004</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>王家文</t>
+          <t>王又杰</t>
         </is>
       </c>
       <c r="C342" s="4"/>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>0908176140</t>
+          <t>0909771449</t>
         </is>
       </c>
       <c r="E342" s="4"/>
@@ -10208,18 +10208,18 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>M2602080001</t>
+          <t>M2601080001</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>王巽璋</t>
+          <t>王家文</t>
         </is>
       </c>
       <c r="C343" s="4"/>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>0932943159</t>
+          <t>0908176140</t>
         </is>
       </c>
       <c r="E343" s="4"/>
@@ -10237,18 +10237,18 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>M2512230001</t>
+          <t>M2602080001</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>王志維</t>
+          <t>王巽璋</t>
         </is>
       </c>
       <c r="C344" s="4"/>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>0931262170</t>
+          <t>0932943159</t>
         </is>
       </c>
       <c r="E344" s="4"/>
@@ -10266,18 +10266,18 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>M2511180003</t>
+          <t>M2512230001</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>王明輝</t>
+          <t>王志維</t>
         </is>
       </c>
       <c r="C345" s="4"/>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>0937002585</t>
+          <t>0931262170</t>
         </is>
       </c>
       <c r="E345" s="4"/>
@@ -10295,18 +10295,18 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>M2510140007</t>
+          <t>M2511180003</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>王羿佳</t>
+          <t>王明輝</t>
         </is>
       </c>
       <c r="C346" s="4"/>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>0968831773</t>
+          <t>0937002585</t>
         </is>
       </c>
       <c r="E346" s="4"/>
@@ -10324,22 +10324,18 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>M2509260013</t>
+          <t>M2510140007</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>王舜平</t>
-        </is>
-      </c>
-      <c r="C347" s="4" t="inlineStr">
-        <is>
-          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
-        </is>
-      </c>
+          <t>王羿佳</t>
+        </is>
+      </c>
+      <c r="C347" s="4"/>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>0917215021</t>
+          <t>0968831773</t>
         </is>
       </c>
       <c r="E347" s="4"/>
@@ -10357,18 +10353,22 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>M2601170002</t>
+          <t>M2509260013</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>王閔弘</t>
-        </is>
-      </c>
-      <c r="C348" s="4"/>
+          <t>王舜平</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
+        </is>
+      </c>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>0931056292</t>
+          <t>0917215021</t>
         </is>
       </c>
       <c r="E348" s="4"/>
@@ -10386,18 +10386,18 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>M2511230003</t>
+          <t>M2601170002</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>王靜芸</t>
+          <t>王閔弘</t>
         </is>
       </c>
       <c r="C349" s="4"/>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>0970224238</t>
+          <t>0931056292</t>
         </is>
       </c>
       <c r="E349" s="4"/>
@@ -10415,18 +10415,18 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>M2510040009</t>
+          <t>M2511230003</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>王駿宏</t>
+          <t>王靜芸</t>
         </is>
       </c>
       <c r="C350" s="4"/>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>0919336854</t>
+          <t>0970224238</t>
         </is>
       </c>
       <c r="E350" s="4"/>
@@ -10444,18 +10444,18 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>M2601010001</t>
+          <t>M2510040009</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>甘玨瑋</t>
+          <t>王駿宏</t>
         </is>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>0987214102</t>
+          <t>0919336854</t>
         </is>
       </c>
       <c r="E351" s="4"/>
@@ -10473,22 +10473,18 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>M2510290002</t>
+          <t>M2601010001</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>生生</t>
-        </is>
-      </c>
-      <c r="C352" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街427號</t>
-        </is>
-      </c>
+          <t>甘玨瑋</t>
+        </is>
+      </c>
+      <c r="C352" s="4"/>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>0919001722</t>
+          <t>0987214102</t>
         </is>
       </c>
       <c r="E352" s="4"/>
@@ -10506,18 +10502,22 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>M2509260050</t>
+          <t>M2510290002</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>甩爪</t>
-        </is>
-      </c>
-      <c r="C353" s="4"/>
+          <t>生生</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街427號</t>
+        </is>
+      </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>0970754804</t>
+          <t>0919001722</t>
         </is>
       </c>
       <c r="E353" s="4"/>
@@ -10535,18 +10535,18 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>M2509270005</t>
+          <t>M2509260050</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>甯偉</t>
+          <t>甩爪</t>
         </is>
       </c>
       <c r="C354" s="4"/>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>0955617290</t>
+          <t>0970754804</t>
         </is>
       </c>
       <c r="E354" s="4"/>
@@ -10564,18 +10564,18 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>M2510240007</t>
+          <t>M2509270005</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>盧其辰</t>
+          <t>甯偉</t>
         </is>
       </c>
       <c r="C355" s="4"/>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>0982119779</t>
+          <t>0955617290</t>
         </is>
       </c>
       <c r="E355" s="4"/>
@@ -10593,18 +10593,18 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>M2604110001</t>
+          <t>M2510240007</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>盧炳宏</t>
+          <t>盧其辰</t>
         </is>
       </c>
       <c r="C356" s="4"/>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>0921062300</t>
+          <t>0982119779</t>
         </is>
       </c>
       <c r="E356" s="4"/>
@@ -10622,20 +10622,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>V0013</t>
+          <t>M2604110001</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>真大帥</t>
+          <t>盧炳宏</t>
         </is>
       </c>
       <c r="C357" s="4"/>
-      <c r="D357" s="4"/>
+      <c r="D357" s="4" t="inlineStr">
+        <is>
+          <t>0921062300</t>
+        </is>
+      </c>
       <c r="E357" s="4"/>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
@@ -10647,24 +10651,20 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>M2510310002</t>
+          <t>V0013</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>祁麟</t>
+          <t>真大帥</t>
         </is>
       </c>
       <c r="C358" s="4"/>
-      <c r="D358" s="4" t="inlineStr">
-        <is>
-          <t>0982883101</t>
-        </is>
-      </c>
+      <c r="D358" s="4"/>
       <c r="E358" s="4"/>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">
@@ -10676,18 +10676,18 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>M2602130001</t>
+          <t>M2510310002</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>祐</t>
+          <t>祁麟</t>
         </is>
       </c>
       <c r="C359" s="4"/>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>0983407890</t>
+          <t>0982883101</t>
         </is>
       </c>
       <c r="E359" s="4"/>
@@ -10705,18 +10705,18 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>M2510050001</t>
+          <t>M2602130001</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>程sir/Ashbur</t>
+          <t>祐</t>
         </is>
       </c>
       <c r="C360" s="4"/>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>0963612395</t>
+          <t>0983407890</t>
         </is>
       </c>
       <c r="E360" s="4"/>
@@ -10734,18 +10734,18 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>M2510300001</t>
+          <t>M2510050001</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>程品勝</t>
+          <t>程sir/Ashbur</t>
         </is>
       </c>
       <c r="C361" s="4"/>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>0913780727</t>
+          <t>0963612395</t>
         </is>
       </c>
       <c r="E361" s="4"/>
@@ -10763,18 +10763,18 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>M2601270002</t>
+          <t>M2510300001</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>程建智</t>
+          <t>程品勝</t>
         </is>
       </c>
       <c r="C362" s="4"/>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>0988919027</t>
+          <t>0913780727</t>
         </is>
       </c>
       <c r="E362" s="4"/>
@@ -10792,18 +10792,18 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>M2603120004</t>
+          <t>M2601270002</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>程郁勛</t>
+          <t>程建智</t>
         </is>
       </c>
       <c r="C363" s="4"/>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>0955671407</t>
+          <t>0988919027</t>
         </is>
       </c>
       <c r="E363" s="4"/>
@@ -10821,22 +10821,18 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>M2509160001</t>
+          <t>M2603120004</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>穆莉茹</t>
-        </is>
-      </c>
-      <c r="C364" s="4" t="inlineStr">
-        <is>
-          <t>桃園平鎮區上海路169號</t>
-        </is>
-      </c>
+          <t>程郁勛</t>
+        </is>
+      </c>
+      <c r="C364" s="4"/>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>0955777312</t>
+          <t>0955671407</t>
         </is>
       </c>
       <c r="E364" s="4"/>
@@ -10854,18 +10850,22 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>M2511160003</t>
+          <t>M2509160001</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>簡士傑</t>
-        </is>
-      </c>
-      <c r="C365" s="4"/>
+          <t>穆莉茹</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>桃園平鎮區上海路169號</t>
+        </is>
+      </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>0963817398</t>
+          <t>0955777312</t>
         </is>
       </c>
       <c r="E365" s="4"/>
@@ -10883,18 +10883,18 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>M2509300013</t>
+          <t>M2511160003</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>簡子偉</t>
+          <t>簡士傑</t>
         </is>
       </c>
       <c r="C366" s="4"/>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>0955462926</t>
+          <t>0963817398</t>
         </is>
       </c>
       <c r="E366" s="4"/>
@@ -10912,18 +10912,18 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>M2602280002</t>
+          <t>M2509300013</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>簡子洋</t>
+          <t>簡子偉</t>
         </is>
       </c>
       <c r="C367" s="4"/>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>0933921933</t>
+          <t>0955462926</t>
         </is>
       </c>
       <c r="E367" s="4"/>
@@ -10941,18 +10941,18 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>M2510040003</t>
+          <t>M2602280002</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>簡小琪</t>
+          <t>簡子洋</t>
         </is>
       </c>
       <c r="C368" s="4"/>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>0930033829</t>
+          <t>0933921933</t>
         </is>
       </c>
       <c r="E368" s="4"/>
@@ -10970,18 +10970,18 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>M2510260002</t>
+          <t>M2510040003</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>簡揚城</t>
+          <t>簡小琪</t>
         </is>
       </c>
       <c r="C369" s="4"/>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>0913153353</t>
+          <t>0930033829</t>
         </is>
       </c>
       <c r="E369" s="4"/>
@@ -10999,18 +10999,18 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>M2509300001</t>
+          <t>M2510260002</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>簡瑋成</t>
+          <t>簡揚城</t>
         </is>
       </c>
       <c r="C370" s="4"/>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>0936389969</t>
+          <t>0913153353</t>
         </is>
       </c>
       <c r="E370" s="4"/>
@@ -11028,18 +11028,18 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>M2509290020</t>
+          <t>M2509300001</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>簡茂州</t>
+          <t>簡瑋成</t>
         </is>
       </c>
       <c r="C371" s="4"/>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>0985217379</t>
+          <t>0936389969</t>
         </is>
       </c>
       <c r="E371" s="4"/>
@@ -11057,18 +11057,18 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>M2512130001</t>
+          <t>M2509290020</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>紀彥銘</t>
+          <t>簡茂州</t>
         </is>
       </c>
       <c r="C372" s="4"/>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>0988752337</t>
+          <t>0985217379</t>
         </is>
       </c>
       <c r="E372" s="4"/>
@@ -11086,20 +11086,24 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>V0001</t>
+          <t>M2512130001</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>統有企業</t>
+          <t>紀彥銘</t>
         </is>
       </c>
       <c r="C373" s="4"/>
-      <c r="D373" s="4"/>
+      <c r="D373" s="4" t="inlineStr">
+        <is>
+          <t>0988752337</t>
+        </is>
+      </c>
       <c r="E373" s="4"/>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G373" s="5" t="inlineStr">
@@ -11111,24 +11115,20 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>M2509280008</t>
+          <t>V0001</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>維克斯</t>
+          <t>統有企業</t>
         </is>
       </c>
       <c r="C374" s="4"/>
-      <c r="D374" s="4" t="inlineStr">
-        <is>
-          <t>0917771787</t>
-        </is>
-      </c>
+      <c r="D374" s="4"/>
       <c r="E374" s="4"/>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G374" s="5" t="inlineStr">
@@ -11140,18 +11140,18 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>M2510170002</t>
+          <t>M2509280008</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>練鎮宇</t>
+          <t>維克斯</t>
         </is>
       </c>
       <c r="C375" s="4"/>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>0952288706</t>
+          <t>0917771787</t>
         </is>
       </c>
       <c r="E375" s="4"/>
@@ -11169,22 +11169,18 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>M2602220003</t>
+          <t>M2510170002</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>羅丁一夫</t>
-        </is>
-      </c>
-      <c r="C376" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
-        </is>
-      </c>
+          <t>練鎮宇</t>
+        </is>
+      </c>
+      <c r="C376" s="4"/>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>0919339614</t>
+          <t>0952288706</t>
         </is>
       </c>
       <c r="E376" s="4"/>
@@ -11202,18 +11198,22 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>M2510180002</t>
+          <t>M2602220003</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>羅元隆</t>
-        </is>
-      </c>
-      <c r="C377" s="4"/>
+          <t>羅丁一夫</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
+        </is>
+      </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>0975866635</t>
+          <t>0919339614</t>
         </is>
       </c>
       <c r="E377" s="4"/>
@@ -11231,25 +11231,21 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>M2510090003</t>
+          <t>M2510180002</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>羅嘉銘</t>
+          <t>羅元隆</t>
         </is>
       </c>
       <c r="C378" s="4"/>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>0928093385</t>
-        </is>
-      </c>
-      <c r="E378" s="4" t="inlineStr">
-        <is>
-          <t>0985866052</t>
-        </is>
-      </c>
+          <t>0975866635</t>
+        </is>
+      </c>
+      <c r="E378" s="4"/>
       <c r="F378" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11264,21 +11260,25 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>M2602240001</t>
+          <t>M2510090003</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>羅浩中</t>
+          <t>羅嘉銘</t>
         </is>
       </c>
       <c r="C379" s="4"/>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>0970905092</t>
-        </is>
-      </c>
-      <c r="E379" s="4"/>
+          <t>0928093385</t>
+        </is>
+      </c>
+      <c r="E379" s="4" t="inlineStr">
+        <is>
+          <t>0985866052</t>
+        </is>
+      </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11293,18 +11293,18 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>M2511060003</t>
+          <t>M2602240001</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>翁名勳</t>
+          <t>羅浩中</t>
         </is>
       </c>
       <c r="C380" s="4"/>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>0955083317</t>
+          <t>0970905092</t>
         </is>
       </c>
       <c r="E380" s="4"/>
@@ -11322,18 +11322,18 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>M2509260057</t>
+          <t>M2511060003</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>翁國昌</t>
+          <t>翁名勳</t>
         </is>
       </c>
       <c r="C381" s="4"/>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>0918718772</t>
+          <t>0955083317</t>
         </is>
       </c>
       <c r="E381" s="4"/>
@@ -11351,22 +11351,18 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>M2511290001</t>
+          <t>M2509260057</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>翁國祥</t>
-        </is>
-      </c>
-      <c r="C382" s="4" t="inlineStr">
-        <is>
-          <t>新北新莊中信街65號1樓賣菜攤</t>
-        </is>
-      </c>
+          <t>翁國昌</t>
+        </is>
+      </c>
+      <c r="C382" s="4"/>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>0983900052</t>
+          <t>0918718772</t>
         </is>
       </c>
       <c r="E382" s="4"/>
@@ -11384,22 +11380,22 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>M2510010009</t>
+          <t>M2511290001</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩</t>
+          <t>翁國祥</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>未決定</t>
+          <t>新北新莊中信街65號1樓賣菜攤</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>0972757015</t>
+          <t>0983900052</t>
         </is>
       </c>
       <c r="E383" s="4"/>
@@ -11417,53 +11413,53 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
+          <t>M2510010009</t>
+        </is>
+      </c>
+      <c r="B384" s="4" t="inlineStr">
+        <is>
+          <t>翁敬恩</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr">
+        <is>
+          <t>未決定</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>0972757015</t>
+        </is>
+      </c>
+      <c r="E384" s="4"/>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G384" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="4" t="inlineStr">
+        <is>
           <t>M2510010009-4</t>
         </is>
       </c>
-      <c r="B384" s="4" t="inlineStr">
+      <c r="B385" s="4" t="inlineStr">
         <is>
           <t>翁敬恩-文山</t>
         </is>
       </c>
-      <c r="C384" s="6" t="inlineStr">
+      <c r="C385" s="6" t="inlineStr">
         <is>
           <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
 收件聯絡電話:0937462412</t>
         </is>
       </c>
-      <c r="D384" s="4" t="inlineStr">
-        <is>
-          <t>0972757015</t>
-        </is>
-      </c>
-      <c r="E384" s="4"/>
-      <c r="F384" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
-      <c r="G384" s="5" t="inlineStr">
-        <is>
-          <t>附件管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="4" t="inlineStr">
-        <is>
-          <t>M2510010009-2</t>
-        </is>
-      </c>
-      <c r="B385" s="4" t="inlineStr">
-        <is>
-          <t>翁敬恩-樂華</t>
-        </is>
-      </c>
-      <c r="C385" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
-        </is>
-      </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
           <t>0972757015</t>
@@ -11484,17 +11480,17 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-3</t>
+          <t>M2510010009-2</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-永和</t>
+          <t>翁敬恩-樂華</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
+          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -11517,22 +11513,22 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-1</t>
+          <t>M2510010009-3</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-饒河</t>
+          <t>翁敬恩-永和</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>0975953978</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E387" s="4"/>
@@ -11550,18 +11546,22 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>M2510140004</t>
+          <t>M2510010009-1</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>翁漢忠</t>
-        </is>
-      </c>
-      <c r="C388" s="4"/>
+          <t>翁敬恩-饒河</t>
+        </is>
+      </c>
+      <c r="C388" s="4" t="inlineStr">
+        <is>
+          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+        </is>
+      </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>0916150750</t>
+          <t>0975953978</t>
         </is>
       </c>
       <c r="E388" s="4"/>
@@ -11579,18 +11579,18 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>M2509260037</t>
+          <t>M2510140004</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>翁翌禎</t>
+          <t>翁漢忠</t>
         </is>
       </c>
       <c r="C389" s="4"/>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>0902308293</t>
+          <t>0916150750</t>
         </is>
       </c>
       <c r="E389" s="4"/>
@@ -11608,18 +11608,18 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>M2509280002</t>
+          <t>M2509260037</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>聶大中</t>
+          <t>翁翌禎</t>
         </is>
       </c>
       <c r="C390" s="4"/>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>0955059148</t>
+          <t>0902308293</t>
         </is>
       </c>
       <c r="E390" s="4"/>
@@ -11637,18 +11637,18 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>M2510220001</t>
+          <t>M2509280002</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>胡HU</t>
+          <t>聶大中</t>
         </is>
       </c>
       <c r="C391" s="4"/>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>0988603554</t>
+          <t>0955059148</t>
         </is>
       </c>
       <c r="E391" s="4"/>
@@ -11666,18 +11666,18 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2510100011</t>
+          <t>M2510220001</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>胡凱傑</t>
+          <t>胡HU</t>
         </is>
       </c>
       <c r="C392" s="4"/>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>0955888840</t>
+          <t>0988603554</t>
         </is>
       </c>
       <c r="E392" s="4"/>
@@ -11695,18 +11695,18 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>M2510090005</t>
+          <t>M2510100011</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>胡家榮</t>
+          <t>胡凱傑</t>
         </is>
       </c>
       <c r="C393" s="4"/>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>0933059025</t>
+          <t>0955888840</t>
         </is>
       </c>
       <c r="E393" s="4"/>
@@ -11724,18 +11724,18 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>M2511150001</t>
+          <t>M2510090005</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>胡家銘</t>
+          <t>胡家榮</t>
         </is>
       </c>
       <c r="C394" s="4"/>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>0986362263</t>
+          <t>0933059025</t>
         </is>
       </c>
       <c r="E394" s="4"/>
@@ -11753,18 +11753,18 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>M2511290003</t>
+          <t>M2511150001</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>胡峻強</t>
+          <t>胡家銘</t>
         </is>
       </c>
       <c r="C395" s="4"/>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>0953088041</t>
+          <t>0986362263</t>
         </is>
       </c>
       <c r="E395" s="4"/>
@@ -11782,18 +11782,18 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>M2603010001</t>
+          <t>M2511290003</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>胡辰煜</t>
+          <t>胡峻強</t>
         </is>
       </c>
       <c r="C396" s="4"/>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>0963903685</t>
+          <t>0953088041</t>
         </is>
       </c>
       <c r="E396" s="4"/>
@@ -11811,18 +11811,18 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>M2510040002</t>
+          <t>M2603010001</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>胡辰軒</t>
+          <t>胡辰煜</t>
         </is>
       </c>
       <c r="C397" s="4"/>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>0972094622</t>
+          <t>0963903685</t>
         </is>
       </c>
       <c r="E397" s="4"/>
@@ -11840,18 +11840,18 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>M2602280001</t>
+          <t>M2510040002</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>胡閎翔</t>
+          <t>胡辰軒</t>
         </is>
       </c>
       <c r="C398" s="4"/>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>0970556309</t>
+          <t>0972094622</t>
         </is>
       </c>
       <c r="E398" s="4"/>
@@ -11869,18 +11869,18 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>M2511290002</t>
+          <t>M2602280001</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>舒老闆</t>
+          <t>胡閎翔</t>
         </is>
       </c>
       <c r="C399" s="4"/>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>0979788818</t>
+          <t>0970556309</t>
         </is>
       </c>
       <c r="E399" s="4"/>
@@ -11898,19 +11898,15 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-6</t>
+          <t>M2511290002</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-冬冬/虎林</t>
-        </is>
-      </c>
-      <c r="C400" s="4" t="inlineStr">
-        <is>
-          <t>台北市信義區虎林街164巷60弄19號</t>
-        </is>
-      </c>
+          <t>舒老闆</t>
+        </is>
+      </c>
+      <c r="C400" s="4"/>
       <c r="D400" s="4" t="inlineStr">
         <is>
           <t>0979788818</t>
@@ -11931,17 +11927,17 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-8</t>
+          <t>M2511290002-6</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德17號</t>
+          <t>舒老闆-冬冬/虎林</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區八德路三段155巷17號</t>
+          <t>台北市信義區虎林街164巷60弄19號</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -11964,17 +11960,17 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-2</t>
+          <t>M2511290002-8</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德46號</t>
+          <t>舒老闆-夾鬥陣/八德17號</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區八德路三段12巷51弄46號</t>
+          <t>台北市松山區八德路三段155巷17號</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
@@ -11997,17 +11993,17 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-7</t>
+          <t>M2511290002-2</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/臥龍</t>
+          <t>舒老闆-夾鬥陣/八德46號</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>台北市大安區臥龍街254號</t>
+          <t>台北市松山區八德路三段12巷51弄46號</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -12030,17 +12026,17 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-4</t>
+          <t>M2511290002-7</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/中正</t>
+          <t>舒老闆-夾鬥陣/臥龍</t>
         </is>
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路14號</t>
+          <t>台北市大安區臥龍街254號</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
@@ -12063,17 +12059,17 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-5</t>
+          <t>M2511290002-4</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/吳興</t>
+          <t>舒老闆-寧寧/中正</t>
         </is>
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>台北市信義區吳興街342號</t>
+          <t>新北市永和區中正路14號</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -12096,17 +12092,17 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-3</t>
+          <t>M2511290002-5</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/智光</t>
+          <t>舒老闆-寧寧/吳興</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區智光街98號</t>
+          <t>台北市信義區吳興街342號</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
@@ -12129,17 +12125,17 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-1</t>
+          <t>M2511290002-3</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/秀山</t>
+          <t>舒老闆-寧寧/智光</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+          <t>新北市永和區智光街98號</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
@@ -12162,18 +12158,22 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>M2510140002</t>
+          <t>M2511290002-1</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>范姜敏中</t>
-        </is>
-      </c>
-      <c r="C408" s="4"/>
+          <t>舒老闆-寧寧/秀山</t>
+        </is>
+      </c>
+      <c r="C408" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+        </is>
+      </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>0937464692</t>
+          <t>0979788818</t>
         </is>
       </c>
       <c r="E408" s="4"/>
@@ -12191,18 +12191,18 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>M2510140003</t>
+          <t>M2510140002</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>范姜群成</t>
+          <t>范姜敏中</t>
         </is>
       </c>
       <c r="C409" s="4"/>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>0920565234</t>
+          <t>0937464692</t>
         </is>
       </c>
       <c r="E409" s="4"/>
@@ -12220,22 +12220,18 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>M2511300003</t>
+          <t>M2510140003</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>莊正當</t>
-        </is>
-      </c>
-      <c r="C410" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區建安街27號3樓</t>
-        </is>
-      </c>
+          <t>范姜群成</t>
+        </is>
+      </c>
+      <c r="C410" s="4"/>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>0983337218</t>
+          <t>0920565234</t>
         </is>
       </c>
       <c r="E410" s="4"/>
@@ -12253,22 +12249,22 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>M2510270004</t>
+          <t>M2511300003</t>
         </is>
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>莊淑玲</t>
+          <t>莊正當</t>
         </is>
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>新北市新莊區五工三路78巷36號</t>
+          <t>新北市新莊區建安街27號3樓</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>0922277383</t>
+          <t>0983337218</t>
         </is>
       </c>
       <c r="E411" s="4"/>
@@ -12286,18 +12282,22 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>M2510190002</t>
+          <t>M2510270004</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>莊耿華</t>
-        </is>
-      </c>
-      <c r="C412" s="4"/>
+          <t>莊淑玲</t>
+        </is>
+      </c>
+      <c r="C412" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工三路78巷36號</t>
+        </is>
+      </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>0938600334</t>
+          <t>0922277383</t>
         </is>
       </c>
       <c r="E412" s="4"/>
@@ -12315,18 +12315,18 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>M2509260005</t>
+          <t>M2510190002</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>莊莊</t>
+          <t>莊耿華</t>
         </is>
       </c>
       <c r="C413" s="4"/>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>0955985557</t>
+          <t>0938600334</t>
         </is>
       </c>
       <c r="E413" s="4"/>
@@ -12344,18 +12344,18 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>M2510100007</t>
+          <t>M2509260005</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>莊閔丞</t>
+          <t>莊莊</t>
         </is>
       </c>
       <c r="C414" s="4"/>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>0963320370</t>
+          <t>0955985557</t>
         </is>
       </c>
       <c r="E414" s="4"/>
@@ -12373,18 +12373,18 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>M2602240002</t>
+          <t>M2510100007</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>萬宗霖</t>
+          <t>莊閔丞</t>
         </is>
       </c>
       <c r="C415" s="4"/>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>0977082365</t>
+          <t>0963320370</t>
         </is>
       </c>
       <c r="E415" s="4"/>
@@ -12402,18 +12402,18 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>M2510160001</t>
+          <t>M2602240002</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>葉力瑋</t>
+          <t>萬宗霖</t>
         </is>
       </c>
       <c r="C416" s="4"/>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>0979611911</t>
+          <t>0977082365</t>
         </is>
       </c>
       <c r="E416" s="4"/>
@@ -12431,18 +12431,18 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>M2510030002</t>
+          <t>M2510160001</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>葉家睿</t>
+          <t>葉力瑋</t>
         </is>
       </c>
       <c r="C417" s="4"/>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>0928112227</t>
+          <t>0979611911</t>
         </is>
       </c>
       <c r="E417" s="4"/>
@@ -12460,18 +12460,18 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>M2511050003</t>
+          <t>M2510030002</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>葉庭綸</t>
+          <t>葉家睿</t>
         </is>
       </c>
       <c r="C418" s="4"/>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>0966638685</t>
+          <t>0928112227</t>
         </is>
       </c>
       <c r="E418" s="4"/>
@@ -12489,18 +12489,18 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>M2510180001</t>
+          <t>M2511050003</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>葉建財</t>
+          <t>葉庭綸</t>
         </is>
       </c>
       <c r="C419" s="4"/>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>0989713349</t>
+          <t>0966638685</t>
         </is>
       </c>
       <c r="E419" s="4"/>
@@ -12518,18 +12518,18 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>M2510150001</t>
+          <t>M2510180001</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>葉彥均</t>
+          <t>葉建財</t>
         </is>
       </c>
       <c r="C420" s="4"/>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>0921436111</t>
+          <t>0989713349</t>
         </is>
       </c>
       <c r="E420" s="4"/>
@@ -12547,18 +12547,18 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>M2601220001</t>
+          <t>M2510150001</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>葉方奕</t>
+          <t>葉彥均</t>
         </is>
       </c>
       <c r="C421" s="4"/>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>0918386488</t>
+          <t>0921436111</t>
         </is>
       </c>
       <c r="E421" s="4"/>
@@ -12576,18 +12576,18 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>M2510260005</t>
+          <t>M2601220001</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>葉祈賢</t>
+          <t>葉方奕</t>
         </is>
       </c>
       <c r="C422" s="4"/>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>0955313212</t>
+          <t>0918386488</t>
         </is>
       </c>
       <c r="E422" s="4"/>
@@ -12605,18 +12605,18 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>M2509290012</t>
+          <t>M2510260005</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>葉維霆</t>
+          <t>葉祈賢</t>
         </is>
       </c>
       <c r="C423" s="4"/>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>0905120835</t>
+          <t>0955313212</t>
         </is>
       </c>
       <c r="E423" s="4"/>
@@ -12634,18 +12634,18 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>M2603050001</t>
+          <t>M2509290012</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>蔡仲凱</t>
+          <t>葉維霆</t>
         </is>
       </c>
       <c r="C424" s="4"/>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>0910733748</t>
+          <t>0905120835</t>
         </is>
       </c>
       <c r="E424" s="4"/>
@@ -12663,18 +12663,18 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>M2511080009</t>
+          <t>M2603050001</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>蔡伯鼎</t>
+          <t>蔡仲凱</t>
         </is>
       </c>
       <c r="C425" s="4"/>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>0933842593</t>
+          <t>0910733748</t>
         </is>
       </c>
       <c r="E425" s="4"/>
@@ -12692,18 +12692,18 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>M2512100001</t>
+          <t>M2511080009</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>蔡其騰</t>
+          <t>蔡伯鼎</t>
         </is>
       </c>
       <c r="C426" s="4"/>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>0988556732</t>
+          <t>0933842593</t>
         </is>
       </c>
       <c r="E426" s="4"/>
@@ -12721,22 +12721,18 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>M2603220001</t>
+          <t>M2512100001</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>蔡嘉章</t>
-        </is>
-      </c>
-      <c r="C427" s="4" t="inlineStr">
-        <is>
-          <t>樹林區太平路150巷8號娃娃機</t>
-        </is>
-      </c>
+          <t>蔡其騰</t>
+        </is>
+      </c>
+      <c r="C427" s="4"/>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>0973658657</t>
+          <t>0988556732</t>
         </is>
       </c>
       <c r="E427" s="4"/>
@@ -12754,18 +12750,22 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>M2509280001</t>
+          <t>M2603220001</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>蔡康志</t>
-        </is>
-      </c>
-      <c r="C428" s="4"/>
+          <t>蔡嘉章</t>
+        </is>
+      </c>
+      <c r="C428" s="4" t="inlineStr">
+        <is>
+          <t>樹林區太平路150巷8號娃娃機</t>
+        </is>
+      </c>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>0933942089</t>
+          <t>0973658657</t>
         </is>
       </c>
       <c r="E428" s="4"/>
@@ -12783,18 +12783,18 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>M2509260052</t>
+          <t>M2509280001</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>蔡志海</t>
+          <t>蔡康志</t>
         </is>
       </c>
       <c r="C429" s="4"/>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>0926616521</t>
+          <t>0933942089</t>
         </is>
       </c>
       <c r="E429" s="4"/>
@@ -12812,18 +12812,18 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>M2602120003</t>
+          <t>M2509260052</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>蔡承勳</t>
+          <t>蔡志海</t>
         </is>
       </c>
       <c r="C430" s="4"/>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>0979975919</t>
+          <t>0926616521</t>
         </is>
       </c>
       <c r="E430" s="4"/>
@@ -12841,18 +12841,18 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>M2509290002</t>
+          <t>M2602120003</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>蔡振元</t>
+          <t>蔡承勳</t>
         </is>
       </c>
       <c r="C431" s="4"/>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>0908590858</t>
+          <t>0979975919</t>
         </is>
       </c>
       <c r="E431" s="4"/>
@@ -12870,18 +12870,18 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>M2601090001</t>
+          <t>M2509290002</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>蔡昌翔</t>
+          <t>蔡振元</t>
         </is>
       </c>
       <c r="C432" s="4"/>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>0973324888</t>
+          <t>0908590858</t>
         </is>
       </c>
       <c r="E432" s="4"/>
@@ -12899,22 +12899,18 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>M2509260011</t>
+          <t>M2601090001</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>蔡智全</t>
-        </is>
-      </c>
-      <c r="C433" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區雙園街110號1樓</t>
-        </is>
-      </c>
+          <t>蔡昌翔</t>
+        </is>
+      </c>
+      <c r="C433" s="4"/>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>0930167280</t>
+          <t>0973324888</t>
         </is>
       </c>
       <c r="E433" s="4"/>
@@ -12932,22 +12928,22 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>M2509260049</t>
+          <t>M2509260011</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>蔡瀚霆</t>
+          <t>蔡智全</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區保平路207號</t>
+          <t>台北市萬華區雙園街110號1樓</t>
         </is>
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>0932014776</t>
+          <t>0930167280</t>
         </is>
       </c>
       <c r="E434" s="4"/>
@@ -12965,18 +12961,22 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>M2510010007</t>
+          <t>M2509260049</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>蔡秉橋</t>
-        </is>
-      </c>
-      <c r="C435" s="4"/>
+          <t>蔡瀚霆</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區保平路207號</t>
+        </is>
+      </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>0987000184</t>
+          <t>0932014776</t>
         </is>
       </c>
       <c r="E435" s="4"/>
@@ -12994,18 +12994,18 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>M2509270009</t>
+          <t>M2510010007</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>蔡育昇</t>
+          <t>蔡秉橋</t>
         </is>
       </c>
       <c r="C436" s="4"/>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>0918058903</t>
+          <t>0987000184</t>
         </is>
       </c>
       <c r="E436" s="4"/>
@@ -13023,18 +13023,18 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>M2603180001</t>
+          <t>M2509270009</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>蔡貞瑜</t>
+          <t>蔡育昇</t>
         </is>
       </c>
       <c r="C437" s="4"/>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>0917372131</t>
+          <t>0918058903</t>
         </is>
       </c>
       <c r="E437" s="4"/>
@@ -13052,18 +13052,18 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>M2510070001</t>
+          <t>M2603180001</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>蔡辰旻</t>
+          <t>蔡貞瑜</t>
         </is>
       </c>
       <c r="C438" s="4"/>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>0982621245</t>
+          <t>0917372131</t>
         </is>
       </c>
       <c r="E438" s="4"/>
@@ -13081,7 +13081,7 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>M2602010003</t>
+          <t>M2510070001</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
@@ -13092,7 +13092,7 @@
       <c r="C439" s="4"/>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>0903162818</t>
+          <t>0982621245</t>
         </is>
       </c>
       <c r="E439" s="4"/>
@@ -13110,18 +13110,18 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>M2511270001</t>
+          <t>M2602010003</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>蔡進盛</t>
+          <t>蔡辰旻</t>
         </is>
       </c>
       <c r="C440" s="4"/>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>0989387966</t>
+          <t>0903162818</t>
         </is>
       </c>
       <c r="E440" s="4"/>
@@ -13139,18 +13139,18 @@
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>M2511030001</t>
+          <t>M2511270001</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>蔡鳳來</t>
+          <t>蔡進盛</t>
         </is>
       </c>
       <c r="C441" s="4"/>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>0963550931</t>
+          <t>0989387966</t>
         </is>
       </c>
       <c r="E441" s="4"/>
@@ -13168,18 +13168,18 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>M2509270016</t>
+          <t>M2511030001</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>蕭仲安</t>
+          <t>蔡鳳來</t>
         </is>
       </c>
       <c r="C442" s="4"/>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>0930601899</t>
+          <t>0963550931</t>
         </is>
       </c>
       <c r="E442" s="4"/>
@@ -13197,18 +13197,18 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>M2509270017</t>
+          <t>M2509270016</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>蕭又瑋</t>
+          <t>蕭仲安</t>
         </is>
       </c>
       <c r="C443" s="4"/>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>0922675798</t>
+          <t>0930601899</t>
         </is>
       </c>
       <c r="E443" s="4"/>
@@ -13226,18 +13226,18 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>M2509280009</t>
+          <t>M2509270017</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>蕭宇傑</t>
+          <t>蕭又瑋</t>
         </is>
       </c>
       <c r="C444" s="4"/>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>0989977822</t>
+          <t>0922675798</t>
         </is>
       </c>
       <c r="E444" s="4"/>
@@ -13255,18 +13255,18 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>M2510190006</t>
+          <t>M2509280009</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>蕭毓</t>
+          <t>蕭宇傑</t>
         </is>
       </c>
       <c r="C445" s="4"/>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>0975199046</t>
+          <t>0989977822</t>
         </is>
       </c>
       <c r="E445" s="4"/>
@@ -13284,22 +13284,18 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>M2510090006</t>
+          <t>M2510190006</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>蕭燁鴻</t>
-        </is>
-      </c>
-      <c r="C446" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區金龍路183號1樓</t>
-        </is>
-      </c>
+          <t>蕭毓</t>
+        </is>
+      </c>
+      <c r="C446" s="4"/>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>0917882269</t>
+          <t>0975199046</t>
         </is>
       </c>
       <c r="E446" s="4"/>
@@ -13317,18 +13313,22 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>M2510160008</t>
+          <t>M2510090006</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>蕭韻文</t>
-        </is>
-      </c>
-      <c r="C447" s="4"/>
+          <t>蕭燁鴻</t>
+        </is>
+      </c>
+      <c r="C447" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區金龍路183號1樓</t>
+        </is>
+      </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>0911297473</t>
+          <t>0917882269</t>
         </is>
       </c>
       <c r="E447" s="4"/>
@@ -13346,18 +13346,18 @@
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>M2509300014</t>
+          <t>M2510160008</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>藍駿偉</t>
+          <t>蕭韻文</t>
         </is>
       </c>
       <c r="C448" s="4"/>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>0936152586</t>
+          <t>0911297473</t>
         </is>
       </c>
       <c r="E448" s="4"/>
@@ -13375,18 +13375,18 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>M2511080007</t>
+          <t>M2509300014</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>蘇嘉蓉</t>
+          <t>藍駿偉</t>
         </is>
       </c>
       <c r="C449" s="4"/>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>0937074336</t>
+          <t>0936152586</t>
         </is>
       </c>
       <c r="E449" s="4"/>
@@ -13404,18 +13404,18 @@
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>M2511060002</t>
+          <t>M2511080007</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>蘇國貿</t>
+          <t>蘇嘉蓉</t>
         </is>
       </c>
       <c r="C450" s="4"/>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>0922250285</t>
+          <t>0937074336</t>
         </is>
       </c>
       <c r="E450" s="4"/>
@@ -13433,18 +13433,18 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>M2511280004</t>
+          <t>M2511060002</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>蘇家明</t>
+          <t>蘇國貿</t>
         </is>
       </c>
       <c r="C451" s="4"/>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>0916836765</t>
+          <t>0922250285</t>
         </is>
       </c>
       <c r="E451" s="4"/>
@@ -13462,18 +13462,18 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>M2510300002</t>
+          <t>M2511280004</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>蘇小好</t>
+          <t>蘇家明</t>
         </is>
       </c>
       <c r="C452" s="4"/>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>0981870981</t>
+          <t>0916836765</t>
         </is>
       </c>
       <c r="E452" s="4"/>
@@ -13491,18 +13491,18 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>M2509260021</t>
+          <t>M2510300002</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>蘇彥彰</t>
+          <t>蘇小好</t>
         </is>
       </c>
       <c r="C453" s="4"/>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>0983060026</t>
+          <t>0981870981</t>
         </is>
       </c>
       <c r="E453" s="4"/>
@@ -13520,22 +13520,18 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>M2510240001</t>
+          <t>M2509260021</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>蘇志勇</t>
-        </is>
-      </c>
-      <c r="C454" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
-        </is>
-      </c>
+          <t>蘇彥彰</t>
+        </is>
+      </c>
+      <c r="C454" s="4"/>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>0910051586</t>
+          <t>0983060026</t>
         </is>
       </c>
       <c r="E454" s="4"/>
@@ -13553,18 +13549,22 @@
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>M2602150002</t>
+          <t>M2510240001</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>蘇昱銘</t>
-        </is>
-      </c>
-      <c r="C455" s="4"/>
+          <t>蘇志勇</t>
+        </is>
+      </c>
+      <c r="C455" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
+        </is>
+      </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>0916324119</t>
+          <t>0910051586</t>
         </is>
       </c>
       <c r="E455" s="4"/>
@@ -13582,18 +13582,18 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>M2510050003</t>
+          <t>M2602150002</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>蘇睿慶</t>
+          <t>蘇昱銘</t>
         </is>
       </c>
       <c r="C456" s="4"/>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>0937766339</t>
+          <t>0916324119</t>
         </is>
       </c>
       <c r="E456" s="4"/>
@@ -13611,18 +13611,18 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>M2601180001</t>
+          <t>M2510050003</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>蠟筆</t>
+          <t>蘇睿慶</t>
         </is>
       </c>
       <c r="C457" s="4"/>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>0976321321</t>
+          <t>0937766339</t>
         </is>
       </c>
       <c r="E457" s="4"/>
@@ -13640,18 +13640,18 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>M2512160002</t>
+          <t>M2601180001</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>褚朕誠</t>
+          <t>蠟筆</t>
         </is>
       </c>
       <c r="C458" s="4"/>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>0972217495</t>
+          <t>0976321321</t>
         </is>
       </c>
       <c r="E458" s="4"/>
@@ -13669,18 +13669,18 @@
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>M2512200002</t>
+          <t>M2512160002</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>褚銘漢</t>
+          <t>褚朕誠</t>
         </is>
       </c>
       <c r="C459" s="4"/>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>0925886065</t>
+          <t>0972217495</t>
         </is>
       </c>
       <c r="E459" s="4"/>
@@ -13698,18 +13698,18 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>M2512170002</t>
+          <t>M2512200002</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>許俊鴻</t>
+          <t>褚銘漢</t>
         </is>
       </c>
       <c r="C460" s="4"/>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>0973630391</t>
+          <t>0925886065</t>
         </is>
       </c>
       <c r="E460" s="4"/>
@@ -13727,18 +13727,18 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>M2510050013</t>
+          <t>M2512170002</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>許凱傑</t>
+          <t>許俊鴻</t>
         </is>
       </c>
       <c r="C461" s="4"/>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>0955306971</t>
+          <t>0973630391</t>
         </is>
       </c>
       <c r="E461" s="4"/>
@@ -13756,18 +13756,18 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>M2511110001</t>
+          <t>M2510050013</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>許哲豪</t>
+          <t>許凱傑</t>
         </is>
       </c>
       <c r="C462" s="4"/>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>0985191149</t>
+          <t>0955306971</t>
         </is>
       </c>
       <c r="E462" s="4"/>
@@ -13785,18 +13785,18 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>M2602030001</t>
+          <t>M2511110001</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>許士彥</t>
+          <t>許哲豪</t>
         </is>
       </c>
       <c r="C463" s="4"/>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>0913558692</t>
+          <t>0985191149</t>
         </is>
       </c>
       <c r="E463" s="4"/>
@@ -13814,18 +13814,18 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>M2509290018</t>
+          <t>M2602030001</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>許天寶</t>
+          <t>許士彥</t>
         </is>
       </c>
       <c r="C464" s="4"/>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>0936088850</t>
+          <t>0913558692</t>
         </is>
       </c>
       <c r="E464" s="4"/>
@@ -13843,18 +13843,18 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>M2510160005</t>
+          <t>M2509290018</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>許宥蓁</t>
+          <t>許天寶</t>
         </is>
       </c>
       <c r="C465" s="4"/>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>0938473255</t>
+          <t>0936088850</t>
         </is>
       </c>
       <c r="E465" s="4"/>
@@ -13872,18 +13872,18 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>M2512020001</t>
+          <t>M2510160005</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>許家豪</t>
+          <t>許宥蓁</t>
         </is>
       </c>
       <c r="C466" s="4"/>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>0983215242</t>
+          <t>0938473255</t>
         </is>
       </c>
       <c r="E466" s="4"/>
@@ -13901,18 +13901,18 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>M2510110007</t>
+          <t>M2512020001</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>許峻銓</t>
+          <t>許家豪</t>
         </is>
       </c>
       <c r="C467" s="4"/>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>0979770033</t>
+          <t>0983215242</t>
         </is>
       </c>
       <c r="E467" s="4"/>
@@ -13930,18 +13930,18 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>M2511260001</t>
+          <t>M2510110007</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>許志帆</t>
+          <t>許峻銓</t>
         </is>
       </c>
       <c r="C468" s="4"/>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>0936639358</t>
+          <t>0979770033</t>
         </is>
       </c>
       <c r="E468" s="4"/>
@@ -13959,18 +13959,18 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>M2510310001</t>
+          <t>M2511260001</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>許志豪</t>
+          <t>許志帆</t>
         </is>
       </c>
       <c r="C469" s="4"/>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>0971080606</t>
+          <t>0936639358</t>
         </is>
       </c>
       <c r="E469" s="4"/>
@@ -13988,18 +13988,18 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>M2601040001</t>
+          <t>M2510310001</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>許惠笙</t>
+          <t>許志豪</t>
         </is>
       </c>
       <c r="C470" s="4"/>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>0987890463</t>
+          <t>0971080606</t>
         </is>
       </c>
       <c r="E470" s="4"/>
@@ -14017,18 +14017,18 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>M2603080002</t>
+          <t>M2601040001</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>許汶瑋</t>
+          <t>許惠笙</t>
         </is>
       </c>
       <c r="C471" s="4"/>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>0988166792</t>
+          <t>0987890463</t>
         </is>
       </c>
       <c r="E471" s="4"/>
@@ -14046,22 +14046,18 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>M2509140001</t>
+          <t>M2603080002</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>許煥杰</t>
-        </is>
-      </c>
-      <c r="C472" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區藝文二街88號8樓</t>
-        </is>
-      </c>
+          <t>許汶瑋</t>
+        </is>
+      </c>
+      <c r="C472" s="4"/>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>0913785888</t>
+          <t>0988166792</t>
         </is>
       </c>
       <c r="E472" s="4"/>
@@ -14079,18 +14075,22 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>M2510010001</t>
+          <t>M2509140001</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>許硯棠</t>
-        </is>
-      </c>
-      <c r="C473" s="4"/>
+          <t>許煥杰</t>
+        </is>
+      </c>
+      <c r="C473" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區藝文二街88號8樓</t>
+        </is>
+      </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>0983238652</t>
+          <t>0913785888</t>
         </is>
       </c>
       <c r="E473" s="4"/>
@@ -14108,18 +14108,18 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>M2509270001</t>
+          <t>M2510010001</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>許竣榤</t>
+          <t>許硯棠</t>
         </is>
       </c>
       <c r="C474" s="4"/>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>0955598097</t>
+          <t>0983238652</t>
         </is>
       </c>
       <c r="E474" s="4"/>
@@ -14137,18 +14137,18 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>M2510240002</t>
+          <t>M2509270001</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>許芫睿</t>
+          <t>許竣榤</t>
         </is>
       </c>
       <c r="C475" s="4"/>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>0975057699</t>
+          <t>0955598097</t>
         </is>
       </c>
       <c r="E475" s="4"/>
@@ -14166,18 +14166,18 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>M2509290013</t>
+          <t>M2510240002</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>許雅蓁</t>
+          <t>許芫睿</t>
         </is>
       </c>
       <c r="C476" s="4"/>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>0982339939</t>
+          <t>0975057699</t>
         </is>
       </c>
       <c r="E476" s="4"/>
@@ -14195,18 +14195,18 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>M2509260055</t>
+          <t>M2509290013</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>許靜蔆</t>
+          <t>許雅蓁</t>
         </is>
       </c>
       <c r="C477" s="4"/>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>0928060395</t>
+          <t>0982339939</t>
         </is>
       </c>
       <c r="E477" s="4"/>
@@ -14224,18 +14224,18 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>M2509260027</t>
+          <t>M2509260055</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>詹傑克</t>
+          <t>許靜蔆</t>
         </is>
       </c>
       <c r="C478" s="4"/>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>0968688080</t>
+          <t>0928060395</t>
         </is>
       </c>
       <c r="E478" s="4"/>
@@ -14253,18 +14253,18 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>M2602010004</t>
+          <t>M2509260027</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>詹凱翔</t>
+          <t>詹傑克</t>
         </is>
       </c>
       <c r="C479" s="4"/>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>0963496660</t>
+          <t>0968688080</t>
         </is>
       </c>
       <c r="E479" s="4"/>
@@ -14282,18 +14282,18 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>M2601270001</t>
+          <t>M2602010004</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>詹朝輝</t>
+          <t>詹凱翔</t>
         </is>
       </c>
       <c r="C480" s="4"/>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>0968490321</t>
+          <t>0963496660</t>
         </is>
       </c>
       <c r="E480" s="4"/>
@@ -14311,18 +14311,18 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>M2601170004</t>
+          <t>M2601270001</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>詹煜騰</t>
+          <t>詹朝輝</t>
         </is>
       </c>
       <c r="C481" s="4"/>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>0939919344</t>
+          <t>0968490321</t>
         </is>
       </c>
       <c r="E481" s="4"/>
@@ -14340,18 +14340,18 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>M2509280003</t>
+          <t>M2601170004</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>詹皇</t>
+          <t>詹煜騰</t>
         </is>
       </c>
       <c r="C482" s="4"/>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>0916037915</t>
+          <t>0939919344</t>
         </is>
       </c>
       <c r="E482" s="4"/>
@@ -14369,18 +14369,18 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>M2510030001</t>
+          <t>M2509280003</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>詹皇宥</t>
+          <t>詹皇</t>
         </is>
       </c>
       <c r="C483" s="4"/>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>0919367080</t>
+          <t>0916037915</t>
         </is>
       </c>
       <c r="E483" s="4"/>
@@ -14398,22 +14398,18 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>M2509290016</t>
+          <t>M2510030001</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>詹育銘</t>
-        </is>
-      </c>
-      <c r="C484" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區撫順街25號1樓</t>
-        </is>
-      </c>
+          <t>詹皇宥</t>
+        </is>
+      </c>
+      <c r="C484" s="4"/>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>0926962322</t>
+          <t>0919367080</t>
         </is>
       </c>
       <c r="E484" s="4"/>
@@ -14431,22 +14427,22 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>M2510270001</t>
+          <t>M2509290016</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>謝亞倫</t>
+          <t>詹育銘</t>
         </is>
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>新北市淡水區北投里北投子49-1號</t>
+          <t>台北市中山區撫順街25號1樓</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>0922409070</t>
+          <t>0926962322</t>
         </is>
       </c>
       <c r="E485" s="4"/>
@@ -14464,18 +14460,22 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>M2510040004</t>
+          <t>M2510270001</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>謝佳蓉</t>
-        </is>
-      </c>
-      <c r="C486" s="4"/>
+          <t>謝亞倫</t>
+        </is>
+      </c>
+      <c r="C486" s="4" t="inlineStr">
+        <is>
+          <t>新北市淡水區北投里北投子49-1號</t>
+        </is>
+      </c>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>0976958679</t>
+          <t>0922409070</t>
         </is>
       </c>
       <c r="E486" s="4"/>
@@ -14493,18 +14493,18 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>M2509300019</t>
+          <t>M2510040004</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>謝光明</t>
+          <t>謝佳蓉</t>
         </is>
       </c>
       <c r="C487" s="4"/>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>0983011754</t>
+          <t>0976958679</t>
         </is>
       </c>
       <c r="E487" s="4"/>
@@ -14522,22 +14522,18 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>M2512140002</t>
+          <t>M2509300019</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>謝孟辰</t>
-        </is>
-      </c>
-      <c r="C488" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
-        </is>
-      </c>
+          <t>謝光明</t>
+        </is>
+      </c>
+      <c r="C488" s="4"/>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>0953900309</t>
+          <t>0983011754</t>
         </is>
       </c>
       <c r="E488" s="4"/>
@@ -14555,18 +14551,22 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>M2509270007</t>
+          <t>M2512140002</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>謝建衫</t>
-        </is>
-      </c>
-      <c r="C489" s="4"/>
+          <t>謝孟辰</t>
+        </is>
+      </c>
+      <c r="C489" s="4" t="inlineStr">
+        <is>
+          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
+        </is>
+      </c>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>0918238090</t>
+          <t>0953900309</t>
         </is>
       </c>
       <c r="E489" s="4"/>
@@ -14584,18 +14584,18 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>M2510150005</t>
+          <t>M2509270007</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>謝文懷</t>
+          <t>謝建衫</t>
         </is>
       </c>
       <c r="C490" s="4"/>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>0989813659</t>
+          <t>0918238090</t>
         </is>
       </c>
       <c r="E490" s="4"/>
@@ -14613,18 +14613,18 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>M2510130004</t>
+          <t>M2510150005</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>謝桂仁</t>
+          <t>謝文懷</t>
         </is>
       </c>
       <c r="C491" s="4"/>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>0938357603</t>
+          <t>0989813659</t>
         </is>
       </c>
       <c r="E491" s="4"/>
@@ -14642,18 +14642,18 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>M2510050002</t>
+          <t>M2510130004</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>謝舒帆</t>
+          <t>謝桂仁</t>
         </is>
       </c>
       <c r="C492" s="4"/>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>0980699503</t>
+          <t>0938357603</t>
         </is>
       </c>
       <c r="E492" s="4"/>
@@ -14671,18 +14671,18 @@
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>M2510040008</t>
+          <t>M2510050002</t>
         </is>
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>謝荌核</t>
+          <t>謝舒帆</t>
         </is>
       </c>
       <c r="C493" s="4"/>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>0988302836</t>
+          <t>0980699503</t>
         </is>
       </c>
       <c r="E493" s="4"/>
@@ -14700,18 +14700,18 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>M2511300006</t>
+          <t>M2510040008</t>
         </is>
       </c>
       <c r="B494" s="4" t="inlineStr">
         <is>
-          <t>謝詠全</t>
+          <t>謝荌核</t>
         </is>
       </c>
       <c r="C494" s="4"/>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>0977077044</t>
+          <t>0988302836</t>
         </is>
       </c>
       <c r="E494" s="4"/>
@@ -14729,18 +14729,18 @@
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>M2603200003</t>
+          <t>M2511300006</t>
         </is>
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>譚淵修</t>
+          <t>謝詠全</t>
         </is>
       </c>
       <c r="C495" s="4"/>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>0910322500</t>
+          <t>0977077044</t>
         </is>
       </c>
       <c r="E495" s="4"/>
@@ -14758,18 +14758,18 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>M2510040011</t>
+          <t>M2603200003</t>
         </is>
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>賴先生</t>
+          <t>譚淵修</t>
         </is>
       </c>
       <c r="C496" s="4"/>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>0965351801</t>
+          <t>0910322500</t>
         </is>
       </c>
       <c r="E496" s="4"/>
@@ -14787,18 +14787,18 @@
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>M2603080001</t>
+          <t>M2510040011</t>
         </is>
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>賴品豪</t>
+          <t>賴先生</t>
         </is>
       </c>
       <c r="C497" s="4"/>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>0981379127</t>
+          <t>0965351801</t>
         </is>
       </c>
       <c r="E497" s="4"/>
@@ -14816,18 +14816,18 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>M2511010005</t>
+          <t>M2603080001</t>
         </is>
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>賴彥安</t>
+          <t>賴品豪</t>
         </is>
       </c>
       <c r="C498" s="4"/>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>0913102110</t>
+          <t>0981379127</t>
         </is>
       </c>
       <c r="E498" s="4"/>
@@ -14845,22 +14845,18 @@
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>M2603280001</t>
+          <t>M2511010005</t>
         </is>
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>賴柏舟</t>
-        </is>
-      </c>
-      <c r="C499" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股五福路11號</t>
-        </is>
-      </c>
+          <t>賴彥安</t>
+        </is>
+      </c>
+      <c r="C499" s="4"/>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>0979131818</t>
+          <t>0913102110</t>
         </is>
       </c>
       <c r="E499" s="4"/>
@@ -14878,18 +14874,22 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
-        </is>
-      </c>
-      <c r="C500" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C500" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E500" s="4"/>
@@ -14907,18 +14907,18 @@
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
+          <t>賴珊珊</t>
         </is>
       </c>
       <c r="C501" s="4"/>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E501" s="4"/>
@@ -14936,22 +14936,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C502" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14969,22 +14965,22 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C503" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E503" s="4"/>
@@ -15002,22 +14998,22 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>趙云璟</t>
         </is>
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
         </is>
       </c>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -15035,18 +15031,22 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C505" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C505" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E505" s="4"/>
@@ -15064,18 +15064,18 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C506" s="4"/>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15093,18 +15093,18 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C507" s="4"/>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0986258793</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15122,20 +15122,24 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C508" s="4"/>
-      <c r="D508" s="4"/>
+      <c r="D508" s="4" t="inlineStr">
+        <is>
+          <t>0982484963</t>
+        </is>
+      </c>
       <c r="E508" s="4"/>
       <c r="F508" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G508" s="5" t="inlineStr">
@@ -15147,24 +15151,20 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C509" s="4"/>
-      <c r="D509" s="4" t="inlineStr">
-        <is>
-          <t>0981898339</t>
-        </is>
-      </c>
+      <c r="D509" s="4"/>
       <c r="E509" s="4"/>
       <c r="F509" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G509" s="5" t="inlineStr">
@@ -15176,18 +15176,18 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C510" s="4"/>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>0903921531</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E510" s="4"/>
@@ -15205,18 +15205,18 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C511" s="4"/>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E511" s="4"/>
@@ -15234,18 +15234,18 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C512" s="4"/>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E512" s="4"/>
@@ -15263,18 +15263,18 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C513" s="4"/>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E513" s="4"/>
@@ -15292,18 +15292,18 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱振為</t>
         </is>
       </c>
       <c r="C514" s="4"/>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E514" s="4"/>
@@ -15321,22 +15321,18 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C515" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱政傑</t>
+        </is>
+      </c>
+      <c r="C515" s="4"/>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E515" s="4"/>
@@ -15354,18 +15350,22 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
-        </is>
-      </c>
-      <c r="C516" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C516" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E516" s="4"/>
@@ -15383,18 +15383,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15412,18 +15412,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C518" s="4"/>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E518" s="4"/>
@@ -15441,7 +15441,7 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
@@ -15470,18 +15470,18 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C520" s="4"/>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E520" s="4"/>
@@ -15499,16 +15499,20 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C521" s="4"/>
-      <c r="D521" s="4"/>
+      <c r="D521" s="4" t="inlineStr">
+        <is>
+          <t>0935329653</t>
+        </is>
+      </c>
       <c r="E521" s="4"/>
       <c r="F521" s="4" t="inlineStr">
         <is>
@@ -15524,20 +15528,16 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C522" s="4"/>
-      <c r="D522" s="4" t="inlineStr">
-        <is>
-          <t>0976588171</t>
-        </is>
-      </c>
+      <c r="D522" s="4"/>
       <c r="E522" s="4"/>
       <c r="F522" s="4" t="inlineStr">
         <is>
@@ -15553,18 +15553,18 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C523" s="4"/>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>0972128080</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E523" s="4"/>
@@ -15582,18 +15582,18 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C524" s="4"/>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E524" s="4"/>
@@ -15611,18 +15611,18 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C525" s="4"/>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E525" s="4"/>
@@ -15640,18 +15640,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C526" s="4"/>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15669,18 +15669,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C527" s="4"/>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15698,18 +15698,18 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C528" s="4"/>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15727,18 +15727,18 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C529" s="4"/>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15756,18 +15756,18 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭鼎昇</t>
         </is>
       </c>
       <c r="C530" s="4"/>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15785,22 +15785,18 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C531" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>鄒育燁</t>
+        </is>
+      </c>
+      <c r="C531" s="4"/>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15818,18 +15814,22 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
-        </is>
-      </c>
-      <c r="C532" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C532" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15847,18 +15847,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C533" s="4"/>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15876,18 +15876,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E534" s="4"/>
@@ -15905,18 +15905,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C535" s="4"/>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15934,18 +15934,18 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C536" s="4"/>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E536" s="4"/>
@@ -15963,18 +15963,18 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C537" s="4"/>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E537" s="4"/>
@@ -15992,18 +15992,18 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭秉霖</t>
         </is>
       </c>
       <c r="C538" s="4"/>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E538" s="4"/>
@@ -16021,22 +16021,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C539" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E539" s="4"/>
@@ -16054,22 +16050,22 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>鄭雁予</t>
+          <t>鄭鉅耀</t>
         </is>
       </c>
       <c r="C540" s="4" t="inlineStr">
         <is>
-          <t>桃園區國聖二街145號5樓之1</t>
+          <t>新北市五股區成泰路二段208號</t>
         </is>
       </c>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16087,18 +16083,22 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C541" s="4"/>
+          <t>鄭雁予</t>
+        </is>
+      </c>
+      <c r="C541" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16116,18 +16116,18 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C542" s="4"/>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E542" s="4"/>
@@ -16145,18 +16145,18 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C543" s="4"/>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16174,18 +16174,18 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C544" s="4"/>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E544" s="4"/>
@@ -16203,18 +16203,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾銘峰</t>
         </is>
       </c>
       <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16232,22 +16232,18 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C546" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鐘國禎</t>
+        </is>
+      </c>
+      <c r="C546" s="4"/>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16265,24 +16261,28 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2603270001</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>鐘駿霆</t>
-        </is>
-      </c>
-      <c r="C547" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0919331886</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E547" s="4"/>
       <c r="F547" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G547" s="5" t="inlineStr">
@@ -16294,24 +16294,24 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
+          <t>鐘駿霆</t>
         </is>
       </c>
       <c r="C548" s="4"/>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E548" s="4"/>
       <c r="F548" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G548" s="5" t="inlineStr">
@@ -16323,22 +16323,18 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C549" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>阮海德</t>
+        </is>
+      </c>
+      <c r="C549" s="4"/>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E549" s="4"/>
@@ -16356,18 +16352,22 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
-        </is>
-      </c>
-      <c r="C550" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E550" s="4"/>
@@ -16385,18 +16385,18 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
+          <t>阿源</t>
         </is>
       </c>
       <c r="C551" s="4"/>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E551" s="4"/>
@@ -16414,22 +16414,18 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C552" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿良</t>
+        </is>
+      </c>
+      <c r="C552" s="4"/>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16447,18 +16443,22 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
-        </is>
-      </c>
-      <c r="C553" s="4"/>
+          <t>陳仲盟</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
+        </is>
+      </c>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16476,22 +16476,18 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
-        </is>
-      </c>
-      <c r="C554" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區日和街7號22樓</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C554" s="4"/>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16509,22 +16505,22 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
+          <t>陳俊安</t>
         </is>
       </c>
       <c r="C555" s="4" t="inlineStr">
         <is>
-          <t>板橋大觀路1段28巷118-1號</t>
+          <t>新北市土城區日和街7號22樓</t>
         </is>
       </c>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16542,18 +16538,22 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C556" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C556" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16571,18 +16571,18 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C557" s="4"/>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16600,18 +16600,18 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C558" s="4"/>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16629,18 +16629,18 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C559" s="4"/>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16658,18 +16658,18 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C560" s="4"/>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16687,18 +16687,18 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C561" s="4"/>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16716,18 +16716,18 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C562" s="4"/>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16745,18 +16745,18 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C563" s="4"/>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16774,18 +16774,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16803,18 +16803,18 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳奕融</t>
         </is>
       </c>
       <c r="C565" s="4"/>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16832,22 +16832,18 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C566" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕閔</t>
+        </is>
+      </c>
+      <c r="C566" s="4"/>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16865,18 +16861,22 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2603260001</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳威宇</t>
-        </is>
-      </c>
-      <c r="C567" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C567" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0958186337</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16894,18 +16894,18 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C568" s="4"/>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16923,18 +16923,18 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C569" s="4"/>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16952,18 +16952,18 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C570" s="4"/>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16981,18 +16981,18 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
+          <t>陳子杰</t>
         </is>
       </c>
       <c r="C571" s="4"/>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -17010,18 +17010,18 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
+          <t>陳宏文</t>
         </is>
       </c>
       <c r="C572" s="4"/>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -17039,22 +17039,18 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C573" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳宏達</t>
+        </is>
+      </c>
+      <c r="C573" s="4"/>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17072,18 +17068,22 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
-        </is>
-      </c>
-      <c r="C574" s="4"/>
+          <t>陳家偉</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市神農路一段72號</t>
+        </is>
+      </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17101,18 +17101,18 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
+          <t>陳小雨</t>
         </is>
       </c>
       <c r="C575" s="4"/>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17130,22 +17130,18 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
-        </is>
-      </c>
-      <c r="C576" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
-        </is>
-      </c>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="C576" s="4"/>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17163,22 +17159,22 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
+          <t>陳建宏(花蓮)</t>
         </is>
       </c>
       <c r="C577" s="4" t="inlineStr">
         <is>
-          <t>新北市三重區仁美街125號</t>
+          <t>花蓮縣新城鄉佳林31之19號</t>
         </is>
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17196,18 +17192,22 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
-        </is>
-      </c>
-      <c r="C578" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C578" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17225,18 +17225,18 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C579" s="4"/>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17254,18 +17254,18 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C580" s="4"/>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17283,18 +17283,18 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C581" s="4"/>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17312,18 +17312,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳怡如(彥鈞)</t>
         </is>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17341,18 +17341,18 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳慶壎</t>
         </is>
       </c>
       <c r="C583" s="4"/>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17370,22 +17370,18 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C584" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳敬惟</t>
+        </is>
+      </c>
+      <c r="C584" s="4"/>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17403,18 +17399,22 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
-        </is>
-      </c>
-      <c r="C585" s="4"/>
+          <t>陳智盛</t>
+        </is>
+      </c>
+      <c r="C585" s="4" t="inlineStr">
+        <is>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
+        </is>
+      </c>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17432,22 +17432,18 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
-        </is>
-      </c>
-      <c r="C586" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區星雲街30號</t>
-        </is>
-      </c>
+          <t>陳朋堅</t>
+        </is>
+      </c>
+      <c r="C586" s="4"/>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17465,22 +17461,22 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
+          <t>陳松廉</t>
         </is>
       </c>
       <c r="C587" s="4" t="inlineStr">
         <is>
-          <t>桃園市南豐街258號</t>
+          <t>台北市內湖區星雲街30號</t>
         </is>
       </c>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17498,18 +17494,22 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
-        </is>
-      </c>
-      <c r="C588" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C588" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17527,18 +17527,18 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C589" s="4"/>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17556,7 +17556,7 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
@@ -17567,7 +17567,7 @@
       <c r="C590" s="4"/>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17585,18 +17585,18 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C591" s="4"/>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17614,22 +17614,18 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C592" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳正傑</t>
+        </is>
+      </c>
+      <c r="C592" s="4"/>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17647,18 +17643,22 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
-        </is>
-      </c>
-      <c r="C593" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C593" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17676,18 +17676,18 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C594" s="4"/>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17705,18 +17705,18 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
+          <t>陳琇珊</t>
         </is>
       </c>
       <c r="C595" s="4"/>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17734,18 +17734,18 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳琬瑜</t>
         </is>
       </c>
       <c r="C596" s="4"/>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17763,22 +17763,18 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C597" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳璽文</t>
+        </is>
+      </c>
+      <c r="C597" s="4"/>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17796,18 +17792,22 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
-        </is>
-      </c>
-      <c r="C598" s="4"/>
+          <t>陳益銓</t>
+        </is>
+      </c>
+      <c r="C598" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區民生街15巷10號3樓</t>
+        </is>
+      </c>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17825,22 +17825,18 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
-        </is>
-      </c>
-      <c r="C599" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
-        </is>
-      </c>
+          <t>陳秋蓉</t>
+        </is>
+      </c>
+      <c r="C599" s="4"/>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17858,18 +17854,22 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
-        </is>
-      </c>
-      <c r="C600" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C600" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E600" s="4"/>
@@ -17887,18 +17887,18 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
+          <t>陳貴源</t>
         </is>
       </c>
       <c r="C601" s="4"/>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17916,18 +17916,18 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
+          <t>陳達鋒</t>
         </is>
       </c>
       <c r="C602" s="4"/>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17945,22 +17945,18 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2604190004</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C603" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳鋐緯</t>
+        </is>
+      </c>
+      <c r="C603" s="4"/>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0925805535</t>
         </is>
       </c>
       <c r="E603" s="4"/>
@@ -17978,22 +17974,18 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
-        </is>
-      </c>
-      <c r="C604" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C604" s="4"/>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E604" s="4"/>
@@ -18011,22 +18003,22 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
+          <t>陳長志</t>
         </is>
       </c>
       <c r="C605" s="4" t="inlineStr">
         <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
+          <t>新北市新店區安康路</t>
         </is>
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E605" s="4"/>
@@ -18044,18 +18036,22 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C606" s="4"/>
+          <t>陳雯瑄</t>
+        </is>
+      </c>
+      <c r="C606" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+        </is>
+      </c>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E606" s="4"/>
@@ -18073,18 +18069,22 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
-        </is>
-      </c>
-      <c r="C607" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C607" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E607" s="4"/>
@@ -18102,18 +18102,18 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C608" s="4"/>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E608" s="4"/>
@@ -18131,18 +18131,18 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C609" s="4"/>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18160,18 +18160,18 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C610" s="4"/>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18189,18 +18189,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18218,18 +18218,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18247,18 +18247,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18276,18 +18276,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18305,18 +18305,18 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C615" s="4"/>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18334,18 +18334,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18363,18 +18363,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18392,22 +18392,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C618" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>顏宏坤</t>
+        </is>
+      </c>
+      <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18425,18 +18421,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
+          <t>馬迪</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18454,18 +18450,22 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
-        </is>
-      </c>
-      <c r="C620" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C620" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18483,18 +18483,18 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C621" s="4"/>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18512,18 +18512,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18541,18 +18541,18 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C623" s="4"/>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E623" s="4"/>
@@ -18570,18 +18570,18 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C624" s="4"/>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E624" s="4"/>
@@ -18599,18 +18599,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18628,22 +18628,18 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C626" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高聖景</t>
+        </is>
+      </c>
+      <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E626" s="4"/>
@@ -18661,18 +18657,18 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
+          <t>高莉婷</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E627" s="4"/>
@@ -18690,18 +18686,22 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
-        </is>
-      </c>
-      <c r="C628" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C628" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18719,16 +18719,20 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C629" s="4"/>
-      <c r="D629" s="4"/>
+      <c r="D629" s="4" t="inlineStr">
+        <is>
+          <t>0937742352</t>
+        </is>
+      </c>
       <c r="E629" s="4"/>
       <c r="F629" s="4" t="inlineStr">
         <is>
@@ -18744,18 +18748,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0958180882</t>
+          <t>0989116588</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18773,24 +18777,16 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C631" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
-      <c r="D631" s="4" t="inlineStr">
-        <is>
-          <t>0903975921</t>
-        </is>
-      </c>
+          <t>鴻</t>
+        </is>
+      </c>
+      <c r="C631" s="4"/>
+      <c r="D631" s="4"/>
       <c r="E631" s="4"/>
       <c r="F631" s="4" t="inlineStr">
         <is>
@@ -18806,16 +18802,20 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
+          <t>黃俊翰</t>
         </is>
       </c>
       <c r="C632" s="4"/>
-      <c r="D632" s="4"/>
+      <c r="D632" s="4" t="inlineStr">
+        <is>
+          <t>0958180882</t>
+        </is>
+      </c>
       <c r="E632" s="4"/>
       <c r="F632" s="4" t="inlineStr">
         <is>
@@ -18831,18 +18831,22 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
-        </is>
-      </c>
-      <c r="C633" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C633" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>0938722217</t>
+          <t>0903975921</t>
         </is>
       </c>
       <c r="E633" s="4"/>
@@ -18860,20 +18864,16 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B634" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C634" s="4"/>
-      <c r="D634" s="4" t="inlineStr">
-        <is>
-          <t>0989628136</t>
-        </is>
-      </c>
+      <c r="D634" s="4"/>
       <c r="E634" s="4"/>
       <c r="F634" s="4" t="inlineStr">
         <is>
@@ -18889,18 +18889,18 @@
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C635" s="4"/>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E635" s="4"/>
@@ -18918,18 +18918,18 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B636" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C636" s="4"/>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E636" s="4"/>
@@ -18947,18 +18947,18 @@
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C637" s="4"/>
       <c r="D637" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E637" s="4"/>
@@ -18976,18 +18976,18 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2604190003</t>
         </is>
       </c>
       <c r="B638" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃士凱</t>
         </is>
       </c>
       <c r="C638" s="4"/>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0934179571</t>
         </is>
       </c>
       <c r="E638" s="4"/>
@@ -19005,18 +19005,18 @@
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
         <is>
-          <t>M2604120001</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>黃宥文</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C639" s="4"/>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>0953082147</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E639" s="4"/>
@@ -19034,18 +19034,18 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B640" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C640" s="4"/>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E640" s="4"/>
@@ -19063,18 +19063,18 @@
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C641" s="4"/>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E641" s="4"/>
@@ -19092,22 +19092,18 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2604120001</t>
         </is>
       </c>
       <c r="B642" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C642" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃宥文</t>
+        </is>
+      </c>
+      <c r="C642" s="4"/>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0953082147</t>
         </is>
       </c>
       <c r="E642" s="4"/>
@@ -19125,18 +19121,18 @@
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C643" s="4"/>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E643" s="4"/>
@@ -19154,18 +19150,18 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B644" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃庠豪</t>
         </is>
       </c>
       <c r="C644" s="4"/>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E644" s="4"/>
@@ -19183,18 +19179,22 @@
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
-        </is>
-      </c>
-      <c r="C645" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C645" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E645" s="4"/>
@@ -19212,18 +19212,18 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B646" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C646" s="4"/>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E646" s="4"/>
@@ -19241,18 +19241,18 @@
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C647" s="4"/>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E647" s="4"/>
@@ -19270,18 +19270,18 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B648" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C648" s="4"/>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E648" s="4"/>
@@ -19299,18 +19299,18 @@
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C649" s="4"/>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E649" s="4"/>
@@ -19328,18 +19328,18 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B650" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C650" s="4"/>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E650" s="4"/>
@@ -19357,18 +19357,18 @@
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B651" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C651" s="4"/>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E651" s="4"/>
@@ -19386,18 +19386,18 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B652" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C652" s="4"/>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E652" s="4"/>
@@ -19415,18 +19415,18 @@
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B653" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C653" s="4"/>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E653" s="4"/>
@@ -19444,18 +19444,18 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B654" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C654" s="4"/>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E654" s="4"/>
@@ -19473,18 +19473,18 @@
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B655" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C655" s="4"/>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E655" s="4"/>
@@ -19502,18 +19502,18 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B656" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C656" s="4"/>
       <c r="D656" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E656" s="4"/>
@@ -19531,18 +19531,18 @@
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B657" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C657" s="4"/>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E657" s="4"/>
@@ -19560,18 +19560,18 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B658" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C658" s="4"/>
       <c r="D658" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E658" s="4"/>
@@ -19589,18 +19589,18 @@
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2604190001</t>
         </is>
       </c>
       <c r="B659" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃貞菱</t>
         </is>
       </c>
       <c r="C659" s="4"/>
       <c r="D659" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0987793062</t>
         </is>
       </c>
       <c r="E659" s="4"/>
@@ -19618,18 +19618,18 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B660" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C660" s="4"/>
       <c r="D660" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E660" s="4"/>
@@ -19645,9 +19645,125 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>2026/04/19  13:00:14</t>
+      <c r="A661" s="4" t="inlineStr">
+        <is>
+          <t>M2509290011</t>
+        </is>
+      </c>
+      <c r="B661" s="4" t="inlineStr">
+        <is>
+          <t>黃鉑元</t>
+        </is>
+      </c>
+      <c r="C661" s="4"/>
+      <c r="D661" s="4" t="inlineStr">
+        <is>
+          <t>0970993863</t>
+        </is>
+      </c>
+      <c r="E661" s="4"/>
+      <c r="F661" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G661" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="4" t="inlineStr">
+        <is>
+          <t>M2510020007</t>
+        </is>
+      </c>
+      <c r="B662" s="4" t="inlineStr">
+        <is>
+          <t>黃鴻麒</t>
+        </is>
+      </c>
+      <c r="C662" s="4"/>
+      <c r="D662" s="4" t="inlineStr">
+        <is>
+          <t>0930571975</t>
+        </is>
+      </c>
+      <c r="E662" s="4"/>
+      <c r="F662" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G662" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="4" t="inlineStr">
+        <is>
+          <t>M2602270002</t>
+        </is>
+      </c>
+      <c r="B663" s="4" t="inlineStr">
+        <is>
+          <t>黎信宏</t>
+        </is>
+      </c>
+      <c r="C663" s="4"/>
+      <c r="D663" s="4" t="inlineStr">
+        <is>
+          <t>0911024337</t>
+        </is>
+      </c>
+      <c r="E663" s="4"/>
+      <c r="F663" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G663" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B664" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C664" s="4"/>
+      <c r="D664" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E664" s="4"/>
+      <c r="F664" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G664" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026/04/20  17:13:20</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -19763,7 +19763,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026/04/20  17:13:20</t>
+          <t>2026/04/21  17:27:07</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -8054,26 +8054,22 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>M2511160002</t>
+          <t>M2604211000</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>林瑩昇</t>
+          <t>林玉蘭</t>
         </is>
       </c>
       <c r="C269" s="4"/>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>0939577028</t>
+          <t>0985225695</t>
         </is>
       </c>
       <c r="E269" s="4"/>
-      <c r="F269" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
+      <c r="F269" s="4"/>
       <c r="G269" s="5" t="inlineStr">
         <is>
           <t>附件管理</t>
@@ -8083,18 +8079,18 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>M2509260046</t>
+          <t>M2511160002</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>林甫吉</t>
+          <t>林瑩昇</t>
         </is>
       </c>
       <c r="C270" s="4"/>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>0909520365</t>
+          <t>0939577028</t>
         </is>
       </c>
       <c r="E270" s="4"/>
@@ -8112,22 +8108,18 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>M2603280002</t>
+          <t>M2509260046</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>林秀英</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>台北市士林區中山北路七段81巷16弄11-2號1樓</t>
-        </is>
-      </c>
+          <t>林甫吉</t>
+        </is>
+      </c>
+      <c r="C271" s="4"/>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>0922316858</t>
+          <t>0909520365</t>
         </is>
       </c>
       <c r="E271" s="4"/>
@@ -8145,18 +8137,22 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>M2509260053</t>
+          <t>M2603280002</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>林美雲</t>
-        </is>
-      </c>
-      <c r="C272" s="4"/>
+          <t>林秀英</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區中山北路七段81巷16弄11-2號1樓</t>
+        </is>
+      </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>0920436214</t>
+          <t>0922316858</t>
         </is>
       </c>
       <c r="E272" s="4"/>
@@ -8174,18 +8170,18 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>M2510280002</t>
+          <t>M2509260053</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>林耀武</t>
+          <t>林美雲</t>
         </is>
       </c>
       <c r="C273" s="4"/>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>0911552967</t>
+          <t>0920436214</t>
         </is>
       </c>
       <c r="E273" s="4"/>
@@ -8203,18 +8199,18 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>M2604190002</t>
+          <t>M2510280002</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>林裕勝</t>
+          <t>林耀武</t>
         </is>
       </c>
       <c r="C274" s="4"/>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>0972220939</t>
+          <t>0911552967</t>
         </is>
       </c>
       <c r="E274" s="4"/>
@@ -8232,22 +8228,18 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>M2604160002</t>
+          <t>M2604190002</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>林辰奕</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市黎明路323巷31號</t>
-        </is>
-      </c>
+          <t>林裕勝</t>
+        </is>
+      </c>
+      <c r="C275" s="4"/>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>0903807636</t>
+          <t>0972220939</t>
         </is>
       </c>
       <c r="E275" s="4"/>
@@ -8265,18 +8257,22 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>M2509300005</t>
+          <t>M2604160002</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>林通海</t>
-        </is>
-      </c>
-      <c r="C276" s="4"/>
+          <t>林辰奕</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市黎明路323巷31號</t>
+        </is>
+      </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>0958589472</t>
+          <t>0903807636</t>
         </is>
       </c>
       <c r="E276" s="4"/>
@@ -8294,18 +8290,18 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>M2511220001</t>
+          <t>M2509300005</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>林鈺倫</t>
+          <t>林通海</t>
         </is>
       </c>
       <c r="C277" s="4"/>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>0988210410</t>
+          <t>0958589472</t>
         </is>
       </c>
       <c r="E277" s="4"/>
@@ -8323,18 +8319,18 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>M2510190005</t>
+          <t>M2511220001</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>林鈺瑩</t>
+          <t>林鈺倫</t>
         </is>
       </c>
       <c r="C278" s="4"/>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>0973789355</t>
+          <t>0988210410</t>
         </is>
       </c>
       <c r="E278" s="4"/>
@@ -8352,18 +8348,18 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>M2603311001</t>
+          <t>M2510190005</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>林銘宇</t>
+          <t>林鈺瑩</t>
         </is>
       </c>
       <c r="C279" s="4"/>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>0903101817</t>
+          <t>0973789355</t>
         </is>
       </c>
       <c r="E279" s="4"/>
@@ -8381,18 +8377,18 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>M2511250001</t>
+          <t>M2603311001</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>林雅琦</t>
+          <t>林銘宇</t>
         </is>
       </c>
       <c r="C280" s="4"/>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>0917361103</t>
+          <t>0903101817</t>
         </is>
       </c>
       <c r="E280" s="4"/>
@@ -8410,18 +8406,18 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>M2510100002</t>
+          <t>M2511250001</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>林鴻丞</t>
+          <t>林雅琦</t>
         </is>
       </c>
       <c r="C281" s="4"/>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>0989764757</t>
+          <t>0917361103</t>
         </is>
       </c>
       <c r="E281" s="4"/>
@@ -8439,18 +8435,18 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>M2601030004</t>
+          <t>M2510100002</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>柯偉強</t>
+          <t>林鴻丞</t>
         </is>
       </c>
       <c r="C282" s="4"/>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>0976720368</t>
+          <t>0989764757</t>
         </is>
       </c>
       <c r="E282" s="4"/>
@@ -8468,18 +8464,18 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>M2510050009</t>
+          <t>M2601030004</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>梁涵鈞</t>
+          <t>柯偉強</t>
         </is>
       </c>
       <c r="C283" s="4"/>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>0961007059</t>
+          <t>0976720368</t>
         </is>
       </c>
       <c r="E283" s="4"/>
@@ -8497,18 +8493,18 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>M2512210002</t>
+          <t>M2510050009</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>楊啓煌</t>
+          <t>梁涵鈞</t>
         </is>
       </c>
       <c r="C284" s="4"/>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>0970290888</t>
+          <t>0961007059</t>
         </is>
       </c>
       <c r="E284" s="4"/>
@@ -8526,7 +8522,7 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>M2603240002</t>
+          <t>M2512210002</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -8534,11 +8530,7 @@
           <t>楊啓煌</t>
         </is>
       </c>
-      <c r="C285" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區新生北路三段84巷33號2樓</t>
-        </is>
-      </c>
+      <c r="C285" s="4"/>
       <c r="D285" s="4" t="inlineStr">
         <is>
           <t>0970290888</t>
@@ -8559,18 +8551,22 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>M2509260042</t>
+          <t>M2603240002</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>楊士毅</t>
-        </is>
-      </c>
-      <c r="C286" s="4"/>
+          <t>楊啓煌</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>台北市中山區新生北路三段84巷33號2樓</t>
+        </is>
+      </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>0917523878</t>
+          <t>0970290888</t>
         </is>
       </c>
       <c r="E286" s="4"/>
@@ -8588,18 +8584,18 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>M2510100008</t>
+          <t>M2509260042</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>楊孝斌</t>
+          <t>楊士毅</t>
         </is>
       </c>
       <c r="C287" s="4"/>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>0916001788</t>
+          <t>0917523878</t>
         </is>
       </c>
       <c r="E287" s="4"/>
@@ -8617,22 +8613,18 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>M2509270002</t>
+          <t>M2510100008</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>楊岱惊</t>
-        </is>
-      </c>
-      <c r="C288" s="4" t="inlineStr">
-        <is>
-          <t>桃園市長安街26巷3號</t>
-        </is>
-      </c>
+          <t>楊孝斌</t>
+        </is>
+      </c>
+      <c r="C288" s="4"/>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>0989612191</t>
+          <t>0916001788</t>
         </is>
       </c>
       <c r="E288" s="4"/>
@@ -8650,22 +8642,22 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>M2509270011</t>
+          <t>M2509270002</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>楊庭瑋</t>
+          <t>楊岱惊</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>基隆市中山區復興路151號</t>
+          <t>桃園市長安街26巷3號</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>0963922276</t>
+          <t>0989612191</t>
         </is>
       </c>
       <c r="E289" s="4"/>
@@ -8683,18 +8675,22 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>M2511060001</t>
+          <t>M2509270011</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>楊明晁(四哥)</t>
-        </is>
-      </c>
-      <c r="C290" s="4"/>
+          <t>楊庭瑋</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區復興路151號</t>
+        </is>
+      </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>0968732839</t>
+          <t>0963922276</t>
         </is>
       </c>
       <c r="E290" s="4"/>
@@ -8712,18 +8708,18 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>M2601250001</t>
+          <t>M2511060001</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>楊智傑</t>
+          <t>楊明晁(四哥)</t>
         </is>
       </c>
       <c r="C291" s="4"/>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>0931131821</t>
+          <t>0968732839</t>
         </is>
       </c>
       <c r="E291" s="4"/>
@@ -8741,18 +8737,18 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>M2510030003</t>
+          <t>M2601250001</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>楊智翔</t>
+          <t>楊智傑</t>
         </is>
       </c>
       <c r="C292" s="4"/>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>0975128278</t>
+          <t>0931131821</t>
         </is>
       </c>
       <c r="E292" s="4"/>
@@ -8770,18 +8766,18 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>M2510060004</t>
+          <t>M2510030003</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>楊重九</t>
+          <t>楊智翔</t>
         </is>
       </c>
       <c r="C293" s="4"/>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>0920626999</t>
+          <t>0975128278</t>
         </is>
       </c>
       <c r="E293" s="4"/>
@@ -8799,18 +8795,18 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>M2510080001</t>
+          <t>M2510060004</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>楊錦加</t>
+          <t>楊重九</t>
         </is>
       </c>
       <c r="C294" s="4"/>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>0918872988</t>
+          <t>0920626999</t>
         </is>
       </c>
       <c r="E294" s="4"/>
@@ -8828,18 +8824,18 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>M2603280003</t>
+          <t>M2510080001</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>楊鎮良</t>
+          <t>楊錦加</t>
         </is>
       </c>
       <c r="C295" s="4"/>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>0976121606</t>
+          <t>0918872988</t>
         </is>
       </c>
       <c r="E295" s="4"/>
@@ -8857,16 +8853,20 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>V0020</t>
+          <t>M2603280003</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>榮豪</t>
+          <t>楊鎮良</t>
         </is>
       </c>
       <c r="C296" s="4"/>
-      <c r="D296" s="4"/>
+      <c r="D296" s="4" t="inlineStr">
+        <is>
+          <t>0976121606</t>
+        </is>
+      </c>
       <c r="E296" s="4"/>
       <c r="F296" s="4" t="inlineStr">
         <is>
@@ -8882,20 +8882,16 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>M2602130002</t>
+          <t>V0020</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>榮豪-許</t>
+          <t>榮豪</t>
         </is>
       </c>
       <c r="C297" s="4"/>
-      <c r="D297" s="4" t="inlineStr">
-        <is>
-          <t>0931100879</t>
-        </is>
-      </c>
+      <c r="D297" s="4"/>
       <c r="E297" s="4"/>
       <c r="F297" s="4" t="inlineStr">
         <is>
@@ -8911,18 +8907,18 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>M2602080007</t>
+          <t>M2602130002</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>樓俊瑋</t>
+          <t>榮豪-許</t>
         </is>
       </c>
       <c r="C298" s="4"/>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>0910900256</t>
+          <t>0931100879</t>
         </is>
       </c>
       <c r="E298" s="4"/>
@@ -8940,22 +8936,18 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>M2511010001</t>
+          <t>M2602080007</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>武林</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區集美街222號5樓</t>
-        </is>
-      </c>
+          <t>樓俊瑋</t>
+        </is>
+      </c>
+      <c r="C299" s="4"/>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>0913211688</t>
+          <t>0910900256</t>
         </is>
       </c>
       <c r="E299" s="4"/>
@@ -8973,18 +8965,22 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>M2511080005</t>
+          <t>M2511010001</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>毛毛</t>
-        </is>
-      </c>
-      <c r="C300" s="4"/>
+          <t>武林</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區集美街222號5樓</t>
+        </is>
+      </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>0919286386</t>
+          <t>0913211688</t>
         </is>
       </c>
       <c r="E300" s="4"/>
@@ -9002,24 +8998,24 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>Z0001</t>
+          <t>M2511080005</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>民享店</t>
-        </is>
-      </c>
-      <c r="C301" s="4" t="inlineStr">
-        <is>
-          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
-        </is>
-      </c>
-      <c r="D301" s="4"/>
+          <t>毛毛</t>
+        </is>
+      </c>
+      <c r="C301" s="4"/>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>0919286386</t>
+        </is>
+      </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -9031,15 +9027,19 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>V0014</t>
+          <t>Z0001</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>民享房東</t>
-        </is>
-      </c>
-      <c r="C302" s="4"/>
+          <t>民享店</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>新北市中和區民享街6-7號 黃色招牌夾吧</t>
+        </is>
+      </c>
       <c r="D302" s="4"/>
       <c r="E302" s="4"/>
       <c r="F302" s="4" t="inlineStr">
@@ -9056,12 +9056,12 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>V0019</t>
+          <t>V0014</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>永豐餘</t>
+          <t>民享房東</t>
         </is>
       </c>
       <c r="C303" s="4"/>
@@ -9069,7 +9069,7 @@
       <c r="E303" s="4"/>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -9081,24 +9081,20 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>M2509260041</t>
+          <t>V0019</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>江世隆(新莊區)</t>
+          <t>永豐餘</t>
         </is>
       </c>
       <c r="C304" s="4"/>
-      <c r="D304" s="4" t="inlineStr">
-        <is>
-          <t>0981243133</t>
-        </is>
-      </c>
+      <c r="D304" s="4"/>
       <c r="E304" s="4"/>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -9110,18 +9106,18 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>M2510050010</t>
+          <t>M2509260041</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>江仁堂</t>
+          <t>江世隆(新莊區)</t>
         </is>
       </c>
       <c r="C305" s="4"/>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>0986696777</t>
+          <t>0981243133</t>
         </is>
       </c>
       <c r="E305" s="4"/>
@@ -9139,18 +9135,18 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>M2511220002</t>
+          <t>M2510050010</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>江凱逸</t>
+          <t>江仁堂</t>
         </is>
       </c>
       <c r="C306" s="4"/>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>0912312896</t>
+          <t>0986696777</t>
         </is>
       </c>
       <c r="E306" s="4"/>
@@ -9168,16 +9164,20 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>M2509120001</t>
+          <t>M2511220002</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>江哥</t>
+          <t>江凱逸</t>
         </is>
       </c>
       <c r="C307" s="4"/>
-      <c r="D307" s="4"/>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>0912312896</t>
+        </is>
+      </c>
       <c r="E307" s="4"/>
       <c r="F307" s="4" t="inlineStr">
         <is>
@@ -9193,20 +9193,16 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>M2509280006</t>
+          <t>M2509120001</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>江宏恩</t>
+          <t>江哥</t>
         </is>
       </c>
       <c r="C308" s="4"/>
-      <c r="D308" s="4" t="inlineStr">
-        <is>
-          <t>0988677410</t>
-        </is>
-      </c>
+      <c r="D308" s="4"/>
       <c r="E308" s="4"/>
       <c r="F308" s="4" t="inlineStr">
         <is>
@@ -9222,18 +9218,18 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>M2510160009</t>
+          <t>M2509280006</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>江育哲</t>
+          <t>江宏恩</t>
         </is>
       </c>
       <c r="C309" s="4"/>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>0916586618</t>
+          <t>0988677410</t>
         </is>
       </c>
       <c r="E309" s="4"/>
@@ -9251,18 +9247,18 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>M2511060005</t>
+          <t>M2510160009</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>池沛潔</t>
+          <t>江育哲</t>
         </is>
       </c>
       <c r="C310" s="4"/>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>0963900636</t>
+          <t>0916586618</t>
         </is>
       </c>
       <c r="E310" s="4"/>
@@ -9280,18 +9276,18 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>M2510240003</t>
+          <t>M2511060005</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>汪鈺修</t>
+          <t>池沛潔</t>
         </is>
       </c>
       <c r="C311" s="4"/>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>0971792952</t>
+          <t>0963900636</t>
         </is>
       </c>
       <c r="E311" s="4"/>
@@ -9309,18 +9305,18 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>M2601030003</t>
+          <t>M2510240003</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>沈大哥</t>
+          <t>汪鈺修</t>
         </is>
       </c>
       <c r="C312" s="4"/>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>0978562818</t>
+          <t>0971792952</t>
         </is>
       </c>
       <c r="E312" s="4"/>
@@ -9338,18 +9334,18 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>M2509300002</t>
+          <t>M2601030003</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>沈明鋒</t>
+          <t>沈大哥</t>
         </is>
       </c>
       <c r="C313" s="4"/>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>0908356227</t>
+          <t>0978562818</t>
         </is>
       </c>
       <c r="E313" s="4"/>
@@ -9367,20 +9363,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>V0005</t>
+          <t>M2509300002</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>波蜜企業</t>
+          <t>沈明鋒</t>
         </is>
       </c>
       <c r="C314" s="4"/>
-      <c r="D314" s="4"/>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>0908356227</t>
+        </is>
+      </c>
       <c r="E314" s="4"/>
       <c r="F314" s="4" t="inlineStr">
         <is>
-          <t>批發ㆍ門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -9392,24 +9392,20 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>M2512200004</t>
+          <t>V0005</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>洪丞鍇</t>
+          <t>波蜜企業</t>
         </is>
       </c>
       <c r="C315" s="4"/>
-      <c r="D315" s="4" t="inlineStr">
-        <is>
-          <t>0952119213</t>
-        </is>
-      </c>
+      <c r="D315" s="4"/>
       <c r="E315" s="4"/>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>批發ㆍ門店</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -9421,18 +9417,18 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>M2602270003</t>
+          <t>M2512200004</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>洪儒明</t>
+          <t>洪丞鍇</t>
         </is>
       </c>
       <c r="C316" s="4"/>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>0960097097</t>
+          <t>0952119213</t>
         </is>
       </c>
       <c r="E316" s="4"/>
@@ -9450,18 +9446,18 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>M2509280012</t>
+          <t>M2602270003</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>洪勝忠</t>
+          <t>洪儒明</t>
         </is>
       </c>
       <c r="C317" s="4"/>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>0917962020</t>
+          <t>0960097097</t>
         </is>
       </c>
       <c r="E317" s="4"/>
@@ -9479,18 +9475,18 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>M2510060001</t>
+          <t>M2509280012</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>洪文輝</t>
+          <t>洪勝忠</t>
         </is>
       </c>
       <c r="C318" s="4"/>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>0909183013</t>
+          <t>0917962020</t>
         </is>
       </c>
       <c r="E318" s="4"/>
@@ -9508,18 +9504,18 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>M2510300003</t>
+          <t>M2510060001</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>洪毅平</t>
+          <t>洪文輝</t>
         </is>
       </c>
       <c r="C319" s="4"/>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>0958266132</t>
+          <t>0909183013</t>
         </is>
       </c>
       <c r="E319" s="4"/>
@@ -9537,18 +9533,18 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>M2510240005</t>
+          <t>M2510300003</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>洪浩鈞</t>
+          <t>洪毅平</t>
         </is>
       </c>
       <c r="C320" s="4"/>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>0939553096</t>
+          <t>0958266132</t>
         </is>
       </c>
       <c r="E320" s="4"/>
@@ -9566,18 +9562,18 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>M2509260019</t>
+          <t>M2510240005</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>洪秋麗</t>
+          <t>洪浩鈞</t>
         </is>
       </c>
       <c r="C321" s="4"/>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>0922210223</t>
+          <t>0939553096</t>
         </is>
       </c>
       <c r="E321" s="4"/>
@@ -9595,18 +9591,18 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>M2512140001</t>
+          <t>M2509260019</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>洪翊珊</t>
+          <t>洪秋麗</t>
         </is>
       </c>
       <c r="C322" s="4"/>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>0968884119</t>
+          <t>0922210223</t>
         </is>
       </c>
       <c r="E322" s="4"/>
@@ -9624,22 +9620,18 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>M2510060006</t>
+          <t>M2512140001</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>洪金賢</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr">
-        <is>
-          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
-        </is>
-      </c>
+          <t>洪翊珊</t>
+        </is>
+      </c>
+      <c r="C323" s="4"/>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>0933702515</t>
+          <t>0968884119</t>
         </is>
       </c>
       <c r="E323" s="4"/>
@@ -9657,22 +9649,22 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>M2602040001</t>
+          <t>M2510060006</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>涂宏忠</t>
+          <t>洪金賢</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>高雄市開發路15-3號</t>
+          <t>新竹縣新豐鄉學府街72巷10號3樓之3</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>0963222826</t>
+          <t>0933702515</t>
         </is>
       </c>
       <c r="E324" s="4"/>
@@ -9690,18 +9682,22 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>M2510090009</t>
+          <t>M2602040001</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>游仲強</t>
-        </is>
-      </c>
-      <c r="C325" s="4"/>
+          <t>涂宏忠</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>高雄市開發路15-3號</t>
+        </is>
+      </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>0910671480</t>
+          <t>0963222826</t>
         </is>
       </c>
       <c r="E325" s="4"/>
@@ -9719,18 +9715,18 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>M2602030002</t>
+          <t>M2510090009</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>游凱翔</t>
+          <t>游仲強</t>
         </is>
       </c>
       <c r="C326" s="4"/>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>0978317186</t>
+          <t>0910671480</t>
         </is>
       </c>
       <c r="E326" s="4"/>
@@ -9748,18 +9744,18 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>M2601290001</t>
+          <t>M2602030002</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>游家誠</t>
+          <t>游凱翔</t>
         </is>
       </c>
       <c r="C327" s="4"/>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>0920727320</t>
+          <t>0978317186</t>
         </is>
       </c>
       <c r="E327" s="4"/>
@@ -9777,18 +9773,18 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>M2510090002</t>
+          <t>M2601290001</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>游煥清</t>
+          <t>游家誠</t>
         </is>
       </c>
       <c r="C328" s="4"/>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>0932139705</t>
+          <t>0920727320</t>
         </is>
       </c>
       <c r="E328" s="4"/>
@@ -9806,18 +9802,18 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>M2510100004</t>
+          <t>M2510090002</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>潘文展</t>
+          <t>游煥清</t>
         </is>
       </c>
       <c r="C329" s="4"/>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>0930842995</t>
+          <t>0932139705</t>
         </is>
       </c>
       <c r="E329" s="4"/>
@@ -9835,22 +9831,18 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>M2511230004</t>
+          <t>M2510100004</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>潘正霖(瘋爪子)</t>
-        </is>
-      </c>
-      <c r="C330" s="4" t="inlineStr">
-        <is>
-          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
-        </is>
-      </c>
+          <t>潘文展</t>
+        </is>
+      </c>
+      <c r="C330" s="4"/>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>0983777818</t>
+          <t>0930842995</t>
         </is>
       </c>
       <c r="E330" s="4"/>
@@ -9868,18 +9860,22 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>M2509280010</t>
+          <t>M2511230004</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>潘秀茹</t>
-        </is>
-      </c>
-      <c r="C331" s="4"/>
+          <t>潘正霖(瘋爪子)</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>板橋區廣權路2號(瘋爪子)送前電聯</t>
+        </is>
+      </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>0911900520</t>
+          <t>0983777818</t>
         </is>
       </c>
       <c r="E331" s="4"/>
@@ -9897,18 +9893,18 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>M2601200002</t>
+          <t>M2509280010</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>潘糖糖</t>
+          <t>潘秀茹</t>
         </is>
       </c>
       <c r="C332" s="4"/>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>0976297272</t>
+          <t>0911900520</t>
         </is>
       </c>
       <c r="E332" s="4"/>
@@ -9926,18 +9922,18 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>M2509300016</t>
+          <t>M2601200002</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>潘鳯斌</t>
+          <t>潘糖糖</t>
         </is>
       </c>
       <c r="C333" s="4"/>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>0935502290</t>
+          <t>0976297272</t>
         </is>
       </c>
       <c r="E333" s="4"/>
@@ -9955,16 +9951,20 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>M2509290010</t>
+          <t>M2509300016</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>火牛-批發</t>
+          <t>潘鳯斌</t>
         </is>
       </c>
       <c r="C334" s="4"/>
-      <c r="D334" s="4"/>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>0935502290</t>
+        </is>
+      </c>
       <c r="E334" s="4"/>
       <c r="F334" s="4" t="inlineStr">
         <is>
@@ -9980,12 +9980,12 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>M2512180002</t>
+          <t>M2509290010</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>火牛-老秦</t>
+          <t>火牛-批發</t>
         </is>
       </c>
       <c r="C335" s="4"/>
@@ -10005,12 +10005,12 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>M2512180001</t>
+          <t>M2512180002</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>火牛-阿昌</t>
+          <t>火牛-老秦</t>
         </is>
       </c>
       <c r="C336" s="4"/>
@@ -10030,20 +10030,16 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>M2602140002</t>
+          <t>M2512180001</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>灰灰</t>
+          <t>火牛-阿昌</t>
         </is>
       </c>
       <c r="C337" s="4"/>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>0987829134</t>
-        </is>
-      </c>
+      <c r="D337" s="4"/>
       <c r="E337" s="4"/>
       <c r="F337" s="4" t="inlineStr">
         <is>
@@ -10059,18 +10055,18 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>M2509300011</t>
+          <t>M2602140002</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>熊駿天(大熊)</t>
+          <t>灰灰</t>
         </is>
       </c>
       <c r="C338" s="4"/>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>0933131800</t>
+          <t>0987829134</t>
         </is>
       </c>
       <c r="E338" s="4"/>
@@ -10088,18 +10084,18 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>M2602070001</t>
+          <t>M2509300011</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>王RICK</t>
+          <t>熊駿天(大熊)</t>
         </is>
       </c>
       <c r="C339" s="4"/>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>0930106976</t>
+          <t>0933131800</t>
         </is>
       </c>
       <c r="E339" s="4"/>
@@ -10117,22 +10113,18 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>M2510240006</t>
+          <t>M2602070001</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>王中南</t>
-        </is>
-      </c>
-      <c r="C340" s="4" t="inlineStr">
-        <is>
-          <t>桃園市平鎮區快速路166號3樓</t>
-        </is>
-      </c>
+          <t>王RICK</t>
+        </is>
+      </c>
+      <c r="C340" s="4"/>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>0937124082</t>
+          <t>0930106976</t>
         </is>
       </c>
       <c r="E340" s="4"/>
@@ -10150,18 +10142,22 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>M2601020001</t>
+          <t>M2510240006</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>王仁澤</t>
-        </is>
-      </c>
-      <c r="C341" s="4"/>
+          <t>王中南</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區快速路166號3樓</t>
+        </is>
+      </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>0976503359</t>
+          <t>0937124082</t>
         </is>
       </c>
       <c r="E341" s="4"/>
@@ -10179,18 +10175,18 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>M2603010004</t>
+          <t>M2601020001</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>王又杰</t>
+          <t>王仁澤</t>
         </is>
       </c>
       <c r="C342" s="4"/>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>0909771449</t>
+          <t>0976503359</t>
         </is>
       </c>
       <c r="E342" s="4"/>
@@ -10208,18 +10204,18 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>M2601080001</t>
+          <t>M2603010004</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>王家文</t>
+          <t>王又杰</t>
         </is>
       </c>
       <c r="C343" s="4"/>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>0908176140</t>
+          <t>0909771449</t>
         </is>
       </c>
       <c r="E343" s="4"/>
@@ -10237,18 +10233,18 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>M2602080001</t>
+          <t>M2601080001</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>王巽璋</t>
+          <t>王家文</t>
         </is>
       </c>
       <c r="C344" s="4"/>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>0932943159</t>
+          <t>0908176140</t>
         </is>
       </c>
       <c r="E344" s="4"/>
@@ -10266,18 +10262,18 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>M2512230001</t>
+          <t>M2602080001</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>王志維</t>
+          <t>王巽璋</t>
         </is>
       </c>
       <c r="C345" s="4"/>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>0931262170</t>
+          <t>0932943159</t>
         </is>
       </c>
       <c r="E345" s="4"/>
@@ -10295,18 +10291,18 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>M2511180003</t>
+          <t>M2512230001</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>王明輝</t>
+          <t>王志維</t>
         </is>
       </c>
       <c r="C346" s="4"/>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>0937002585</t>
+          <t>0931262170</t>
         </is>
       </c>
       <c r="E346" s="4"/>
@@ -10324,18 +10320,18 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>M2510140007</t>
+          <t>M2511180003</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>王羿佳</t>
+          <t>王明輝</t>
         </is>
       </c>
       <c r="C347" s="4"/>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>0968831773</t>
+          <t>0937002585</t>
         </is>
       </c>
       <c r="E347" s="4"/>
@@ -10353,22 +10349,18 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>M2509260013</t>
+          <t>M2510140007</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>王舜平</t>
-        </is>
-      </c>
-      <c r="C348" s="4" t="inlineStr">
-        <is>
-          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
-        </is>
-      </c>
+          <t>王羿佳</t>
+        </is>
+      </c>
+      <c r="C348" s="4"/>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>0917215021</t>
+          <t>0968831773</t>
         </is>
       </c>
       <c r="E348" s="4"/>
@@ -10386,18 +10378,22 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>M2601170002</t>
+          <t>M2509260013</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>王閔弘</t>
-        </is>
-      </c>
-      <c r="C349" s="4"/>
+          <t>王舜平</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
+        </is>
+      </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>0931056292</t>
+          <t>0917215021</t>
         </is>
       </c>
       <c r="E349" s="4"/>
@@ -10415,18 +10411,18 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>M2511230003</t>
+          <t>M2601170002</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>王靜芸</t>
+          <t>王閔弘</t>
         </is>
       </c>
       <c r="C350" s="4"/>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>0970224238</t>
+          <t>0931056292</t>
         </is>
       </c>
       <c r="E350" s="4"/>
@@ -10444,18 +10440,18 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>M2510040009</t>
+          <t>M2511230003</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>王駿宏</t>
+          <t>王靜芸</t>
         </is>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>0919336854</t>
+          <t>0970224238</t>
         </is>
       </c>
       <c r="E351" s="4"/>
@@ -10473,18 +10469,18 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>M2601010001</t>
+          <t>M2510040009</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>甘玨瑋</t>
+          <t>王駿宏</t>
         </is>
       </c>
       <c r="C352" s="4"/>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>0987214102</t>
+          <t>0919336854</t>
         </is>
       </c>
       <c r="E352" s="4"/>
@@ -10502,22 +10498,18 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>M2510290002</t>
+          <t>M2601010001</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>生生</t>
-        </is>
-      </c>
-      <c r="C353" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街427號</t>
-        </is>
-      </c>
+          <t>甘玨瑋</t>
+        </is>
+      </c>
+      <c r="C353" s="4"/>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>0919001722</t>
+          <t>0987214102</t>
         </is>
       </c>
       <c r="E353" s="4"/>
@@ -10535,18 +10527,22 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>M2509260050</t>
+          <t>M2510290002</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>甩爪</t>
-        </is>
-      </c>
-      <c r="C354" s="4"/>
+          <t>生生</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街427號</t>
+        </is>
+      </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>0970754804</t>
+          <t>0919001722</t>
         </is>
       </c>
       <c r="E354" s="4"/>
@@ -10564,18 +10560,18 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>M2509270005</t>
+          <t>M2509260050</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>甯偉</t>
+          <t>甩爪</t>
         </is>
       </c>
       <c r="C355" s="4"/>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>0955617290</t>
+          <t>0970754804</t>
         </is>
       </c>
       <c r="E355" s="4"/>
@@ -10593,18 +10589,18 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>M2510240007</t>
+          <t>M2509270005</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>盧其辰</t>
+          <t>甯偉</t>
         </is>
       </c>
       <c r="C356" s="4"/>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>0982119779</t>
+          <t>0955617290</t>
         </is>
       </c>
       <c r="E356" s="4"/>
@@ -10622,18 +10618,18 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>M2604110001</t>
+          <t>M2510240007</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>盧炳宏</t>
+          <t>盧其辰</t>
         </is>
       </c>
       <c r="C357" s="4"/>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>0921062300</t>
+          <t>0982119779</t>
         </is>
       </c>
       <c r="E357" s="4"/>
@@ -10651,20 +10647,24 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>V0013</t>
+          <t>M2604110001</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>真大帥</t>
+          <t>盧炳宏</t>
         </is>
       </c>
       <c r="C358" s="4"/>
-      <c r="D358" s="4"/>
+      <c r="D358" s="4" t="inlineStr">
+        <is>
+          <t>0921062300</t>
+        </is>
+      </c>
       <c r="E358" s="4"/>
       <c r="F358" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G358" s="5" t="inlineStr">
@@ -10676,24 +10676,20 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>M2510310002</t>
+          <t>V0013</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>祁麟</t>
+          <t>真大帥</t>
         </is>
       </c>
       <c r="C359" s="4"/>
-      <c r="D359" s="4" t="inlineStr">
-        <is>
-          <t>0982883101</t>
-        </is>
-      </c>
+      <c r="D359" s="4"/>
       <c r="E359" s="4"/>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -10705,18 +10701,18 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>M2602130001</t>
+          <t>M2510310002</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>祐</t>
+          <t>祁麟</t>
         </is>
       </c>
       <c r="C360" s="4"/>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>0983407890</t>
+          <t>0982883101</t>
         </is>
       </c>
       <c r="E360" s="4"/>
@@ -10734,18 +10730,18 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>M2510050001</t>
+          <t>M2602130001</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>程sir/Ashbur</t>
+          <t>祐</t>
         </is>
       </c>
       <c r="C361" s="4"/>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>0963612395</t>
+          <t>0983407890</t>
         </is>
       </c>
       <c r="E361" s="4"/>
@@ -10763,18 +10759,18 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>M2510300001</t>
+          <t>M2510050001</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>程品勝</t>
+          <t>程sir/Ashbur</t>
         </is>
       </c>
       <c r="C362" s="4"/>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>0913780727</t>
+          <t>0963612395</t>
         </is>
       </c>
       <c r="E362" s="4"/>
@@ -10792,18 +10788,18 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>M2601270002</t>
+          <t>M2510300001</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>程建智</t>
+          <t>程品勝</t>
         </is>
       </c>
       <c r="C363" s="4"/>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>0988919027</t>
+          <t>0913780727</t>
         </is>
       </c>
       <c r="E363" s="4"/>
@@ -10821,18 +10817,18 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>M2603120004</t>
+          <t>M2601270002</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>程郁勛</t>
+          <t>程建智</t>
         </is>
       </c>
       <c r="C364" s="4"/>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>0955671407</t>
+          <t>0988919027</t>
         </is>
       </c>
       <c r="E364" s="4"/>
@@ -10850,22 +10846,18 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>M2509160001</t>
+          <t>M2603120004</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>穆莉茹</t>
-        </is>
-      </c>
-      <c r="C365" s="4" t="inlineStr">
-        <is>
-          <t>桃園平鎮區上海路169號</t>
-        </is>
-      </c>
+          <t>程郁勛</t>
+        </is>
+      </c>
+      <c r="C365" s="4"/>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>0955777312</t>
+          <t>0955671407</t>
         </is>
       </c>
       <c r="E365" s="4"/>
@@ -10883,18 +10875,22 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>M2511160003</t>
+          <t>M2509160001</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>簡士傑</t>
-        </is>
-      </c>
-      <c r="C366" s="4"/>
+          <t>穆莉茹</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>桃園平鎮區上海路169號</t>
+        </is>
+      </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>0963817398</t>
+          <t>0955777312</t>
         </is>
       </c>
       <c r="E366" s="4"/>
@@ -10912,18 +10908,18 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>M2509300013</t>
+          <t>M2511160003</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>簡子偉</t>
+          <t>簡士傑</t>
         </is>
       </c>
       <c r="C367" s="4"/>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>0955462926</t>
+          <t>0963817398</t>
         </is>
       </c>
       <c r="E367" s="4"/>
@@ -10941,18 +10937,18 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>M2602280002</t>
+          <t>M2509300013</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>簡子洋</t>
+          <t>簡子偉</t>
         </is>
       </c>
       <c r="C368" s="4"/>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>0933921933</t>
+          <t>0955462926</t>
         </is>
       </c>
       <c r="E368" s="4"/>
@@ -10970,18 +10966,18 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>M2510040003</t>
+          <t>M2602280002</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>簡小琪</t>
+          <t>簡子洋</t>
         </is>
       </c>
       <c r="C369" s="4"/>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>0930033829</t>
+          <t>0933921933</t>
         </is>
       </c>
       <c r="E369" s="4"/>
@@ -10999,18 +10995,18 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>M2510260002</t>
+          <t>M2510040003</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>簡揚城</t>
+          <t>簡小琪</t>
         </is>
       </c>
       <c r="C370" s="4"/>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>0913153353</t>
+          <t>0930033829</t>
         </is>
       </c>
       <c r="E370" s="4"/>
@@ -11028,18 +11024,18 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>M2509300001</t>
+          <t>M2510260002</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>簡瑋成</t>
+          <t>簡揚城</t>
         </is>
       </c>
       <c r="C371" s="4"/>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>0936389969</t>
+          <t>0913153353</t>
         </is>
       </c>
       <c r="E371" s="4"/>
@@ -11057,18 +11053,18 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>M2509290020</t>
+          <t>M2509300001</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>簡茂州</t>
+          <t>簡瑋成</t>
         </is>
       </c>
       <c r="C372" s="4"/>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>0985217379</t>
+          <t>0936389969</t>
         </is>
       </c>
       <c r="E372" s="4"/>
@@ -11086,18 +11082,18 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>M2512130001</t>
+          <t>M2509290020</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>紀彥銘</t>
+          <t>簡茂州</t>
         </is>
       </c>
       <c r="C373" s="4"/>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>0988752337</t>
+          <t>0985217379</t>
         </is>
       </c>
       <c r="E373" s="4"/>
@@ -11115,20 +11111,24 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>V0001</t>
+          <t>M2512130001</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>統有企業</t>
+          <t>紀彥銘</t>
         </is>
       </c>
       <c r="C374" s="4"/>
-      <c r="D374" s="4"/>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>0988752337</t>
+        </is>
+      </c>
       <c r="E374" s="4"/>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G374" s="5" t="inlineStr">
@@ -11140,24 +11140,20 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>M2509280008</t>
+          <t>V0001</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>維克斯</t>
+          <t>統有企業</t>
         </is>
       </c>
       <c r="C375" s="4"/>
-      <c r="D375" s="4" t="inlineStr">
-        <is>
-          <t>0917771787</t>
-        </is>
-      </c>
+      <c r="D375" s="4"/>
       <c r="E375" s="4"/>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G375" s="5" t="inlineStr">
@@ -11169,18 +11165,18 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>M2510170002</t>
+          <t>M2509280008</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>練鎮宇</t>
+          <t>維克斯</t>
         </is>
       </c>
       <c r="C376" s="4"/>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>0952288706</t>
+          <t>0917771787</t>
         </is>
       </c>
       <c r="E376" s="4"/>
@@ -11198,22 +11194,18 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>M2602220003</t>
+          <t>M2510170002</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>羅丁一夫</t>
-        </is>
-      </c>
-      <c r="C377" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
-        </is>
-      </c>
+          <t>練鎮宇</t>
+        </is>
+      </c>
+      <c r="C377" s="4"/>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>0919339614</t>
+          <t>0952288706</t>
         </is>
       </c>
       <c r="E377" s="4"/>
@@ -11231,18 +11223,22 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>M2510180002</t>
+          <t>M2602220003</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>羅元隆</t>
-        </is>
-      </c>
-      <c r="C378" s="4"/>
+          <t>羅丁一夫</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
+        </is>
+      </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>0975866635</t>
+          <t>0919339614</t>
         </is>
       </c>
       <c r="E378" s="4"/>
@@ -11260,25 +11256,21 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>M2510090003</t>
+          <t>M2510180002</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>羅嘉銘</t>
+          <t>羅元隆</t>
         </is>
       </c>
       <c r="C379" s="4"/>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>0928093385</t>
-        </is>
-      </c>
-      <c r="E379" s="4" t="inlineStr">
-        <is>
-          <t>0985866052</t>
-        </is>
-      </c>
+          <t>0975866635</t>
+        </is>
+      </c>
+      <c r="E379" s="4"/>
       <c r="F379" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11293,21 +11285,25 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>M2602240001</t>
+          <t>M2510090003</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>羅浩中</t>
+          <t>羅嘉銘</t>
         </is>
       </c>
       <c r="C380" s="4"/>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>0970905092</t>
-        </is>
-      </c>
-      <c r="E380" s="4"/>
+          <t>0928093385</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>0985866052</t>
+        </is>
+      </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11322,18 +11318,18 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>M2511060003</t>
+          <t>M2602240001</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>翁名勳</t>
+          <t>羅浩中</t>
         </is>
       </c>
       <c r="C381" s="4"/>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>0955083317</t>
+          <t>0970905092</t>
         </is>
       </c>
       <c r="E381" s="4"/>
@@ -11351,18 +11347,18 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>M2509260057</t>
+          <t>M2511060003</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>翁國昌</t>
+          <t>翁名勳</t>
         </is>
       </c>
       <c r="C382" s="4"/>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>0918718772</t>
+          <t>0955083317</t>
         </is>
       </c>
       <c r="E382" s="4"/>
@@ -11380,22 +11376,18 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>M2511290001</t>
+          <t>M2509260057</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>翁國祥</t>
-        </is>
-      </c>
-      <c r="C383" s="4" t="inlineStr">
-        <is>
-          <t>新北新莊中信街65號1樓賣菜攤</t>
-        </is>
-      </c>
+          <t>翁國昌</t>
+        </is>
+      </c>
+      <c r="C383" s="4"/>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>0983900052</t>
+          <t>0918718772</t>
         </is>
       </c>
       <c r="E383" s="4"/>
@@ -11413,22 +11405,22 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>M2510010009</t>
+          <t>M2511290001</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩</t>
+          <t>翁國祥</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>未決定</t>
+          <t>新北新莊中信街65號1樓賣菜攤</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>0972757015</t>
+          <t>0983900052</t>
         </is>
       </c>
       <c r="E384" s="4"/>
@@ -11446,53 +11438,53 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
+          <t>M2510010009</t>
+        </is>
+      </c>
+      <c r="B385" s="4" t="inlineStr">
+        <is>
+          <t>翁敬恩</t>
+        </is>
+      </c>
+      <c r="C385" s="4" t="inlineStr">
+        <is>
+          <t>未決定</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>0972757015</t>
+        </is>
+      </c>
+      <c r="E385" s="4"/>
+      <c r="F385" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G385" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="4" t="inlineStr">
+        <is>
           <t>M2510010009-4</t>
         </is>
       </c>
-      <c r="B385" s="4" t="inlineStr">
+      <c r="B386" s="4" t="inlineStr">
         <is>
           <t>翁敬恩-文山</t>
         </is>
       </c>
-      <c r="C385" s="6" t="inlineStr">
+      <c r="C386" s="6" t="inlineStr">
         <is>
           <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
 收件聯絡電話:0937462412</t>
         </is>
       </c>
-      <c r="D385" s="4" t="inlineStr">
-        <is>
-          <t>0972757015</t>
-        </is>
-      </c>
-      <c r="E385" s="4"/>
-      <c r="F385" s="4" t="inlineStr">
-        <is>
-          <t>批發</t>
-        </is>
-      </c>
-      <c r="G385" s="5" t="inlineStr">
-        <is>
-          <t>附件管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="4" t="inlineStr">
-        <is>
-          <t>M2510010009-2</t>
-        </is>
-      </c>
-      <c r="B386" s="4" t="inlineStr">
-        <is>
-          <t>翁敬恩-樂華</t>
-        </is>
-      </c>
-      <c r="C386" s="4" t="inlineStr">
-        <is>
-          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
-        </is>
-      </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
           <t>0972757015</t>
@@ -11513,17 +11505,17 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-3</t>
+          <t>M2510010009-2</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-永和</t>
+          <t>翁敬恩-樂華</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
+          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -11546,22 +11538,22 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-1</t>
+          <t>M2510010009-3</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-饒河</t>
+          <t>翁敬恩-永和</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>0975953978</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E388" s="4"/>
@@ -11579,18 +11571,22 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>M2510140004</t>
+          <t>M2510010009-1</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>翁漢忠</t>
-        </is>
-      </c>
-      <c r="C389" s="4"/>
+          <t>翁敬恩-饒河</t>
+        </is>
+      </c>
+      <c r="C389" s="4" t="inlineStr">
+        <is>
+          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
+        </is>
+      </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>0916150750</t>
+          <t>0975953978</t>
         </is>
       </c>
       <c r="E389" s="4"/>
@@ -11608,18 +11604,18 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>M2509260037</t>
+          <t>M2510140004</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>翁翌禎</t>
+          <t>翁漢忠</t>
         </is>
       </c>
       <c r="C390" s="4"/>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>0902308293</t>
+          <t>0916150750</t>
         </is>
       </c>
       <c r="E390" s="4"/>
@@ -11637,18 +11633,18 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>M2509280002</t>
+          <t>M2509260037</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>聶大中</t>
+          <t>翁翌禎</t>
         </is>
       </c>
       <c r="C391" s="4"/>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>0955059148</t>
+          <t>0902308293</t>
         </is>
       </c>
       <c r="E391" s="4"/>
@@ -11666,18 +11662,18 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2510220001</t>
+          <t>M2509280002</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>胡HU</t>
+          <t>聶大中</t>
         </is>
       </c>
       <c r="C392" s="4"/>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>0988603554</t>
+          <t>0955059148</t>
         </is>
       </c>
       <c r="E392" s="4"/>
@@ -11695,18 +11691,18 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>M2510100011</t>
+          <t>M2510220001</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>胡凱傑</t>
+          <t>胡HU</t>
         </is>
       </c>
       <c r="C393" s="4"/>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>0955888840</t>
+          <t>0988603554</t>
         </is>
       </c>
       <c r="E393" s="4"/>
@@ -11724,18 +11720,18 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>M2510090005</t>
+          <t>M2510100011</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>胡家榮</t>
+          <t>胡凱傑</t>
         </is>
       </c>
       <c r="C394" s="4"/>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>0933059025</t>
+          <t>0955888840</t>
         </is>
       </c>
       <c r="E394" s="4"/>
@@ -11753,18 +11749,18 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>M2511150001</t>
+          <t>M2510090005</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>胡家銘</t>
+          <t>胡家榮</t>
         </is>
       </c>
       <c r="C395" s="4"/>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>0986362263</t>
+          <t>0933059025</t>
         </is>
       </c>
       <c r="E395" s="4"/>
@@ -11782,18 +11778,18 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>M2511290003</t>
+          <t>M2511150001</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>胡峻強</t>
+          <t>胡家銘</t>
         </is>
       </c>
       <c r="C396" s="4"/>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>0953088041</t>
+          <t>0986362263</t>
         </is>
       </c>
       <c r="E396" s="4"/>
@@ -11811,18 +11807,18 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>M2603010001</t>
+          <t>M2511290003</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>胡辰煜</t>
+          <t>胡峻強</t>
         </is>
       </c>
       <c r="C397" s="4"/>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>0963903685</t>
+          <t>0953088041</t>
         </is>
       </c>
       <c r="E397" s="4"/>
@@ -11840,18 +11836,18 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>M2510040002</t>
+          <t>M2603010001</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>胡辰軒</t>
+          <t>胡辰煜</t>
         </is>
       </c>
       <c r="C398" s="4"/>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>0972094622</t>
+          <t>0963903685</t>
         </is>
       </c>
       <c r="E398" s="4"/>
@@ -11869,18 +11865,18 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>M2602280001</t>
+          <t>M2510040002</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>胡閎翔</t>
+          <t>胡辰軒</t>
         </is>
       </c>
       <c r="C399" s="4"/>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>0970556309</t>
+          <t>0972094622</t>
         </is>
       </c>
       <c r="E399" s="4"/>
@@ -11898,18 +11894,18 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>M2511290002</t>
+          <t>M2602280001</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>舒老闆</t>
+          <t>胡閎翔</t>
         </is>
       </c>
       <c r="C400" s="4"/>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>0979788818</t>
+          <t>0970556309</t>
         </is>
       </c>
       <c r="E400" s="4"/>
@@ -11927,19 +11923,15 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-6</t>
+          <t>M2511290002</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-冬冬/虎林</t>
-        </is>
-      </c>
-      <c r="C401" s="4" t="inlineStr">
-        <is>
-          <t>台北市信義區虎林街164巷60弄19號</t>
-        </is>
-      </c>
+          <t>舒老闆</t>
+        </is>
+      </c>
+      <c r="C401" s="4"/>
       <c r="D401" s="4" t="inlineStr">
         <is>
           <t>0979788818</t>
@@ -11960,17 +11952,17 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-8</t>
+          <t>M2511290002-6</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德17號</t>
+          <t>舒老闆-冬冬/虎林</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區八德路三段155巷17號</t>
+          <t>台北市信義區虎林街164巷60弄19號</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
@@ -11993,17 +11985,17 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-2</t>
+          <t>M2511290002-8</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/八德46號</t>
+          <t>舒老闆-夾鬥陣/八德17號</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>台北市松山區八德路三段12巷51弄46號</t>
+          <t>台北市松山區八德路三段155巷17號</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -12026,17 +12018,17 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-7</t>
+          <t>M2511290002-2</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-夾鬥陣/臥龍</t>
+          <t>舒老闆-夾鬥陣/八德46號</t>
         </is>
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>台北市大安區臥龍街254號</t>
+          <t>台北市松山區八德路三段12巷51弄46號</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
@@ -12059,17 +12051,17 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-4</t>
+          <t>M2511290002-7</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/中正</t>
+          <t>舒老闆-夾鬥陣/臥龍</t>
         </is>
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路14號</t>
+          <t>台北市大安區臥龍街254號</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -12092,17 +12084,17 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-5</t>
+          <t>M2511290002-4</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/吳興</t>
+          <t>舒老闆-寧寧/中正</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>台北市信義區吳興街342號</t>
+          <t>新北市永和區中正路14號</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
@@ -12125,17 +12117,17 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-3</t>
+          <t>M2511290002-5</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/智光</t>
+          <t>舒老闆-寧寧/吳興</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區智光街98號</t>
+          <t>台北市信義區吳興街342號</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
@@ -12158,17 +12150,17 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>M2511290002-1</t>
+          <t>M2511290002-3</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>舒老闆-寧寧/秀山</t>
+          <t>舒老闆-寧寧/智光</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+          <t>新北市永和區智光街98號</t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
@@ -12191,18 +12183,22 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>M2510140002</t>
+          <t>M2511290002-1</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>范姜敏中</t>
-        </is>
-      </c>
-      <c r="C409" s="4"/>
+          <t>舒老闆-寧寧/秀山</t>
+        </is>
+      </c>
+      <c r="C409" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區秀朗路三段10巷37弄14號</t>
+        </is>
+      </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>0937464692</t>
+          <t>0979788818</t>
         </is>
       </c>
       <c r="E409" s="4"/>
@@ -12220,18 +12216,18 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>M2510140003</t>
+          <t>M2510140002</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>范姜群成</t>
+          <t>范姜敏中</t>
         </is>
       </c>
       <c r="C410" s="4"/>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>0920565234</t>
+          <t>0937464692</t>
         </is>
       </c>
       <c r="E410" s="4"/>
@@ -12249,22 +12245,18 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>M2511300003</t>
+          <t>M2510140003</t>
         </is>
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>莊正當</t>
-        </is>
-      </c>
-      <c r="C411" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區建安街27號3樓</t>
-        </is>
-      </c>
+          <t>范姜群成</t>
+        </is>
+      </c>
+      <c r="C411" s="4"/>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>0983337218</t>
+          <t>0920565234</t>
         </is>
       </c>
       <c r="E411" s="4"/>
@@ -12282,22 +12274,22 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>M2510270004</t>
+          <t>M2511300003</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>莊淑玲</t>
+          <t>莊正當</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>新北市新莊區五工三路78巷36號</t>
+          <t>新北市新莊區建安街27號3樓</t>
         </is>
       </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>0922277383</t>
+          <t>0983337218</t>
         </is>
       </c>
       <c r="E412" s="4"/>
@@ -12315,18 +12307,22 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>M2510190002</t>
+          <t>M2510270004</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>莊耿華</t>
-        </is>
-      </c>
-      <c r="C413" s="4"/>
+          <t>莊淑玲</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工三路78巷36號</t>
+        </is>
+      </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>0938600334</t>
+          <t>0922277383</t>
         </is>
       </c>
       <c r="E413" s="4"/>
@@ -12344,18 +12340,18 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>M2509260005</t>
+          <t>M2510190002</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>莊莊</t>
+          <t>莊耿華</t>
         </is>
       </c>
       <c r="C414" s="4"/>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>0955985557</t>
+          <t>0938600334</t>
         </is>
       </c>
       <c r="E414" s="4"/>
@@ -12373,18 +12369,18 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>M2510100007</t>
+          <t>M2509260005</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>莊閔丞</t>
+          <t>莊莊</t>
         </is>
       </c>
       <c r="C415" s="4"/>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>0963320370</t>
+          <t>0955985557</t>
         </is>
       </c>
       <c r="E415" s="4"/>
@@ -12402,18 +12398,18 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>M2602240002</t>
+          <t>M2510100007</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>萬宗霖</t>
+          <t>莊閔丞</t>
         </is>
       </c>
       <c r="C416" s="4"/>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>0977082365</t>
+          <t>0963320370</t>
         </is>
       </c>
       <c r="E416" s="4"/>
@@ -12431,18 +12427,18 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>M2510160001</t>
+          <t>M2602240002</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>葉力瑋</t>
+          <t>萬宗霖</t>
         </is>
       </c>
       <c r="C417" s="4"/>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>0979611911</t>
+          <t>0977082365</t>
         </is>
       </c>
       <c r="E417" s="4"/>
@@ -12460,18 +12456,18 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>M2510030002</t>
+          <t>M2510160001</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>葉家睿</t>
+          <t>葉力瑋</t>
         </is>
       </c>
       <c r="C418" s="4"/>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>0928112227</t>
+          <t>0979611911</t>
         </is>
       </c>
       <c r="E418" s="4"/>
@@ -12489,18 +12485,18 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>M2511050003</t>
+          <t>M2510030002</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>葉庭綸</t>
+          <t>葉家睿</t>
         </is>
       </c>
       <c r="C419" s="4"/>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>0966638685</t>
+          <t>0928112227</t>
         </is>
       </c>
       <c r="E419" s="4"/>
@@ -12518,18 +12514,18 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>M2510180001</t>
+          <t>M2511050003</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>葉建財</t>
+          <t>葉庭綸</t>
         </is>
       </c>
       <c r="C420" s="4"/>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>0989713349</t>
+          <t>0966638685</t>
         </is>
       </c>
       <c r="E420" s="4"/>
@@ -12547,18 +12543,18 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>M2510150001</t>
+          <t>M2510180001</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>葉彥均</t>
+          <t>葉建財</t>
         </is>
       </c>
       <c r="C421" s="4"/>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>0921436111</t>
+          <t>0989713349</t>
         </is>
       </c>
       <c r="E421" s="4"/>
@@ -12576,18 +12572,18 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>M2601220001</t>
+          <t>M2510150001</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>葉方奕</t>
+          <t>葉彥均</t>
         </is>
       </c>
       <c r="C422" s="4"/>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>0918386488</t>
+          <t>0921436111</t>
         </is>
       </c>
       <c r="E422" s="4"/>
@@ -12605,18 +12601,18 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>M2510260005</t>
+          <t>M2601220001</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>葉祈賢</t>
+          <t>葉方奕</t>
         </is>
       </c>
       <c r="C423" s="4"/>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>0955313212</t>
+          <t>0918386488</t>
         </is>
       </c>
       <c r="E423" s="4"/>
@@ -12634,18 +12630,18 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>M2509290012</t>
+          <t>M2510260005</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>葉維霆</t>
+          <t>葉祈賢</t>
         </is>
       </c>
       <c r="C424" s="4"/>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>0905120835</t>
+          <t>0955313212</t>
         </is>
       </c>
       <c r="E424" s="4"/>
@@ -12663,18 +12659,18 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>M2603050001</t>
+          <t>M2509290012</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>蔡仲凱</t>
+          <t>葉維霆</t>
         </is>
       </c>
       <c r="C425" s="4"/>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>0910733748</t>
+          <t>0905120835</t>
         </is>
       </c>
       <c r="E425" s="4"/>
@@ -12692,18 +12688,18 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>M2511080009</t>
+          <t>M2603050001</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>蔡伯鼎</t>
+          <t>蔡仲凱</t>
         </is>
       </c>
       <c r="C426" s="4"/>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>0933842593</t>
+          <t>0910733748</t>
         </is>
       </c>
       <c r="E426" s="4"/>
@@ -12721,18 +12717,18 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>M2512100001</t>
+          <t>M2511080009</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>蔡其騰</t>
+          <t>蔡伯鼎</t>
         </is>
       </c>
       <c r="C427" s="4"/>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>0988556732</t>
+          <t>0933842593</t>
         </is>
       </c>
       <c r="E427" s="4"/>
@@ -12750,22 +12746,18 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>M2603220001</t>
+          <t>M2512100001</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>蔡嘉章</t>
-        </is>
-      </c>
-      <c r="C428" s="4" t="inlineStr">
-        <is>
-          <t>樹林區太平路150巷8號娃娃機</t>
-        </is>
-      </c>
+          <t>蔡其騰</t>
+        </is>
+      </c>
+      <c r="C428" s="4"/>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>0973658657</t>
+          <t>0988556732</t>
         </is>
       </c>
       <c r="E428" s="4"/>
@@ -12783,18 +12775,22 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>M2509280001</t>
+          <t>M2603220001</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>蔡康志</t>
-        </is>
-      </c>
-      <c r="C429" s="4"/>
+          <t>蔡嘉章</t>
+        </is>
+      </c>
+      <c r="C429" s="4" t="inlineStr">
+        <is>
+          <t>樹林區太平路150巷8號娃娃機</t>
+        </is>
+      </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>0933942089</t>
+          <t>0973658657</t>
         </is>
       </c>
       <c r="E429" s="4"/>
@@ -12812,18 +12808,18 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>M2509260052</t>
+          <t>M2509280001</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>蔡志海</t>
+          <t>蔡康志</t>
         </is>
       </c>
       <c r="C430" s="4"/>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>0926616521</t>
+          <t>0933942089</t>
         </is>
       </c>
       <c r="E430" s="4"/>
@@ -12841,18 +12837,18 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>M2602120003</t>
+          <t>M2509260052</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>蔡承勳</t>
+          <t>蔡志海</t>
         </is>
       </c>
       <c r="C431" s="4"/>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>0979975919</t>
+          <t>0926616521</t>
         </is>
       </c>
       <c r="E431" s="4"/>
@@ -12870,18 +12866,18 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>M2509290002</t>
+          <t>M2602120003</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>蔡振元</t>
+          <t>蔡承勳</t>
         </is>
       </c>
       <c r="C432" s="4"/>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>0908590858</t>
+          <t>0979975919</t>
         </is>
       </c>
       <c r="E432" s="4"/>
@@ -12899,18 +12895,18 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>M2601090001</t>
+          <t>M2509290002</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>蔡昌翔</t>
+          <t>蔡振元</t>
         </is>
       </c>
       <c r="C433" s="4"/>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>0973324888</t>
+          <t>0908590858</t>
         </is>
       </c>
       <c r="E433" s="4"/>
@@ -12928,22 +12924,18 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>M2509260011</t>
+          <t>M2601090001</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>蔡智全</t>
-        </is>
-      </c>
-      <c r="C434" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區雙園街110號1樓</t>
-        </is>
-      </c>
+          <t>蔡昌翔</t>
+        </is>
+      </c>
+      <c r="C434" s="4"/>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>0930167280</t>
+          <t>0973324888</t>
         </is>
       </c>
       <c r="E434" s="4"/>
@@ -12961,22 +12953,22 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>M2509260049</t>
+          <t>M2509260011</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>蔡瀚霆</t>
+          <t>蔡智全</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區保平路207號</t>
+          <t>台北市萬華區雙園街110號1樓</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>0932014776</t>
+          <t>0930167280</t>
         </is>
       </c>
       <c r="E435" s="4"/>
@@ -12994,18 +12986,22 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>M2510010007</t>
+          <t>M2509260049</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>蔡秉橋</t>
-        </is>
-      </c>
-      <c r="C436" s="4"/>
+          <t>蔡瀚霆</t>
+        </is>
+      </c>
+      <c r="C436" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區保平路207號</t>
+        </is>
+      </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>0987000184</t>
+          <t>0932014776</t>
         </is>
       </c>
       <c r="E436" s="4"/>
@@ -13023,18 +13019,18 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>M2509270009</t>
+          <t>M2510010007</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>蔡育昇</t>
+          <t>蔡秉橋</t>
         </is>
       </c>
       <c r="C437" s="4"/>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>0918058903</t>
+          <t>0987000184</t>
         </is>
       </c>
       <c r="E437" s="4"/>
@@ -13052,18 +13048,18 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>M2603180001</t>
+          <t>M2509270009</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>蔡貞瑜</t>
+          <t>蔡育昇</t>
         </is>
       </c>
       <c r="C438" s="4"/>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>0917372131</t>
+          <t>0918058903</t>
         </is>
       </c>
       <c r="E438" s="4"/>
@@ -13081,18 +13077,18 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>M2510070001</t>
+          <t>M2603180001</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>蔡辰旻</t>
+          <t>蔡貞瑜</t>
         </is>
       </c>
       <c r="C439" s="4"/>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>0982621245</t>
+          <t>0917372131</t>
         </is>
       </c>
       <c r="E439" s="4"/>
@@ -13110,7 +13106,7 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>M2602010003</t>
+          <t>M2510070001</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
@@ -13121,7 +13117,7 @@
       <c r="C440" s="4"/>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>0903162818</t>
+          <t>0982621245</t>
         </is>
       </c>
       <c r="E440" s="4"/>
@@ -13139,18 +13135,18 @@
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>M2511270001</t>
+          <t>M2602010003</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>蔡進盛</t>
+          <t>蔡辰旻</t>
         </is>
       </c>
       <c r="C441" s="4"/>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>0989387966</t>
+          <t>0903162818</t>
         </is>
       </c>
       <c r="E441" s="4"/>
@@ -13168,18 +13164,18 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>M2511030001</t>
+          <t>M2511270001</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>蔡鳳來</t>
+          <t>蔡進盛</t>
         </is>
       </c>
       <c r="C442" s="4"/>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>0963550931</t>
+          <t>0989387966</t>
         </is>
       </c>
       <c r="E442" s="4"/>
@@ -13197,18 +13193,18 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>M2509270016</t>
+          <t>M2511030001</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>蕭仲安</t>
+          <t>蔡鳳來</t>
         </is>
       </c>
       <c r="C443" s="4"/>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>0930601899</t>
+          <t>0963550931</t>
         </is>
       </c>
       <c r="E443" s="4"/>
@@ -13226,18 +13222,18 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>M2509270017</t>
+          <t>M2509270016</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>蕭又瑋</t>
+          <t>蕭仲安</t>
         </is>
       </c>
       <c r="C444" s="4"/>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>0922675798</t>
+          <t>0930601899</t>
         </is>
       </c>
       <c r="E444" s="4"/>
@@ -13255,18 +13251,18 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>M2509280009</t>
+          <t>M2509270017</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>蕭宇傑</t>
+          <t>蕭又瑋</t>
         </is>
       </c>
       <c r="C445" s="4"/>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>0989977822</t>
+          <t>0922675798</t>
         </is>
       </c>
       <c r="E445" s="4"/>
@@ -13284,18 +13280,18 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>M2510190006</t>
+          <t>M2509280009</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>蕭毓</t>
+          <t>蕭宇傑</t>
         </is>
       </c>
       <c r="C446" s="4"/>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>0975199046</t>
+          <t>0989977822</t>
         </is>
       </c>
       <c r="E446" s="4"/>
@@ -13313,22 +13309,18 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>M2510090006</t>
+          <t>M2510190006</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>蕭燁鴻</t>
-        </is>
-      </c>
-      <c r="C447" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區金龍路183號1樓</t>
-        </is>
-      </c>
+          <t>蕭毓</t>
+        </is>
+      </c>
+      <c r="C447" s="4"/>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>0917882269</t>
+          <t>0975199046</t>
         </is>
       </c>
       <c r="E447" s="4"/>
@@ -13346,18 +13338,22 @@
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>M2510160008</t>
+          <t>M2510090006</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>蕭韻文</t>
-        </is>
-      </c>
-      <c r="C448" s="4"/>
+          <t>蕭燁鴻</t>
+        </is>
+      </c>
+      <c r="C448" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區金龍路183號1樓</t>
+        </is>
+      </c>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>0911297473</t>
+          <t>0917882269</t>
         </is>
       </c>
       <c r="E448" s="4"/>
@@ -13375,18 +13371,18 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>M2509300014</t>
+          <t>M2510160008</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>藍駿偉</t>
+          <t>蕭韻文</t>
         </is>
       </c>
       <c r="C449" s="4"/>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>0936152586</t>
+          <t>0911297473</t>
         </is>
       </c>
       <c r="E449" s="4"/>
@@ -13404,18 +13400,18 @@
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>M2511080007</t>
+          <t>M2509300014</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>蘇嘉蓉</t>
+          <t>藍駿偉</t>
         </is>
       </c>
       <c r="C450" s="4"/>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>0937074336</t>
+          <t>0936152586</t>
         </is>
       </c>
       <c r="E450" s="4"/>
@@ -13433,18 +13429,18 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>M2511060002</t>
+          <t>M2511080007</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>蘇國貿</t>
+          <t>蘇嘉蓉</t>
         </is>
       </c>
       <c r="C451" s="4"/>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>0922250285</t>
+          <t>0937074336</t>
         </is>
       </c>
       <c r="E451" s="4"/>
@@ -13462,18 +13458,18 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>M2511280004</t>
+          <t>M2511060002</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>蘇家明</t>
+          <t>蘇國貿</t>
         </is>
       </c>
       <c r="C452" s="4"/>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>0916836765</t>
+          <t>0922250285</t>
         </is>
       </c>
       <c r="E452" s="4"/>
@@ -13491,18 +13487,18 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>M2510300002</t>
+          <t>M2511280004</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>蘇小好</t>
+          <t>蘇家明</t>
         </is>
       </c>
       <c r="C453" s="4"/>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>0981870981</t>
+          <t>0916836765</t>
         </is>
       </c>
       <c r="E453" s="4"/>
@@ -13520,18 +13516,18 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>M2509260021</t>
+          <t>M2510300002</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>蘇彥彰</t>
+          <t>蘇小好</t>
         </is>
       </c>
       <c r="C454" s="4"/>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>0983060026</t>
+          <t>0981870981</t>
         </is>
       </c>
       <c r="E454" s="4"/>
@@ -13549,22 +13545,18 @@
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>M2510240001</t>
+          <t>M2509260021</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>蘇志勇</t>
-        </is>
-      </c>
-      <c r="C455" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
-        </is>
-      </c>
+          <t>蘇彥彰</t>
+        </is>
+      </c>
+      <c r="C455" s="4"/>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>0910051586</t>
+          <t>0983060026</t>
         </is>
       </c>
       <c r="E455" s="4"/>
@@ -13582,18 +13574,22 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>M2602150002</t>
+          <t>M2510240001</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>蘇昱銘</t>
-        </is>
-      </c>
-      <c r="C456" s="4"/>
+          <t>蘇志勇</t>
+        </is>
+      </c>
+      <c r="C456" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中山區中山一路117號1樓（胖喵喵夾娃娃機店）</t>
+        </is>
+      </c>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>0916324119</t>
+          <t>0910051586</t>
         </is>
       </c>
       <c r="E456" s="4"/>
@@ -13611,18 +13607,18 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>M2510050003</t>
+          <t>M2602150002</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>蘇睿慶</t>
+          <t>蘇昱銘</t>
         </is>
       </c>
       <c r="C457" s="4"/>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>0937766339</t>
+          <t>0916324119</t>
         </is>
       </c>
       <c r="E457" s="4"/>
@@ -13640,18 +13636,18 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>M2601180001</t>
+          <t>M2510050003</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>蠟筆</t>
+          <t>蘇睿慶</t>
         </is>
       </c>
       <c r="C458" s="4"/>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>0976321321</t>
+          <t>0937766339</t>
         </is>
       </c>
       <c r="E458" s="4"/>
@@ -13669,18 +13665,18 @@
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>M2512160002</t>
+          <t>M2601180001</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>褚朕誠</t>
+          <t>蠟筆</t>
         </is>
       </c>
       <c r="C459" s="4"/>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>0972217495</t>
+          <t>0976321321</t>
         </is>
       </c>
       <c r="E459" s="4"/>
@@ -13698,18 +13694,18 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>M2512200002</t>
+          <t>M2512160002</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>褚銘漢</t>
+          <t>褚朕誠</t>
         </is>
       </c>
       <c r="C460" s="4"/>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>0925886065</t>
+          <t>0972217495</t>
         </is>
       </c>
       <c r="E460" s="4"/>
@@ -13727,18 +13723,18 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>M2512170002</t>
+          <t>M2512200002</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>許俊鴻</t>
+          <t>褚銘漢</t>
         </is>
       </c>
       <c r="C461" s="4"/>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>0973630391</t>
+          <t>0925886065</t>
         </is>
       </c>
       <c r="E461" s="4"/>
@@ -13756,18 +13752,18 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>M2510050013</t>
+          <t>M2512170002</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>許凱傑</t>
+          <t>許俊鴻</t>
         </is>
       </c>
       <c r="C462" s="4"/>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>0955306971</t>
+          <t>0973630391</t>
         </is>
       </c>
       <c r="E462" s="4"/>
@@ -13785,18 +13781,18 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>M2511110001</t>
+          <t>M2510050013</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>許哲豪</t>
+          <t>許凱傑</t>
         </is>
       </c>
       <c r="C463" s="4"/>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>0985191149</t>
+          <t>0955306971</t>
         </is>
       </c>
       <c r="E463" s="4"/>
@@ -13814,18 +13810,18 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>M2602030001</t>
+          <t>M2511110001</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>許士彥</t>
+          <t>許哲豪</t>
         </is>
       </c>
       <c r="C464" s="4"/>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>0913558692</t>
+          <t>0985191149</t>
         </is>
       </c>
       <c r="E464" s="4"/>
@@ -13843,18 +13839,18 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>M2509290018</t>
+          <t>M2602030001</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>許天寶</t>
+          <t>許士彥</t>
         </is>
       </c>
       <c r="C465" s="4"/>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>0936088850</t>
+          <t>0913558692</t>
         </is>
       </c>
       <c r="E465" s="4"/>
@@ -13872,18 +13868,18 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>M2510160005</t>
+          <t>M2509290018</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>許宥蓁</t>
+          <t>許天寶</t>
         </is>
       </c>
       <c r="C466" s="4"/>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>0938473255</t>
+          <t>0936088850</t>
         </is>
       </c>
       <c r="E466" s="4"/>
@@ -13901,18 +13897,18 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>M2512020001</t>
+          <t>M2510160005</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>許家豪</t>
+          <t>許宥蓁</t>
         </is>
       </c>
       <c r="C467" s="4"/>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>0983215242</t>
+          <t>0938473255</t>
         </is>
       </c>
       <c r="E467" s="4"/>
@@ -13930,18 +13926,18 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>M2510110007</t>
+          <t>M2512020001</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>許峻銓</t>
+          <t>許家豪</t>
         </is>
       </c>
       <c r="C468" s="4"/>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>0979770033</t>
+          <t>0983215242</t>
         </is>
       </c>
       <c r="E468" s="4"/>
@@ -13959,18 +13955,18 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>M2511260001</t>
+          <t>M2510110007</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>許志帆</t>
+          <t>許峻銓</t>
         </is>
       </c>
       <c r="C469" s="4"/>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>0936639358</t>
+          <t>0979770033</t>
         </is>
       </c>
       <c r="E469" s="4"/>
@@ -13988,18 +13984,18 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>M2510310001</t>
+          <t>M2511260001</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>許志豪</t>
+          <t>許志帆</t>
         </is>
       </c>
       <c r="C470" s="4"/>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>0971080606</t>
+          <t>0936639358</t>
         </is>
       </c>
       <c r="E470" s="4"/>
@@ -14017,18 +14013,18 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>M2601040001</t>
+          <t>M2510310001</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>許惠笙</t>
+          <t>許志豪</t>
         </is>
       </c>
       <c r="C471" s="4"/>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>0987890463</t>
+          <t>0971080606</t>
         </is>
       </c>
       <c r="E471" s="4"/>
@@ -14046,18 +14042,18 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>M2603080002</t>
+          <t>M2601040001</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>許汶瑋</t>
+          <t>許惠笙</t>
         </is>
       </c>
       <c r="C472" s="4"/>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>0988166792</t>
+          <t>0987890463</t>
         </is>
       </c>
       <c r="E472" s="4"/>
@@ -14075,22 +14071,18 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>M2509140001</t>
+          <t>M2603080002</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>許煥杰</t>
-        </is>
-      </c>
-      <c r="C473" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區藝文二街88號8樓</t>
-        </is>
-      </c>
+          <t>許汶瑋</t>
+        </is>
+      </c>
+      <c r="C473" s="4"/>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>0913785888</t>
+          <t>0988166792</t>
         </is>
       </c>
       <c r="E473" s="4"/>
@@ -14108,18 +14100,22 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>M2510010001</t>
+          <t>M2509140001</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>許硯棠</t>
-        </is>
-      </c>
-      <c r="C474" s="4"/>
+          <t>許煥杰</t>
+        </is>
+      </c>
+      <c r="C474" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區藝文二街88號8樓</t>
+        </is>
+      </c>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>0983238652</t>
+          <t>0913785888</t>
         </is>
       </c>
       <c r="E474" s="4"/>
@@ -14137,18 +14133,18 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>M2509270001</t>
+          <t>M2510010001</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>許竣榤</t>
+          <t>許硯棠</t>
         </is>
       </c>
       <c r="C475" s="4"/>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>0955598097</t>
+          <t>0983238652</t>
         </is>
       </c>
       <c r="E475" s="4"/>
@@ -14166,18 +14162,18 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>M2510240002</t>
+          <t>M2509270001</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>許芫睿</t>
+          <t>許竣榤</t>
         </is>
       </c>
       <c r="C476" s="4"/>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>0975057699</t>
+          <t>0955598097</t>
         </is>
       </c>
       <c r="E476" s="4"/>
@@ -14195,18 +14191,18 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>M2509290013</t>
+          <t>M2510240002</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>許雅蓁</t>
+          <t>許芫睿</t>
         </is>
       </c>
       <c r="C477" s="4"/>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>0982339939</t>
+          <t>0975057699</t>
         </is>
       </c>
       <c r="E477" s="4"/>
@@ -14224,18 +14220,18 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>M2509260055</t>
+          <t>M2509290013</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>許靜蔆</t>
+          <t>許雅蓁</t>
         </is>
       </c>
       <c r="C478" s="4"/>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>0928060395</t>
+          <t>0982339939</t>
         </is>
       </c>
       <c r="E478" s="4"/>
@@ -14253,18 +14249,18 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>M2509260027</t>
+          <t>M2509260055</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>詹傑克</t>
+          <t>許靜蔆</t>
         </is>
       </c>
       <c r="C479" s="4"/>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>0968688080</t>
+          <t>0928060395</t>
         </is>
       </c>
       <c r="E479" s="4"/>
@@ -14282,18 +14278,18 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>M2602010004</t>
+          <t>M2509260027</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>詹凱翔</t>
+          <t>詹傑克</t>
         </is>
       </c>
       <c r="C480" s="4"/>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>0963496660</t>
+          <t>0968688080</t>
         </is>
       </c>
       <c r="E480" s="4"/>
@@ -14311,18 +14307,18 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>M2601270001</t>
+          <t>M2602010004</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>詹朝輝</t>
+          <t>詹凱翔</t>
         </is>
       </c>
       <c r="C481" s="4"/>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>0968490321</t>
+          <t>0963496660</t>
         </is>
       </c>
       <c r="E481" s="4"/>
@@ -14340,18 +14336,18 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>M2601170004</t>
+          <t>M2601270001</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>詹煜騰</t>
+          <t>詹朝輝</t>
         </is>
       </c>
       <c r="C482" s="4"/>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>0939919344</t>
+          <t>0968490321</t>
         </is>
       </c>
       <c r="E482" s="4"/>
@@ -14369,18 +14365,18 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>M2509280003</t>
+          <t>M2601170004</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>詹皇</t>
+          <t>詹煜騰</t>
         </is>
       </c>
       <c r="C483" s="4"/>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>0916037915</t>
+          <t>0939919344</t>
         </is>
       </c>
       <c r="E483" s="4"/>
@@ -14398,18 +14394,18 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>M2510030001</t>
+          <t>M2509280003</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>詹皇宥</t>
+          <t>詹皇</t>
         </is>
       </c>
       <c r="C484" s="4"/>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>0919367080</t>
+          <t>0916037915</t>
         </is>
       </c>
       <c r="E484" s="4"/>
@@ -14427,22 +14423,18 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>M2509290016</t>
+          <t>M2510030001</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>詹育銘</t>
-        </is>
-      </c>
-      <c r="C485" s="4" t="inlineStr">
-        <is>
-          <t>台北市中山區撫順街25號1樓</t>
-        </is>
-      </c>
+          <t>詹皇宥</t>
+        </is>
+      </c>
+      <c r="C485" s="4"/>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>0926962322</t>
+          <t>0919367080</t>
         </is>
       </c>
       <c r="E485" s="4"/>
@@ -14460,22 +14452,22 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>M2510270001</t>
+          <t>M2509290016</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>謝亞倫</t>
+          <t>詹育銘</t>
         </is>
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>新北市淡水區北投里北投子49-1號</t>
+          <t>台北市中山區撫順街25號1樓</t>
         </is>
       </c>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>0922409070</t>
+          <t>0926962322</t>
         </is>
       </c>
       <c r="E486" s="4"/>
@@ -14493,18 +14485,22 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>M2510040004</t>
+          <t>M2510270001</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>謝佳蓉</t>
-        </is>
-      </c>
-      <c r="C487" s="4"/>
+          <t>謝亞倫</t>
+        </is>
+      </c>
+      <c r="C487" s="4" t="inlineStr">
+        <is>
+          <t>新北市淡水區北投里北投子49-1號</t>
+        </is>
+      </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>0976958679</t>
+          <t>0922409070</t>
         </is>
       </c>
       <c r="E487" s="4"/>
@@ -14522,18 +14518,18 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>M2509300019</t>
+          <t>M2510040004</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>謝光明</t>
+          <t>謝佳蓉</t>
         </is>
       </c>
       <c r="C488" s="4"/>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>0983011754</t>
+          <t>0976958679</t>
         </is>
       </c>
       <c r="E488" s="4"/>
@@ -14551,22 +14547,18 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>M2512140002</t>
+          <t>M2509300019</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>謝孟辰</t>
-        </is>
-      </c>
-      <c r="C489" s="4" t="inlineStr">
-        <is>
-          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
-        </is>
-      </c>
+          <t>謝光明</t>
+        </is>
+      </c>
+      <c r="C489" s="4"/>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>0953900309</t>
+          <t>0983011754</t>
         </is>
       </c>
       <c r="E489" s="4"/>
@@ -14584,18 +14576,22 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>M2509270007</t>
+          <t>M2512140002</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>謝建衫</t>
-        </is>
-      </c>
-      <c r="C490" s="4"/>
+          <t>謝孟辰</t>
+        </is>
+      </c>
+      <c r="C490" s="4" t="inlineStr">
+        <is>
+          <t>台北市萬華區東園街66巷53弄55號(抓抓族娃娃機店)</t>
+        </is>
+      </c>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>0918238090</t>
+          <t>0953900309</t>
         </is>
       </c>
       <c r="E490" s="4"/>
@@ -14613,18 +14609,18 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>M2510150005</t>
+          <t>M2509270007</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>謝文懷</t>
+          <t>謝建衫</t>
         </is>
       </c>
       <c r="C491" s="4"/>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>0989813659</t>
+          <t>0918238090</t>
         </is>
       </c>
       <c r="E491" s="4"/>
@@ -14642,18 +14638,18 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>M2510130004</t>
+          <t>M2510150005</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>謝桂仁</t>
+          <t>謝文懷</t>
         </is>
       </c>
       <c r="C492" s="4"/>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>0938357603</t>
+          <t>0989813659</t>
         </is>
       </c>
       <c r="E492" s="4"/>
@@ -14671,18 +14667,18 @@
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
         <is>
-          <t>M2510050002</t>
+          <t>M2510130004</t>
         </is>
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>謝舒帆</t>
+          <t>謝桂仁</t>
         </is>
       </c>
       <c r="C493" s="4"/>
       <c r="D493" s="4" t="inlineStr">
         <is>
-          <t>0980699503</t>
+          <t>0938357603</t>
         </is>
       </c>
       <c r="E493" s="4"/>
@@ -14700,18 +14696,18 @@
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
         <is>
-          <t>M2510040008</t>
+          <t>M2510050002</t>
         </is>
       </c>
       <c r="B494" s="4" t="inlineStr">
         <is>
-          <t>謝荌核</t>
+          <t>謝舒帆</t>
         </is>
       </c>
       <c r="C494" s="4"/>
       <c r="D494" s="4" t="inlineStr">
         <is>
-          <t>0988302836</t>
+          <t>0980699503</t>
         </is>
       </c>
       <c r="E494" s="4"/>
@@ -14729,18 +14725,18 @@
     <row r="495">
       <c r="A495" s="4" t="inlineStr">
         <is>
-          <t>M2511300006</t>
+          <t>M2510040008</t>
         </is>
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>謝詠全</t>
+          <t>謝荌核</t>
         </is>
       </c>
       <c r="C495" s="4"/>
       <c r="D495" s="4" t="inlineStr">
         <is>
-          <t>0977077044</t>
+          <t>0988302836</t>
         </is>
       </c>
       <c r="E495" s="4"/>
@@ -14758,18 +14754,18 @@
     <row r="496">
       <c r="A496" s="4" t="inlineStr">
         <is>
-          <t>M2603200003</t>
+          <t>M2511300006</t>
         </is>
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>譚淵修</t>
+          <t>謝詠全</t>
         </is>
       </c>
       <c r="C496" s="4"/>
       <c r="D496" s="4" t="inlineStr">
         <is>
-          <t>0910322500</t>
+          <t>0977077044</t>
         </is>
       </c>
       <c r="E496" s="4"/>
@@ -14787,18 +14783,18 @@
     <row r="497">
       <c r="A497" s="4" t="inlineStr">
         <is>
-          <t>M2510040011</t>
+          <t>M2603200003</t>
         </is>
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>賴先生</t>
+          <t>譚淵修</t>
         </is>
       </c>
       <c r="C497" s="4"/>
       <c r="D497" s="4" t="inlineStr">
         <is>
-          <t>0965351801</t>
+          <t>0910322500</t>
         </is>
       </c>
       <c r="E497" s="4"/>
@@ -14816,18 +14812,18 @@
     <row r="498">
       <c r="A498" s="4" t="inlineStr">
         <is>
-          <t>M2603080001</t>
+          <t>M2510040011</t>
         </is>
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>賴品豪</t>
+          <t>賴先生</t>
         </is>
       </c>
       <c r="C498" s="4"/>
       <c r="D498" s="4" t="inlineStr">
         <is>
-          <t>0981379127</t>
+          <t>0965351801</t>
         </is>
       </c>
       <c r="E498" s="4"/>
@@ -14845,18 +14841,18 @@
     <row r="499">
       <c r="A499" s="4" t="inlineStr">
         <is>
-          <t>M2511010005</t>
+          <t>M2603080001</t>
         </is>
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>賴彥安</t>
+          <t>賴品豪</t>
         </is>
       </c>
       <c r="C499" s="4"/>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>0913102110</t>
+          <t>0981379127</t>
         </is>
       </c>
       <c r="E499" s="4"/>
@@ -14874,22 +14870,18 @@
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>M2603280001</t>
+          <t>M2511010005</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>賴柏舟</t>
-        </is>
-      </c>
-      <c r="C500" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股五福路11號</t>
-        </is>
-      </c>
+          <t>賴彥安</t>
+        </is>
+      </c>
+      <c r="C500" s="4"/>
       <c r="D500" s="4" t="inlineStr">
         <is>
-          <t>0979131818</t>
+          <t>0913102110</t>
         </is>
       </c>
       <c r="E500" s="4"/>
@@ -14907,18 +14899,22 @@
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
-        </is>
-      </c>
-      <c r="C501" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C501" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D501" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E501" s="4"/>
@@ -14936,18 +14932,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
+          <t>賴珊珊</t>
         </is>
       </c>
       <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14965,22 +14961,18 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C503" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C503" s="4"/>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E503" s="4"/>
@@ -14998,22 +14990,22 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -15031,22 +15023,22 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>趙云璟</t>
         </is>
       </c>
       <c r="C505" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
         </is>
       </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E505" s="4"/>
@@ -15064,18 +15056,22 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C506" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C506" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15093,18 +15089,18 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C507" s="4"/>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15122,18 +15118,18 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C508" s="4"/>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0986258793</t>
         </is>
       </c>
       <c r="E508" s="4"/>
@@ -15151,20 +15147,24 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C509" s="4"/>
-      <c r="D509" s="4"/>
+      <c r="D509" s="4" t="inlineStr">
+        <is>
+          <t>0982484963</t>
+        </is>
+      </c>
       <c r="E509" s="4"/>
       <c r="F509" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G509" s="5" t="inlineStr">
@@ -15176,24 +15176,20 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C510" s="4"/>
-      <c r="D510" s="4" t="inlineStr">
-        <is>
-          <t>0981898339</t>
-        </is>
-      </c>
+      <c r="D510" s="4"/>
       <c r="E510" s="4"/>
       <c r="F510" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G510" s="5" t="inlineStr">
@@ -15205,18 +15201,18 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C511" s="4"/>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>0903921531</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E511" s="4"/>
@@ -15234,18 +15230,18 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C512" s="4"/>
       <c r="D512" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E512" s="4"/>
@@ -15263,18 +15259,18 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C513" s="4"/>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E513" s="4"/>
@@ -15292,18 +15288,18 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C514" s="4"/>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E514" s="4"/>
@@ -15321,18 +15317,18 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱振為</t>
         </is>
       </c>
       <c r="C515" s="4"/>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E515" s="4"/>
@@ -15350,22 +15346,18 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C516" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱政傑</t>
+        </is>
+      </c>
+      <c r="C516" s="4"/>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E516" s="4"/>
@@ -15383,18 +15375,22 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
-        </is>
-      </c>
-      <c r="C517" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C517" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15412,18 +15408,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C518" s="4"/>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E518" s="4"/>
@@ -15441,18 +15437,18 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C519" s="4"/>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E519" s="4"/>
@@ -15470,7 +15466,7 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
@@ -15499,18 +15495,18 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C521" s="4"/>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E521" s="4"/>
@@ -15528,16 +15524,20 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C522" s="4"/>
-      <c r="D522" s="4"/>
+      <c r="D522" s="4" t="inlineStr">
+        <is>
+          <t>0935329653</t>
+        </is>
+      </c>
       <c r="E522" s="4"/>
       <c r="F522" s="4" t="inlineStr">
         <is>
@@ -15553,20 +15553,16 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C523" s="4"/>
-      <c r="D523" s="4" t="inlineStr">
-        <is>
-          <t>0976588171</t>
-        </is>
-      </c>
+      <c r="D523" s="4"/>
       <c r="E523" s="4"/>
       <c r="F523" s="4" t="inlineStr">
         <is>
@@ -15582,18 +15578,18 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C524" s="4"/>
       <c r="D524" s="4" t="inlineStr">
         <is>
-          <t>0972128080</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E524" s="4"/>
@@ -15611,18 +15607,18 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C525" s="4"/>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E525" s="4"/>
@@ -15640,18 +15636,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C526" s="4"/>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15669,18 +15665,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C527" s="4"/>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15698,18 +15694,18 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C528" s="4"/>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15727,18 +15723,18 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C529" s="4"/>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15756,18 +15752,18 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C530" s="4"/>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15785,18 +15781,18 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭鼎昇</t>
         </is>
       </c>
       <c r="C531" s="4"/>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15814,22 +15810,18 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C532" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>鄒育燁</t>
+        </is>
+      </c>
+      <c r="C532" s="4"/>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15847,18 +15839,22 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
-        </is>
-      </c>
-      <c r="C533" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C533" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15876,18 +15872,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E534" s="4"/>
@@ -15905,18 +15901,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C535" s="4"/>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15934,18 +15930,18 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C536" s="4"/>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E536" s="4"/>
@@ -15963,18 +15959,18 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C537" s="4"/>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E537" s="4"/>
@@ -15992,18 +15988,18 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C538" s="4"/>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E538" s="4"/>
@@ -16021,18 +16017,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭秉霖</t>
         </is>
       </c>
       <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E539" s="4"/>
@@ -16050,22 +16046,18 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C540" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C540" s="4"/>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16083,22 +16075,22 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>鄭雁予</t>
+          <t>鄭鉅耀</t>
         </is>
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>桃園區國聖二街145號5樓之1</t>
+          <t>新北市五股區成泰路二段208號</t>
         </is>
       </c>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16116,18 +16108,22 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C542" s="4"/>
+          <t>鄭雁予</t>
+        </is>
+      </c>
+      <c r="C542" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E542" s="4"/>
@@ -16145,18 +16141,18 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C543" s="4"/>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16174,18 +16170,18 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C544" s="4"/>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E544" s="4"/>
@@ -16203,18 +16199,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16232,18 +16228,18 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾銘峰</t>
         </is>
       </c>
       <c r="C546" s="4"/>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16261,22 +16257,18 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C547" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鐘國禎</t>
+        </is>
+      </c>
+      <c r="C547" s="4"/>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E547" s="4"/>
@@ -16294,24 +16286,28 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2603270001</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>鐘駿霆</t>
-        </is>
-      </c>
-      <c r="C548" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C548" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0919331886</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E548" s="4"/>
       <c r="F548" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G548" s="5" t="inlineStr">
@@ -16323,24 +16319,24 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
+          <t>鐘駿霆</t>
         </is>
       </c>
       <c r="C549" s="4"/>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E549" s="4"/>
       <c r="F549" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G549" s="5" t="inlineStr">
@@ -16352,22 +16348,18 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C550" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>阮海德</t>
+        </is>
+      </c>
+      <c r="C550" s="4"/>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E550" s="4"/>
@@ -16385,18 +16377,22 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
-        </is>
-      </c>
-      <c r="C551" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E551" s="4"/>
@@ -16414,18 +16410,18 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
+          <t>阿源</t>
         </is>
       </c>
       <c r="C552" s="4"/>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16443,22 +16439,18 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C553" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿良</t>
+        </is>
+      </c>
+      <c r="C553" s="4"/>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16476,18 +16468,22 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
-        </is>
-      </c>
-      <c r="C554" s="4"/>
+          <t>陳仲盟</t>
+        </is>
+      </c>
+      <c r="C554" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
+        </is>
+      </c>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16505,22 +16501,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
-        </is>
-      </c>
-      <c r="C555" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區日和街7號22樓</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C555" s="4"/>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16538,22 +16530,22 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
+          <t>陳俊安</t>
         </is>
       </c>
       <c r="C556" s="4" t="inlineStr">
         <is>
-          <t>板橋大觀路1段28巷118-1號</t>
+          <t>新北市土城區日和街7號22樓</t>
         </is>
       </c>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16571,18 +16563,22 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C557" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C557" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16600,18 +16596,18 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C558" s="4"/>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16629,18 +16625,18 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C559" s="4"/>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16658,18 +16654,18 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C560" s="4"/>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16687,18 +16683,18 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C561" s="4"/>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16716,18 +16712,18 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C562" s="4"/>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16745,18 +16741,18 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C563" s="4"/>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16774,18 +16770,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16803,18 +16799,18 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C565" s="4"/>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16832,18 +16828,18 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳奕融</t>
         </is>
       </c>
       <c r="C566" s="4"/>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16861,22 +16857,18 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C567" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕閔</t>
+        </is>
+      </c>
+      <c r="C567" s="4"/>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16894,18 +16886,22 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2603260001</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳威宇</t>
-        </is>
-      </c>
-      <c r="C568" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C568" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0958186337</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16923,18 +16919,18 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C569" s="4"/>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16952,18 +16948,18 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C570" s="4"/>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16981,18 +16977,18 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C571" s="4"/>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -17010,18 +17006,18 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
+          <t>陳子杰</t>
         </is>
       </c>
       <c r="C572" s="4"/>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -17039,18 +17035,18 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
+          <t>陳宏文</t>
         </is>
       </c>
       <c r="C573" s="4"/>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17068,22 +17064,18 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C574" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳宏達</t>
+        </is>
+      </c>
+      <c r="C574" s="4"/>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17101,18 +17093,22 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
-        </is>
-      </c>
-      <c r="C575" s="4"/>
+          <t>陳家偉</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市神農路一段72號</t>
+        </is>
+      </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17130,18 +17126,18 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
+          <t>陳小雨</t>
         </is>
       </c>
       <c r="C576" s="4"/>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17159,22 +17155,18 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
-        </is>
-      </c>
-      <c r="C577" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
-        </is>
-      </c>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="C577" s="4"/>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17192,22 +17184,22 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
+          <t>陳建宏(花蓮)</t>
         </is>
       </c>
       <c r="C578" s="4" t="inlineStr">
         <is>
-          <t>新北市三重區仁美街125號</t>
+          <t>花蓮縣新城鄉佳林31之19號</t>
         </is>
       </c>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17225,18 +17217,22 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
-        </is>
-      </c>
-      <c r="C579" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17254,18 +17250,18 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C580" s="4"/>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17283,18 +17279,18 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C581" s="4"/>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17312,18 +17308,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17341,18 +17337,18 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳怡如(彥鈞)</t>
         </is>
       </c>
       <c r="C583" s="4"/>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17370,18 +17366,18 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳慶壎</t>
         </is>
       </c>
       <c r="C584" s="4"/>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17399,22 +17395,18 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C585" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳敬惟</t>
+        </is>
+      </c>
+      <c r="C585" s="4"/>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17432,18 +17424,22 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
-        </is>
-      </c>
-      <c r="C586" s="4"/>
+          <t>陳智盛</t>
+        </is>
+      </c>
+      <c r="C586" s="4" t="inlineStr">
+        <is>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
+        </is>
+      </c>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17461,22 +17457,18 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
-        </is>
-      </c>
-      <c r="C587" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區星雲街30號</t>
-        </is>
-      </c>
+          <t>陳朋堅</t>
+        </is>
+      </c>
+      <c r="C587" s="4"/>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17494,22 +17486,22 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
+          <t>陳松廉</t>
         </is>
       </c>
       <c r="C588" s="4" t="inlineStr">
         <is>
-          <t>桃園市南豐街258號</t>
+          <t>台北市內湖區星雲街30號</t>
         </is>
       </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17527,18 +17519,22 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
-        </is>
-      </c>
-      <c r="C589" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17556,18 +17552,18 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C590" s="4"/>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17585,7 +17581,7 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
@@ -17596,7 +17592,7 @@
       <c r="C591" s="4"/>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17614,18 +17610,18 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C592" s="4"/>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17643,22 +17639,18 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C593" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳正傑</t>
+        </is>
+      </c>
+      <c r="C593" s="4"/>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17676,18 +17668,22 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
-        </is>
-      </c>
-      <c r="C594" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C594" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17705,18 +17701,18 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C595" s="4"/>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17734,18 +17730,18 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
+          <t>陳琇珊</t>
         </is>
       </c>
       <c r="C596" s="4"/>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17763,18 +17759,18 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳琬瑜</t>
         </is>
       </c>
       <c r="C597" s="4"/>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17792,22 +17788,18 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C598" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳璽文</t>
+        </is>
+      </c>
+      <c r="C598" s="4"/>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17825,18 +17817,22 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
-        </is>
-      </c>
-      <c r="C599" s="4"/>
+          <t>陳益銓</t>
+        </is>
+      </c>
+      <c r="C599" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區民生街15巷10號3樓</t>
+        </is>
+      </c>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17854,22 +17850,18 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
-        </is>
-      </c>
-      <c r="C600" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
-        </is>
-      </c>
+          <t>陳秋蓉</t>
+        </is>
+      </c>
+      <c r="C600" s="4"/>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E600" s="4"/>
@@ -17887,18 +17879,22 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
-        </is>
-      </c>
-      <c r="C601" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17916,18 +17912,18 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
+          <t>陳貴源</t>
         </is>
       </c>
       <c r="C602" s="4"/>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17945,18 +17941,18 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2604190004</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>陳鋐緯</t>
+          <t>陳達鋒</t>
         </is>
       </c>
       <c r="C603" s="4"/>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>0925805535</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E603" s="4"/>
@@ -17974,18 +17970,18 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2604190004</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
+          <t>陳鋐緯</t>
         </is>
       </c>
       <c r="C604" s="4"/>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0925805535</t>
         </is>
       </c>
       <c r="E604" s="4"/>
@@ -18003,22 +17999,18 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C605" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C605" s="4"/>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E605" s="4"/>
@@ -18036,22 +18028,22 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
+          <t>陳長志</t>
         </is>
       </c>
       <c r="C606" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+          <t>新北市新店區安康路</t>
         </is>
       </c>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E606" s="4"/>
@@ -18069,22 +18061,22 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
+          <t>陳雯瑄</t>
         </is>
       </c>
       <c r="C607" s="4" t="inlineStr">
         <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
         </is>
       </c>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E607" s="4"/>
@@ -18102,18 +18094,22 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C608" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C608" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E608" s="4"/>
@@ -18131,18 +18127,18 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C609" s="4"/>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18160,18 +18156,18 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C610" s="4"/>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18189,18 +18185,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18218,18 +18214,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18247,18 +18243,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18276,18 +18272,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18305,18 +18301,18 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C615" s="4"/>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18334,18 +18330,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18363,18 +18359,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18392,18 +18388,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18421,18 +18417,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏宏坤</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18450,22 +18446,18 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C620" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>馬迪</t>
+        </is>
+      </c>
+      <c r="C620" s="4"/>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18483,18 +18475,22 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
-        </is>
-      </c>
-      <c r="C621" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C621" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18512,18 +18508,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18541,18 +18537,18 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C623" s="4"/>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E623" s="4"/>
@@ -18570,18 +18566,18 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C624" s="4"/>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E624" s="4"/>
@@ -18599,18 +18595,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18628,18 +18624,18 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E626" s="4"/>
@@ -18657,18 +18653,18 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高聖景</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E627" s="4"/>
@@ -18686,22 +18682,18 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C628" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高莉婷</t>
+        </is>
+      </c>
+      <c r="C628" s="4"/>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18719,18 +18711,22 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
-        </is>
-      </c>
-      <c r="C629" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C629" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E629" s="4"/>
@@ -18748,18 +18744,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0937742352</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18777,16 +18773,20 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C631" s="4"/>
-      <c r="D631" s="4"/>
+      <c r="D631" s="4" t="inlineStr">
+        <is>
+          <t>0989116588</t>
+        </is>
+      </c>
       <c r="E631" s="4"/>
       <c r="F631" s="4" t="inlineStr">
         <is>
@@ -18802,20 +18802,16 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>鴻</t>
         </is>
       </c>
       <c r="C632" s="4"/>
-      <c r="D632" s="4" t="inlineStr">
-        <is>
-          <t>0958180882</t>
-        </is>
-      </c>
+      <c r="D632" s="4"/>
       <c r="E632" s="4"/>
       <c r="F632" s="4" t="inlineStr">
         <is>
@@ -18831,22 +18827,18 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C633" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
+          <t>黃俊翰</t>
+        </is>
+      </c>
+      <c r="C633" s="4"/>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>0903975921</t>
+          <t>0958180882</t>
         </is>
       </c>
       <c r="E633" s="4"/>
@@ -18864,16 +18856,24 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B634" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
-        </is>
-      </c>
-      <c r="C634" s="4"/>
-      <c r="D634" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C634" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
+      <c r="D634" s="4" t="inlineStr">
+        <is>
+          <t>0903975921</t>
+        </is>
+      </c>
       <c r="E634" s="4"/>
       <c r="F634" s="4" t="inlineStr">
         <is>
@@ -18889,20 +18889,16 @@
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C635" s="4"/>
-      <c r="D635" s="4" t="inlineStr">
-        <is>
-          <t>0938722217</t>
-        </is>
-      </c>
+      <c r="D635" s="4"/>
       <c r="E635" s="4"/>
       <c r="F635" s="4" t="inlineStr">
         <is>
@@ -18918,18 +18914,18 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B636" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C636" s="4"/>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>0989628136</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E636" s="4"/>
@@ -18947,18 +18943,18 @@
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C637" s="4"/>
       <c r="D637" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E637" s="4"/>
@@ -18976,18 +18972,18 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>M2604190003</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B638" s="4" t="inlineStr">
         <is>
-          <t>黃士凱</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C638" s="4"/>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>0934179571</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E638" s="4"/>
@@ -19005,18 +19001,18 @@
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2604190003</t>
         </is>
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃士凱</t>
         </is>
       </c>
       <c r="C639" s="4"/>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0934179571</t>
         </is>
       </c>
       <c r="E639" s="4"/>
@@ -19034,18 +19030,18 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B640" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C640" s="4"/>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E640" s="4"/>
@@ -19063,18 +19059,18 @@
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C641" s="4"/>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E641" s="4"/>
@@ -19092,18 +19088,18 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>M2604120001</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B642" s="4" t="inlineStr">
         <is>
-          <t>黃宥文</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C642" s="4"/>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>0953082147</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E642" s="4"/>
@@ -19121,18 +19117,18 @@
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2604120001</t>
         </is>
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宥文</t>
         </is>
       </c>
       <c r="C643" s="4"/>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0953082147</t>
         </is>
       </c>
       <c r="E643" s="4"/>
@@ -19150,18 +19146,18 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B644" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C644" s="4"/>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E644" s="4"/>
@@ -19179,22 +19175,18 @@
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C645" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃庠豪</t>
+        </is>
+      </c>
+      <c r="C645" s="4"/>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E645" s="4"/>
@@ -19212,18 +19204,22 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B646" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
-        </is>
-      </c>
-      <c r="C646" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C646" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E646" s="4"/>
@@ -19241,18 +19237,18 @@
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C647" s="4"/>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E647" s="4"/>
@@ -19270,18 +19266,18 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B648" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C648" s="4"/>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E648" s="4"/>
@@ -19299,18 +19295,18 @@
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C649" s="4"/>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E649" s="4"/>
@@ -19328,18 +19324,18 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B650" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C650" s="4"/>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E650" s="4"/>
@@ -19357,18 +19353,18 @@
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B651" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C651" s="4"/>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E651" s="4"/>
@@ -19386,18 +19382,18 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B652" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C652" s="4"/>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E652" s="4"/>
@@ -19415,18 +19411,18 @@
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B653" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C653" s="4"/>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E653" s="4"/>
@@ -19444,18 +19440,18 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B654" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C654" s="4"/>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E654" s="4"/>
@@ -19473,18 +19469,18 @@
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B655" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C655" s="4"/>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E655" s="4"/>
@@ -19502,18 +19498,18 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B656" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C656" s="4"/>
       <c r="D656" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E656" s="4"/>
@@ -19531,18 +19527,18 @@
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B657" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C657" s="4"/>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E657" s="4"/>
@@ -19560,18 +19556,18 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B658" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C658" s="4"/>
       <c r="D658" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E658" s="4"/>
@@ -19589,18 +19585,18 @@
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
         <is>
-          <t>M2604190001</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B659" s="4" t="inlineStr">
         <is>
-          <t>黃貞菱</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C659" s="4"/>
       <c r="D659" s="4" t="inlineStr">
         <is>
-          <t>0987793062</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E659" s="4"/>
@@ -19618,18 +19614,18 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2604190001</t>
         </is>
       </c>
       <c r="B660" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃貞菱</t>
         </is>
       </c>
       <c r="C660" s="4"/>
       <c r="D660" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0987793062</t>
         </is>
       </c>
       <c r="E660" s="4"/>
@@ -19647,18 +19643,18 @@
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B661" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C661" s="4"/>
       <c r="D661" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E661" s="4"/>
@@ -19676,18 +19672,18 @@
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B662" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C662" s="4"/>
       <c r="D662" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E662" s="4"/>
@@ -19705,18 +19701,18 @@
     <row r="663">
       <c r="A663" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2510020007</t>
         </is>
       </c>
       <c r="B663" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃鴻麒</t>
         </is>
       </c>
       <c r="C663" s="4"/>
       <c r="D663" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0930571975</t>
         </is>
       </c>
       <c r="E663" s="4"/>
@@ -19734,18 +19730,18 @@
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2602270002</t>
         </is>
       </c>
       <c r="B664" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黎信宏</t>
         </is>
       </c>
       <c r="C664" s="4"/>
       <c r="D664" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0911024337</t>
         </is>
       </c>
       <c r="E664" s="4"/>
@@ -19761,9 +19757,38 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>2026/04/21  17:27:07</t>
+      <c r="A665" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B665" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C665" s="4"/>
+      <c r="D665" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E665" s="4"/>
+      <c r="F665" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G665" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026/04/21  23:51:08</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -10038,12 +10038,12 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>M2512180002</t>
+          <t>M2512180001</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>火牛-老秦</t>
+          <t>火牛-阿昌</t>
         </is>
       </c>
       <c r="C337" s="4"/>
@@ -10063,16 +10063,20 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>M2512180001</t>
+          <t>M2602140002</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>火牛-阿昌</t>
+          <t>灰灰</t>
         </is>
       </c>
       <c r="C338" s="4"/>
-      <c r="D338" s="4"/>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>0987829134</t>
+        </is>
+      </c>
       <c r="E338" s="4"/>
       <c r="F338" s="4" t="inlineStr">
         <is>
@@ -10088,18 +10092,18 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>M2602140002</t>
+          <t>M2509300011</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>灰灰</t>
+          <t>熊駿天(大熊)</t>
         </is>
       </c>
       <c r="C339" s="4"/>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>0987829134</t>
+          <t>0933131800</t>
         </is>
       </c>
       <c r="E339" s="4"/>
@@ -10117,18 +10121,18 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>M2509300011</t>
+          <t>M2602070001</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>熊駿天(大熊)</t>
+          <t>王RICK</t>
         </is>
       </c>
       <c r="C340" s="4"/>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>0933131800</t>
+          <t>0930106976</t>
         </is>
       </c>
       <c r="E340" s="4"/>
@@ -10146,18 +10150,22 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>M2602070001</t>
+          <t>M2510240006</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>王RICK</t>
-        </is>
-      </c>
-      <c r="C341" s="4"/>
+          <t>王中南</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區快速路166號3樓</t>
+        </is>
+      </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>0930106976</t>
+          <t>0937124082</t>
         </is>
       </c>
       <c r="E341" s="4"/>
@@ -10175,22 +10183,18 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>M2510240006</t>
+          <t>M2601020001</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>王中南</t>
-        </is>
-      </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>桃園市平鎮區快速路166號3樓</t>
-        </is>
-      </c>
+          <t>王仁澤</t>
+        </is>
+      </c>
+      <c r="C342" s="4"/>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>0937124082</t>
+          <t>0976503359</t>
         </is>
       </c>
       <c r="E342" s="4"/>
@@ -10208,18 +10212,18 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>M2601020001</t>
+          <t>M2603010004</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>王仁澤</t>
+          <t>王又杰</t>
         </is>
       </c>
       <c r="C343" s="4"/>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>0976503359</t>
+          <t>0909771449</t>
         </is>
       </c>
       <c r="E343" s="4"/>
@@ -10237,18 +10241,18 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>M2603010004</t>
+          <t>M2601080001</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>王又杰</t>
+          <t>王家文</t>
         </is>
       </c>
       <c r="C344" s="4"/>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>0909771449</t>
+          <t>0908176140</t>
         </is>
       </c>
       <c r="E344" s="4"/>
@@ -10266,18 +10270,18 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>M2601080001</t>
+          <t>M2602080001</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>王家文</t>
+          <t>王巽璋</t>
         </is>
       </c>
       <c r="C345" s="4"/>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>0908176140</t>
+          <t>0932943159</t>
         </is>
       </c>
       <c r="E345" s="4"/>
@@ -10295,18 +10299,18 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>M2602080001</t>
+          <t>M2512230001</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>王巽璋</t>
+          <t>王志維</t>
         </is>
       </c>
       <c r="C346" s="4"/>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>0932943159</t>
+          <t>0931262170</t>
         </is>
       </c>
       <c r="E346" s="4"/>
@@ -10324,18 +10328,18 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>M2512230001</t>
+          <t>M2511180003</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>王志維</t>
+          <t>王明輝</t>
         </is>
       </c>
       <c r="C347" s="4"/>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>0931262170</t>
+          <t>0937002585</t>
         </is>
       </c>
       <c r="E347" s="4"/>
@@ -10353,18 +10357,18 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>M2511180003</t>
+          <t>M2510140007</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>王明輝</t>
+          <t>王羿佳</t>
         </is>
       </c>
       <c r="C348" s="4"/>
       <c r="D348" s="4" t="inlineStr">
         <is>
-          <t>0937002585</t>
+          <t>0968831773</t>
         </is>
       </c>
       <c r="E348" s="4"/>
@@ -10382,18 +10386,22 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>M2510140007</t>
+          <t>M2509260013</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>王羿佳</t>
-        </is>
-      </c>
-      <c r="C349" s="4"/>
+          <t>王舜平</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
+        </is>
+      </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>0968831773</t>
+          <t>0917215021</t>
         </is>
       </c>
       <c r="E349" s="4"/>
@@ -10411,22 +10419,18 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>M2509260013</t>
+          <t>M2601170002</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>王舜平</t>
-        </is>
-      </c>
-      <c r="C350" s="4" t="inlineStr">
-        <is>
-          <t>苗栗縣頭份鎮金艾夾娃娃屋</t>
-        </is>
-      </c>
+          <t>王閔弘</t>
+        </is>
+      </c>
+      <c r="C350" s="4"/>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>0917215021</t>
+          <t>0931056292</t>
         </is>
       </c>
       <c r="E350" s="4"/>
@@ -10444,18 +10448,18 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>M2601170002</t>
+          <t>M2511230003</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>王閔弘</t>
+          <t>王靜芸</t>
         </is>
       </c>
       <c r="C351" s="4"/>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>0931056292</t>
+          <t>0970224238</t>
         </is>
       </c>
       <c r="E351" s="4"/>
@@ -10473,18 +10477,18 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>M2511230003</t>
+          <t>M2510040009</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>王靜芸</t>
+          <t>王駿宏</t>
         </is>
       </c>
       <c r="C352" s="4"/>
       <c r="D352" s="4" t="inlineStr">
         <is>
-          <t>0970224238</t>
+          <t>0919336854</t>
         </is>
       </c>
       <c r="E352" s="4"/>
@@ -10502,18 +10506,18 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>M2510040009</t>
+          <t>M2601010001</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>王駿宏</t>
+          <t>甘玨瑋</t>
         </is>
       </c>
       <c r="C353" s="4"/>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>0919336854</t>
+          <t>0987214102</t>
         </is>
       </c>
       <c r="E353" s="4"/>
@@ -10531,18 +10535,22 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>M2601010001</t>
+          <t>M2510290002</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>甘玨瑋</t>
-        </is>
-      </c>
-      <c r="C354" s="4"/>
+          <t>生生</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街427號</t>
+        </is>
+      </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>0987214102</t>
+          <t>0919001722</t>
         </is>
       </c>
       <c r="E354" s="4"/>
@@ -10560,22 +10568,18 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>M2510290002</t>
+          <t>M2509260050</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>生生</t>
-        </is>
-      </c>
-      <c r="C355" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街427號</t>
-        </is>
-      </c>
+          <t>甩爪</t>
+        </is>
+      </c>
+      <c r="C355" s="4"/>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>0919001722</t>
+          <t>0970754804</t>
         </is>
       </c>
       <c r="E355" s="4"/>
@@ -10593,18 +10597,18 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>M2509260050</t>
+          <t>M2509270005</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>甩爪</t>
+          <t>甯偉</t>
         </is>
       </c>
       <c r="C356" s="4"/>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>0970754804</t>
+          <t>0955617290</t>
         </is>
       </c>
       <c r="E356" s="4"/>
@@ -10622,18 +10626,18 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>M2509270005</t>
+          <t>M2510240007</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>甯偉</t>
+          <t>盧其辰</t>
         </is>
       </c>
       <c r="C357" s="4"/>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>0955617290</t>
+          <t>0982119779</t>
         </is>
       </c>
       <c r="E357" s="4"/>
@@ -10651,18 +10655,18 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>M2510240007</t>
+          <t>M2604110001</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>盧其辰</t>
+          <t>盧炳宏</t>
         </is>
       </c>
       <c r="C358" s="4"/>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>0982119779</t>
+          <t>0921062300</t>
         </is>
       </c>
       <c r="E358" s="4"/>
@@ -10680,24 +10684,20 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>M2604110001</t>
+          <t>V0013</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>盧炳宏</t>
+          <t>真大帥</t>
         </is>
       </c>
       <c r="C359" s="4"/>
-      <c r="D359" s="4" t="inlineStr">
-        <is>
-          <t>0921062300</t>
-        </is>
-      </c>
+      <c r="D359" s="4"/>
       <c r="E359" s="4"/>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -10709,20 +10709,24 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>V0013</t>
+          <t>M2510310002</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>真大帥</t>
+          <t>祁麟</t>
         </is>
       </c>
       <c r="C360" s="4"/>
-      <c r="D360" s="4"/>
+      <c r="D360" s="4" t="inlineStr">
+        <is>
+          <t>0982883101</t>
+        </is>
+      </c>
       <c r="E360" s="4"/>
       <c r="F360" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -10734,18 +10738,18 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>M2510310002</t>
+          <t>M2602130001</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>祁麟</t>
+          <t>祐</t>
         </is>
       </c>
       <c r="C361" s="4"/>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>0982883101</t>
+          <t>0983407890</t>
         </is>
       </c>
       <c r="E361" s="4"/>
@@ -10763,18 +10767,18 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>M2602130001</t>
+          <t>M2510050001</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>祐</t>
+          <t>程sir/Ashbur</t>
         </is>
       </c>
       <c r="C362" s="4"/>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>0983407890</t>
+          <t>0963612395</t>
         </is>
       </c>
       <c r="E362" s="4"/>
@@ -10792,18 +10796,18 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>M2510050001</t>
+          <t>M2510300001</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>程sir/Ashbur</t>
+          <t>程品勝</t>
         </is>
       </c>
       <c r="C363" s="4"/>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>0963612395</t>
+          <t>0913780727</t>
         </is>
       </c>
       <c r="E363" s="4"/>
@@ -10821,18 +10825,18 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>M2510300001</t>
+          <t>M2601270002</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>程品勝</t>
+          <t>程建智</t>
         </is>
       </c>
       <c r="C364" s="4"/>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>0913780727</t>
+          <t>0988919027</t>
         </is>
       </c>
       <c r="E364" s="4"/>
@@ -10850,18 +10854,18 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>M2601270002</t>
+          <t>M2603120004</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>程建智</t>
+          <t>程郁勛</t>
         </is>
       </c>
       <c r="C365" s="4"/>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>0988919027</t>
+          <t>0955671407</t>
         </is>
       </c>
       <c r="E365" s="4"/>
@@ -10879,18 +10883,22 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>M2603120004</t>
+          <t>M2509160001</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>程郁勛</t>
-        </is>
-      </c>
-      <c r="C366" s="4"/>
+          <t>穆莉茹</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>桃園平鎮區上海路169號</t>
+        </is>
+      </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>0955671407</t>
+          <t>0955777312</t>
         </is>
       </c>
       <c r="E366" s="4"/>
@@ -10908,22 +10916,18 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>M2509160001</t>
+          <t>M2511160003</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>穆莉茹</t>
-        </is>
-      </c>
-      <c r="C367" s="4" t="inlineStr">
-        <is>
-          <t>桃園平鎮區上海路169號</t>
-        </is>
-      </c>
+          <t>簡士傑</t>
+        </is>
+      </c>
+      <c r="C367" s="4"/>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>0955777312</t>
+          <t>0963817398</t>
         </is>
       </c>
       <c r="E367" s="4"/>
@@ -10941,18 +10945,18 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>M2511160003</t>
+          <t>M2509300013</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>簡士傑</t>
+          <t>簡子偉</t>
         </is>
       </c>
       <c r="C368" s="4"/>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>0963817398</t>
+          <t>0955462926</t>
         </is>
       </c>
       <c r="E368" s="4"/>
@@ -10970,18 +10974,18 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>M2509300013</t>
+          <t>M2602280002</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>簡子偉</t>
+          <t>簡子洋</t>
         </is>
       </c>
       <c r="C369" s="4"/>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>0955462926</t>
+          <t>0933921933</t>
         </is>
       </c>
       <c r="E369" s="4"/>
@@ -10999,18 +11003,18 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>M2602280002</t>
+          <t>M2510040003</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>簡子洋</t>
+          <t>簡小琪</t>
         </is>
       </c>
       <c r="C370" s="4"/>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>0933921933</t>
+          <t>0930033829</t>
         </is>
       </c>
       <c r="E370" s="4"/>
@@ -11028,18 +11032,18 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>M2510040003</t>
+          <t>M2510260002</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>簡小琪</t>
+          <t>簡揚城</t>
         </is>
       </c>
       <c r="C371" s="4"/>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>0930033829</t>
+          <t>0913153353</t>
         </is>
       </c>
       <c r="E371" s="4"/>
@@ -11057,18 +11061,18 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>M2510260002</t>
+          <t>M2509300001</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>簡揚城</t>
+          <t>簡瑋成</t>
         </is>
       </c>
       <c r="C372" s="4"/>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>0913153353</t>
+          <t>0936389969</t>
         </is>
       </c>
       <c r="E372" s="4"/>
@@ -11086,18 +11090,18 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>M2509300001</t>
+          <t>M2509290020</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>簡瑋成</t>
+          <t>簡茂州</t>
         </is>
       </c>
       <c r="C373" s="4"/>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>0936389969</t>
+          <t>0985217379</t>
         </is>
       </c>
       <c r="E373" s="4"/>
@@ -11115,18 +11119,18 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>M2509290020</t>
+          <t>M2512130001</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>簡茂州</t>
+          <t>紀彥銘</t>
         </is>
       </c>
       <c r="C374" s="4"/>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>0985217379</t>
+          <t>0988752337</t>
         </is>
       </c>
       <c r="E374" s="4"/>
@@ -11144,24 +11148,20 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>M2512130001</t>
+          <t>V0001</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>紀彥銘</t>
+          <t>統有企業</t>
         </is>
       </c>
       <c r="C375" s="4"/>
-      <c r="D375" s="4" t="inlineStr">
-        <is>
-          <t>0988752337</t>
-        </is>
-      </c>
+      <c r="D375" s="4"/>
       <c r="E375" s="4"/>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G375" s="5" t="inlineStr">
@@ -11173,20 +11173,24 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>V0001</t>
+          <t>M2509280008</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>統有企業</t>
+          <t>維克斯</t>
         </is>
       </c>
       <c r="C376" s="4"/>
-      <c r="D376" s="4"/>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>0917771787</t>
+        </is>
+      </c>
       <c r="E376" s="4"/>
       <c r="F376" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G376" s="5" t="inlineStr">
@@ -11198,18 +11202,18 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>M2509280008</t>
+          <t>M2510170002</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>維克斯</t>
+          <t>練鎮宇</t>
         </is>
       </c>
       <c r="C377" s="4"/>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>0917771787</t>
+          <t>0952288706</t>
         </is>
       </c>
       <c r="E377" s="4"/>
@@ -11227,18 +11231,22 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>M2510170002</t>
+          <t>M2602220003</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>練鎮宇</t>
-        </is>
-      </c>
-      <c r="C378" s="4"/>
+          <t>羅丁一夫</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="inlineStr">
+        <is>
+          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
+        </is>
+      </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>0952288706</t>
+          <t>0919339614</t>
         </is>
       </c>
       <c r="E378" s="4"/>
@@ -11256,22 +11264,18 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>M2602220003</t>
+          <t>M2510180002</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>羅丁一夫</t>
-        </is>
-      </c>
-      <c r="C379" s="4" t="inlineStr">
-        <is>
-          <t>桃園市桃園區莊敬路一段210巷3號19樓</t>
-        </is>
-      </c>
+          <t>羅元隆</t>
+        </is>
+      </c>
+      <c r="C379" s="4"/>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>0919339614</t>
+          <t>0975866635</t>
         </is>
       </c>
       <c r="E379" s="4"/>
@@ -11289,21 +11293,25 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>M2510180002</t>
+          <t>M2510090003</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>羅元隆</t>
+          <t>羅嘉銘</t>
         </is>
       </c>
       <c r="C380" s="4"/>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>0975866635</t>
-        </is>
-      </c>
-      <c r="E380" s="4"/>
+          <t>0928093385</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>0985866052</t>
+        </is>
+      </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11318,25 +11326,21 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>M2510090003</t>
+          <t>M2602240001</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>羅嘉銘</t>
+          <t>羅浩中</t>
         </is>
       </c>
       <c r="C381" s="4"/>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>0928093385</t>
-        </is>
-      </c>
-      <c r="E381" s="4" t="inlineStr">
-        <is>
-          <t>0985866052</t>
-        </is>
-      </c>
+          <t>0970905092</t>
+        </is>
+      </c>
+      <c r="E381" s="4"/>
       <c r="F381" s="4" t="inlineStr">
         <is>
           <t>批發</t>
@@ -11351,18 +11355,18 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>M2602240001</t>
+          <t>M2511060003</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>羅浩中</t>
+          <t>翁名勳</t>
         </is>
       </c>
       <c r="C382" s="4"/>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>0970905092</t>
+          <t>0955083317</t>
         </is>
       </c>
       <c r="E382" s="4"/>
@@ -11380,18 +11384,18 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>M2511060003</t>
+          <t>M2509260057</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>翁名勳</t>
+          <t>翁國昌</t>
         </is>
       </c>
       <c r="C383" s="4"/>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>0955083317</t>
+          <t>0918718772</t>
         </is>
       </c>
       <c r="E383" s="4"/>
@@ -11409,18 +11413,22 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>M2509260057</t>
+          <t>M2511290001</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>翁國昌</t>
-        </is>
-      </c>
-      <c r="C384" s="4"/>
+          <t>翁國祥</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr">
+        <is>
+          <t>新北新莊中信街65號1樓賣菜攤</t>
+        </is>
+      </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>0918718772</t>
+          <t>0983900052</t>
         </is>
       </c>
       <c r="E384" s="4"/>
@@ -11438,22 +11446,22 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>M2511290001</t>
+          <t>M2510010009</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>翁國祥</t>
+          <t>翁敬恩</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>新北新莊中信街65號1樓賣菜攤</t>
+          <t>未決定</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>0983900052</t>
+          <t>0972757015</t>
         </is>
       </c>
       <c r="E385" s="4"/>
@@ -11471,17 +11479,18 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>M2510010009</t>
+          <t>M2510010009-4</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩</t>
-        </is>
-      </c>
-      <c r="C386" s="4" t="inlineStr">
-        <is>
-          <t>未決定</t>
+          <t>翁敬恩-文山</t>
+        </is>
+      </c>
+      <c r="C386" s="6" t="inlineStr">
+        <is>
+          <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
+收件聯絡電話:0937462412</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -11504,18 +11513,17 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-4</t>
+          <t>M2510010009-2</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-文山</t>
-        </is>
-      </c>
-      <c r="C387" s="6" t="inlineStr">
-        <is>
-          <t>台北市文山區興隆路2段301巷2號1樓(送貨時間:平常日5點後不收貨,假日不收貨)
-收件聯絡電話:0937462412</t>
+          <t>翁敬恩-樂華</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="inlineStr">
+        <is>
+          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -11538,17 +11546,17 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-2</t>
+          <t>M2510010009-3</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-樂華</t>
+          <t>翁敬恩-永和</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區永平路174號(送貨時間:11:00-16:00)</t>
+          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -11571,22 +11579,22 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-3</t>
+          <t>M2510010009-1</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-永和</t>
+          <t>翁敬恩-饒河</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>新北市永和區中正路233號(送貨時間:週二到周日 11:00-15:30)</t>
+          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>0972757015</t>
+          <t>0975953978</t>
         </is>
       </c>
       <c r="E389" s="4"/>
@@ -11604,22 +11612,18 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>M2510010009-1</t>
+          <t>M2510140004</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>翁敬恩-饒河</t>
-        </is>
-      </c>
-      <c r="C390" s="4" t="inlineStr">
-        <is>
-          <t>台北市松山區饒河街133號1樓(送貨時間週二到週日11:00-15:30)杜先生0975953978</t>
-        </is>
-      </c>
+          <t>翁漢忠</t>
+        </is>
+      </c>
+      <c r="C390" s="4"/>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>0975953978</t>
+          <t>0916150750</t>
         </is>
       </c>
       <c r="E390" s="4"/>
@@ -11637,18 +11641,18 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>M2510140004</t>
+          <t>M2509260037</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>翁漢忠</t>
+          <t>翁翌禎</t>
         </is>
       </c>
       <c r="C391" s="4"/>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>0916150750</t>
+          <t>0902308293</t>
         </is>
       </c>
       <c r="E391" s="4"/>
@@ -11666,20 +11670,16 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2509260037</t>
+          <t>M2512180002</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>翁翌禎</t>
+          <t>老秦</t>
         </is>
       </c>
       <c r="C392" s="4"/>
-      <c r="D392" s="4" t="inlineStr">
-        <is>
-          <t>0902308293</t>
-        </is>
-      </c>
+      <c r="D392" s="4"/>
       <c r="E392" s="4"/>
       <c r="F392" s="4" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026/04/22  13:00:09</t>
+          <t>2026/04/23  13:00:10</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -9226,7 +9226,7 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>M2509120001</t>
+          <t>M2509290010-3</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -10038,7 +10038,7 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>M2512180001</t>
+          <t>M2509290010-1</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
@@ -11670,7 +11670,7 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>M2512180002</t>
+          <t>M2509290010-2</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
@@ -19821,7 +19821,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026/04/23  13:00:10</t>
+          <t>2026/04/24  13:00:09</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -19821,7 +19821,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026/04/24  13:00:09</t>
+          <t>2026/04/25  13:00:10</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -17076,7 +17076,11 @@
           <t>陳宏文</t>
         </is>
       </c>
-      <c r="C574" s="4"/>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中正區信七路1號</t>
+        </is>
+      </c>
       <c r="D574" s="4" t="inlineStr">
         <is>
           <t>0985400202</t>
@@ -18276,18 +18280,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2604250001</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>雷動蛟</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0983617034</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18305,18 +18309,18 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C615" s="4"/>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18334,18 +18338,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18363,18 +18367,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18392,18 +18396,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18421,18 +18425,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18450,18 +18454,18 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C620" s="4"/>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18479,18 +18483,18 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏宏坤</t>
         </is>
       </c>
       <c r="C621" s="4"/>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18508,22 +18512,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C622" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>馬迪</t>
+        </is>
+      </c>
+      <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18541,18 +18541,22 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
-        </is>
-      </c>
-      <c r="C623" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C623" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E623" s="4"/>
@@ -18570,18 +18574,18 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C624" s="4"/>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E624" s="4"/>
@@ -18599,18 +18603,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18628,18 +18632,18 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E626" s="4"/>
@@ -18657,18 +18661,18 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E627" s="4"/>
@@ -18686,18 +18690,18 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C628" s="4"/>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18715,18 +18719,18 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高聖景</t>
         </is>
       </c>
       <c r="C629" s="4"/>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E629" s="4"/>
@@ -18744,22 +18748,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C630" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高莉婷</t>
+        </is>
+      </c>
+      <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18777,18 +18777,22 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
-        </is>
-      </c>
-      <c r="C631" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C631" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E631" s="4"/>
@@ -18806,18 +18810,18 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C632" s="4"/>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0937742352</t>
         </is>
       </c>
       <c r="E632" s="4"/>
@@ -18835,16 +18839,20 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C633" s="4"/>
-      <c r="D633" s="4"/>
+      <c r="D633" s="4" t="inlineStr">
+        <is>
+          <t>0989116588</t>
+        </is>
+      </c>
       <c r="E633" s="4"/>
       <c r="F633" s="4" t="inlineStr">
         <is>
@@ -18860,20 +18868,16 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B634" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>鴻</t>
         </is>
       </c>
       <c r="C634" s="4"/>
-      <c r="D634" s="4" t="inlineStr">
-        <is>
-          <t>0958180882</t>
-        </is>
-      </c>
+      <c r="D634" s="4"/>
       <c r="E634" s="4"/>
       <c r="F634" s="4" t="inlineStr">
         <is>
@@ -18889,22 +18893,18 @@
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C635" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
+          <t>黃俊翰</t>
+        </is>
+      </c>
+      <c r="C635" s="4"/>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>0903975921</t>
+          <t>0958180882</t>
         </is>
       </c>
       <c r="E635" s="4"/>
@@ -18922,16 +18922,24 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B636" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
-        </is>
-      </c>
-      <c r="C636" s="4"/>
-      <c r="D636" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C636" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
+      <c r="D636" s="4" t="inlineStr">
+        <is>
+          <t>0903975921</t>
+        </is>
+      </c>
       <c r="E636" s="4"/>
       <c r="F636" s="4" t="inlineStr">
         <is>
@@ -18947,20 +18955,16 @@
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C637" s="4"/>
-      <c r="D637" s="4" t="inlineStr">
-        <is>
-          <t>0938722217</t>
-        </is>
-      </c>
+      <c r="D637" s="4"/>
       <c r="E637" s="4"/>
       <c r="F637" s="4" t="inlineStr">
         <is>
@@ -18976,18 +18980,18 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B638" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C638" s="4"/>
       <c r="D638" s="4" t="inlineStr">
         <is>
-          <t>0989628136</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E638" s="4"/>
@@ -19005,18 +19009,18 @@
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C639" s="4"/>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E639" s="4"/>
@@ -19034,18 +19038,18 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>M2604190003</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B640" s="4" t="inlineStr">
         <is>
-          <t>黃士凱</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C640" s="4"/>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>0934179571</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E640" s="4"/>
@@ -19063,18 +19067,18 @@
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2604190003</t>
         </is>
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃士凱</t>
         </is>
       </c>
       <c r="C641" s="4"/>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0934179571</t>
         </is>
       </c>
       <c r="E641" s="4"/>
@@ -19092,18 +19096,18 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B642" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C642" s="4"/>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E642" s="4"/>
@@ -19121,18 +19125,18 @@
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C643" s="4"/>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E643" s="4"/>
@@ -19150,18 +19154,18 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>M2604120001</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B644" s="4" t="inlineStr">
         <is>
-          <t>黃宥文</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C644" s="4"/>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>0953082147</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E644" s="4"/>
@@ -19179,18 +19183,18 @@
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2604120001</t>
         </is>
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宥文</t>
         </is>
       </c>
       <c r="C645" s="4"/>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0953082147</t>
         </is>
       </c>
       <c r="E645" s="4"/>
@@ -19208,18 +19212,18 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B646" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C646" s="4"/>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E646" s="4"/>
@@ -19237,22 +19241,18 @@
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C647" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃庠豪</t>
+        </is>
+      </c>
+      <c r="C647" s="4"/>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E647" s="4"/>
@@ -19270,18 +19270,22 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B648" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
-        </is>
-      </c>
-      <c r="C648" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C648" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E648" s="4"/>
@@ -19299,18 +19303,18 @@
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C649" s="4"/>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E649" s="4"/>
@@ -19328,18 +19332,18 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B650" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C650" s="4"/>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E650" s="4"/>
@@ -19357,18 +19361,18 @@
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B651" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C651" s="4"/>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E651" s="4"/>
@@ -19386,18 +19390,18 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B652" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C652" s="4"/>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E652" s="4"/>
@@ -19415,18 +19419,18 @@
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B653" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C653" s="4"/>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E653" s="4"/>
@@ -19444,18 +19448,18 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B654" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C654" s="4"/>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E654" s="4"/>
@@ -19473,18 +19477,18 @@
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B655" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C655" s="4"/>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E655" s="4"/>
@@ -19502,18 +19506,18 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B656" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C656" s="4"/>
       <c r="D656" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E656" s="4"/>
@@ -19531,18 +19535,18 @@
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B657" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C657" s="4"/>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E657" s="4"/>
@@ -19560,18 +19564,18 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B658" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C658" s="4"/>
       <c r="D658" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E658" s="4"/>
@@ -19589,18 +19593,18 @@
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B659" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C659" s="4"/>
       <c r="D659" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E659" s="4"/>
@@ -19618,18 +19622,18 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B660" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C660" s="4"/>
       <c r="D660" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E660" s="4"/>
@@ -19647,18 +19651,18 @@
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
         <is>
-          <t>M2604190001</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B661" s="4" t="inlineStr">
         <is>
-          <t>黃貞菱</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C661" s="4"/>
       <c r="D661" s="4" t="inlineStr">
         <is>
-          <t>0987793062</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E661" s="4"/>
@@ -19676,18 +19680,18 @@
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2604190001</t>
         </is>
       </c>
       <c r="B662" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃貞菱</t>
         </is>
       </c>
       <c r="C662" s="4"/>
       <c r="D662" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0987793062</t>
         </is>
       </c>
       <c r="E662" s="4"/>
@@ -19705,18 +19709,18 @@
     <row r="663">
       <c r="A663" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B663" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C663" s="4"/>
       <c r="D663" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E663" s="4"/>
@@ -19734,18 +19738,18 @@
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B664" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C664" s="4"/>
       <c r="D664" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E664" s="4"/>
@@ -19763,18 +19767,18 @@
     <row r="665">
       <c r="A665" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2510020007</t>
         </is>
       </c>
       <c r="B665" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃鴻麒</t>
         </is>
       </c>
       <c r="C665" s="4"/>
       <c r="D665" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0930571975</t>
         </is>
       </c>
       <c r="E665" s="4"/>
@@ -19792,18 +19796,18 @@
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2602270002</t>
         </is>
       </c>
       <c r="B666" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黎信宏</t>
         </is>
       </c>
       <c r="C666" s="4"/>
       <c r="D666" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0911024337</t>
         </is>
       </c>
       <c r="E666" s="4"/>
@@ -19819,9 +19823,38 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>2026/04/25  13:00:10</t>
+      <c r="A667" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B667" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C667" s="4"/>
+      <c r="D667" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E667" s="4"/>
+      <c r="F667" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G667" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026/04/26  13:00:09</t>
         </is>
       </c>
     </row>

--- a/data/_tmp_ecount_cust.xlsx
+++ b/data/_tmp_ecount_cust.xlsx
@@ -14932,22 +14932,18 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>M2603280001</t>
+          <t>M2604260001</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>賴柏舟</t>
-        </is>
-      </c>
-      <c r="C502" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股五福路11號</t>
-        </is>
-      </c>
+          <t>賴柏嘉</t>
+        </is>
+      </c>
+      <c r="C502" s="4"/>
       <c r="D502" s="4" t="inlineStr">
         <is>
-          <t>0979131818</t>
+          <t>0966410241</t>
         </is>
       </c>
       <c r="E502" s="4"/>
@@ -14965,18 +14961,22 @@
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>M2509300017</t>
+          <t>M2603280001</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>賴珊珊</t>
-        </is>
-      </c>
-      <c r="C503" s="4"/>
+          <t>賴柏舟</t>
+        </is>
+      </c>
+      <c r="C503" s="4" t="inlineStr">
+        <is>
+          <t>新北市五股五福路11號</t>
+        </is>
+      </c>
       <c r="D503" s="4" t="inlineStr">
         <is>
-          <t>0963692398</t>
+          <t>0979131818</t>
         </is>
       </c>
       <c r="E503" s="4"/>
@@ -14994,18 +14994,18 @@
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>M2510260006</t>
+          <t>M2509300017</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>賴瑞軒</t>
+          <t>賴珊珊</t>
         </is>
       </c>
       <c r="C504" s="4"/>
       <c r="D504" s="4" t="inlineStr">
         <is>
-          <t>0934323252</t>
+          <t>0963692398</t>
         </is>
       </c>
       <c r="E504" s="4"/>
@@ -15023,22 +15023,18 @@
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>M2602150001</t>
+          <t>M2510260006</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>賴長鍾</t>
-        </is>
-      </c>
-      <c r="C505" s="4" t="inlineStr">
-        <is>
-          <t>新北市金山區美田里中山路363號</t>
-        </is>
-      </c>
+          <t>賴瑞軒</t>
+        </is>
+      </c>
+      <c r="C505" s="4"/>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>0988981898</t>
+          <t>0934323252</t>
         </is>
       </c>
       <c r="E505" s="4"/>
@@ -15056,22 +15052,22 @@
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>M2509270018</t>
+          <t>M2602150001</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>趙云璟</t>
+          <t>賴長鍾</t>
         </is>
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>新北市中和區中山路2段366巷13-1號1樓</t>
+          <t>新北市金山區美田里中山路363號</t>
         </is>
       </c>
       <c r="D506" s="4" t="inlineStr">
         <is>
-          <t>0930566511</t>
+          <t>0988981898</t>
         </is>
       </c>
       <c r="E506" s="4"/>
@@ -15089,22 +15085,22 @@
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>M2510260001</t>
+          <t>M2509270018</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>趙偉庭</t>
+          <t>趙云璟</t>
         </is>
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北市中和區中山路2段366巷13-1號1樓</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>0939115565</t>
+          <t>0930566511</t>
         </is>
       </c>
       <c r="E507" s="4"/>
@@ -15122,18 +15118,22 @@
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>M2603060001</t>
+          <t>M2510260001</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>趙溫仁</t>
-        </is>
-      </c>
-      <c r="C508" s="4"/>
+          <t>趙偉庭</t>
+        </is>
+      </c>
+      <c r="C508" s="4" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
       <c r="D508" s="4" t="inlineStr">
         <is>
-          <t>0982168220</t>
+          <t>0939115565</t>
         </is>
       </c>
       <c r="E508" s="4"/>
@@ -15151,18 +15151,18 @@
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>M2601170001</t>
+          <t>M2603060001</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>辰彥希</t>
+          <t>趙溫仁</t>
         </is>
       </c>
       <c r="C509" s="4"/>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>0986258793</t>
+          <t>0982168220</t>
         </is>
       </c>
       <c r="E509" s="4"/>
@@ -15180,18 +15180,18 @@
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>M2510130009</t>
+          <t>M2601170001</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>連宏泰(阿泰)</t>
+          <t>辰彥希</t>
         </is>
       </c>
       <c r="C510" s="4"/>
       <c r="D510" s="4" t="inlineStr">
         <is>
-          <t>0982484963</t>
+          <t>0986258793</t>
         </is>
       </c>
       <c r="E510" s="4"/>
@@ -15209,20 +15209,24 @@
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>V0004</t>
+          <t>M2510130009</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>逸忠食品</t>
+          <t>連宏泰(阿泰)</t>
         </is>
       </c>
       <c r="C511" s="4"/>
-      <c r="D511" s="4"/>
+      <c r="D511" s="4" t="inlineStr">
+        <is>
+          <t>0982484963</t>
+        </is>
+      </c>
       <c r="E511" s="4"/>
       <c r="F511" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G511" s="5" t="inlineStr">
@@ -15234,24 +15238,20 @@
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>M2602120004</t>
+          <t>V0004</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>邱健哲</t>
+          <t>逸忠食品</t>
         </is>
       </c>
       <c r="C512" s="4"/>
-      <c r="D512" s="4" t="inlineStr">
-        <is>
-          <t>0981898339</t>
-        </is>
-      </c>
+      <c r="D512" s="4"/>
       <c r="E512" s="4"/>
       <c r="F512" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G512" s="5" t="inlineStr">
@@ -15263,18 +15263,18 @@
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>M2511010004</t>
+          <t>M2602120004</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>邱品媗</t>
+          <t>邱健哲</t>
         </is>
       </c>
       <c r="C513" s="4"/>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>0903921531</t>
+          <t>0981898339</t>
         </is>
       </c>
       <c r="E513" s="4"/>
@@ -15292,18 +15292,18 @@
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>M2509290009</t>
+          <t>M2511010004</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>邱妙方</t>
+          <t>邱品媗</t>
         </is>
       </c>
       <c r="C514" s="4"/>
       <c r="D514" s="4" t="inlineStr">
         <is>
-          <t>0973618284</t>
+          <t>0903921531</t>
         </is>
       </c>
       <c r="E514" s="4"/>
@@ -15321,18 +15321,18 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>M2509300009</t>
+          <t>M2509290009</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>邱彥棋</t>
+          <t>邱妙方</t>
         </is>
       </c>
       <c r="C515" s="4"/>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>0930038997</t>
+          <t>0973618284</t>
         </is>
       </c>
       <c r="E515" s="4"/>
@@ -15350,18 +15350,18 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>M2509270013</t>
+          <t>M2509300009</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>邱振為</t>
+          <t>邱彥棋</t>
         </is>
       </c>
       <c r="C516" s="4"/>
       <c r="D516" s="4" t="inlineStr">
         <is>
-          <t>0972462790</t>
+          <t>0930038997</t>
         </is>
       </c>
       <c r="E516" s="4"/>
@@ -15379,18 +15379,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>M2512060002</t>
+          <t>M2509270013</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>邱政傑</t>
+          <t>邱振為</t>
         </is>
       </c>
       <c r="C517" s="4"/>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>0958526321</t>
+          <t>0972462790</t>
         </is>
       </c>
       <c r="E517" s="4"/>
@@ -15408,22 +15408,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>M2509260051</t>
+          <t>M2512060002</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>邱棕茗</t>
-        </is>
-      </c>
-      <c r="C518" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區青雲路517號</t>
-        </is>
-      </c>
+          <t>邱政傑</t>
+        </is>
+      </c>
+      <c r="C518" s="4"/>
       <c r="D518" s="4" t="inlineStr">
         <is>
-          <t>0987763212</t>
+          <t>0958526321</t>
         </is>
       </c>
       <c r="E518" s="4"/>
@@ -15441,18 +15437,22 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>M2509270006</t>
+          <t>M2509260051</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>邱程皓</t>
-        </is>
-      </c>
-      <c r="C519" s="4"/>
+          <t>邱棕茗</t>
+        </is>
+      </c>
+      <c r="C519" s="4" t="inlineStr">
+        <is>
+          <t>新北市土城區青雲路517號</t>
+        </is>
+      </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>0932069947</t>
+          <t>0987763212</t>
         </is>
       </c>
       <c r="E519" s="4"/>
@@ -15470,18 +15470,18 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>M2510260003</t>
+          <t>M2509270006</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>郭一帆</t>
+          <t>邱程皓</t>
         </is>
       </c>
       <c r="C520" s="4"/>
       <c r="D520" s="4" t="inlineStr">
         <is>
-          <t>0952590597</t>
+          <t>0932069947</t>
         </is>
       </c>
       <c r="E520" s="4"/>
@@ -15499,18 +15499,18 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>M2510120002</t>
+          <t>M2510260003</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>郭佳穎</t>
+          <t>郭一帆</t>
         </is>
       </c>
       <c r="C521" s="4"/>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>0908227630</t>
+          <t>0952590597</t>
         </is>
       </c>
       <c r="E521" s="4"/>
@@ -15528,7 +15528,7 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>M2510150004</t>
+          <t>M2510120002</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
@@ -15557,18 +15557,18 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>M2511080001</t>
+          <t>M2510150004</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>郭啓祥</t>
+          <t>郭佳穎</t>
         </is>
       </c>
       <c r="C523" s="4"/>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>0935329653</t>
+          <t>0908227630</t>
         </is>
       </c>
       <c r="E523" s="4"/>
@@ -15586,16 +15586,20 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>M2510080007</t>
+          <t>M2511080001</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>郭妍希</t>
+          <t>郭啓祥</t>
         </is>
       </c>
       <c r="C524" s="4"/>
-      <c r="D524" s="4"/>
+      <c r="D524" s="4" t="inlineStr">
+        <is>
+          <t>0935329653</t>
+        </is>
+      </c>
       <c r="E524" s="4"/>
       <c r="F524" s="4" t="inlineStr">
         <is>
@@ -15611,20 +15615,16 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>M2509280005</t>
+          <t>M2510080007</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>郭婷昀</t>
+          <t>郭妍希</t>
         </is>
       </c>
       <c r="C525" s="4"/>
-      <c r="D525" s="4" t="inlineStr">
-        <is>
-          <t>0976588171</t>
-        </is>
-      </c>
+      <c r="D525" s="4"/>
       <c r="E525" s="4"/>
       <c r="F525" s="4" t="inlineStr">
         <is>
@@ -15640,18 +15640,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>M2603240001</t>
+          <t>M2509280005</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>郭宗裕</t>
+          <t>郭婷昀</t>
         </is>
       </c>
       <c r="C526" s="4"/>
       <c r="D526" s="4" t="inlineStr">
         <is>
-          <t>0972128080</t>
+          <t>0976588171</t>
         </is>
       </c>
       <c r="E526" s="4"/>
@@ -15669,18 +15669,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>M2509300006</t>
+          <t>M2603240001</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>郭富森</t>
+          <t>郭宗裕</t>
         </is>
       </c>
       <c r="C527" s="4"/>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>0988070004</t>
+          <t>0972128080</t>
         </is>
       </c>
       <c r="E527" s="4"/>
@@ -15698,18 +15698,18 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>M2511100002</t>
+          <t>M2509300006</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>郭文藝</t>
+          <t>郭富森</t>
         </is>
       </c>
       <c r="C528" s="4"/>
       <c r="D528" s="4" t="inlineStr">
         <is>
-          <t>0922001777</t>
+          <t>0988070004</t>
         </is>
       </c>
       <c r="E528" s="4"/>
@@ -15727,18 +15727,18 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>M2509270003</t>
+          <t>M2511100002</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>郭明財</t>
+          <t>郭文藝</t>
         </is>
       </c>
       <c r="C529" s="4"/>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>0938555280</t>
+          <t>0922001777</t>
         </is>
       </c>
       <c r="E529" s="4"/>
@@ -15756,18 +15756,18 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>M2511130003</t>
+          <t>M2509270003</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>郭正岳</t>
+          <t>郭明財</t>
         </is>
       </c>
       <c r="C530" s="4"/>
       <c r="D530" s="4" t="inlineStr">
         <is>
-          <t>0980205325</t>
+          <t>0938555280</t>
         </is>
       </c>
       <c r="E530" s="4"/>
@@ -15785,18 +15785,18 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>M2509290017</t>
+          <t>M2511130003</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>郭菁菁</t>
+          <t>郭正岳</t>
         </is>
       </c>
       <c r="C531" s="4"/>
       <c r="D531" s="4" t="inlineStr">
         <is>
-          <t>0953755312</t>
+          <t>0980205325</t>
         </is>
       </c>
       <c r="E531" s="4"/>
@@ -15814,18 +15814,18 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>M2510190003</t>
+          <t>M2509290017</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>郭鼎昇</t>
+          <t>郭菁菁</t>
         </is>
       </c>
       <c r="C532" s="4"/>
       <c r="D532" s="4" t="inlineStr">
         <is>
-          <t>0920234911</t>
+          <t>0953755312</t>
         </is>
       </c>
       <c r="E532" s="4"/>
@@ -15843,18 +15843,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>M2511080002</t>
+          <t>M2510190003</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>鄒育燁</t>
+          <t>郭鼎昇</t>
         </is>
       </c>
       <c r="C533" s="4"/>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>0928597862</t>
+          <t>0920234911</t>
         </is>
       </c>
       <c r="E533" s="4"/>
@@ -15872,22 +15872,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>M2511200001</t>
+          <t>M2511080002</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>鄭冠淵</t>
-        </is>
-      </c>
-      <c r="C534" s="4" t="inlineStr">
-        <is>
-          <t>高雄市大寮區內厝路240號</t>
-        </is>
-      </c>
+          <t>鄒育燁</t>
+        </is>
+      </c>
+      <c r="C534" s="4"/>
       <c r="D534" s="4" t="inlineStr">
         <is>
-          <t>0981690569</t>
+          <t>0928597862</t>
         </is>
       </c>
       <c r="E534" s="4"/>
@@ -15905,18 +15901,22 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>M2510110002</t>
+          <t>M2511200001</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>鄭太淵</t>
-        </is>
-      </c>
-      <c r="C535" s="4"/>
+          <t>鄭冠淵</t>
+        </is>
+      </c>
+      <c r="C535" s="4" t="inlineStr">
+        <is>
+          <t>高雄市大寮區內厝路240號</t>
+        </is>
+      </c>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>0983021311</t>
+          <t>0981690569</t>
         </is>
       </c>
       <c r="E535" s="4"/>
@@ -15934,18 +15934,18 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>M2509260012</t>
+          <t>M2510110002</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>鄭宇清</t>
+          <t>鄭太淵</t>
         </is>
       </c>
       <c r="C536" s="4"/>
       <c r="D536" s="4" t="inlineStr">
         <is>
-          <t>0987221636</t>
+          <t>0983021311</t>
         </is>
       </c>
       <c r="E536" s="4"/>
@@ -15963,18 +15963,18 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>M2512070001</t>
+          <t>M2509260012</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>鄭宇翔</t>
+          <t>鄭宇清</t>
         </is>
       </c>
       <c r="C537" s="4"/>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>0910903435</t>
+          <t>0987221636</t>
         </is>
       </c>
       <c r="E537" s="4"/>
@@ -15992,18 +15992,18 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>M2510020009</t>
+          <t>M2512070001</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>鄭家展</t>
+          <t>鄭宇翔</t>
         </is>
       </c>
       <c r="C538" s="4"/>
       <c r="D538" s="4" t="inlineStr">
         <is>
-          <t>0912004455</t>
+          <t>0910903435</t>
         </is>
       </c>
       <c r="E538" s="4"/>
@@ -16021,18 +16021,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>M2510130007</t>
+          <t>M2510020009</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>鄭益維</t>
+          <t>鄭家展</t>
         </is>
       </c>
       <c r="C539" s="4"/>
       <c r="D539" s="4" t="inlineStr">
         <is>
-          <t>0955453515</t>
+          <t>0912004455</t>
         </is>
       </c>
       <c r="E539" s="4"/>
@@ -16050,18 +16050,18 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>M2511190001</t>
+          <t>M2510130007</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>鄭秉霖</t>
+          <t>鄭益維</t>
         </is>
       </c>
       <c r="C540" s="4"/>
       <c r="D540" s="4" t="inlineStr">
         <is>
-          <t>0903781839</t>
+          <t>0955453515</t>
         </is>
       </c>
       <c r="E540" s="4"/>
@@ -16079,18 +16079,18 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>M2509260025</t>
+          <t>M2511190001</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>鄭竣元</t>
+          <t>鄭秉霖</t>
         </is>
       </c>
       <c r="C541" s="4"/>
       <c r="D541" s="4" t="inlineStr">
         <is>
-          <t>0928555551</t>
+          <t>0903781839</t>
         </is>
       </c>
       <c r="E541" s="4"/>
@@ -16108,22 +16108,18 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>M2510260004</t>
+          <t>M2509260025</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>鄭鉅耀</t>
-        </is>
-      </c>
-      <c r="C542" s="4" t="inlineStr">
-        <is>
-          <t>新北市五股區成泰路二段208號</t>
-        </is>
-      </c>
+          <t>鄭竣元</t>
+        </is>
+      </c>
+      <c r="C542" s="4"/>
       <c r="D542" s="4" t="inlineStr">
         <is>
-          <t>0962029589</t>
+          <t>0928555551</t>
         </is>
       </c>
       <c r="E542" s="4"/>
@@ -16141,22 +16137,22 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>M2510120001</t>
+          <t>M2510260004</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>鄭雁予</t>
+          <t>鄭鉅耀</t>
         </is>
       </c>
       <c r="C543" s="4" t="inlineStr">
         <is>
-          <t>桃園區國聖二街145號5樓之1</t>
+          <t>新北市五股區成泰路二段208號</t>
         </is>
       </c>
       <c r="D543" s="4" t="inlineStr">
         <is>
-          <t>0968001310</t>
+          <t>0962029589</t>
         </is>
       </c>
       <c r="E543" s="4"/>
@@ -16174,18 +16170,22 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>M2601070001</t>
+          <t>M2510120001</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>鍾佑鑫</t>
-        </is>
-      </c>
-      <c r="C544" s="4"/>
+          <t>鄭雁予</t>
+        </is>
+      </c>
+      <c r="C544" s="4" t="inlineStr">
+        <is>
+          <t>桃園區國聖二街145號5樓之1</t>
+        </is>
+      </c>
       <c r="D544" s="4" t="inlineStr">
         <is>
-          <t>0925070281</t>
+          <t>0968001310</t>
         </is>
       </c>
       <c r="E544" s="4"/>
@@ -16203,18 +16203,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>M2510060007</t>
+          <t>M2601070001</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>鍾佳臻</t>
+          <t>鍾佑鑫</t>
         </is>
       </c>
       <c r="C545" s="4"/>
       <c r="D545" s="4" t="inlineStr">
         <is>
-          <t>0973933069</t>
+          <t>0925070281</t>
         </is>
       </c>
       <c r="E545" s="4"/>
@@ -16232,18 +16232,18 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>M2509260010</t>
+          <t>M2510060007</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>鍾宜潔</t>
+          <t>鍾佳臻</t>
         </is>
       </c>
       <c r="C546" s="4"/>
       <c r="D546" s="4" t="inlineStr">
         <is>
-          <t>0906073109</t>
+          <t>0973933069</t>
         </is>
       </c>
       <c r="E546" s="4"/>
@@ -16261,18 +16261,18 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>M2509290007</t>
+          <t>M2509260010</t>
         </is>
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>鍾銘峰</t>
+          <t>鍾宜潔</t>
         </is>
       </c>
       <c r="C547" s="4"/>
       <c r="D547" s="4" t="inlineStr">
         <is>
-          <t>0981895637</t>
+          <t>0906073109</t>
         </is>
       </c>
       <c r="E547" s="4"/>
@@ -16290,18 +16290,18 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>M2512070002</t>
+          <t>M2509290007</t>
         </is>
       </c>
       <c r="B548" s="4" t="inlineStr">
         <is>
-          <t>鐘國禎</t>
+          <t>鍾銘峰</t>
         </is>
       </c>
       <c r="C548" s="4"/>
       <c r="D548" s="4" t="inlineStr">
         <is>
-          <t>0984297889</t>
+          <t>0981895637</t>
         </is>
       </c>
       <c r="E548" s="4"/>
@@ -16319,22 +16319,18 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>M2603200001</t>
+          <t>M2512070002</t>
         </is>
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>鐘志和</t>
-        </is>
-      </c>
-      <c r="C549" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
-        </is>
-      </c>
+          <t>鐘國禎</t>
+        </is>
+      </c>
+      <c r="C549" s="4"/>
       <c r="D549" s="4" t="inlineStr">
         <is>
-          <t>0920482535</t>
+          <t>0984297889</t>
         </is>
       </c>
       <c r="E549" s="4"/>
@@ -16352,24 +16348,28 @@
     <row r="550">
       <c r="A550" s="4" t="inlineStr">
         <is>
-          <t>M2603270001</t>
+          <t>M2603200001</t>
         </is>
       </c>
       <c r="B550" s="4" t="inlineStr">
         <is>
-          <t>鐘駿霆</t>
-        </is>
-      </c>
-      <c r="C550" s="4"/>
+          <t>鐘志和</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>台北市內湖區陽光街92巷24弄4號一樓</t>
+        </is>
+      </c>
       <c r="D550" s="4" t="inlineStr">
         <is>
-          <t>0919331886</t>
+          <t>0920482535</t>
         </is>
       </c>
       <c r="E550" s="4"/>
       <c r="F550" s="4" t="inlineStr">
         <is>
-          <t>門店</t>
+          <t>批發</t>
         </is>
       </c>
       <c r="G550" s="5" t="inlineStr">
@@ -16381,24 +16381,24 @@
     <row r="551">
       <c r="A551" s="4" t="inlineStr">
         <is>
-          <t>M2510100009</t>
+          <t>M2603270001</t>
         </is>
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>阮海德</t>
+          <t>鐘駿霆</t>
         </is>
       </c>
       <c r="C551" s="4"/>
       <c r="D551" s="4" t="inlineStr">
         <is>
-          <t>0938961670</t>
+          <t>0919331886</t>
         </is>
       </c>
       <c r="E551" s="4"/>
       <c r="F551" s="4" t="inlineStr">
         <is>
-          <t>批發</t>
+          <t>門店</t>
         </is>
       </c>
       <c r="G551" s="5" t="inlineStr">
@@ -16410,22 +16410,18 @@
     <row r="552">
       <c r="A552" s="4" t="inlineStr">
         <is>
-          <t>M2510080006</t>
+          <t>M2510100009</t>
         </is>
       </c>
       <c r="B552" s="4" t="inlineStr">
         <is>
-          <t>阿宗</t>
-        </is>
-      </c>
-      <c r="C552" s="4" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
-        </is>
-      </c>
+          <t>阮海德</t>
+        </is>
+      </c>
+      <c r="C552" s="4"/>
       <c r="D552" s="4" t="inlineStr">
         <is>
-          <t>0905599633</t>
+          <t>0938961670</t>
         </is>
       </c>
       <c r="E552" s="4"/>
@@ -16443,18 +16439,22 @@
     <row r="553">
       <c r="A553" s="4" t="inlineStr">
         <is>
-          <t>M2510220002</t>
+          <t>M2510080006</t>
         </is>
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>阿源</t>
-        </is>
-      </c>
-      <c r="C553" s="4"/>
+          <t>阿宗</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="inlineStr">
+        <is>
+          <t>新北市八里區龍米路二段37號9樓（管理室代收）</t>
+        </is>
+      </c>
       <c r="D553" s="4" t="inlineStr">
         <is>
-          <t>0917526547</t>
+          <t>0905599633</t>
         </is>
       </c>
       <c r="E553" s="4"/>
@@ -16472,18 +16472,18 @@
     <row r="554">
       <c r="A554" s="4" t="inlineStr">
         <is>
-          <t>M2510070002</t>
+          <t>M2510220002</t>
         </is>
       </c>
       <c r="B554" s="4" t="inlineStr">
         <is>
-          <t>阿良</t>
+          <t>阿源</t>
         </is>
       </c>
       <c r="C554" s="4"/>
       <c r="D554" s="4" t="inlineStr">
         <is>
-          <t>0920971386</t>
+          <t>0917526547</t>
         </is>
       </c>
       <c r="E554" s="4"/>
@@ -16501,22 +16501,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>M2512020002</t>
+          <t>M2510070002</t>
         </is>
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>陳仲盟</t>
-        </is>
-      </c>
-      <c r="C555" s="4" t="inlineStr">
-        <is>
-          <t>板橋大觀路一段38巷200弄12-1號</t>
-        </is>
-      </c>
+          <t>阿良</t>
+        </is>
+      </c>
+      <c r="C555" s="4"/>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>0958800768</t>
+          <t>0920971386</t>
         </is>
       </c>
       <c r="E555" s="4"/>
@@ -16534,18 +16530,22 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>M2510140005</t>
+          <t>M2512020002</t>
         </is>
       </c>
       <c r="B556" s="4" t="inlineStr">
         <is>
-          <t>陳俊嘉</t>
-        </is>
-      </c>
-      <c r="C556" s="4"/>
+          <t>陳仲盟</t>
+        </is>
+      </c>
+      <c r="C556" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路一段38巷200弄12-1號</t>
+        </is>
+      </c>
       <c r="D556" s="4" t="inlineStr">
         <is>
-          <t>0952737870</t>
+          <t>0958800768</t>
         </is>
       </c>
       <c r="E556" s="4"/>
@@ -16563,22 +16563,18 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>M2511190002</t>
+          <t>M2510140005</t>
         </is>
       </c>
       <c r="B557" s="4" t="inlineStr">
         <is>
-          <t>陳俊安</t>
-        </is>
-      </c>
-      <c r="C557" s="4" t="inlineStr">
-        <is>
-          <t>新北市土城區日和街7號22樓</t>
-        </is>
-      </c>
+          <t>陳俊嘉</t>
+        </is>
+      </c>
+      <c r="C557" s="4"/>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>0958035183</t>
+          <t>0952737870</t>
         </is>
       </c>
       <c r="E557" s="4"/>
@@ -16596,22 +16592,22 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>M2511230005</t>
+          <t>M2511190002</t>
         </is>
       </c>
       <c r="B558" s="4" t="inlineStr">
         <is>
-          <t>陳俊宏</t>
+          <t>陳俊安</t>
         </is>
       </c>
       <c r="C558" s="4" t="inlineStr">
         <is>
-          <t>板橋大觀路1段28巷118-1號</t>
+          <t>新北市土城區日和街7號22樓</t>
         </is>
       </c>
       <c r="D558" s="4" t="inlineStr">
         <is>
-          <t>0913860159</t>
+          <t>0958035183</t>
         </is>
       </c>
       <c r="E558" s="4"/>
@@ -16629,18 +16625,22 @@
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>M2603210001</t>
+          <t>M2511230005</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>陳俊豪</t>
-        </is>
-      </c>
-      <c r="C559" s="4"/>
+          <t>陳俊宏</t>
+        </is>
+      </c>
+      <c r="C559" s="4" t="inlineStr">
+        <is>
+          <t>板橋大觀路1段28巷118-1號</t>
+        </is>
+      </c>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>0963552750</t>
+          <t>0913860159</t>
         </is>
       </c>
       <c r="E559" s="4"/>
@@ -16658,18 +16658,18 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>M2603150001</t>
+          <t>M2603210001</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>陳冠竹</t>
+          <t>陳俊豪</t>
         </is>
       </c>
       <c r="C560" s="4"/>
       <c r="D560" s="4" t="inlineStr">
         <is>
-          <t>0955399866</t>
+          <t>0963552750</t>
         </is>
       </c>
       <c r="E560" s="4"/>
@@ -16687,18 +16687,18 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>M2602040002</t>
+          <t>M2603150001</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>陳冠錚</t>
+          <t>陳冠竹</t>
         </is>
       </c>
       <c r="C561" s="4"/>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>0988077245</t>
+          <t>0955399866</t>
         </is>
       </c>
       <c r="E561" s="4"/>
@@ -16716,18 +16716,18 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>M2511010003</t>
+          <t>M2602040002</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>陳冠霖</t>
+          <t>陳冠錚</t>
         </is>
       </c>
       <c r="C562" s="4"/>
       <c r="D562" s="4" t="inlineStr">
         <is>
-          <t>0907780109</t>
+          <t>0988077245</t>
         </is>
       </c>
       <c r="E562" s="4"/>
@@ -16745,18 +16745,18 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>M2511220004</t>
+          <t>M2511010003</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>陳劭鈞</t>
+          <t>陳冠霖</t>
         </is>
       </c>
       <c r="C563" s="4"/>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>0928462448</t>
+          <t>0907780109</t>
         </is>
       </c>
       <c r="E563" s="4"/>
@@ -16774,18 +16774,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>M2509260015</t>
+          <t>M2511220004</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>陳勝榮</t>
+          <t>陳劭鈞</t>
         </is>
       </c>
       <c r="C564" s="4"/>
       <c r="D564" s="4" t="inlineStr">
         <is>
-          <t>0986289611</t>
+          <t>0928462448</t>
         </is>
       </c>
       <c r="E564" s="4"/>
@@ -16803,18 +16803,18 @@
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>M2601170005</t>
+          <t>M2509260015</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>陳君鑫</t>
+          <t>陳勝榮</t>
         </is>
       </c>
       <c r="C565" s="4"/>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>0910168841</t>
+          <t>0986289611</t>
         </is>
       </c>
       <c r="E565" s="4"/>
@@ -16832,18 +16832,18 @@
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>M2602260002</t>
+          <t>M2601170005</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>陳嘉齊</t>
+          <t>陳君鑫</t>
         </is>
       </c>
       <c r="C566" s="4"/>
       <c r="D566" s="4" t="inlineStr">
         <is>
-          <t>0963669931</t>
+          <t>0910168841</t>
         </is>
       </c>
       <c r="E566" s="4"/>
@@ -16861,18 +16861,18 @@
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>M2510030008</t>
+          <t>M2602260002</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>陳奕融</t>
+          <t>陳嘉齊</t>
         </is>
       </c>
       <c r="C567" s="4"/>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>0925123906</t>
+          <t>0963669931</t>
         </is>
       </c>
       <c r="E567" s="4"/>
@@ -16890,18 +16890,18 @@
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>M2601130002</t>
+          <t>M2510030008</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>陳奕閔</t>
+          <t>陳奕融</t>
         </is>
       </c>
       <c r="C568" s="4"/>
       <c r="D568" s="4" t="inlineStr">
         <is>
-          <t>0913590319</t>
+          <t>0925123906</t>
         </is>
       </c>
       <c r="E568" s="4"/>
@@ -16919,22 +16919,18 @@
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>M2510120003</t>
+          <t>M2601130002</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>陳姿鋆</t>
-        </is>
-      </c>
-      <c r="C569" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁安街85號11樓</t>
-        </is>
-      </c>
+          <t>陳奕閔</t>
+        </is>
+      </c>
+      <c r="C569" s="4"/>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>0925262307</t>
+          <t>0913590319</t>
         </is>
       </c>
       <c r="E569" s="4"/>
@@ -16952,18 +16948,22 @@
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>M2603260001</t>
+          <t>M2510120003</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>陳威宇</t>
-        </is>
-      </c>
-      <c r="C570" s="4"/>
+          <t>陳姿鋆</t>
+        </is>
+      </c>
+      <c r="C570" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁安街85號11樓</t>
+        </is>
+      </c>
       <c r="D570" s="4" t="inlineStr">
         <is>
-          <t>0958186337</t>
+          <t>0925262307</t>
         </is>
       </c>
       <c r="E570" s="4"/>
@@ -16981,18 +16981,18 @@
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>M2509290019</t>
+          <t>M2603260001</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>陳威燊</t>
+          <t>陳威宇</t>
         </is>
       </c>
       <c r="C571" s="4"/>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>0977070635</t>
+          <t>0958186337</t>
         </is>
       </c>
       <c r="E571" s="4"/>
@@ -17010,18 +17010,18 @@
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>M2510060008</t>
+          <t>M2509290019</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>陳子揚</t>
+          <t>陳威燊</t>
         </is>
       </c>
       <c r="C572" s="4"/>
       <c r="D572" s="4" t="inlineStr">
         <is>
-          <t>0968000493</t>
+          <t>0977070635</t>
         </is>
       </c>
       <c r="E572" s="4"/>
@@ -17039,18 +17039,18 @@
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>M2509260038</t>
+          <t>M2510060008</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>陳子杰</t>
+          <t>陳子揚</t>
         </is>
       </c>
       <c r="C573" s="4"/>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>0981382095</t>
+          <t>0968000493</t>
         </is>
       </c>
       <c r="E573" s="4"/>
@@ -17068,22 +17068,18 @@
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>M2603120002</t>
+          <t>M2509260038</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>陳宏文</t>
-        </is>
-      </c>
-      <c r="C574" s="4" t="inlineStr">
-        <is>
-          <t>基隆市中正區信七路1號</t>
-        </is>
-      </c>
+          <t>陳子杰</t>
+        </is>
+      </c>
+      <c r="C574" s="4"/>
       <c r="D574" s="4" t="inlineStr">
         <is>
-          <t>0985400202</t>
+          <t>0981382095</t>
         </is>
       </c>
       <c r="E574" s="4"/>
@@ -17101,18 +17097,22 @@
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>M2509260060</t>
+          <t>M2603120002</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>陳宏達</t>
-        </is>
-      </c>
-      <c r="C575" s="4"/>
+          <t>陳宏文</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="inlineStr">
+        <is>
+          <t>基隆市中正區信七路1號</t>
+        </is>
+      </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>0975912713</t>
+          <t>0985400202</t>
         </is>
       </c>
       <c r="E575" s="4"/>
@@ -17130,22 +17130,18 @@
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>M2510090011</t>
+          <t>M2509260060</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>陳家偉</t>
-        </is>
-      </c>
-      <c r="C576" s="4" t="inlineStr">
-        <is>
-          <t>宜蘭市神農路一段72號</t>
-        </is>
-      </c>
+          <t>陳宏達</t>
+        </is>
+      </c>
+      <c r="C576" s="4"/>
       <c r="D576" s="4" t="inlineStr">
         <is>
-          <t>0911102248</t>
+          <t>0975912713</t>
         </is>
       </c>
       <c r="E576" s="4"/>
@@ -17163,18 +17159,22 @@
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>M2510110010</t>
+          <t>M2510090011</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>陳小雨</t>
-        </is>
-      </c>
-      <c r="C577" s="4"/>
+          <t>陳家偉</t>
+        </is>
+      </c>
+      <c r="C577" s="4" t="inlineStr">
+        <is>
+          <t>宜蘭市神農路一段72號</t>
+        </is>
+      </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>0970099259</t>
+          <t>0911102248</t>
         </is>
       </c>
       <c r="E577" s="4"/>
@@ -17192,18 +17192,18 @@
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>M2512160001</t>
+          <t>M2510110010</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>陳建宏</t>
+          <t>陳小雨</t>
         </is>
       </c>
       <c r="C578" s="4"/>
       <c r="D578" s="4" t="inlineStr">
         <is>
-          <t>0910776812</t>
+          <t>0970099259</t>
         </is>
       </c>
       <c r="E578" s="4"/>
@@ -17221,22 +17221,18 @@
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>M2602010001</t>
+          <t>M2512160001</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>陳建宏(花蓮)</t>
-        </is>
-      </c>
-      <c r="C579" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉佳林31之19號</t>
-        </is>
-      </c>
+          <t>陳建宏</t>
+        </is>
+      </c>
+      <c r="C579" s="4"/>
       <c r="D579" s="4" t="inlineStr">
         <is>
-          <t>0963672312</t>
+          <t>0910776812</t>
         </is>
       </c>
       <c r="E579" s="4"/>
@@ -17254,22 +17250,22 @@
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>M2512030001</t>
+          <t>M2602010001</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>陳建華</t>
+          <t>陳建宏(花蓮)</t>
         </is>
       </c>
       <c r="C580" s="4" t="inlineStr">
         <is>
-          <t>新北市三重區仁美街125號</t>
+          <t>花蓮縣新城鄉佳林31之19號</t>
         </is>
       </c>
       <c r="D580" s="4" t="inlineStr">
         <is>
-          <t>0933886054</t>
+          <t>0963672312</t>
         </is>
       </c>
       <c r="E580" s="4"/>
@@ -17287,18 +17283,22 @@
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>M2509260002</t>
+          <t>M2512030001</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>陳志瑋</t>
-        </is>
-      </c>
-      <c r="C581" s="4"/>
+          <t>陳建華</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁美街125號</t>
+        </is>
+      </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>0920436103</t>
+          <t>0933886054</t>
         </is>
       </c>
       <c r="E581" s="4"/>
@@ -17316,18 +17316,18 @@
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>M2601130001</t>
+          <t>M2509260002</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>陳志銘</t>
+          <t>陳志瑋</t>
         </is>
       </c>
       <c r="C582" s="4"/>
       <c r="D582" s="4" t="inlineStr">
         <is>
-          <t>0925112114</t>
+          <t>0920436103</t>
         </is>
       </c>
       <c r="E582" s="4"/>
@@ -17345,18 +17345,18 @@
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>M2511080006</t>
+          <t>M2601130001</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>陳思亮</t>
+          <t>陳志銘</t>
         </is>
       </c>
       <c r="C583" s="4"/>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>0932323317</t>
+          <t>0925112114</t>
         </is>
       </c>
       <c r="E583" s="4"/>
@@ -17374,18 +17374,18 @@
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>M2510080008</t>
+          <t>M2511080006</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>陳怡如(彥鈞)</t>
+          <t>陳思亮</t>
         </is>
       </c>
       <c r="C584" s="4"/>
       <c r="D584" s="4" t="inlineStr">
         <is>
-          <t>0953829000</t>
+          <t>0932323317</t>
         </is>
       </c>
       <c r="E584" s="4"/>
@@ -17403,18 +17403,18 @@
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>M2601030001</t>
+          <t>M2510080008</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>陳慶壎</t>
+          <t>陳怡如(彥鈞)</t>
         </is>
       </c>
       <c r="C585" s="4"/>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>0981785402</t>
+          <t>0953829000</t>
         </is>
       </c>
       <c r="E585" s="4"/>
@@ -17432,18 +17432,18 @@
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>M2512300002</t>
+          <t>M2601030001</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>陳敬惟</t>
+          <t>陳慶壎</t>
         </is>
       </c>
       <c r="C586" s="4"/>
       <c r="D586" s="4" t="inlineStr">
         <is>
-          <t>0970182988</t>
+          <t>0981785402</t>
         </is>
       </c>
       <c r="E586" s="4"/>
@@ -17461,22 +17461,18 @@
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>M2510290001</t>
+          <t>M2512300002</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>陳智盛</t>
-        </is>
-      </c>
-      <c r="C587" s="4" t="inlineStr">
-        <is>
-          <t>金好夾-新北市板橋區三民路二段139號</t>
-        </is>
-      </c>
+          <t>陳敬惟</t>
+        </is>
+      </c>
+      <c r="C587" s="4"/>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>0981166735</t>
+          <t>0970182988</t>
         </is>
       </c>
       <c r="E587" s="4"/>
@@ -17494,18 +17490,22 @@
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>M2509260014</t>
+          <t>M2510290001</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>陳朋堅</t>
-        </is>
-      </c>
-      <c r="C588" s="4"/>
+          <t>陳智盛</t>
+        </is>
+      </c>
+      <c r="C588" s="4" t="inlineStr">
+        <is>
+          <t>金好夾-新北市板橋區三民路二段139號</t>
+        </is>
+      </c>
       <c r="D588" s="4" t="inlineStr">
         <is>
-          <t>0953303829</t>
+          <t>0981166735</t>
         </is>
       </c>
       <c r="E588" s="4"/>
@@ -17523,22 +17523,18 @@
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>M2512060004</t>
+          <t>M2509260014</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>陳松廉</t>
-        </is>
-      </c>
-      <c r="C589" s="4" t="inlineStr">
-        <is>
-          <t>台北市內湖區星雲街30號</t>
-        </is>
-      </c>
+          <t>陳朋堅</t>
+        </is>
+      </c>
+      <c r="C589" s="4"/>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>0970012579</t>
+          <t>0953303829</t>
         </is>
       </c>
       <c r="E589" s="4"/>
@@ -17556,22 +17552,22 @@
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>M2511260002</t>
+          <t>M2512060004</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>陳柏瑞</t>
+          <t>陳松廉</t>
         </is>
       </c>
       <c r="C590" s="4" t="inlineStr">
         <is>
-          <t>桃園市南豐街258號</t>
+          <t>台北市內湖區星雲街30號</t>
         </is>
       </c>
       <c r="D590" s="4" t="inlineStr">
         <is>
-          <t>0974525272</t>
+          <t>0970012579</t>
         </is>
       </c>
       <c r="E590" s="4"/>
@@ -17589,18 +17585,22 @@
     <row r="591">
       <c r="A591" s="4" t="inlineStr">
         <is>
-          <t>M2511140002</t>
+          <t>M2511260002</t>
         </is>
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>陳柏衡</t>
-        </is>
-      </c>
-      <c r="C591" s="4"/>
+          <t>陳柏瑞</t>
+        </is>
+      </c>
+      <c r="C591" s="4" t="inlineStr">
+        <is>
+          <t>桃園市南豐街258號</t>
+        </is>
+      </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>0911484086</t>
+          <t>0974525272</t>
         </is>
       </c>
       <c r="E591" s="4"/>
@@ -17618,18 +17618,18 @@
     <row r="592">
       <c r="A592" s="4" t="inlineStr">
         <is>
-          <t>M2510100005</t>
+          <t>M2511140002</t>
         </is>
       </c>
       <c r="B592" s="4" t="inlineStr">
         <is>
-          <t>陳柏豪</t>
+          <t>陳柏衡</t>
         </is>
       </c>
       <c r="C592" s="4"/>
       <c r="D592" s="4" t="inlineStr">
         <is>
-          <t>0938719110</t>
+          <t>0911484086</t>
         </is>
       </c>
       <c r="E592" s="4"/>
@@ -17647,7 +17647,7 @@
     <row r="593">
       <c r="A593" s="4" t="inlineStr">
         <is>
-          <t>M2512060003</t>
+          <t>M2510100005</t>
         </is>
       </c>
       <c r="B593" s="4" t="inlineStr">
@@ -17658,7 +17658,7 @@
       <c r="C593" s="4"/>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>0972839078</t>
+          <t>0938719110</t>
         </is>
       </c>
       <c r="E593" s="4"/>
@@ -17676,18 +17676,18 @@
     <row r="594">
       <c r="A594" s="4" t="inlineStr">
         <is>
-          <t>M2510050011</t>
+          <t>M2512060003</t>
         </is>
       </c>
       <c r="B594" s="4" t="inlineStr">
         <is>
-          <t>陳正傑</t>
+          <t>陳柏豪</t>
         </is>
       </c>
       <c r="C594" s="4"/>
       <c r="D594" s="4" t="inlineStr">
         <is>
-          <t>0909975931</t>
+          <t>0972839078</t>
         </is>
       </c>
       <c r="E594" s="4"/>
@@ -17705,22 +17705,18 @@
     <row r="595">
       <c r="A595" s="4" t="inlineStr">
         <is>
-          <t>M2603070001</t>
+          <t>M2510050011</t>
         </is>
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>陳永民</t>
-        </is>
-      </c>
-      <c r="C595" s="4" t="inlineStr">
-        <is>
-          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
-        </is>
-      </c>
+          <t>陳正傑</t>
+        </is>
+      </c>
+      <c r="C595" s="4"/>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>0975851762</t>
+          <t>0909975931</t>
         </is>
       </c>
       <c r="E595" s="4"/>
@@ -17738,18 +17734,22 @@
     <row r="596">
       <c r="A596" s="4" t="inlineStr">
         <is>
-          <t>M2510270005</t>
+          <t>M2603070001</t>
         </is>
       </c>
       <c r="B596" s="4" t="inlineStr">
         <is>
-          <t>陳瀚森</t>
-        </is>
-      </c>
-      <c r="C596" s="4"/>
+          <t>陳永民</t>
+        </is>
+      </c>
+      <c r="C596" s="4" t="inlineStr">
+        <is>
+          <t>桃園市龜山區長慶二街117號7樓(警衛室收)</t>
+        </is>
+      </c>
       <c r="D596" s="4" t="inlineStr">
         <is>
-          <t>0930753731</t>
+          <t>0975851762</t>
         </is>
       </c>
       <c r="E596" s="4"/>
@@ -17767,18 +17767,18 @@
     <row r="597">
       <c r="A597" s="4" t="inlineStr">
         <is>
-          <t>M2510010005</t>
+          <t>M2510270005</t>
         </is>
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>陳琇珊</t>
+          <t>陳瀚森</t>
         </is>
       </c>
       <c r="C597" s="4"/>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>0982170760</t>
+          <t>0930753731</t>
         </is>
       </c>
       <c r="E597" s="4"/>
@@ -17796,18 +17796,18 @@
     <row r="598">
       <c r="A598" s="4" t="inlineStr">
         <is>
-          <t>M2510110009</t>
+          <t>M2510010005</t>
         </is>
       </c>
       <c r="B598" s="4" t="inlineStr">
         <is>
-          <t>陳琬瑜</t>
+          <t>陳琇珊</t>
         </is>
       </c>
       <c r="C598" s="4"/>
       <c r="D598" s="4" t="inlineStr">
         <is>
-          <t>0970513773</t>
+          <t>0982170760</t>
         </is>
       </c>
       <c r="E598" s="4"/>
@@ -17825,18 +17825,18 @@
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>M2510240004</t>
+          <t>M2510110009</t>
         </is>
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>陳璽文</t>
+          <t>陳琬瑜</t>
         </is>
       </c>
       <c r="C599" s="4"/>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>0935012090</t>
+          <t>0970513773</t>
         </is>
       </c>
       <c r="E599" s="4"/>
@@ -17854,22 +17854,18 @@
     <row r="600">
       <c r="A600" s="4" t="inlineStr">
         <is>
-          <t>M2509180001</t>
+          <t>M2510240004</t>
         </is>
       </c>
       <c r="B600" s="4" t="inlineStr">
         <is>
-          <t>陳益銓</t>
-        </is>
-      </c>
-      <c r="C600" s="4" t="inlineStr">
-        <is>
-          <t>新北市新莊區民生街15巷10號3樓</t>
-        </is>
-      </c>
+          <t>陳璽文</t>
+        </is>
+      </c>
+      <c r="C600" s="4"/>
       <c r="D600" s="4" t="inlineStr">
         <is>
-          <t>0918813336</t>
+          <t>0935012090</t>
         </is>
       </c>
       <c r="E600" s="4"/>
@@ -17887,18 +17883,22 @@
     <row r="601">
       <c r="A601" s="4" t="inlineStr">
         <is>
-          <t>M2509260058</t>
+          <t>M2509180001</t>
         </is>
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>陳秋蓉</t>
-        </is>
-      </c>
-      <c r="C601" s="4"/>
+          <t>陳益銓</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>新北市新莊區民生街15巷10號3樓</t>
+        </is>
+      </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>0952718772</t>
+          <t>0918813336</t>
         </is>
       </c>
       <c r="E601" s="4"/>
@@ -17916,22 +17916,18 @@
     <row r="602">
       <c r="A602" s="4" t="inlineStr">
         <is>
-          <t>M2511050001</t>
+          <t>M2509260058</t>
         </is>
       </c>
       <c r="B602" s="4" t="inlineStr">
         <is>
-          <t>陳致鈞</t>
-        </is>
-      </c>
-      <c r="C602" s="4" t="inlineStr">
-        <is>
-          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
-        </is>
-      </c>
+          <t>陳秋蓉</t>
+        </is>
+      </c>
+      <c r="C602" s="4"/>
       <c r="D602" s="4" t="inlineStr">
         <is>
-          <t>0932797600</t>
+          <t>0952718772</t>
         </is>
       </c>
       <c r="E602" s="4"/>
@@ -17949,18 +17945,22 @@
     <row r="603">
       <c r="A603" s="4" t="inlineStr">
         <is>
-          <t>M2510050007</t>
+          <t>M2511050001</t>
         </is>
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>陳貴源</t>
-        </is>
-      </c>
-      <c r="C603" s="4"/>
+          <t>陳致鈞</t>
+        </is>
+      </c>
+      <c r="C603" s="4" t="inlineStr">
+        <is>
+          <t>新北市汐止區福德二路236號6樓602室(放管理室)</t>
+        </is>
+      </c>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>0972303095</t>
+          <t>0932797600</t>
         </is>
       </c>
       <c r="E603" s="4"/>
@@ -17978,18 +17978,18 @@
     <row r="604">
       <c r="A604" s="4" t="inlineStr">
         <is>
-          <t>M2512200001</t>
+          <t>M2510050007</t>
         </is>
       </c>
       <c r="B604" s="4" t="inlineStr">
         <is>
-          <t>陳達鋒</t>
+          <t>陳貴源</t>
         </is>
       </c>
       <c r="C604" s="4"/>
       <c r="D604" s="4" t="inlineStr">
         <is>
-          <t>0965179777</t>
+          <t>0972303095</t>
         </is>
       </c>
       <c r="E604" s="4"/>
@@ -18007,18 +18007,18 @@
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
         <is>
-          <t>M2604190004</t>
+          <t>M2512200001</t>
         </is>
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>陳鋐緯</t>
+          <t>陳達鋒</t>
         </is>
       </c>
       <c r="C605" s="4"/>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>0925805535</t>
+          <t>0965179777</t>
         </is>
       </c>
       <c r="E605" s="4"/>
@@ -18036,18 +18036,18 @@
     <row r="606">
       <c r="A606" s="4" t="inlineStr">
         <is>
-          <t>M2511050005</t>
+          <t>M2604190004</t>
         </is>
       </c>
       <c r="B606" s="4" t="inlineStr">
         <is>
-          <t>陳錡叡</t>
+          <t>陳鋐緯</t>
         </is>
       </c>
       <c r="C606" s="4"/>
       <c r="D606" s="4" t="inlineStr">
         <is>
-          <t>0976319363</t>
+          <t>0925805535</t>
         </is>
       </c>
       <c r="E606" s="4"/>
@@ -18065,22 +18065,18 @@
     <row r="607">
       <c r="A607" s="4" t="inlineStr">
         <is>
-          <t>M2509260004</t>
+          <t>M2511050005</t>
         </is>
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>陳長志</t>
-        </is>
-      </c>
-      <c r="C607" s="4" t="inlineStr">
-        <is>
-          <t>新北市新店區安康路</t>
-        </is>
-      </c>
+          <t>陳錡叡</t>
+        </is>
+      </c>
+      <c r="C607" s="4"/>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>0938595083</t>
+          <t>0976319363</t>
         </is>
       </c>
       <c r="E607" s="4"/>
@@ -18098,22 +18094,22 @@
     <row r="608">
       <c r="A608" s="4" t="inlineStr">
         <is>
-          <t>M2509270012</t>
+          <t>M2509260004</t>
         </is>
       </c>
       <c r="B608" s="4" t="inlineStr">
         <is>
-          <t>陳雯瑄</t>
+          <t>陳長志</t>
         </is>
       </c>
       <c r="C608" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
+          <t>新北市新店區安康路</t>
         </is>
       </c>
       <c r="D608" s="4" t="inlineStr">
         <is>
-          <t>0919996509</t>
+          <t>0938595083</t>
         </is>
       </c>
       <c r="E608" s="4"/>
@@ -18131,22 +18127,22 @@
     <row r="609">
       <c r="A609" s="4" t="inlineStr">
         <is>
-          <t>M2509260039</t>
+          <t>M2509270012</t>
         </is>
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>陳靖森</t>
+          <t>陳雯瑄</t>
         </is>
       </c>
       <c r="C609" s="4" t="inlineStr">
         <is>
-          <t>台北市士林區通河街141巷4號1樓</t>
+          <t>宜蘭縣五結鄉溪濱路二段55巷12號</t>
         </is>
       </c>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>0981353077</t>
+          <t>0919996509</t>
         </is>
       </c>
       <c r="E609" s="4"/>
@@ -18164,18 +18160,22 @@
     <row r="610">
       <c r="A610" s="4" t="inlineStr">
         <is>
-          <t>M2509260003</t>
+          <t>M2509260039</t>
         </is>
       </c>
       <c r="B610" s="4" t="inlineStr">
         <is>
-          <t>陳韋傑</t>
-        </is>
-      </c>
-      <c r="C610" s="4"/>
+          <t>陳靖森</t>
+        </is>
+      </c>
+      <c r="C610" s="4" t="inlineStr">
+        <is>
+          <t>台北市士林區通河街141巷4號1樓</t>
+        </is>
+      </c>
       <c r="D610" s="4" t="inlineStr">
         <is>
-          <t>0920549111</t>
+          <t>0981353077</t>
         </is>
       </c>
       <c r="E610" s="4"/>
@@ -18193,18 +18193,18 @@
     <row r="611">
       <c r="A611" s="4" t="inlineStr">
         <is>
-          <t>M2511050004</t>
+          <t>M2509260003</t>
         </is>
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>陳鴻源</t>
+          <t>陳韋傑</t>
         </is>
       </c>
       <c r="C611" s="4"/>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>0933523338</t>
+          <t>0920549111</t>
         </is>
       </c>
       <c r="E611" s="4"/>
@@ -18222,18 +18222,18 @@
     <row r="612">
       <c r="A612" s="4" t="inlineStr">
         <is>
-          <t>M2510090007</t>
+          <t>M2511050004</t>
         </is>
       </c>
       <c r="B612" s="4" t="inlineStr">
         <is>
-          <t>陳麒方</t>
+          <t>陳鴻源</t>
         </is>
       </c>
       <c r="C612" s="4"/>
       <c r="D612" s="4" t="inlineStr">
         <is>
-          <t>0935766963</t>
+          <t>0933523338</t>
         </is>
       </c>
       <c r="E612" s="4"/>
@@ -18251,18 +18251,18 @@
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>M2509290006</t>
+          <t>M2510090007</t>
         </is>
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>陸仁</t>
+          <t>陳麒方</t>
         </is>
       </c>
       <c r="C613" s="4"/>
       <c r="D613" s="4" t="inlineStr">
         <is>
-          <t>0972535506</t>
+          <t>0935766963</t>
         </is>
       </c>
       <c r="E613" s="4"/>
@@ -18280,18 +18280,18 @@
     <row r="614">
       <c r="A614" s="4" t="inlineStr">
         <is>
-          <t>M2604250001</t>
+          <t>M2509290006</t>
         </is>
       </c>
       <c r="B614" s="4" t="inlineStr">
         <is>
-          <t>雷動蛟</t>
+          <t>陸仁</t>
         </is>
       </c>
       <c r="C614" s="4"/>
       <c r="D614" s="4" t="inlineStr">
         <is>
-          <t>0983617034</t>
+          <t>0972535506</t>
         </is>
       </c>
       <c r="E614" s="4"/>
@@ -18309,18 +18309,18 @@
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>M2509300008</t>
+          <t>M2604250001</t>
         </is>
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>雷咪咪</t>
+          <t>雷動蛟</t>
         </is>
       </c>
       <c r="C615" s="4"/>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>0987748183</t>
+          <t>0983617034</t>
         </is>
       </c>
       <c r="E615" s="4"/>
@@ -18338,18 +18338,18 @@
     <row r="616">
       <c r="A616" s="4" t="inlineStr">
         <is>
-          <t>M2603010002</t>
+          <t>M2509300008</t>
         </is>
       </c>
       <c r="B616" s="4" t="inlineStr">
         <is>
-          <t>韋榮富</t>
+          <t>雷咪咪</t>
         </is>
       </c>
       <c r="C616" s="4"/>
       <c r="D616" s="4" t="inlineStr">
         <is>
-          <t>0936104392</t>
+          <t>0987748183</t>
         </is>
       </c>
       <c r="E616" s="4"/>
@@ -18367,18 +18367,18 @@
     <row r="617">
       <c r="A617" s="4" t="inlineStr">
         <is>
-          <t>M2601110003</t>
+          <t>M2603010002</t>
         </is>
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>顏佐青</t>
+          <t>韋榮富</t>
         </is>
       </c>
       <c r="C617" s="4"/>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>0925750920</t>
+          <t>0936104392</t>
         </is>
       </c>
       <c r="E617" s="4"/>
@@ -18396,18 +18396,18 @@
     <row r="618">
       <c r="A618" s="4" t="inlineStr">
         <is>
-          <t>M2603140001</t>
+          <t>M2601110003</t>
         </is>
       </c>
       <c r="B618" s="4" t="inlineStr">
         <is>
-          <t>顏千傑</t>
+          <t>顏佐青</t>
         </is>
       </c>
       <c r="C618" s="4"/>
       <c r="D618" s="4" t="inlineStr">
         <is>
-          <t>0989232644</t>
+          <t>0925750920</t>
         </is>
       </c>
       <c r="E618" s="4"/>
@@ -18425,18 +18425,18 @@
     <row r="619">
       <c r="A619" s="4" t="inlineStr">
         <is>
-          <t>M2510160006</t>
+          <t>M2603140001</t>
         </is>
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>顏可杰</t>
+          <t>顏千傑</t>
         </is>
       </c>
       <c r="C619" s="4"/>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>0974336085</t>
+          <t>0989232644</t>
         </is>
       </c>
       <c r="E619" s="4"/>
@@ -18454,18 +18454,18 @@
     <row r="620">
       <c r="A620" s="4" t="inlineStr">
         <is>
-          <t>M2511060004</t>
+          <t>M2510160006</t>
         </is>
       </c>
       <c r="B620" s="4" t="inlineStr">
         <is>
-          <t>顏坤川</t>
+          <t>顏可杰</t>
         </is>
       </c>
       <c r="C620" s="4"/>
       <c r="D620" s="4" t="inlineStr">
         <is>
-          <t>0917375899</t>
+          <t>0974336085</t>
         </is>
       </c>
       <c r="E620" s="4"/>
@@ -18483,18 +18483,18 @@
     <row r="621">
       <c r="A621" s="4" t="inlineStr">
         <is>
-          <t>M2603080003</t>
+          <t>M2511060004</t>
         </is>
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>顏宏坤</t>
+          <t>顏坤川</t>
         </is>
       </c>
       <c r="C621" s="4"/>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>0978357113</t>
+          <t>0917375899</t>
         </is>
       </c>
       <c r="E621" s="4"/>
@@ -18512,18 +18512,18 @@
     <row r="622">
       <c r="A622" s="4" t="inlineStr">
         <is>
-          <t>M2510100010</t>
+          <t>M2603080003</t>
         </is>
       </c>
       <c r="B622" s="4" t="inlineStr">
         <is>
-          <t>馬迪</t>
+          <t>顏宏坤</t>
         </is>
       </c>
       <c r="C622" s="4"/>
       <c r="D622" s="4" t="inlineStr">
         <is>
-          <t>0970164660</t>
+          <t>0978357113</t>
         </is>
       </c>
       <c r="E622" s="4"/>
@@ -18541,22 +18541,18 @@
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>M2509260022</t>
+          <t>M2510100010</t>
         </is>
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>馬陳璟</t>
-        </is>
-      </c>
-      <c r="C623" s="4" t="inlineStr">
-        <is>
-          <t>基隆市七堵區百六街100巷28號</t>
-        </is>
-      </c>
+          <t>馬迪</t>
+        </is>
+      </c>
+      <c r="C623" s="4"/>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>0963356671</t>
+          <t>0970164660</t>
         </is>
       </c>
       <c r="E623" s="4"/>
@@ -18574,18 +18570,22 @@
     <row r="624">
       <c r="A624" s="4" t="inlineStr">
         <is>
-          <t>M2512200003</t>
+          <t>M2509260022</t>
         </is>
       </c>
       <c r="B624" s="4" t="inlineStr">
         <is>
-          <t>馮鈺惠</t>
-        </is>
-      </c>
-      <c r="C624" s="4"/>
+          <t>馬陳璟</t>
+        </is>
+      </c>
+      <c r="C624" s="4" t="inlineStr">
+        <is>
+          <t>基隆市七堵區百六街100巷28號</t>
+        </is>
+      </c>
       <c r="D624" s="4" t="inlineStr">
         <is>
-          <t>0905068632</t>
+          <t>0963356671</t>
         </is>
       </c>
       <c r="E624" s="4"/>
@@ -18603,18 +18603,18 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>M2602150003</t>
+          <t>M2512200003</t>
         </is>
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>駱馳玩具</t>
+          <t>馮鈺惠</t>
         </is>
       </c>
       <c r="C625" s="4"/>
       <c r="D625" s="4" t="inlineStr">
         <is>
-          <t>0938011575</t>
+          <t>0905068632</t>
         </is>
       </c>
       <c r="E625" s="4"/>
@@ -18632,18 +18632,18 @@
     <row r="626">
       <c r="A626" s="4" t="inlineStr">
         <is>
-          <t>M2602080004</t>
+          <t>M2602150003</t>
         </is>
       </c>
       <c r="B626" s="4" t="inlineStr">
         <is>
-          <t>高偉智</t>
+          <t>駱馳玩具</t>
         </is>
       </c>
       <c r="C626" s="4"/>
       <c r="D626" s="4" t="inlineStr">
         <is>
-          <t>0975696310</t>
+          <t>0938011575</t>
         </is>
       </c>
       <c r="E626" s="4"/>
@@ -18661,18 +18661,18 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>M2510010002</t>
+          <t>M2602080004</t>
         </is>
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>高振淵</t>
+          <t>高偉智</t>
         </is>
       </c>
       <c r="C627" s="4"/>
       <c r="D627" s="4" t="inlineStr">
         <is>
-          <t>0966361811</t>
+          <t>0975696310</t>
         </is>
       </c>
       <c r="E627" s="4"/>
@@ -18690,18 +18690,18 @@
     <row r="628">
       <c r="A628" s="4" t="inlineStr">
         <is>
-          <t>M2512170003</t>
+          <t>M2510010002</t>
         </is>
       </c>
       <c r="B628" s="4" t="inlineStr">
         <is>
-          <t>高文宏</t>
+          <t>高振淵</t>
         </is>
       </c>
       <c r="C628" s="4"/>
       <c r="D628" s="4" t="inlineStr">
         <is>
-          <t>0966380600</t>
+          <t>0966361811</t>
         </is>
       </c>
       <c r="E628" s="4"/>
@@ -18719,18 +18719,18 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>M2509260031</t>
+          <t>M2512170003</t>
         </is>
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>高聖景</t>
+          <t>高文宏</t>
         </is>
       </c>
       <c r="C629" s="4"/>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>0919200598</t>
+          <t>0966380600</t>
         </is>
       </c>
       <c r="E629" s="4"/>
@@ -18748,18 +18748,18 @@
     <row r="630">
       <c r="A630" s="4" t="inlineStr">
         <is>
-          <t>M2511020005</t>
+          <t>M2509260031</t>
         </is>
       </c>
       <c r="B630" s="4" t="inlineStr">
         <is>
-          <t>高莉婷</t>
+          <t>高聖景</t>
         </is>
       </c>
       <c r="C630" s="4"/>
       <c r="D630" s="4" t="inlineStr">
         <is>
-          <t>0953520673</t>
+          <t>0919200598</t>
         </is>
       </c>
       <c r="E630" s="4"/>
@@ -18777,22 +18777,18 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>M2511180005</t>
+          <t>M2511020005</t>
         </is>
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>高雅琴</t>
-        </is>
-      </c>
-      <c r="C631" s="4" t="inlineStr">
-        <is>
-          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
-        </is>
-      </c>
+          <t>高莉婷</t>
+        </is>
+      </c>
+      <c r="C631" s="4"/>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>0977121772</t>
+          <t>0953520673</t>
         </is>
       </c>
       <c r="E631" s="4"/>
@@ -18810,18 +18806,22 @@
     <row r="632">
       <c r="A632" s="4" t="inlineStr">
         <is>
-          <t>M2509260048</t>
+          <t>M2511180005</t>
         </is>
       </c>
       <c r="B632" s="4" t="inlineStr">
         <is>
-          <t>魏大鈞</t>
-        </is>
-      </c>
-      <c r="C632" s="4"/>
+          <t>高雅琴</t>
+        </is>
+      </c>
+      <c r="C632" s="4" t="inlineStr">
+        <is>
+          <t>花蓮縣新城鄉嘉里村中正路懷德巷28號</t>
+        </is>
+      </c>
       <c r="D632" s="4" t="inlineStr">
         <is>
-          <t>0937742352</t>
+          <t>0977121772</t>
         </is>
       </c>
       <c r="E632" s="4"/>
@@ -18839,18 +18839,18 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>M2509300015</t>
+          <t>M2509260048</t>
         </is>
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>魏金漢</t>
+          <t>魏大鈞</t>
         </is>
       </c>
       <c r="C633" s="4"/>
       <c r="D633" s="4" t="inlineStr">
         <is>
-          <t>0989116588</t>
+          <t>0937742352</t>
         </is>
       </c>
       <c r="E633" s="4"/>
@@ -18868,16 +18868,20 @@
     <row r="634">
       <c r="A634" s="4" t="inlineStr">
         <is>
-          <t>M2511120004</t>
+          <t>M2509300015</t>
         </is>
       </c>
       <c r="B634" s="4" t="inlineStr">
         <is>
-          <t>鴻</t>
+          <t>魏金漢</t>
         </is>
       </c>
       <c r="C634" s="4"/>
-      <c r="D634" s="4"/>
+      <c r="D634" s="4" t="inlineStr">
+        <is>
+          <t>0989116588</t>
+        </is>
+      </c>
       <c r="E634" s="4"/>
       <c r="F634" s="4" t="inlineStr">
         <is>
@@ -18893,20 +18897,16 @@
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
         <is>
-          <t>M2510060009</t>
+          <t>M2511120004</t>
         </is>
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>黃俊翰</t>
+          <t>鴻</t>
         </is>
       </c>
       <c r="C635" s="4"/>
-      <c r="D635" s="4" t="inlineStr">
-        <is>
-          <t>0958180882</t>
-        </is>
-      </c>
+      <c r="D635" s="4"/>
       <c r="E635" s="4"/>
       <c r="F635" s="4" t="inlineStr">
         <is>
@@ -18922,22 +18922,18 @@
     <row r="636">
       <c r="A636" s="4" t="inlineStr">
         <is>
-          <t>M2509300003</t>
+          <t>M2510060009</t>
         </is>
       </c>
       <c r="B636" s="4" t="inlineStr">
         <is>
-          <t>黃俊銘</t>
-        </is>
-      </c>
-      <c r="C636" s="4" t="inlineStr">
-        <is>
-          <t>新北市三重區仁愛街397巷36號9樓</t>
-        </is>
-      </c>
+          <t>黃俊翰</t>
+        </is>
+      </c>
+      <c r="C636" s="4"/>
       <c r="D636" s="4" t="inlineStr">
         <is>
-          <t>0903975921</t>
+          <t>0958180882</t>
         </is>
       </c>
       <c r="E636" s="4"/>
@@ -18955,16 +18951,24 @@
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
         <is>
-          <t>M2510130002</t>
+          <t>M2509300003</t>
         </is>
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>黃信禎</t>
-        </is>
-      </c>
-      <c r="C637" s="4"/>
-      <c r="D637" s="4"/>
+          <t>黃俊銘</t>
+        </is>
+      </c>
+      <c r="C637" s="4" t="inlineStr">
+        <is>
+          <t>新北市三重區仁愛街397巷36號9樓</t>
+        </is>
+      </c>
+      <c r="D637" s="4" t="inlineStr">
+        <is>
+          <t>0903975921</t>
+        </is>
+      </c>
       <c r="E637" s="4"/>
       <c r="F637" s="4" t="inlineStr">
         <is>
@@ -18980,20 +18984,16 @@
     <row r="638">
       <c r="A638" s="4" t="inlineStr">
         <is>
-          <t>M2511130001</t>
+          <t>M2510130002</t>
         </is>
       </c>
       <c r="B638" s="4" t="inlineStr">
         <is>
-          <t>黃勝賢</t>
+          <t>黃信禎</t>
         </is>
       </c>
       <c r="C638" s="4"/>
-      <c r="D638" s="4" t="inlineStr">
-        <is>
-          <t>0938722217</t>
-        </is>
-      </c>
+      <c r="D638" s="4"/>
       <c r="E638" s="4"/>
       <c r="F638" s="4" t="inlineStr">
         <is>
@@ -19009,18 +19009,18 @@
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
         <is>
-          <t>M2512210001</t>
+          <t>M2511130001</t>
         </is>
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>黃吉豪</t>
+          <t>黃勝賢</t>
         </is>
       </c>
       <c r="C639" s="4"/>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>0989628136</t>
+          <t>0938722217</t>
         </is>
       </c>
       <c r="E639" s="4"/>
@@ -19038,18 +19038,18 @@
     <row r="640">
       <c r="A640" s="4" t="inlineStr">
         <is>
-          <t>M2509300004</t>
+          <t>M2512210001</t>
         </is>
       </c>
       <c r="B640" s="4" t="inlineStr">
         <is>
-          <t>黃國展</t>
+          <t>黃吉豪</t>
         </is>
       </c>
       <c r="C640" s="4"/>
       <c r="D640" s="4" t="inlineStr">
         <is>
-          <t>0981218639</t>
+          <t>0989628136</t>
         </is>
       </c>
       <c r="E640" s="4"/>
@@ -19067,18 +19067,18 @@
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
         <is>
-          <t>M2604190003</t>
+          <t>M2509300004</t>
         </is>
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>黃士凱</t>
+          <t>黃國展</t>
         </is>
       </c>
       <c r="C641" s="4"/>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>0934179571</t>
+          <t>0981218639</t>
         </is>
       </c>
       <c r="E641" s="4"/>
@@ -19096,18 +19096,18 @@
     <row r="642">
       <c r="A642" s="4" t="inlineStr">
         <is>
-          <t>M2511130002</t>
+          <t>M2604190003</t>
         </is>
       </c>
       <c r="B642" s="4" t="inlineStr">
         <is>
-          <t>黃威綸</t>
+          <t>黃士凱</t>
         </is>
       </c>
       <c r="C642" s="4"/>
       <c r="D642" s="4" t="inlineStr">
         <is>
-          <t>0936175587</t>
+          <t>0934179571</t>
         </is>
       </c>
       <c r="E642" s="4"/>
@@ -19125,18 +19125,18 @@
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
         <is>
-          <t>M2511300004</t>
+          <t>M2511130002</t>
         </is>
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>黃宣豪</t>
+          <t>黃威綸</t>
         </is>
       </c>
       <c r="C643" s="4"/>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>0933931665</t>
+          <t>0936175587</t>
         </is>
       </c>
       <c r="E643" s="4"/>
@@ -19154,18 +19154,18 @@
     <row r="644">
       <c r="A644" s="4" t="inlineStr">
         <is>
-          <t>M2509290004</t>
+          <t>M2511300004</t>
         </is>
       </c>
       <c r="B644" s="4" t="inlineStr">
         <is>
-          <t>黃宥惟</t>
+          <t>黃宣豪</t>
         </is>
       </c>
       <c r="C644" s="4"/>
       <c r="D644" s="4" t="inlineStr">
         <is>
-          <t>0925979289</t>
+          <t>0933931665</t>
         </is>
       </c>
       <c r="E644" s="4"/>
@@ -19183,18 +19183,18 @@
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
         <is>
-          <t>M2604120001</t>
+          <t>M2509290004</t>
         </is>
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>黃宥文</t>
+          <t>黃宥惟</t>
         </is>
       </c>
       <c r="C645" s="4"/>
       <c r="D645" s="4" t="inlineStr">
         <is>
-          <t>0953082147</t>
+          <t>0925979289</t>
         </is>
       </c>
       <c r="E645" s="4"/>
@@ -19212,18 +19212,18 @@
     <row r="646">
       <c r="A646" s="4" t="inlineStr">
         <is>
-          <t>M2602280003</t>
+          <t>M2604120001</t>
         </is>
       </c>
       <c r="B646" s="4" t="inlineStr">
         <is>
-          <t>黃家鈺</t>
+          <t>黃宥文</t>
         </is>
       </c>
       <c r="C646" s="4"/>
       <c r="D646" s="4" t="inlineStr">
         <is>
-          <t>0979722656</t>
+          <t>0953082147</t>
         </is>
       </c>
       <c r="E646" s="4"/>
@@ -19241,18 +19241,18 @@
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>M2509260007</t>
+          <t>M2602280003</t>
         </is>
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>黃庠豪</t>
+          <t>黃家鈺</t>
         </is>
       </c>
       <c r="C647" s="4"/>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>0979589772</t>
+          <t>0979722656</t>
         </is>
       </c>
       <c r="E647" s="4"/>
@@ -19270,22 +19270,18 @@
     <row r="648">
       <c r="A648" s="4" t="inlineStr">
         <is>
-          <t>M2510050012</t>
+          <t>M2509260007</t>
         </is>
       </c>
       <c r="B648" s="4" t="inlineStr">
         <is>
-          <t>黃建賓</t>
-        </is>
-      </c>
-      <c r="C648" s="4" t="inlineStr">
-        <is>
-          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
-        </is>
-      </c>
+          <t>黃庠豪</t>
+        </is>
+      </c>
+      <c r="C648" s="4"/>
       <c r="D648" s="4" t="inlineStr">
         <is>
-          <t>0987222744</t>
+          <t>0979589772</t>
         </is>
       </c>
       <c r="E648" s="4"/>
@@ -19303,18 +19299,22 @@
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
         <is>
-          <t>M2510090012</t>
+          <t>M2510050012</t>
         </is>
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>黃彥誠</t>
-        </is>
-      </c>
-      <c r="C649" s="4"/>
+          <t>黃建賓</t>
+        </is>
+      </c>
+      <c r="C649" s="4" t="inlineStr">
+        <is>
+          <t>新北市蘆洲區正和街25號5樓(管理室)</t>
+        </is>
+      </c>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>0910929295</t>
+          <t>0987222744</t>
         </is>
       </c>
       <c r="E649" s="4"/>
@@ -19332,18 +19332,18 @@
     <row r="650">
       <c r="A650" s="4" t="inlineStr">
         <is>
-          <t>M2511150002</t>
+          <t>M2510090012</t>
         </is>
       </c>
       <c r="B650" s="4" t="inlineStr">
         <is>
-          <t>黃德政</t>
+          <t>黃彥誠</t>
         </is>
       </c>
       <c r="C650" s="4"/>
       <c r="D650" s="4" t="inlineStr">
         <is>
-          <t>0955038857</t>
+          <t>0910929295</t>
         </is>
       </c>
       <c r="E650" s="4"/>
@@ -19361,18 +19361,18 @@
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>M2511080003</t>
+          <t>M2511150002</t>
         </is>
       </c>
       <c r="B651" s="4" t="inlineStr">
         <is>
-          <t>黃振坤</t>
+          <t>黃德政</t>
         </is>
       </c>
       <c r="C651" s="4"/>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>0922234986</t>
+          <t>0955038857</t>
         </is>
       </c>
       <c r="E651" s="4"/>
@@ -19390,18 +19390,18 @@
     <row r="652">
       <c r="A652" s="4" t="inlineStr">
         <is>
-          <t>M2510100001</t>
+          <t>M2511080003</t>
         </is>
       </c>
       <c r="B652" s="4" t="inlineStr">
         <is>
-          <t>黃政喜</t>
+          <t>黃振坤</t>
         </is>
       </c>
       <c r="C652" s="4"/>
       <c r="D652" s="4" t="inlineStr">
         <is>
-          <t>0939125949</t>
+          <t>0922234986</t>
         </is>
       </c>
       <c r="E652" s="4"/>
@@ -19419,18 +19419,18 @@
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
         <is>
-          <t>M2510110008</t>
+          <t>M2510100001</t>
         </is>
       </c>
       <c r="B653" s="4" t="inlineStr">
         <is>
-          <t>黃景榮</t>
+          <t>黃政喜</t>
         </is>
       </c>
       <c r="C653" s="4"/>
       <c r="D653" s="4" t="inlineStr">
         <is>
-          <t>0980732000</t>
+          <t>0939125949</t>
         </is>
       </c>
       <c r="E653" s="4"/>
@@ -19448,18 +19448,18 @@
     <row r="654">
       <c r="A654" s="4" t="inlineStr">
         <is>
-          <t>M2510100014</t>
+          <t>M2510110008</t>
         </is>
       </c>
       <c r="B654" s="4" t="inlineStr">
         <is>
-          <t>黃智瑋</t>
+          <t>黃景榮</t>
         </is>
       </c>
       <c r="C654" s="4"/>
       <c r="D654" s="4" t="inlineStr">
         <is>
-          <t>0922575569</t>
+          <t>0980732000</t>
         </is>
       </c>
       <c r="E654" s="4"/>
@@ -19477,18 +19477,18 @@
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>M2511220003</t>
+          <t>M2510100014</t>
         </is>
       </c>
       <c r="B655" s="4" t="inlineStr">
         <is>
-          <t>黃樹林</t>
+          <t>黃智瑋</t>
         </is>
       </c>
       <c r="C655" s="4"/>
       <c r="D655" s="4" t="inlineStr">
         <is>
-          <t>0915600532</t>
+          <t>0922575569</t>
         </is>
       </c>
       <c r="E655" s="4"/>
@@ -19506,18 +19506,18 @@
     <row r="656">
       <c r="A656" s="4" t="inlineStr">
         <is>
-          <t>M2603010003</t>
+          <t>M2511220003</t>
         </is>
       </c>
       <c r="B656" s="4" t="inlineStr">
         <is>
-          <t>黃秉澄</t>
+          <t>黃樹林</t>
         </is>
       </c>
       <c r="C656" s="4"/>
       <c r="D656" s="4" t="inlineStr">
         <is>
-          <t>0989232745</t>
+          <t>0915600532</t>
         </is>
       </c>
       <c r="E656" s="4"/>
@@ -19535,18 +19535,18 @@
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
         <is>
-          <t>M2510080002</t>
+          <t>M2603010003</t>
         </is>
       </c>
       <c r="B657" s="4" t="inlineStr">
         <is>
-          <t>黃竣暉</t>
+          <t>黃秉澄</t>
         </is>
       </c>
       <c r="C657" s="4"/>
       <c r="D657" s="4" t="inlineStr">
         <is>
-          <t>0989350733</t>
+          <t>0989232745</t>
         </is>
       </c>
       <c r="E657" s="4"/>
@@ -19564,18 +19564,18 @@
     <row r="658">
       <c r="A658" s="4" t="inlineStr">
         <is>
-          <t>M2510030005</t>
+          <t>M2510080002</t>
         </is>
       </c>
       <c r="B658" s="4" t="inlineStr">
         <is>
-          <t>黃致宏</t>
+          <t>黃竣暉</t>
         </is>
       </c>
       <c r="C658" s="4"/>
       <c r="D658" s="4" t="inlineStr">
         <is>
-          <t>0979023621</t>
+          <t>0989350733</t>
         </is>
       </c>
       <c r="E658" s="4"/>
@@ -19593,18 +19593,18 @@
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
         <is>
-          <t>M2601170006</t>
+          <t>M2510030005</t>
         </is>
       </c>
       <c r="B659" s="4" t="inlineStr">
         <is>
-          <t>黃苑榕</t>
+          <t>黃致宏</t>
         </is>
       </c>
       <c r="C659" s="4"/>
       <c r="D659" s="4" t="inlineStr">
         <is>
-          <t>0933048750</t>
+          <t>0979023621</t>
         </is>
       </c>
       <c r="E659" s="4"/>
@@ -19622,18 +19622,18 @@
     <row r="660">
       <c r="A660" s="4" t="inlineStr">
         <is>
-          <t>M2510130008</t>
+          <t>M2601170006</t>
         </is>
       </c>
       <c r="B660" s="4" t="inlineStr">
         <is>
-          <t>黃詮益</t>
+          <t>黃苑榕</t>
         </is>
       </c>
       <c r="C660" s="4"/>
       <c r="D660" s="4" t="inlineStr">
         <is>
-          <t>0989085966</t>
+          <t>0933048750</t>
         </is>
       </c>
       <c r="E660" s="4"/>
@@ -19651,18 +19651,18 @@
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
         <is>
-          <t>M2509270008</t>
+          <t>M2510130008</t>
         </is>
       </c>
       <c r="B661" s="4" t="inlineStr">
         <is>
-          <t>黃誠正</t>
+          <t>黃詮益</t>
         </is>
       </c>
       <c r="C661" s="4"/>
       <c r="D661" s="4" t="inlineStr">
         <is>
-          <t>0930505335</t>
+          <t>0989085966</t>
         </is>
       </c>
       <c r="E661" s="4"/>
@@ -19680,18 +19680,18 @@
     <row r="662">
       <c r="A662" s="4" t="inlineStr">
         <is>
-          <t>M2604190001</t>
+          <t>M2509270008</t>
         </is>
       </c>
       <c r="B662" s="4" t="inlineStr">
         <is>
-          <t>黃貞菱</t>
+          <t>黃誠正</t>
         </is>
       </c>
       <c r="C662" s="4"/>
       <c r="D662" s="4" t="inlineStr">
         <is>
-          <t>0987793062</t>
+          <t>0930505335</t>
         </is>
       </c>
       <c r="E662" s="4"/>
@@ -19709,18 +19709,18 @@
     <row r="663">
       <c r="A663" s="4" t="inlineStr">
         <is>
-          <t>M2601270003</t>
+          <t>M2604190001</t>
         </is>
       </c>
       <c r="B663" s="4" t="inlineStr">
         <is>
-          <t>黃郁智</t>
+          <t>黃貞菱</t>
         </is>
       </c>
       <c r="C663" s="4"/>
       <c r="D663" s="4" t="inlineStr">
         <is>
-          <t>0987324125</t>
+          <t>0987793062</t>
         </is>
       </c>
       <c r="E663" s="4"/>
@@ -19738,18 +19738,18 @@
     <row r="664">
       <c r="A664" s="4" t="inlineStr">
         <is>
-          <t>M2509290011</t>
+          <t>M2601270003</t>
         </is>
       </c>
       <c r="B664" s="4" t="inlineStr">
         <is>
-          <t>黃鉑元</t>
+          <t>黃郁智</t>
         </is>
       </c>
       <c r="C664" s="4"/>
       <c r="D664" s="4" t="inlineStr">
         <is>
-          <t>0970993863</t>
+          <t>0987324125</t>
         </is>
       </c>
       <c r="E664" s="4"/>
@@ -19767,18 +19767,18 @@
     <row r="665">
       <c r="A665" s="4" t="inlineStr">
         <is>
-          <t>M2510020007</t>
+          <t>M2509290011</t>
         </is>
       </c>
       <c r="B665" s="4" t="inlineStr">
         <is>
-          <t>黃鴻麒</t>
+          <t>黃鉑元</t>
         </is>
       </c>
       <c r="C665" s="4"/>
       <c r="D665" s="4" t="inlineStr">
         <is>
-          <t>0930571975</t>
+          <t>0970993863</t>
         </is>
       </c>
       <c r="E665" s="4"/>
@@ -19796,18 +19796,18 @@
     <row r="666">
       <c r="A666" s="4" t="inlineStr">
         <is>
-          <t>M2602270002</t>
+          <t>M2510020007</t>
         </is>
       </c>
       <c r="B666" s="4" t="inlineStr">
         <is>
-          <t>黎信宏</t>
+          <t>黃鴻麒</t>
         </is>
       </c>
       <c r="C666" s="4"/>
       <c r="D666" s="4" t="inlineStr">
         <is>
-          <t>0911024337</t>
+          <t>0930571975</t>
         </is>
       </c>
       <c r="E666" s="4"/>
@@ -19825,18 +19825,18 @@
     <row r="667">
       <c r="A667" s="4" t="inlineStr">
         <is>
-          <t>M2509260008</t>
+          <t>M2602270002</t>
         </is>
       </c>
       <c r="B667" s="4" t="inlineStr">
         <is>
-          <t>黎美君</t>
+          <t>黎信宏</t>
         </is>
       </c>
       <c r="C667" s="4"/>
       <c r="D667" s="4" t="inlineStr">
         <is>
-          <t>0939965851</t>
+          <t>0911024337</t>
         </is>
       </c>
       <c r="E667" s="4"/>
@@ -19852,9 +19852,38 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>2026/04/26  13:00:09</t>
+      <c r="A668" s="4" t="inlineStr">
+        <is>
+          <t>M2509260008</t>
+        </is>
+      </c>
+      <c r="B668" s="4" t="inlineStr">
+        <is>
+          <t>黎美君</t>
+        </is>
+      </c>
+      <c r="C668" s="4"/>
+      <c r="D668" s="4" t="inlineStr">
+        <is>
+          <t>0939965851</t>
+        </is>
+      </c>
+      <c r="E668" s="4"/>
+      <c r="F668" s="4" t="inlineStr">
+        <is>
+          <t>批發</t>
+        </is>
+      </c>
+      <c r="G668" s="5" t="inlineStr">
+        <is>
+          <t>附件管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026/04/27  13:00:09</t>
         </is>
       </c>
     </row>
